--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>60.9</v>
+        <v>61.8</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>56.9</v>
+        <v>57</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1105,16 +1105,16 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>52.6</v>
+        <v>52.9</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1136,16 +1136,16 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>52.9</v>
+        <v>53.2</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1167,16 +1167,16 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>53.2</v>
+        <v>52.6</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="F28" s="11" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="F29" s="11" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="F32" s="11" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="F33" s="11" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F34" s="11" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="F35" s="11" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="G46" s="15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="G51" s="18" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>80</v>
       </c>
       <c r="D3" s="22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="21" t="n">
         <v>74</v>
@@ -2380,8 +2380,8 @@
       <c r="C4" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="D4" s="23" t="n">
-        <v>69</v>
+      <c r="D4" s="21" t="n">
+        <v>70</v>
       </c>
       <c r="E4" s="23" t="n">
         <v>62</v>
@@ -2501,7 +2501,7 @@
         <v>34</v>
       </c>
       <c r="D7" s="22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="22" t="n">
         <v>46</v>
@@ -2541,7 +2541,7 @@
         <v>86</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>56</v>
@@ -2581,7 +2581,7 @@
         <v>86</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>52</v>
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="21" t="n">
         <v>80</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>94</v>
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B12" s="20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>68</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E12" s="22" t="n">
         <v>18</v>
@@ -2741,7 +2741,7 @@
         <v>50</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="22" t="n">
         <v>28</v>
@@ -2781,7 +2781,7 @@
         <v>94</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="22" t="n">
         <v>6</v>
@@ -2891,161 +2891,161 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B17" s="20" t="n">
         <v>53</v>
       </c>
       <c r="C17" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>92</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="J17" s="21" t="n">
-        <v>70</v>
-      </c>
-      <c r="K17" s="21" t="n">
-        <v>70</v>
-      </c>
-      <c r="L17" s="23" t="n">
         <v>64</v>
+      </c>
+      <c r="J17" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" s="23" t="n">
+        <v>66</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B18" s="20" t="n">
         <v>53</v>
       </c>
-      <c r="C18" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>84</v>
+      <c r="C18" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>92</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>30</v>
+        <v>96</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>76</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>78</v>
-      </c>
-      <c r="H18" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="I18" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" s="21" t="n">
         <v>76</v>
       </c>
-      <c r="I18" s="23" t="n">
-        <v>64</v>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>66</v>
+      <c r="K18" s="21" t="n">
+        <v>86</v>
       </c>
       <c r="L18" s="22" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B19" s="20" t="n">
         <v>53</v>
       </c>
-      <c r="C19" s="23" t="n">
-        <v>50</v>
+      <c r="C19" s="21" t="n">
+        <v>98</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" s="21" t="n">
-        <v>96</v>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>76</v>
-      </c>
-      <c r="G19" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="H19" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="I19" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="J19" s="21" t="n">
-        <v>76</v>
-      </c>
-      <c r="K19" s="21" t="n">
-        <v>86</v>
+      <c r="E19" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>92</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>68</v>
+      </c>
+      <c r="K19" s="23" t="n">
+        <v>60</v>
       </c>
       <c r="L19" s="22" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B20" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="C20" s="21" t="n">
-        <v>98</v>
+        <v>52</v>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>34</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>20</v>
+        <v>32</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>86</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>92</v>
-      </c>
-      <c r="I20" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="J20" s="23" t="n">
-        <v>68</v>
-      </c>
-      <c r="K20" s="23" t="n">
-        <v>60</v>
-      </c>
-      <c r="L20" s="22" t="n">
-        <v>18</v>
+        <v>80</v>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="L20" s="23" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -3101,7 +3101,7 @@
         <v>50</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" s="22" t="n">
         <v>20</v>
@@ -3301,7 +3301,7 @@
         <v>50</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" s="22" t="n">
         <v>22</v>
@@ -3341,7 +3341,7 @@
         <v>30</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E28" s="22" t="n">
         <v>40</v>
@@ -3381,7 +3381,7 @@
         <v>68</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>60</v>
@@ -3461,7 +3461,7 @@
         <v>34</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" s="22" t="n">
         <v>16</v>
@@ -3501,7 +3501,7 @@
         <v>2</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>82</v>
@@ -3541,7 +3541,7 @@
         <v>68</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>86</v>
@@ -3621,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" s="22" t="n">
         <v>42</v>
@@ -3821,7 +3821,7 @@
         <v>50</v>
       </c>
       <c r="D40" s="23" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E40" s="22" t="n">
         <v>2</v>
@@ -3861,7 +3861,7 @@
         <v>24</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E41" s="22" t="n">
         <v>12</v>
@@ -3981,7 +3981,7 @@
         <v>32</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E44" s="22" t="n">
         <v>14</v>
@@ -4021,7 +4021,7 @@
         <v>48</v>
       </c>
       <c r="D45" s="22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E45" s="22" t="n">
         <v>32</v>
@@ -4061,7 +4061,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E46" s="23" t="n">
         <v>64</v>
@@ -4141,7 +4141,7 @@
         <v>20</v>
       </c>
       <c r="D48" s="22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E48" s="23" t="n">
         <v>66</v>
@@ -4181,7 +4181,7 @@
         <v>10</v>
       </c>
       <c r="D49" s="22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E49" s="21" t="n">
         <v>76</v>
@@ -4722,13 +4722,15 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>61 (B+)</t>
+          <t>62 (B+)</t>
         </is>
       </c>
       <c r="C10" s="24" t="n">
         <v>3.3</v>
       </c>
-      <c r="D10" s="24" t="n"/>
+      <c r="D10" s="24" t="n">
+        <v>64.56999999999999</v>
+      </c>
       <c r="E10" s="24" t="n">
         <v>8.27</v>
       </c>
@@ -4804,7 +4806,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>57 (B)</t>
+          <t>58 (B)</t>
         </is>
       </c>
       <c r="C12" s="24" t="n">
@@ -5009,7 +5011,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
@@ -5018,40 +5020,40 @@
         </is>
       </c>
       <c r="C17" s="24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>63.96</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>2.21</v>
+        <v>7.63</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>5.41</v>
+        <v>5.53</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>3.56</v>
+        <v>3.26</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>1.56</v>
+        <v>9.73</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>14.25</v>
+        <v>-0.14</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.44</v>
+        <v>0.23</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
@@ -5060,40 +5062,40 @@
         </is>
       </c>
       <c r="C18" s="24" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="D18" s="24" t="n">
-        <v>68.23999999999999</v>
+        <v>60.33</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>7.63</v>
+        <v>8.65</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>5.53</v>
+        <v>4.17</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>9.73</v>
+        <v>-18.72</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>-0.14</v>
+        <v>15.05</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.23</v>
+        <v>3.76</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
@@ -5102,76 +5104,76 @@
         </is>
       </c>
       <c r="C19" s="24" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="D19" s="24" t="n">
-        <v>60.33</v>
+        <v>60.56</v>
       </c>
       <c r="E19" s="24" t="n">
-        <v>8.65</v>
+        <v>-0.12</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>4.17</v>
+        <v>7.12</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>3.38</v>
+        <v>1.44</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>33.9</v>
+        <v>35.5</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>-18.72</v>
+        <v>32.24</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>15.05</v>
+        <v>10.88</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>3.76</v>
+        <v>-0.21</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>52 (B)</t>
         </is>
       </c>
       <c r="C20" s="24" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="24" t="n">
-        <v>60.56</v>
+        <v>63.96</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>-0.12</v>
+        <v>2.21</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>7.12</v>
+        <v>5.41</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>1.44</v>
+        <v>3.56</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>35.5</v>
+        <v>34.9</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>32.24</v>
+        <v>1.56</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>10.88</v>
+        <v>14.25</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>-0.21</v>
+        <v>0.44</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -6575,7 +6577,7 @@
         </is>
       </c>
       <c r="F2" s="14" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>4.5</v>
@@ -6613,7 +6615,7 @@
         </is>
       </c>
       <c r="F3" s="14" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>4.8</v>
@@ -6651,7 +6653,7 @@
         </is>
       </c>
       <c r="F4" s="11" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>4.5</v>
@@ -6727,7 +6729,7 @@
         </is>
       </c>
       <c r="F6" s="11" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>4.2</v>
@@ -6765,7 +6767,7 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>3.5</v>
@@ -6803,7 +6805,7 @@
         </is>
       </c>
       <c r="F8" s="11" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>3.8</v>
@@ -6833,7 +6835,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -6841,12 +6843,14 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>60.9</v>
+        <v>61.8</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
+        <v>64.56999999999999</v>
+      </c>
       <c r="I9" s="5" t="n">
         <v>8.27</v>
       </c>
@@ -6869,7 +6873,7 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
@@ -6877,7 +6881,7 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>4</v>
@@ -6915,7 +6919,7 @@
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>3.5</v>
@@ -7029,7 +7033,7 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>4.1</v>
@@ -7067,7 +7071,7 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>4.7</v>
@@ -7219,7 +7223,7 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>4.4</v>
@@ -7295,7 +7299,7 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>4.4</v>
@@ -7333,7 +7337,7 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>3.6</v>
@@ -7371,7 +7375,7 @@
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>3.6</v>
@@ -7401,7 +7405,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
@@ -7409,7 +7413,7 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>3.5</v>
@@ -7447,7 +7451,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>3.7</v>
@@ -7523,7 +7527,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>4.9</v>
@@ -7637,7 +7641,7 @@
         </is>
       </c>
       <c r="F30" s="11" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>5.2</v>
@@ -7675,7 +7679,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>3.6</v>
@@ -7713,7 +7717,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>3.5</v>
@@ -7751,7 +7755,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>3.6</v>
@@ -7789,7 +7793,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>2.5</v>
@@ -7901,7 +7905,7 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>4</v>
@@ -8053,7 +8057,7 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>3.1</v>
@@ -8091,7 +8095,7 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>3</v>
@@ -8129,7 +8133,7 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>3.6</v>
@@ -8167,7 +8171,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>3.1</v>
@@ -8205,7 +8209,7 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>3.3</v>
@@ -8243,7 +8247,7 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>4</v>
@@ -8319,7 +8323,7 @@
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="G48" s="8" t="n">
         <v>2.2</v>
@@ -8395,7 +8399,7 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>4</v>
@@ -8433,7 +8437,7 @@
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>56.9</v>
+        <v>57</v>
       </c>
       <c r="G51" s="8" t="n">
         <v>2.7</v>
@@ -8808,7 +8812,7 @@
         </is>
       </c>
       <c r="C11" s="30" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="30" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -658,20 +658,20 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>66.5</v>
+        <v>68</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -689,16 +689,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -720,20 +720,20 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>66.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>63.9</v>
+        <v>63.2</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -844,20 +844,20 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>63.2</v>
+        <v>61.1</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -875,16 +875,16 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>57.8</v>
+        <v>59.4</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -968,20 +968,20 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>56.6</v>
+        <v>55.7</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -999,20 +999,20 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>56.3</v>
+        <v>54.6</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1030,16 +1030,16 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>54.7</v>
+        <v>54.5</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
@@ -1092,16 +1092,16 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>53.8</v>
+        <v>54.3</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -1185,20 +1185,20 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>53.4</v>
+        <v>54</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>52.6</v>
+        <v>53.2</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1309,20 +1309,20 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>50.6</v>
+        <v>51.9</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -1340,20 +1340,20 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>51.1</v>
+        <v>50.1</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1370,48 +1370,48 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n">
+      <c r="A26" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -1495,16 +1495,16 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -1526,20 +1526,20 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>46.2</v>
+        <v>45.4</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>44.8</v>
+        <v>45.3</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -1650,16 +1650,16 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>41.3</v>
+        <v>40.6</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -1712,20 +1712,20 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -1743,20 +1743,20 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>40.4</v>
+        <v>40.9</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -1774,20 +1774,20 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>37.2</v>
+        <v>39.9</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -1805,20 +1805,20 @@
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>37.1</v>
+        <v>37.5</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="F41" s="11" t="n">
-        <v>37.3</v>
+        <v>37.6</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -1867,16 +1867,16 @@
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D42" s="13" t="n">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="F42" s="11" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -1898,20 +1898,20 @@
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>36.4</v>
+        <v>37.3</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="F44" s="11" t="n">
-        <v>36.2</v>
+        <v>36.5</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -1960,16 +1960,16 @@
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D45" s="13" t="n">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F45" s="11" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -1991,16 +1991,16 @@
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D46" s="13" t="n">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="F46" s="11" t="n">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="F47" s="11" t="n">
-        <v>33.2</v>
+        <v>35.1</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="F48" s="11" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="F49" s="11" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>26.4</v>
+        <v>27.6</v>
       </c>
       <c r="G50" s="15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
@@ -2309,130 +2309,130 @@
         <v>76</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L2" s="19" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="H3" s="18" t="n">
         <v>90</v>
       </c>
-      <c r="D3" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="E3" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="H3" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="I3" s="20" t="n">
-        <v>60</v>
+      <c r="I3" s="18" t="n">
+        <v>86</v>
       </c>
       <c r="J3" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="K3" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="L3" s="19" t="n">
-        <v>42</v>
+        <v>52</v>
+      </c>
+      <c r="K3" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="L3" s="20" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B4" s="17" t="n">
         <v>66</v>
       </c>
-      <c r="C4" s="20" t="n">
-        <v>50</v>
+      <c r="C4" s="18" t="n">
+        <v>90</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="E4" s="20" t="n">
+        <v>98</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>92</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="I4" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" s="20" t="n">
         <v>62</v>
       </c>
-      <c r="F4" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="H4" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="I4" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>66</v>
-      </c>
       <c r="K4" s="20" t="n">
-        <v>64</v>
-      </c>
-      <c r="L4" s="20" t="n">
-        <v>52</v>
+        <v>60</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B5" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="J5" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="C5" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="F5" s="19" t="n">
+      <c r="K5" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="L5" s="19" t="n">
         <v>34</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="I5" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="L5" s="19" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>68</v>
@@ -2453,8 +2453,8 @@
       <c r="E6" s="18" t="n">
         <v>84</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>72</v>
+      <c r="F6" s="20" t="n">
+        <v>68</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
         <v>78</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>80</v>
@@ -2494,7 +2494,7 @@
         <v>74</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G7" s="20" t="n">
         <v>68</v>
@@ -2511,8 +2511,8 @@
       <c r="K7" s="18" t="n">
         <v>78</v>
       </c>
-      <c r="L7" s="18" t="n">
-        <v>74</v>
+      <c r="L7" s="20" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="19" t="n">
         <v>34</v>
@@ -2534,7 +2534,7 @@
         <v>46</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G8" s="18" t="n">
         <v>72</v>
@@ -2552,87 +2552,87 @@
         <v>94</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="E9" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="D9" s="20" t="n">
         <v>56</v>
       </c>
+      <c r="E9" s="18" t="n">
+        <v>94</v>
+      </c>
       <c r="F9" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>58</v>
+        <v>76</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>72</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="L9" s="18" t="n">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="L9" s="19" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B10" s="17" t="n">
         <v>61</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="D10" s="20" t="n">
+        <v>86</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" s="20" t="n">
         <v>56</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="F10" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" s="18" t="n">
         <v>94</v>
       </c>
-      <c r="F10" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="L10" s="19" t="n">
-        <v>42</v>
+      <c r="K10" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="L10" s="18" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -2654,7 +2654,7 @@
         <v>58</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>96</v>
@@ -2669,256 +2669,256 @@
         <v>58</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B12" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>92</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="K12" s="20" t="n">
         <v>58</v>
       </c>
-      <c r="C12" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="L12" s="18" t="n">
-        <v>78</v>
+      <c r="L12" s="19" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>57</v>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>94</v>
+        <v>56</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>68</v>
       </c>
       <c r="D13" s="20" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>92</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="L13" s="19" t="n">
         <v>44</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="L13" s="18" t="n">
-        <v>96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>64</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>18</v>
+        <v>50</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>96</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>46</v>
+        <v>78</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>80</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="I14" s="19" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="L14" s="19" t="n">
-        <v>48</v>
+        <v>86</v>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="C15" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>80</v>
+      <c r="C15" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>32</v>
       </c>
       <c r="H15" s="19" t="n">
         <v>44</v>
       </c>
-      <c r="I15" s="19" t="n">
-        <v>32</v>
+      <c r="I15" s="18" t="n">
+        <v>74</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="L15" s="19" t="n">
-        <v>8</v>
+        <v>98</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="C16" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="C16" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="D16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="G16" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="L16" s="18" t="n">
-        <v>78</v>
+      <c r="L16" s="19" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B17" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C17" s="20" t="n">
-        <v>68</v>
+      <c r="C17" s="19" t="n">
+        <v>6</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="E17" s="20" t="n">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>92</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="I17" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="H17" s="18" t="n">
         <v>76</v>
       </c>
+      <c r="I17" s="19" t="n">
+        <v>46</v>
+      </c>
       <c r="J17" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="L17" s="19" t="n">
-        <v>26</v>
+        <v>16</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="L17" s="18" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
@@ -2928,151 +2928,151 @@
         <v>50</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>62</v>
+        <v>88</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>28</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I18" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>92</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="L18" s="18" t="n">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C19" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="E19" s="19" t="n">
+      <c r="C19" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="D19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>54</v>
+      </c>
       <c r="F19" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>28</v>
+        <v>84</v>
+      </c>
+      <c r="G19" s="20" t="n">
+        <v>60</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="I19" s="20" t="n">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>96</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="L19" s="18" t="n">
-        <v>74</v>
+        <v>96</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>53</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>64</v>
-      </c>
-      <c r="I20" s="20" t="n">
-        <v>64</v>
+        <v>54</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>24</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>48</v>
+        <v>74</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>84</v>
       </c>
       <c r="L20" s="20" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
         <v>53</v>
       </c>
-      <c r="C21" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="D21" s="19" t="n">
+      <c r="C21" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="E21" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="E21" s="19" t="n">
-        <v>8</v>
-      </c>
       <c r="F21" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="G21" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>88</v>
+        <v>4</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <v>64</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K21" s="20" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -3112,207 +3112,207 @@
         <v>70</v>
       </c>
       <c r="L22" s="20" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
         <v>52</v>
       </c>
-      <c r="C23" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="20" t="n">
+      <c r="C23" s="20" t="n">
         <v>50</v>
       </c>
+      <c r="D23" s="18" t="n">
+        <v>92</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>70</v>
+      </c>
       <c r="G23" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>72</v>
+        <v>58</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>42</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="K23" s="18" t="n">
-        <v>98</v>
+        <v>4</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>51</v>
-      </c>
-      <c r="C24" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="E24" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="D24" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="E24" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="G24" s="19" t="n">
-        <v>42</v>
+      <c r="F24" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>50</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="J24" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>34</v>
+        <v>16</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B25" s="17" t="n">
-        <v>51</v>
-      </c>
-      <c r="C25" s="19" t="n">
-        <v>6</v>
+        <v>50</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>50</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="E25" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="H25" s="18" t="n">
         <v>92</v>
       </c>
-      <c r="F25" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G25" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>76</v>
-      </c>
       <c r="I25" s="19" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K25" s="20" t="n">
-        <v>66</v>
+        <v>8</v>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>34</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B26" s="17" t="n">
         <v>50</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="E26" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="F26" s="20" t="n">
-        <v>64</v>
-      </c>
       <c r="G26" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="H26" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="J26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="21" t="n">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="L26" s="19" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B27" s="17" t="n">
         <v>49</v>
       </c>
-      <c r="C27" s="20" t="n">
-        <v>50</v>
+      <c r="C27" s="19" t="n">
+        <v>44</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>58</v>
+        <v>86</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>76</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v>52</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L27" s="19" t="n">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="K27" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="L27" s="18" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="28">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28" s="20" t="n">
         <v>50</v>
@@ -3334,7 +3334,7 @@
         <v>98</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G28" s="19" t="n">
         <v>36</v>
@@ -3352,7 +3352,7 @@
         <v>80</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
@@ -3374,7 +3374,7 @@
         <v>40</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G29" s="19" t="n">
         <v>6</v>
@@ -3392,127 +3392,127 @@
         <v>24</v>
       </c>
       <c r="L29" s="20" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B30" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="C30" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="D30" s="19" t="n">
+      <c r="C30" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="K30" s="19" t="n">
         <v>26</v>
       </c>
-      <c r="E30" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="F30" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="L30" s="19" t="n">
-        <v>2</v>
+      <c r="L30" s="20" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B31" s="17" t="n">
-        <v>46</v>
-      </c>
-      <c r="C31" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="D31" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="E31" s="18" t="n">
         <v>86</v>
       </c>
-      <c r="E31" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="F31" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="H31" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v>52</v>
+      <c r="F31" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>78</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K31" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="L31" s="18" t="n">
-        <v>70</v>
+        <v>10</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B32" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="C32" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="20" t="n">
+      <c r="C32" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" s="20" t="n">
         <v>62</v>
       </c>
-      <c r="E32" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="F32" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="I32" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="K32" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="L32" s="19" t="n">
-        <v>36</v>
+      <c r="H32" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="J32" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="K32" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="L32" s="18" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="33">
@@ -3533,8 +3533,8 @@
       <c r="E33" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="F33" s="19" t="n">
-        <v>6</v>
+      <c r="F33" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="G33" s="19" t="n">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>54</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L33" s="18" t="n">
         <v>98</v>
@@ -3573,8 +3573,8 @@
       <c r="E34" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="F34" s="20" t="n">
-        <v>50</v>
+      <c r="F34" s="19" t="n">
+        <v>40</v>
       </c>
       <c r="G34" s="19" t="n">
         <v>38</v>
@@ -3589,250 +3589,250 @@
         <v>22</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B35" s="17" t="n">
         <v>42</v>
       </c>
-      <c r="C35" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="D35" s="19" t="n">
+      <c r="C35" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I35" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="E35" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="F35" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="G35" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="H35" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="I35" s="18" t="n">
-        <v>92</v>
-      </c>
       <c r="J35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" s="20" t="n">
-        <v>68</v>
+        <v>24</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>38</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
         <v>41</v>
       </c>
-      <c r="C36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>90</v>
+      <c r="C36" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>42</v>
       </c>
       <c r="F36" s="19" t="n">
         <v>46</v>
       </c>
       <c r="G36" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I36" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H36" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="I36" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="J36" s="20" t="n">
-        <v>64</v>
-      </c>
-      <c r="K36" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="L36" s="20" t="n">
-        <v>58</v>
+      <c r="J36" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="L36" s="18" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="E37" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="F37" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="F37" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="G37" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="I37" s="19" t="n">
-        <v>4</v>
+      <c r="G37" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="H37" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="I37" s="18" t="n">
+        <v>92</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="K37" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="L37" s="18" t="n">
-        <v>72</v>
+        <v>2</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="L37" s="19" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="C38" s="19" t="n">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="D38" s="19" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>78</v>
+        <v>90</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>48</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="J38" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="J38" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="K38" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="K38" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="L38" s="19" t="n">
-        <v>14</v>
+      <c r="L38" s="20" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C39" s="19" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D39" s="19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>26</v>
+        <v>78</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>80</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="H39" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="J39" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="K39" s="20" t="n">
-        <v>54</v>
+        <v>2</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C40" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>52</v>
+        <v>14</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>22</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="F40" s="19" t="n">
-        <v>16</v>
+        <v>4</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>90</v>
       </c>
       <c r="G40" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="J40" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="H40" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="I40" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L40" s="18" t="n">
-        <v>92</v>
+      <c r="K40" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41" s="19" t="n">
         <v>34</v>
@@ -3854,7 +3854,7 @@
         <v>10</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>54</v>
@@ -3869,90 +3869,90 @@
         <v>32</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>38</v>
-      </c>
-      <c r="L41" s="20" t="n">
-        <v>66</v>
+        <v>36</v>
+      </c>
+      <c r="L41" s="18" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
         <v>37</v>
       </c>
-      <c r="C42" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="E42" s="19" t="n">
-        <v>2</v>
+      <c r="C42" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>88</v>
       </c>
       <c r="F42" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="I42" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="G42" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="H42" s="19" t="n">
+      <c r="J42" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="K42" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="L42" s="19" t="n">
         <v>28</v>
-      </c>
-      <c r="I42" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="L42" s="19" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="H43" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="C43" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="D43" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="E43" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="G43" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="H43" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="I43" s="19" t="n">
-        <v>38</v>
+      <c r="I43" s="18" t="n">
+        <v>94</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="K43" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="L43" s="20" t="n">
-        <v>66</v>
+        <v>18</v>
+      </c>
+      <c r="K43" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L43" s="18" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="44">
@@ -3989,130 +3989,130 @@
         <v>60</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
         <v>35</v>
       </c>
       <c r="C45" s="19" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D45" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="E45" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="G45" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="H45" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="I45" s="21" t="n">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" s="20" t="n">
+        <v>56</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
         <v>35</v>
       </c>
       <c r="C46" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="I46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="K46" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L46" s="19" t="n">
         <v>8</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>64</v>
-      </c>
-      <c r="F46" s="19" t="n">
-        <v>38</v>
-      </c>
-      <c r="G46" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="I46" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="K46" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="L46" s="19" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C47" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="D47" s="19" t="n">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>72</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>64</v>
+        <v>34</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I47" s="20" t="n">
-        <v>56</v>
+        <v>44</v>
+      </c>
+      <c r="I47" s="19" t="n">
+        <v>30</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -4134,7 +4134,7 @@
         <v>76</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G48" s="19" t="n">
         <v>8</v>
@@ -4149,10 +4149,10 @@
         <v>28</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="L48" s="20" t="n">
-        <v>52</v>
+        <v>18</v>
+      </c>
+      <c r="L48" s="18" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="49">
@@ -4189,10 +4189,10 @@
         <v>46</v>
       </c>
       <c r="K49" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="L49" s="19" t="n">
         <v>16</v>
-      </c>
-      <c r="L49" s="19" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C50" s="19" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
         <v>48</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="L50" s="20" t="n">
-        <v>62</v>
+        <v>44</v>
+      </c>
+      <c r="L50" s="18" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="51">
@@ -4269,7 +4269,7 @@
         <v>26</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L51" s="18" t="n">
         <v>88</v>
@@ -4401,58 +4401,58 @@
         <v>16.78</v>
       </c>
       <c r="K2" s="21" t="n">
-        <v>3.88</v>
+        <v>6.24</v>
       </c>
       <c r="L2" s="21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>66 (B+)</t>
+          <t>68 (B+)</t>
         </is>
       </c>
       <c r="C3" s="21" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="D3" s="21" t="n">
-        <v>76.27</v>
+        <v>72.77</v>
       </c>
       <c r="E3" s="21" t="n">
-        <v>1.62</v>
+        <v>3.15</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>5.78</v>
+        <v>5.2</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>3.9</v>
+        <v>4.76</v>
       </c>
       <c r="H3" s="21" t="n">
-        <v>34.9</v>
+        <v>35.4</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>6.15</v>
+        <v>41.99</v>
       </c>
       <c r="J3" s="21" t="n">
-        <v>10.88</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K3" s="21" t="n">
-        <v>0.13</v>
+        <v>-1.89</v>
       </c>
       <c r="L3" s="21" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B4" s="22" t="inlineStr">
@@ -4461,76 +4461,76 @@
         </is>
       </c>
       <c r="C4" s="21" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>65.65000000000001</v>
+        <v>76.27</v>
       </c>
       <c r="E4" s="21" t="n">
-        <v>4.7</v>
+        <v>1.62</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>4.88</v>
+        <v>5.71</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>35.8</v>
+        <v>34.9</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>22.35</v>
+        <v>6.15</v>
       </c>
       <c r="J4" s="21" t="n">
-        <v>12.7</v>
+        <v>10.88</v>
       </c>
       <c r="K4" s="21" t="n">
-        <v>0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="L4" s="21" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>66 (B+)</t>
+          <t>65 (B+)</t>
         </is>
       </c>
       <c r="C5" s="21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>72.77</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>5.31</v>
+        <v>4.82</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>4.76</v>
+        <v>2.6</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>41.99</v>
+        <v>22.35</v>
       </c>
       <c r="J5" s="21" t="n">
-        <v>9.890000000000001</v>
+        <v>12.7</v>
       </c>
       <c r="K5" s="21" t="n">
-        <v>-1.77</v>
+        <v>0</v>
       </c>
       <c r="L5" s="21" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>64 (B+)</t>
+          <t>63 (B+)</t>
         </is>
       </c>
       <c r="C6" s="21" t="n">
@@ -4554,7 +4554,7 @@
         <v>6.8</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>1.2</v>
@@ -4569,10 +4569,10 @@
         <v>17.56</v>
       </c>
       <c r="K6" s="21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="L6" s="21" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>64 (B+)</t>
+          <t>63 (B+)</t>
         </is>
       </c>
       <c r="C7" s="21" t="n">
@@ -4596,7 +4596,7 @@
         <v>5.12</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="G7" s="21" t="n">
         <v>3.02</v>
@@ -4611,10 +4611,10 @@
         <v>19.85</v>
       </c>
       <c r="K7" s="21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="L7" s="21" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>64 (B+)</t>
+          <t>63 (B+)</t>
         </is>
       </c>
       <c r="C8" s="21" t="n">
@@ -4638,7 +4638,7 @@
         <v>3.13</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="G8" s="21" t="n">
         <v>3.06</v>
@@ -4653,58 +4653,58 @@
         <v>21.27</v>
       </c>
       <c r="K8" s="21" t="n">
-        <v>7.35</v>
+        <v>8.1</v>
       </c>
       <c r="L8" s="21" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>63 (B+)</t>
+          <t>61 (B+)</t>
         </is>
       </c>
       <c r="C9" s="21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>63.19</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>3.73</v>
+        <v>8.27</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.67</v>
+        <v>4.43</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>1.56</v>
+        <v>3.52</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>-23.05</v>
+        <v>-17.49</v>
       </c>
       <c r="J9" s="21" t="n">
-        <v>23.89</v>
+        <v>0.16</v>
       </c>
       <c r="K9" s="21" t="n">
-        <v>4.58</v>
+        <v>-0.34</v>
       </c>
       <c r="L9" s="21" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
@@ -4713,34 +4713,34 @@
         </is>
       </c>
       <c r="C10" s="21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>64.56999999999999</v>
+        <v>63.19</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>8.27</v>
+        <v>3.73</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>4.36</v>
+        <v>4.8</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>3.52</v>
+        <v>1.56</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>-17.49</v>
+        <v>-23.05</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.16</v>
+        <v>23.89</v>
       </c>
       <c r="K10" s="21" t="n">
-        <v>-0.51</v>
+        <v>4.37</v>
       </c>
       <c r="L10" s="21" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -4779,142 +4779,142 @@
         <v>10.4</v>
       </c>
       <c r="K11" s="21" t="n">
-        <v>-1.06</v>
+        <v>-0.91</v>
       </c>
       <c r="L11" s="21" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>58 (B)</t>
+          <t>59 (B)</t>
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>62.74</v>
+        <v>60.56</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>3.37</v>
+        <v>-0.12</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>0.75</v>
+        <v>3.13</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>33.3</v>
+        <v>35.5</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>-19.57</v>
+        <v>43.07</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>15.66</v>
+        <v>14.39</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>3.67</v>
+        <v>-0.21</v>
       </c>
       <c r="L12" s="21" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>57 (B)</t>
+          <t>56 (B)</t>
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>64.7</v>
+        <v>65.27</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.36</v>
+        <v>0.66</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>7.54</v>
+        <v>0.73</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>33.9</v>
+        <v>32.9</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>16.13</v>
+        <v>-18.7</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>28.29</v>
+        <v>18.78</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>-0.54</v>
+        <v>4.87</v>
       </c>
       <c r="L13" s="21" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>56 (B)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>65.27</v>
+        <v>60.33</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>0.66</v>
+        <v>8.65</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>0.5</v>
+        <v>4.18</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>2.34</v>
+        <v>3.38</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>32.9</v>
+        <v>33.9</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>-18.7</v>
+        <v>-13.83</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>18.78</v>
+        <v>17.94</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>5.31</v>
+        <v>4.21</v>
       </c>
       <c r="L14" s="21" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -4923,82 +4923,82 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>60.33</v>
+        <v>64.7</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>8.65</v>
+        <v>-0.36</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>4.17</v>
+        <v>7.56</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>3.38</v>
+        <v>2.12</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>33.9</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>-13.83</v>
+        <v>16.13</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>17.94</v>
+        <v>28.29</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>3.76</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L15" s="21" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>55 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>50.77</v>
+        <v>66.34</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>3.63</v>
+        <v>4.52</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>1.43</v>
+        <v>5.18</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>33.1</v>
+        <v>34.2</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>144.37</v>
+        <v>16.78</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>24.22</v>
+        <v>-1.53</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>8.550000000000001</v>
+        <v>-2.18</v>
       </c>
       <c r="L16" s="21" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -5007,40 +5007,40 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>66.34</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>4.52</v>
+        <v>7.63</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>5.19</v>
+        <v>5.62</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>34.2</v>
+        <v>34.8</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>16.78</v>
+        <v>-1.35</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>-1.53</v>
+        <v>-0.13</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>-2.18</v>
+        <v>0.08</v>
       </c>
       <c r="L17" s="21" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
@@ -5052,37 +5052,37 @@
         <v>3.6</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>64.19</v>
+        <v>63.08</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>1.86</v>
+        <v>-0.44</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>14.35</v>
+        <v>21.54</v>
       </c>
       <c r="K18" s="21" t="n">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="L18" s="21" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -5091,82 +5091,82 @@
         </is>
       </c>
       <c r="C19" s="21" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>63.08</v>
+        <v>50.77</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>1.53</v>
+        <v>3.63</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>-0.44</v>
+        <v>144.37</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>21.54</v>
+        <v>24.22</v>
       </c>
       <c r="K19" s="21" t="n">
-        <v>2.71</v>
+        <v>10.23</v>
       </c>
       <c r="L19" s="21" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>65.61</v>
+        <v>62.74</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>0.86</v>
+        <v>3.37</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>7.48</v>
+        <v>4.82</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>3.76</v>
+        <v>2.38</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>34.3</v>
+        <v>33.3</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>9.82</v>
+        <v>-19.57</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>19.38</v>
+        <v>15.66</v>
       </c>
       <c r="K20" s="21" t="n">
-        <v>-0.66</v>
+        <v>3.26</v>
       </c>
       <c r="L20" s="21" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B21" s="22" t="inlineStr">
@@ -5175,34 +5175,34 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>60.56</v>
+        <v>65.61</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>-0.12</v>
+        <v>0.86</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>7.12</v>
+        <v>7.49</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>1.44</v>
+        <v>3.76</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>35.5</v>
+        <v>34.3</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>43.07</v>
+        <v>9.82</v>
       </c>
       <c r="J21" s="21" t="n">
-        <v>14.39</v>
+        <v>19.38</v>
       </c>
       <c r="K21" s="21" t="n">
-        <v>-0.21</v>
+        <v>-0.82</v>
       </c>
       <c r="L21" s="21" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
@@ -5226,7 +5226,7 @@
         <v>2.21</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>5.41</v>
+        <v>5.4</v>
       </c>
       <c r="G22" s="21" t="n">
         <v>3.56</v>
@@ -5244,13 +5244,13 @@
         <v>0.44</v>
       </c>
       <c r="L22" s="21" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B23" s="22" t="inlineStr">
@@ -5259,164 +5259,164 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>58.01</v>
+        <v>70.39</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="F23" s="21" t="n"/>
+        <v>6.57</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>4.64</v>
+      </c>
       <c r="G23" s="21" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>14.96</v>
+        <v>-6.75</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>4.05</v>
+        <v>-2.07</v>
       </c>
       <c r="K23" s="21" t="n">
-        <v>12.86</v>
+        <v>-3.36</v>
       </c>
       <c r="L23" s="21" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>52 (B)</t>
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>69.61</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>4.87</v>
+        <v>4.63</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>35.5</v>
+        <v>34.9</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>-20.74</v>
+        <v>-22.9</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>-1.52</v>
+        <v>-5.6</v>
       </c>
       <c r="K24" s="21" t="n">
-        <v>-1.8</v>
+        <v>-6.22</v>
       </c>
       <c r="L24" s="21" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>68.23999999999999</v>
+        <v>69.61</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>7.63</v>
+        <v>3.1</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>5.53</v>
+        <v>4.88</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>3.26</v>
+        <v>2.26</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>-1.35</v>
+        <v>-20.74</v>
       </c>
       <c r="J25" s="21" t="n">
-        <v>-0.13</v>
+        <v>-1.52</v>
       </c>
       <c r="K25" s="21" t="n">
-        <v>0.23</v>
+        <v>-1.8</v>
       </c>
       <c r="L25" s="21" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C26" s="21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>73.98999999999999</v>
+        <v>58.01</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>4.68</v>
-      </c>
+        <v>-1.79</v>
+      </c>
+      <c r="F26" s="21" t="n"/>
       <c r="G26" s="21" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>-22.9</v>
+        <v>14.96</v>
       </c>
       <c r="J26" s="21" t="n">
-        <v>-5.6</v>
+        <v>4.05</v>
       </c>
       <c r="K26" s="21" t="n">
-        <v>-5.54</v>
+        <v>12.86</v>
       </c>
       <c r="L26" s="21" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
@@ -5425,34 +5425,34 @@
         </is>
       </c>
       <c r="C27" s="21" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>70.39</v>
+        <v>68.47</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>6.57</v>
+        <v>1.42</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>4.57</v>
+        <v>6.61</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>2.76</v>
+        <v>3.14</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>-6.75</v>
+        <v>1.05</v>
       </c>
       <c r="J27" s="21" t="n">
-        <v>-2.07</v>
+        <v>0.96</v>
       </c>
       <c r="K27" s="21" t="n">
-        <v>-3.37</v>
+        <v>0</v>
       </c>
       <c r="L27" s="21" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C28" s="21" t="n">
@@ -5476,7 +5476,7 @@
         <v>10.22</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="G28" s="21" t="n">
         <v>2.2</v>
@@ -5491,10 +5491,10 @@
         <v>18.41</v>
       </c>
       <c r="K28" s="21" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="L28" s="21" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -5518,7 +5518,7 @@
         <v>2.61</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="G29" s="21" t="n">
         <v>0.82</v>
@@ -5536,13 +5536,13 @@
         <v>-2.29</v>
       </c>
       <c r="L29" s="21" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
@@ -5551,82 +5551,82 @@
         </is>
       </c>
       <c r="C30" s="21" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>62.53</v>
+        <v>65.02</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>7.12</v>
+        <v>6.71</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>5.72</v>
+        <v>5.08</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>35.2</v>
+        <v>34.1</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>20.94</v>
+        <v>40.95</v>
       </c>
       <c r="J30" s="21" t="n">
-        <v>-1.47</v>
+        <v>-0.88</v>
       </c>
       <c r="K30" s="21" t="n">
-        <v>-2.69</v>
+        <v>-2.22</v>
       </c>
       <c r="L30" s="21" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>68.47</v>
+        <v>62.53</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>1.42</v>
+        <v>7.12</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>8.550000000000001</v>
+        <v>5.79</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>3.14</v>
+        <v>1.86</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>33.5</v>
+        <v>35.2</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>1.05</v>
+        <v>20.94</v>
       </c>
       <c r="J31" s="21" t="n">
-        <v>0.96</v>
+        <v>-1.47</v>
       </c>
       <c r="K31" s="21" t="n">
-        <v>-0.22</v>
+        <v>-2.43</v>
       </c>
       <c r="L31" s="21" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
@@ -5635,34 +5635,34 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>65.02</v>
+        <v>64.19</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>6.71</v>
+        <v>1.22</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>5.13</v>
+        <v>7.44</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>34.1</v>
+        <v>33.2</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>40.95</v>
+        <v>1.86</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>-0.88</v>
+        <v>14.35</v>
       </c>
       <c r="K32" s="21" t="n">
-        <v>-2.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L32" s="21" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
@@ -5686,7 +5686,7 @@
         <v>0.59</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>7.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G33" s="21" t="n">
         <v>2.02</v>
@@ -5701,10 +5701,10 @@
         <v>9.98</v>
       </c>
       <c r="K33" s="21" t="n">
-        <v>-2.86</v>
+        <v>-2.36</v>
       </c>
       <c r="L33" s="21" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -5728,7 +5728,7 @@
         <v>1.37</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>4.97</v>
+        <v>5.11</v>
       </c>
       <c r="G34" s="21" t="n">
         <v>2.22</v>
@@ -5743,16 +5743,16 @@
         <v>0.29</v>
       </c>
       <c r="K34" s="21" t="n">
-        <v>-5.12</v>
+        <v>-5.52</v>
       </c>
       <c r="L34" s="21" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
@@ -5761,40 +5761,40 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>59.95</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>4.86</v>
+        <v>-1.52</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>5.25</v>
+        <v>1.25</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>3.08</v>
+        <v>4.14</v>
       </c>
       <c r="H35" s="21" t="n">
-        <v>34.8</v>
+        <v>33.5</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>66.26000000000001</v>
+        <v>-26.68</v>
       </c>
       <c r="J35" s="21" t="n">
-        <v>-2.83</v>
+        <v>0.64</v>
       </c>
       <c r="K35" s="21" t="n">
-        <v>0.41</v>
+        <v>-1.51</v>
       </c>
       <c r="L35" s="21" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
@@ -5803,202 +5803,202 @@
         </is>
       </c>
       <c r="C36" s="21" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>60.33</v>
+        <v>64.75</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>7.6</v>
+        <v>2.84</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>0.78</v>
+        <v>2.3</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>61.97</v>
+        <v>-27.01</v>
       </c>
       <c r="J36" s="21" t="n">
-        <v>11.92</v>
+        <v>5.37</v>
       </c>
       <c r="K36" s="21" t="n">
-        <v>-1.02</v>
+        <v>1.63</v>
       </c>
       <c r="L36" s="21" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>40 (B-)</t>
+          <t>41 (B-)</t>
         </is>
       </c>
       <c r="C37" s="21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>64.75</v>
+        <v>59.95</v>
       </c>
       <c r="E37" s="21" t="n">
-        <v>2.84</v>
+        <v>4.86</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>4.99</v>
+        <v>5.1</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>2.3</v>
+        <v>3.08</v>
       </c>
       <c r="H37" s="21" t="n">
-        <v>33.1</v>
+        <v>34.8</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>-27.01</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="J37" s="21" t="n">
-        <v>5.37</v>
+        <v>-2.83</v>
       </c>
       <c r="K37" s="21" t="n">
-        <v>1.3</v>
+        <v>-0.41</v>
       </c>
       <c r="L37" s="21" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>40 (B-)</t>
+          <t>41 (B-)</t>
         </is>
       </c>
       <c r="C38" s="21" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>60.48</v>
+        <v>60.33</v>
       </c>
       <c r="E38" s="21" t="n">
-        <v>6.16</v>
+        <v>7.6</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>4.12</v>
+        <v>5.05</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>14.06</v>
+        <v>61.97</v>
       </c>
       <c r="J38" s="21" t="n">
-        <v>5.23</v>
+        <v>11.92</v>
       </c>
       <c r="K38" s="21" t="n">
-        <v>-4.35</v>
+        <v>-1.14</v>
       </c>
       <c r="L38" s="21" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>37 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C39" s="21" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>60.37</v>
+        <v>60.48</v>
       </c>
       <c r="E39" s="21" t="n">
-        <v>7.54</v>
+        <v>6.16</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>5.64</v>
+        <v>4.12</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="H39" s="21" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>-8.31</v>
+        <v>14.06</v>
       </c>
       <c r="J39" s="21" t="n">
-        <v>10.03</v>
+        <v>5.23</v>
       </c>
       <c r="K39" s="21" t="n">
-        <v>-0.39</v>
+        <v>-5.54</v>
       </c>
       <c r="L39" s="21" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>37 (C+)</t>
+          <t>38 (C+)</t>
         </is>
       </c>
       <c r="C40" s="21" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>64.45</v>
+        <v>61.27</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>0.49</v>
+        <v>-1.13</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>6.93</v>
+        <v>1.05</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>33.6</v>
+        <v>34</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>142.07</v>
+        <v>-8.4</v>
       </c>
       <c r="J40" s="21" t="n">
-        <v>-0.06</v>
+        <v>3.8</v>
       </c>
       <c r="K40" s="21" t="n">
-        <v>-4.68</v>
+        <v>0.2</v>
       </c>
       <c r="L40" s="21" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>37 (C+)</t>
+          <t>38 (C+)</t>
         </is>
       </c>
       <c r="C41" s="21" t="n">
@@ -6022,7 +6022,7 @@
         <v>0.03</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>7.28</v>
+        <v>7.29</v>
       </c>
       <c r="G41" s="21" t="n">
         <v>2.56</v>
@@ -6037,16 +6037,16 @@
         <v>2.74</v>
       </c>
       <c r="K41" s="21" t="n">
-        <v>-1.42</v>
+        <v>-1.56</v>
       </c>
       <c r="L41" s="21" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
@@ -6055,76 +6055,76 @@
         </is>
       </c>
       <c r="C42" s="21" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>65.43000000000001</v>
+        <v>60.37</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>-1.52</v>
+        <v>7.54</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>5.19</v>
+        <v>5.55</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>4.14</v>
+        <v>1.3</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>33.5</v>
+        <v>34.2</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>-26.68</v>
+        <v>-8.31</v>
       </c>
       <c r="J42" s="21" t="n">
-        <v>0.64</v>
+        <v>10.03</v>
       </c>
       <c r="K42" s="21" t="n">
-        <v>-1.36</v>
+        <v>-0.59</v>
       </c>
       <c r="L42" s="21" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>36 (C+)</t>
+          <t>37 (C+)</t>
         </is>
       </c>
       <c r="C43" s="21" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>61.27</v>
+        <v>64.45</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>-1.13</v>
+        <v>0.49</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>3.12</v>
+        <v>7.18</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="H43" s="21" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>-8.4</v>
+        <v>142.07</v>
       </c>
       <c r="J43" s="21" t="n">
-        <v>3.8</v>
+        <v>-0.06</v>
       </c>
       <c r="K43" s="21" t="n">
-        <v>-0.39</v>
+        <v>-3.63</v>
       </c>
       <c r="L43" s="21" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -6148,7 +6148,7 @@
         <v>0.37</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>5.61</v>
+        <v>5.6</v>
       </c>
       <c r="G44" s="21" t="n">
         <v>3</v>
@@ -6163,16 +6163,16 @@
         <v>10.79</v>
       </c>
       <c r="K44" s="21" t="n">
-        <v>-2.44</v>
+        <v>-2.31</v>
       </c>
       <c r="L44" s="21" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B45" s="22" t="inlineStr">
@@ -6181,40 +6181,40 @@
         </is>
       </c>
       <c r="C45" s="21" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="D45" s="21" t="n">
-        <v>62.78</v>
+        <v>63.3</v>
       </c>
       <c r="E45" s="21" t="n">
-        <v>1.78</v>
+        <v>4.84</v>
       </c>
       <c r="F45" s="21" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G45" s="21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H45" s="21" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="I45" s="21" t="n">
         <v>4.77</v>
       </c>
-      <c r="G45" s="21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="H45" s="21" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="I45" s="21" t="n">
-        <v>-54.45</v>
-      </c>
       <c r="J45" s="21" t="n">
-        <v>4.55</v>
+        <v>5.14</v>
       </c>
       <c r="K45" s="21" t="n">
-        <v>-4.07</v>
+        <v>-1.43</v>
       </c>
       <c r="L45" s="21" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
@@ -6223,76 +6223,76 @@
         </is>
       </c>
       <c r="C46" s="21" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>66.17</v>
+        <v>62.78</v>
       </c>
       <c r="E46" s="21" t="n">
-        <v>4.78</v>
+        <v>1.78</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>5.21</v>
+        <v>4.84</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>33.9</v>
+        <v>35.1</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>-16.6</v>
+        <v>-54.45</v>
       </c>
       <c r="J46" s="21" t="n">
-        <v>-1.1</v>
+        <v>4.55</v>
       </c>
       <c r="K46" s="21" t="n">
-        <v>-1.9</v>
+        <v>-4.07</v>
       </c>
       <c r="L46" s="21" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>33 (C+)</t>
+          <t>35 (C+)</t>
         </is>
       </c>
       <c r="C47" s="21" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>63.3</v>
+        <v>66.17</v>
       </c>
       <c r="E47" s="21" t="n">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>6.57</v>
+        <v>5.25</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>2.98</v>
+        <v>1.22</v>
       </c>
       <c r="H47" s="21" t="n">
-        <v>32.9</v>
+        <v>33.9</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>4.77</v>
+        <v>-16.6</v>
       </c>
       <c r="J47" s="21" t="n">
-        <v>5.14</v>
+        <v>-1.1</v>
       </c>
       <c r="K47" s="21" t="n">
-        <v>-2.44</v>
+        <v>-1.99</v>
       </c>
       <c r="L47" s="21" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
@@ -6316,7 +6316,7 @@
         <v>5.33</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>7.29</v>
+        <v>7.17</v>
       </c>
       <c r="G48" s="21" t="n">
         <v>0.96</v>
@@ -6331,10 +6331,10 @@
         <v>0.86</v>
       </c>
       <c r="K48" s="21" t="n">
-        <v>-1.99</v>
+        <v>-2.37</v>
       </c>
       <c r="L48" s="21" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -6358,7 +6358,7 @@
         <v>5</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="G49" s="21" t="n">
         <v>2.24</v>
@@ -6373,10 +6373,10 @@
         <v>7.27</v>
       </c>
       <c r="K49" s="21" t="n">
-        <v>-2.73</v>
+        <v>-2.58</v>
       </c>
       <c r="L49" s="21" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>26 (C)</t>
+          <t>28 (C)</t>
         </is>
       </c>
       <c r="C50" s="21" t="n">
@@ -6400,7 +6400,7 @@
         <v>2.48</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>5.98</v>
+        <v>6.04</v>
       </c>
       <c r="G50" s="21" t="n">
         <v>0.12</v>
@@ -6415,10 +6415,10 @@
         <v>8.43</v>
       </c>
       <c r="K50" s="21" t="n">
-        <v>-1.36</v>
+        <v>-1.07</v>
       </c>
       <c r="L50" s="21" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
@@ -6442,7 +6442,7 @@
         <v>2.43</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>7.09</v>
+        <v>7.14</v>
       </c>
       <c r="G51" s="21" t="n">
         <v>1.34</v>
@@ -6457,10 +6457,10 @@
         <v>0.78</v>
       </c>
       <c r="K51" s="21" t="n">
-        <v>-3.33</v>
+        <v>-3.69</v>
       </c>
       <c r="L51" s="21" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="F2" s="11" t="n">
-        <v>33.2</v>
+        <v>34.9</v>
       </c>
       <c r="G2" s="11" t="n">
         <v>4.5</v>
@@ -6576,7 +6576,7 @@
         <v>4.84</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>6.57</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="3">
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>4.8</v>
@@ -6614,7 +6614,7 @@
         <v>5.33</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>7.29</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="4">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>40.2</v>
+        <v>40.6</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>4.5</v>
@@ -6652,7 +6652,7 @@
         <v>2.84</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>4.99</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="5">
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>3.6</v>
@@ -6690,7 +6690,7 @@
         <v>3.1</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="6">
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>4.2</v>
@@ -6728,7 +6728,7 @@
         <v>2.61</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="7">
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>45.8</v>
+        <v>45.4</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>3.5</v>
@@ -6766,7 +6766,7 @@
         <v>7.12</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>5.72</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="8">
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3.8</v>
@@ -6804,7 +6804,7 @@
         <v>1.37</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>4.97</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="9">
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>60.6</v>
+        <v>61.1</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3.3</v>
@@ -6842,7 +6842,7 @@
         <v>8.27</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="10">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>4</v>
@@ -6880,7 +6880,7 @@
         <v>2.21</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>5.41</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="11">
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>53.8</v>
+        <v>54.5</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>3.5</v>
@@ -6918,7 +6918,7 @@
         <v>4.52</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="12">
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>46.2</v>
+        <v>48.7</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>3.9</v>
@@ -6956,7 +6956,7 @@
         <v>1.42</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>8.550000000000001</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="13">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>5.1</v>
@@ -6994,7 +6994,7 @@
         <v>7.54</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>5.64</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="14">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>37.1</v>
+        <v>37.3</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>4.1</v>
@@ -7032,7 +7032,7 @@
         <v>0.49</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>6.93</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="15">
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>36.4</v>
+        <v>37.5</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>4.7</v>
@@ -7070,7 +7070,7 @@
         <v>-1.13</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>3.12</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="16">
@@ -7088,7 +7088,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>51.1</v>
+        <v>54.3</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>5</v>
@@ -7108,7 +7108,7 @@
         <v>7.63</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>5.53</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="17">
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>37.3</v>
+        <v>37.6</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>4</v>
@@ -7146,7 +7146,7 @@
         <v>0.03</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>7.28</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="18">
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>4.6</v>
@@ -7184,7 +7184,7 @@
         <v>4.86</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="19">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>4.4</v>
@@ -7222,45 +7222,45 @@
         <v>2.43</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>7.09</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="G20" s="8" t="n">
+      <c r="D20" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="5" t="n">
         <v>70.39</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="5" t="n">
         <v>6.57</v>
       </c>
-      <c r="J20" s="8" t="n">
-        <v>4.57</v>
+      <c r="J20" s="5" t="n">
+        <v>4.64</v>
       </c>
     </row>
     <row r="21">
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>36.2</v>
+        <v>36.5</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>4.4</v>
@@ -7298,83 +7298,83 @@
         <v>0.37</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>5.61</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="G22" s="11" t="n">
+      <c r="D22" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="G22" s="8" t="n">
         <v>3.6</v>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="H22" s="8" t="n">
         <v>65.43000000000001</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="8" t="n">
         <v>-1.52</v>
       </c>
-      <c r="J22" s="11" t="n">
-        <v>5.19</v>
+      <c r="J22" s="8" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="G23" s="5" t="n">
+      <c r="D23" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G23" s="8" t="n">
         <v>3.6</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="8" t="n">
         <v>64.19</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I23" s="8" t="n">
         <v>1.22</v>
       </c>
-      <c r="J23" s="5" t="n">
-        <v>1.34</v>
+      <c r="J23" s="8" t="n">
+        <v>7.44</v>
       </c>
     </row>
     <row r="24">
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>56.3</v>
+        <v>55.7</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>3.5</v>
@@ -7412,7 +7412,7 @@
         <v>0.66</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="25">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="F25" s="11" t="n">
-        <v>35.2</v>
+        <v>34.6</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>3.7</v>
@@ -7450,7 +7450,7 @@
         <v>1.78</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>4.77</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="26">
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>50.5</v>
+        <v>51.9</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>3.2</v>
@@ -7488,7 +7488,7 @@
         <v>3.18</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="27">
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="G27" s="11" t="n">
         <v>4.9</v>
@@ -7526,7 +7526,7 @@
         <v>4.78</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="28">
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>26.4</v>
+        <v>27.6</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>4.8</v>
@@ -7564,7 +7564,7 @@
         <v>2.48</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>5.98</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="29">
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>3.6</v>
@@ -7602,7 +7602,7 @@
         <v>8.65</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="30">
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>44.8</v>
+        <v>45.5</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>5.2</v>
@@ -7640,7 +7640,7 @@
         <v>6.71</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="31">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>3.6</v>
@@ -7678,7 +7678,7 @@
         <v>1.53</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="32">
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.5</v>
@@ -7716,7 +7716,7 @@
         <v>6.8</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="33">
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>53.4</v>
+        <v>53.2</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>3.6</v>
@@ -7754,7 +7754,7 @@
         <v>0.86</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>7.48</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="34">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>2.5</v>
@@ -7796,40 +7796,40 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="G35" s="5" t="n">
+      <c r="D35" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G35" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H35" s="8" t="n">
         <v>58.01</v>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I35" s="8" t="n">
         <v>-1.79</v>
       </c>
-      <c r="J35" s="5" t="n"/>
+      <c r="J35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>66.5</v>
+        <v>65.8</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>3</v>
@@ -7866,7 +7866,7 @@
         <v>1.62</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5.78</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="37">
@@ -7904,7 +7904,7 @@
         <v>0.59</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>7.33</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>3.6</v>
@@ -7942,7 +7942,7 @@
         <v>10.22</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="39">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>4.6</v>
@@ -7980,7 +7980,7 @@
         <v>5</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="40">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>54.7</v>
+        <v>54.2</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>4.3</v>
@@ -8018,7 +8018,7 @@
         <v>3.63</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="41">
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>63.2</v>
+        <v>60.6</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>3.1</v>
@@ -8056,7 +8056,7 @@
         <v>3.73</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.67</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="42">
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>3</v>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>3.6</v>
@@ -8132,7 +8132,7 @@
         <v>4.7</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="44">
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>57.8</v>
+        <v>54</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>3.1</v>
@@ -8170,7 +8170,7 @@
         <v>3.37</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0.75</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="45">
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>63.9</v>
+        <v>63.2</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>3.3</v>
@@ -8208,44 +8208,44 @@
         <v>5.12</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n">
+      <c r="A46" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D46" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="G46" s="8" t="n">
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="G46" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="11" t="n">
         <v>60.48</v>
       </c>
-      <c r="I46" s="8" t="n">
+      <c r="I46" s="11" t="n">
         <v>6.16</v>
       </c>
-      <c r="J46" s="8" t="n">
+      <c r="J46" s="11" t="n">
         <v>4.12</v>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>66.3</v>
+        <v>68</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.4</v>
@@ -8284,7 +8284,7 @@
         <v>3.15</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5.31</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="48">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>52.6</v>
+        <v>59.4</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>2.2</v>
@@ -8322,7 +8322,7 @@
         <v>-0.12</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>7.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="49">
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="F49" s="8" t="n">
-        <v>41.3</v>
+        <v>40.9</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>8.199999999999999</v>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>4</v>
@@ -8398,7 +8398,7 @@
         <v>3.13</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="51">
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>56.6</v>
+        <v>54.9</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>2.7</v>
@@ -8436,7 +8436,7 @@
         <v>-0.36</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>7.54</v>
+        <v>7.56</v>
       </c>
     </row>
   </sheetData>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="G3" s="28" t="n">
@@ -8557,11 +8557,11 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="C4" s="27" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
@@ -8573,11 +8573,11 @@
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="G4" s="28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="28" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C5" s="27" t="n">
@@ -8625,11 +8625,11 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="C6" s="27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="G6" s="28" t="n">
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="G7" s="28" t="n">
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="C8" s="27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
@@ -8709,11 +8709,11 @@
       </c>
       <c r="F8" s="28" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="G8" s="28" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" s="28" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
@@ -8761,11 +8761,11 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C10" s="27" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C11" s="27" t="n">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H11" s="28" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>60.6</v>
+        <v>60.4</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -999,16 +999,16 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1030,20 +1030,20 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>54.9</v>
+        <v>54.4</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1061,16 +1061,16 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>54.5</v>
+        <v>54.2</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
@@ -1092,16 +1092,16 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>54.3</v>
+        <v>54.5</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>53.5</v>
+        <v>54.1</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -1185,20 +1185,20 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -1495,20 +1495,20 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -1526,16 +1526,16 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -1805,20 +1805,20 @@
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>37.5</v>
+        <v>38.9</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -1836,20 +1836,20 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="F41" s="11" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -1867,20 +1867,20 @@
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D42" s="13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="F42" s="11" t="n">
-        <v>37.3</v>
+        <v>37.6</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -1898,16 +1898,16 @@
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D43" s="13" t="n">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="F44" s="11" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="F47" s="11" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="F49" s="11" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>96</v>
@@ -2460,7 +2460,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="19" t="n">
         <v>44</v>
@@ -2497,10 +2497,10 @@
         <v>54</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7" s="19" t="n">
         <v>34</v>
@@ -2537,10 +2537,10 @@
         <v>94</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I8" s="18" t="n">
         <v>82</v>
@@ -2580,7 +2580,7 @@
         <v>82</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I9" s="19" t="n">
         <v>28</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>86</v>
@@ -2617,10 +2617,10 @@
         <v>62</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I10" s="19" t="n">
         <v>14</v>
@@ -2697,7 +2697,7 @@
         <v>82</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>92</v>
@@ -2737,7 +2737,7 @@
         <v>92</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H13" s="19" t="n">
         <v>4</v>
@@ -2758,281 +2758,281 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="C14" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>80</v>
+      <c r="C14" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>31</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>32</v>
+        <v>43</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>74</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="L14" s="21" t="n">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="L14" s="18" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="E15" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="C15" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>57</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="J15" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H15" s="19" t="n">
+      <c r="K15" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="L15" s="19" t="n">
         <v>44</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="L15" s="18" t="n">
-        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C16" s="20" t="n">
-        <v>68</v>
+      <c r="C16" s="19" t="n">
+        <v>6</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>92</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="I16" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="H16" s="18" t="n">
         <v>76</v>
       </c>
+      <c r="I16" s="19" t="n">
+        <v>46</v>
+      </c>
       <c r="J16" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="L16" s="19" t="n">
-        <v>44</v>
+        <v>16</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B17" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C17" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>84</v>
+      <c r="C17" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>26</v>
+        <v>96</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>78</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>43</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="L17" s="18" t="n">
-        <v>94</v>
+        <v>32</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="L17" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C18" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="E18" s="19" t="n">
+      <c r="C18" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="D18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>54</v>
+      </c>
       <c r="F18" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>28</v>
+        <v>84</v>
+      </c>
+      <c r="G18" s="20" t="n">
+        <v>57</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>96</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="D19" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="D19" s="21" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="F19" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>47</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="K19" s="18" t="n">
         <v>84</v>
       </c>
-      <c r="G19" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="K19" s="18" t="n">
-        <v>96</v>
-      </c>
       <c r="L19" s="20" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>54</v>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>86</v>
+        <v>53</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>50</v>
       </c>
       <c r="D20" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="E20" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>58</v>
+      <c r="F20" s="18" t="n">
+        <v>88</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="I20" s="20" t="n">
+        <v>50</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L20" s="20" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
@@ -3060,7 +3060,7 @@
         <v>90</v>
       </c>
       <c r="H21" s="20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I21" s="20" t="n">
         <v>64</v>
@@ -3137,10 +3137,10 @@
         <v>70</v>
       </c>
       <c r="G23" s="20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I23" s="19" t="n">
         <v>42</v>
@@ -3176,8 +3176,8 @@
       <c r="F24" s="18" t="n">
         <v>72</v>
       </c>
-      <c r="G24" s="20" t="n">
-        <v>50</v>
+      <c r="G24" s="19" t="n">
+        <v>49</v>
       </c>
       <c r="H24" s="18" t="n">
         <v>80</v>
@@ -3217,7 +3217,7 @@
         <v>52</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>92</v>
@@ -3257,10 +3257,10 @@
         <v>50</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H26" s="20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I26" s="18" t="n">
         <v>72</v>
@@ -3300,7 +3300,7 @@
         <v>76</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I27" s="20" t="n">
         <v>52</v>
@@ -3337,7 +3337,7 @@
         <v>74</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H28" s="19" t="n">
         <v>12</v>
@@ -3377,7 +3377,7 @@
         <v>64</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>98</v>
@@ -3398,121 +3398,121 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>46</v>
-      </c>
-      <c r="C30" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="C30" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="L30" s="19" t="n">
         <v>2</v>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="F30" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="H30" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="L30" s="20" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B31" s="17" t="n">
         <v>45</v>
       </c>
       <c r="C31" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="J31" s="20" t="n">
         <v>68</v>
       </c>
-      <c r="D31" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="F31" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="G31" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="H31" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="I31" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="J31" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="K31" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="L31" s="19" t="n">
-        <v>2</v>
+      <c r="K31" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="L31" s="18" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B32" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="C32" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="E32" s="19" t="n">
-        <v>22</v>
+      <c r="C32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>82</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="H32" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="I32" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>49</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="L32" s="20" t="n">
         <v>54</v>
-      </c>
-      <c r="J32" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="L32" s="18" t="n">
-        <v>72</v>
       </c>
     </row>
     <row r="33">
@@ -3537,10 +3537,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I33" s="18" t="n">
         <v>98</v>
@@ -3577,10 +3577,10 @@
         <v>40</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H34" s="20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I34" s="19" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
         <v>94</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I35" s="19" t="n">
         <v>6</v>
@@ -3657,7 +3657,7 @@
         <v>46</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H36" s="19" t="n">
         <v>12</v>
@@ -3697,7 +3697,7 @@
         <v>42</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>76</v>
@@ -3740,7 +3740,7 @@
         <v>4</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I38" s="18" t="n">
         <v>90</v>
@@ -3780,7 +3780,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>70</v>
@@ -3798,161 +3798,161 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C40" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D40" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="E40" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="G40" s="19" t="n">
-        <v>26</v>
+      <c r="E40" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>50</v>
       </c>
       <c r="H40" s="20" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I40" s="19" t="n">
-        <v>38</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="J40" s="20" t="n">
+        <v>56</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>88</v>
+        <v>32</v>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>52</v>
       </c>
       <c r="E41" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F41" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="F41" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="I41" s="19" t="n">
+      <c r="G41" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="H41" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="J41" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="J41" s="19" t="n">
-        <v>32</v>
-      </c>
       <c r="K41" s="19" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D42" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="E42" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="D42" s="18" t="n">
         <v>88</v>
       </c>
+      <c r="E42" s="19" t="n">
+        <v>10</v>
+      </c>
       <c r="F42" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G42" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="H42" s="20" t="n">
-        <v>58</v>
+        <v>8</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>22</v>
       </c>
       <c r="I42" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="J42" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="K42" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="L42" s="19" t="n">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="L42" s="18" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
         <v>37</v>
       </c>
       <c r="C43" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>52</v>
+        <v>14</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>22</v>
       </c>
       <c r="E43" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="F43" s="19" t="n">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>90</v>
       </c>
       <c r="G43" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H43" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="I43" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="J43" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="H43" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="I43" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="J43" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="K43" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L43" s="18" t="n">
-        <v>96</v>
+      <c r="K43" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="L43" s="19" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -3977,10 +3977,10 @@
         <v>28</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I44" s="20" t="n">
         <v>66</v>
@@ -4017,7 +4017,7 @@
         <v>16</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H45" s="19" t="n">
         <v>4</v>
@@ -4100,7 +4100,7 @@
         <v>12</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I47" s="19" t="n">
         <v>30</v>
@@ -4177,10 +4177,10 @@
         <v>66</v>
       </c>
       <c r="G49" s="19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I49" s="19" t="n">
         <v>8</v>
@@ -4257,7 +4257,7 @@
         <v>14</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H51" s="21" t="n">
         <v>0</v>
@@ -4389,7 +4389,7 @@
         <v>0.17</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>33.1</v>
@@ -4473,7 +4473,7 @@
         <v>5.71</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="H4" s="21" t="n">
         <v>34.9</v>
@@ -4515,7 +4515,7 @@
         <v>4.82</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="H5" s="21" t="n">
         <v>35.8</v>
@@ -4557,7 +4557,7 @@
         <v>4.64</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>33.6</v>
@@ -4599,7 +4599,7 @@
         <v>4.87</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>33.9</v>
@@ -4641,7 +4641,7 @@
         <v>0.63</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>34.4</v>
@@ -4683,7 +4683,7 @@
         <v>4.43</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>34.6</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>61 (B+)</t>
+          <t>60 (B+)</t>
         </is>
       </c>
       <c r="C10" s="21" t="n">
@@ -4725,7 +4725,7 @@
         <v>4.8</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>34.2</v>
@@ -4767,7 +4767,7 @@
         <v>4.95</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>32.9</v>
@@ -4809,7 +4809,7 @@
         <v>3.13</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>35.5</v>
@@ -4851,7 +4851,7 @@
         <v>0.73</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>32.9</v>
@@ -4872,7 +4872,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
@@ -4881,82 +4881,82 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>60.33</v>
+        <v>64.7</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>8.65</v>
+        <v>-0.36</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>4.18</v>
+        <v>7.56</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>3.38</v>
+        <v>2.06</v>
       </c>
       <c r="H14" s="21" t="n">
         <v>33.9</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>-13.83</v>
+        <v>16.13</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>17.94</v>
+        <v>28.29</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>4.21</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L14" s="21" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>55 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>64.7</v>
+        <v>66.34</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>-0.36</v>
+        <v>4.52</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>7.56</v>
+        <v>5.18</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>16.13</v>
+        <v>16.78</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>28.29</v>
+        <v>-1.53</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.18</v>
       </c>
       <c r="L15" s="21" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
@@ -4965,40 +4965,40 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>66.34</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>4.52</v>
+        <v>7.63</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>5.18</v>
+        <v>5.62</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>34.2</v>
+        <v>34.8</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>16.78</v>
+        <v>-1.35</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>-1.53</v>
+        <v>-0.13</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>-2.18</v>
+        <v>0.08</v>
       </c>
       <c r="L16" s="21" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -5007,40 +5007,40 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>68.23999999999999</v>
+        <v>60.33</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>7.63</v>
+        <v>8.65</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>5.62</v>
+        <v>4.18</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>34.8</v>
+        <v>33.9</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>-1.35</v>
+        <v>-13.83</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>-0.13</v>
+        <v>17.94</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>0.08</v>
+        <v>4.21</v>
       </c>
       <c r="L17" s="21" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
@@ -5049,40 +5049,40 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>63.08</v>
+        <v>50.77</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>1.53</v>
+        <v>3.63</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>2.02</v>
+        <v>2.73</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>-0.44</v>
+        <v>144.37</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>21.54</v>
+        <v>24.22</v>
       </c>
       <c r="K18" s="21" t="n">
-        <v>2.52</v>
+        <v>10.23</v>
       </c>
       <c r="L18" s="21" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -5091,76 +5091,76 @@
         </is>
       </c>
       <c r="C19" s="21" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>50.77</v>
+        <v>62.74</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>3.63</v>
+        <v>3.37</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>1.39</v>
+        <v>4.82</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>2.78</v>
+        <v>2.33</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>144.37</v>
+        <v>-19.57</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>24.22</v>
+        <v>15.66</v>
       </c>
       <c r="K19" s="21" t="n">
-        <v>10.23</v>
+        <v>3.26</v>
       </c>
       <c r="L19" s="21" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>62.74</v>
+        <v>63.08</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>3.37</v>
+        <v>1.53</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>4.82</v>
+        <v>1.09</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>-19.57</v>
+        <v>-0.44</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>15.66</v>
+        <v>21.54</v>
       </c>
       <c r="K20" s="21" t="n">
-        <v>3.26</v>
+        <v>2.52</v>
       </c>
       <c r="L20" s="21" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
@@ -5187,7 +5187,7 @@
         <v>7.49</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>34.3</v>
@@ -5229,7 +5229,7 @@
         <v>5.4</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="H22" s="21" t="n">
         <v>34.9</v>
@@ -5271,7 +5271,7 @@
         <v>4.64</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H23" s="21" t="n">
         <v>33.4</v>
@@ -5313,7 +5313,7 @@
         <v>4.63</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="H24" s="21" t="n">
         <v>34.9</v>
@@ -5355,7 +5355,7 @@
         <v>4.88</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="H25" s="21" t="n">
         <v>35.5</v>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F26" s="21" t="n"/>
       <c r="G26" s="21" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="H26" s="21" t="n">
         <v>34.5</v>
@@ -5437,7 +5437,7 @@
         <v>6.61</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="H27" s="21" t="n">
         <v>33.5</v>
@@ -5479,7 +5479,7 @@
         <v>4.53</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H28" s="21" t="n">
         <v>33.1</v>
@@ -5521,7 +5521,7 @@
         <v>4.72</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="H29" s="21" t="n">
         <v>36.5</v>
@@ -5542,49 +5542,49 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C30" s="21" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>65.02</v>
+        <v>62.53</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>6.71</v>
+        <v>7.12</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>5.08</v>
+        <v>5.79</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>34.1</v>
+        <v>35.2</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>40.95</v>
+        <v>20.94</v>
       </c>
       <c r="J30" s="21" t="n">
-        <v>-0.88</v>
+        <v>-1.47</v>
       </c>
       <c r="K30" s="21" t="n">
-        <v>-2.22</v>
+        <v>-2.43</v>
       </c>
       <c r="L30" s="21" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
@@ -5593,40 +5593,40 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>62.53</v>
+        <v>64.19</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>7.12</v>
+        <v>1.22</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>5.79</v>
+        <v>7.44</v>
       </c>
       <c r="G31" s="21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H31" s="21" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I31" s="21" t="n">
         <v>1.86</v>
       </c>
-      <c r="H31" s="21" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="I31" s="21" t="n">
-        <v>20.94</v>
-      </c>
       <c r="J31" s="21" t="n">
-        <v>-1.47</v>
+        <v>14.35</v>
       </c>
       <c r="K31" s="21" t="n">
-        <v>-2.43</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L31" s="21" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
@@ -5635,34 +5635,34 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>64.19</v>
+        <v>65.02</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>1.22</v>
+        <v>6.71</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>7.44</v>
+        <v>5.08</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>33.2</v>
+        <v>34.1</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>1.86</v>
+        <v>40.95</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>14.35</v>
+        <v>-0.88</v>
       </c>
       <c r="K32" s="21" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.22</v>
       </c>
       <c r="L32" s="21" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
@@ -5773,7 +5773,7 @@
         <v>1.25</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="H35" s="21" t="n">
         <v>33.5</v>
@@ -5815,7 +5815,7 @@
         <v>5.07</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="H36" s="21" t="n">
         <v>33.1</v>
@@ -5857,7 +5857,7 @@
         <v>5.1</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="H37" s="21" t="n">
         <v>34.8</v>
@@ -5899,7 +5899,7 @@
         <v>5.05</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="H38" s="21" t="n">
         <v>33.5</v>
@@ -5941,7 +5941,7 @@
         <v>4.12</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H39" s="21" t="n">
         <v>33.9</v>
@@ -5962,133 +5962,129 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>38 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C40" s="21" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>61.27</v>
+        <v>60.37</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>-1.13</v>
+        <v>7.54</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="G40" s="21" t="n">
-        <v>1.96</v>
-      </c>
+        <v>5.55</v>
+      </c>
+      <c r="G40" s="21" t="n"/>
       <c r="H40" s="21" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>-8.4</v>
+        <v>-8.31</v>
       </c>
       <c r="J40" s="21" t="n">
-        <v>3.8</v>
+        <v>10.03</v>
       </c>
       <c r="K40" s="21" t="n">
-        <v>0.2</v>
+        <v>-0.59</v>
       </c>
       <c r="L40" s="21" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>38 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C41" s="21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>69.03</v>
+        <v>64.45</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>0.03</v>
+        <v>0.49</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>7.29</v>
+        <v>7.18</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="H41" s="21" t="n">
-        <v>33.3</v>
-      </c>
+        <v>2.14</v>
+      </c>
+      <c r="H41" s="21" t="n"/>
       <c r="I41" s="21" t="n">
-        <v>-22.23</v>
+        <v>142.07</v>
       </c>
       <c r="J41" s="21" t="n">
-        <v>2.74</v>
+        <v>-0.06</v>
       </c>
       <c r="K41" s="21" t="n">
-        <v>-1.56</v>
+        <v>-3.63</v>
       </c>
       <c r="L41" s="21" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>37 (C+)</t>
+          <t>38 (C+)</t>
         </is>
       </c>
       <c r="C42" s="21" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>60.37</v>
+        <v>69.03</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>7.54</v>
+        <v>0.03</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>5.55</v>
+        <v>7.29</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>1.3</v>
+        <v>2.51</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>34.2</v>
+        <v>33.3</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>-8.31</v>
+        <v>-22.23</v>
       </c>
       <c r="J42" s="21" t="n">
-        <v>10.03</v>
+        <v>2.74</v>
       </c>
       <c r="K42" s="21" t="n">
-        <v>-0.59</v>
+        <v>-1.56</v>
       </c>
       <c r="L42" s="21" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
@@ -6097,34 +6093,34 @@
         </is>
       </c>
       <c r="C43" s="21" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>64.45</v>
+        <v>61.27</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>0.49</v>
+        <v>-1.13</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>7.18</v>
+        <v>1.05</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="H43" s="21" t="n">
-        <v>33.6</v>
+        <v>34</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>142.07</v>
+        <v>-8.4</v>
       </c>
       <c r="J43" s="21" t="n">
-        <v>-0.06</v>
+        <v>3.8</v>
       </c>
       <c r="K43" s="21" t="n">
-        <v>-3.63</v>
+        <v>0.2</v>
       </c>
       <c r="L43" s="21" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44">
@@ -6151,7 +6147,7 @@
         <v>5.6</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H44" s="21" t="n">
         <v>33.7</v>
@@ -6193,7 +6189,7 @@
         <v>6.87</v>
       </c>
       <c r="G45" s="21" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H45" s="21" t="n">
         <v>32.9</v>
@@ -6235,7 +6231,7 @@
         <v>4.84</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="H46" s="21" t="n">
         <v>35.1</v>
@@ -6277,7 +6273,7 @@
         <v>5.25</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H47" s="21" t="n">
         <v>33.9</v>
@@ -6319,7 +6315,7 @@
         <v>7.17</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H48" s="21" t="n">
         <v>32.9</v>
@@ -6361,7 +6357,7 @@
         <v>4.66</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H49" s="21" t="n">
         <v>33.7</v>
@@ -6403,7 +6399,7 @@
         <v>6.04</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H50" s="21" t="n">
         <v>32.7</v>
@@ -6445,7 +6441,7 @@
         <v>7.14</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H51" s="21" t="n">
         <v>32.6</v>
@@ -6640,7 +6636,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>4.5</v>
@@ -6678,7 +6674,7 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>3.6</v>
@@ -6716,7 +6712,7 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>4.2</v>
@@ -6754,7 +6750,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>3.5</v>
@@ -6830,7 +6826,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3.3</v>
@@ -6868,7 +6864,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>4</v>
@@ -6906,7 +6902,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>3.5</v>
@@ -6974,7 +6970,7 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
@@ -6982,7 +6978,7 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>37.3</v>
+        <v>38.9</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>5.1</v>
@@ -7012,7 +7008,7 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -7020,7 +7016,7 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>37.3</v>
+        <v>38.6</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>4.1</v>
@@ -7050,7 +7046,7 @@
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -7058,7 +7054,7 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>4.7</v>
@@ -7096,7 +7092,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>5</v>
@@ -7172,7 +7168,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>4.6</v>
@@ -7210,7 +7206,7 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>4.4</v>
@@ -7248,7 +7244,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>3.6</v>
@@ -7286,7 +7282,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>4.4</v>
@@ -7324,7 +7320,7 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>3.6</v>
@@ -7400,7 +7396,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>3.5</v>
@@ -7476,7 +7472,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>3.2</v>
@@ -7514,7 +7510,7 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="G27" s="11" t="n">
         <v>4.9</v>
@@ -7582,7 +7578,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
@@ -7590,7 +7586,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>54.6</v>
+        <v>54.5</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>3.6</v>
@@ -7620,7 +7616,7 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
@@ -7628,7 +7624,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>5.2</v>
@@ -7658,7 +7654,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
@@ -7704,7 +7700,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.5</v>
@@ -7742,7 +7738,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>3.6</v>
@@ -7818,7 +7814,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>3.4</v>
@@ -7892,7 +7888,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>4</v>
@@ -7930,7 +7926,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>3.6</v>
@@ -7968,7 +7964,7 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>4.6</v>
@@ -8006,7 +8002,7 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>4.3</v>
@@ -8036,7 +8032,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -8044,7 +8040,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>60.6</v>
+        <v>60.4</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>3.1</v>
@@ -8120,7 +8116,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>3.6</v>
@@ -8196,7 +8192,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>3.3</v>
@@ -8234,7 +8230,7 @@
         </is>
       </c>
       <c r="F46" s="11" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>4</v>
@@ -8310,7 +8306,7 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>2.2</v>
@@ -8348,7 +8344,7 @@
         </is>
       </c>
       <c r="F49" s="8" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>8.199999999999999</v>
@@ -8386,7 +8382,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>4</v>
@@ -8424,7 +8420,7 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>54.9</v>
+        <v>54.7</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>2.7</v>
@@ -8539,11 +8535,11 @@
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="G3" s="28" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="28" t="inlineStr">
         <is>
@@ -8573,7 +8569,7 @@
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="G4" s="28" t="n">
@@ -8799,7 +8795,7 @@
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>54.1</v>
+        <v>53.6</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -1185,20 +1185,20 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D39" s="13" t="n">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>39.8</v>
+        <v>39.5</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -1805,20 +1805,20 @@
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>38.9</v>
+        <v>39.8</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -1836,20 +1836,20 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="F41" s="11" t="n">
-        <v>38.6</v>
+        <v>37.6</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -1867,20 +1867,20 @@
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D42" s="13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="F42" s="11" t="n">
-        <v>37.6</v>
+        <v>37.2</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -1991,16 +1991,16 @@
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="D46" s="13" t="n">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="F46" s="11" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="F47" s="11" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>68</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>37</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>86</v>
@@ -2617,7 +2617,7 @@
         <v>62</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H10" s="20" t="n">
         <v>57</v>
@@ -2697,7 +2697,7 @@
         <v>82</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>92</v>
@@ -2737,7 +2737,7 @@
         <v>92</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H13" s="19" t="n">
         <v>4</v>
@@ -2777,7 +2777,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H14" s="19" t="n">
         <v>43</v>
@@ -2918,121 +2918,121 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="E18" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="D18" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="20" t="n">
-        <v>54</v>
-      </c>
       <c r="F18" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>57</v>
+        <v>88</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>29</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>96</v>
+        <v>29</v>
+      </c>
+      <c r="I18" s="20" t="n">
+        <v>50</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="C19" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="D19" s="19" t="n">
+      <c r="C19" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="D19" s="21" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="F19" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>47</v>
+        <v>54</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="G19" s="20" t="n">
+        <v>59</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>24</v>
+        <v>12</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>96</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="L19" s="20" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>53</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>50</v>
+        <v>54</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>86</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="E20" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="F20" s="18" t="n">
-        <v>88</v>
+      <c r="E20" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>58</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="I20" s="20" t="n">
-        <v>50</v>
+        <v>22</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>24</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L20" s="20" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
@@ -3137,7 +3137,7 @@
         <v>70</v>
       </c>
       <c r="G23" s="20" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H23" s="19" t="n">
         <v>27</v>
@@ -3337,7 +3337,7 @@
         <v>74</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H28" s="19" t="n">
         <v>12</v>
@@ -3377,7 +3377,7 @@
         <v>64</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>98</v>
@@ -3417,7 +3417,7 @@
         <v>22</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H30" s="18" t="n">
         <v>88</v>
@@ -3496,8 +3496,8 @@
       <c r="F32" s="19" t="n">
         <v>44</v>
       </c>
-      <c r="G32" s="19" t="n">
-        <v>49</v>
+      <c r="G32" s="20" t="n">
+        <v>51</v>
       </c>
       <c r="H32" s="20" t="n">
         <v>55</v>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H33" s="18" t="n">
         <v>73</v>
@@ -3577,7 +3577,7 @@
         <v>40</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H34" s="20" t="n">
         <v>67</v>
@@ -3657,7 +3657,7 @@
         <v>46</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H36" s="19" t="n">
         <v>12</v>
@@ -3758,161 +3758,161 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
         <v>40</v>
       </c>
       <c r="C39" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="D39" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H39" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="J39" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="E39" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="I39" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>42</v>
-      </c>
       <c r="K39" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="L39" s="18" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C40" s="19" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D40" s="19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="F40" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="H40" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="I40" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="J40" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="K40" s="20" t="n">
-        <v>52</v>
+        <v>78</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="J41" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="D41" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>33</v>
-      </c>
-      <c r="H41" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="I41" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>18</v>
-      </c>
       <c r="K41" s="19" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="D42" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E42" s="18" t="n">
         <v>88</v>
       </c>
-      <c r="E42" s="19" t="n">
-        <v>10</v>
-      </c>
       <c r="F42" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v>57</v>
       </c>
       <c r="I42" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="L42" s="18" t="n">
-        <v>80</v>
+        <v>40</v>
+      </c>
+      <c r="J42" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="K42" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="L42" s="19" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -3937,7 +3937,7 @@
         <v>90</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H43" s="20" t="n">
         <v>53</v>
@@ -4038,81 +4038,81 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
         <v>35</v>
       </c>
       <c r="C46" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="D46" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="I46" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="E46" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="G46" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="H46" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="I46" s="21" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" s="19" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C47" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <v>64</v>
-      </c>
-      <c r="F47" s="19" t="n">
-        <v>34</v>
+        <v>48</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>56</v>
       </c>
       <c r="G47" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="H47" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="I47" s="19" t="n">
-        <v>30</v>
+      <c r="H47" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="I47" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -4257,7 +4257,7 @@
         <v>14</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H51" s="21" t="n">
         <v>0</v>
@@ -4389,7 +4389,7 @@
         <v>0.17</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>33.1</v>
@@ -4473,7 +4473,7 @@
         <v>5.71</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="H4" s="21" t="n">
         <v>34.9</v>
@@ -4515,7 +4515,7 @@
         <v>4.82</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="H5" s="21" t="n">
         <v>35.8</v>
@@ -4557,7 +4557,7 @@
         <v>4.64</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>33.6</v>
@@ -4599,7 +4599,7 @@
         <v>4.87</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>33.9</v>
@@ -4641,7 +4641,7 @@
         <v>0.63</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>34.4</v>
@@ -4683,7 +4683,7 @@
         <v>4.43</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>34.6</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>60 (B+)</t>
+          <t>61 (B+)</t>
         </is>
       </c>
       <c r="C10" s="21" t="n">
@@ -4725,7 +4725,7 @@
         <v>4.8</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>34.2</v>
@@ -4767,7 +4767,7 @@
         <v>4.95</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>32.9</v>
@@ -4809,7 +4809,7 @@
         <v>3.13</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>35.5</v>
@@ -4851,7 +4851,7 @@
         <v>0.73</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>32.9</v>
@@ -4893,7 +4893,7 @@
         <v>7.56</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H14" s="21" t="n">
         <v>33.9</v>
@@ -4935,7 +4935,7 @@
         <v>5.18</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>34.2</v>
@@ -4977,7 +4977,7 @@
         <v>5.62</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>34.8</v>
@@ -5019,7 +5019,7 @@
         <v>4.18</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>33.9</v>
@@ -5040,7 +5040,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
@@ -5049,40 +5049,40 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>50.77</v>
+        <v>63.08</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>3.63</v>
+        <v>1.53</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>2.73</v>
+        <v>2</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>144.37</v>
+        <v>-0.44</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>24.22</v>
+        <v>21.54</v>
       </c>
       <c r="K18" s="21" t="n">
-        <v>10.23</v>
+        <v>2.52</v>
       </c>
       <c r="L18" s="21" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -5091,76 +5091,76 @@
         </is>
       </c>
       <c r="C19" s="21" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>62.74</v>
+        <v>50.77</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>3.37</v>
+        <v>3.63</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>4.82</v>
+        <v>1.39</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>-19.57</v>
+        <v>144.37</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>15.66</v>
+        <v>24.22</v>
       </c>
       <c r="K19" s="21" t="n">
-        <v>3.26</v>
+        <v>10.23</v>
       </c>
       <c r="L19" s="21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>63.08</v>
+        <v>62.74</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>1.53</v>
+        <v>3.37</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>1.09</v>
+        <v>4.82</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>2.02</v>
+        <v>2.37</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>-0.44</v>
+        <v>-19.57</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>21.54</v>
+        <v>15.66</v>
       </c>
       <c r="K20" s="21" t="n">
-        <v>2.52</v>
+        <v>3.26</v>
       </c>
       <c r="L20" s="21" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -5187,7 +5187,7 @@
         <v>7.49</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>34.3</v>
@@ -5229,7 +5229,7 @@
         <v>5.4</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="H22" s="21" t="n">
         <v>34.9</v>
@@ -5271,7 +5271,7 @@
         <v>4.64</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="H23" s="21" t="n">
         <v>33.4</v>
@@ -5313,7 +5313,7 @@
         <v>4.63</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="H24" s="21" t="n">
         <v>34.9</v>
@@ -5355,7 +5355,7 @@
         <v>4.88</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="H25" s="21" t="n">
         <v>35.5</v>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F26" s="21" t="n"/>
       <c r="G26" s="21" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="H26" s="21" t="n">
         <v>34.5</v>
@@ -5479,7 +5479,7 @@
         <v>4.53</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H28" s="21" t="n">
         <v>33.1</v>
@@ -5521,7 +5521,7 @@
         <v>4.72</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H29" s="21" t="n">
         <v>36.5</v>
@@ -5563,7 +5563,7 @@
         <v>5.79</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H30" s="21" t="n">
         <v>35.2</v>
@@ -5605,7 +5605,7 @@
         <v>7.44</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H31" s="21" t="n">
         <v>33.2</v>
@@ -5647,7 +5647,7 @@
         <v>5.08</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="H32" s="21" t="n">
         <v>34.1</v>
@@ -5773,7 +5773,7 @@
         <v>1.25</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="H35" s="21" t="n">
         <v>33.5</v>
@@ -5815,7 +5815,7 @@
         <v>5.07</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="H36" s="21" t="n">
         <v>33.1</v>
@@ -5857,7 +5857,7 @@
         <v>5.1</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="H37" s="21" t="n">
         <v>34.8</v>
@@ -5899,7 +5899,7 @@
         <v>5.05</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H38" s="21" t="n">
         <v>33.5</v>
@@ -5920,7 +5920,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
@@ -5929,156 +5929,156 @@
         </is>
       </c>
       <c r="C39" s="21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>60.48</v>
+        <v>64.45</v>
       </c>
       <c r="E39" s="21" t="n">
-        <v>6.16</v>
+        <v>0.49</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="G39" s="21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H39" s="21" t="n">
-        <v>33.9</v>
-      </c>
+        <v>7.18</v>
+      </c>
+      <c r="G39" s="21" t="n"/>
+      <c r="H39" s="21" t="n"/>
       <c r="I39" s="21" t="n">
-        <v>14.06</v>
+        <v>142.07</v>
       </c>
       <c r="J39" s="21" t="n">
-        <v>5.23</v>
+        <v>-0.06</v>
       </c>
       <c r="K39" s="21" t="n">
-        <v>-5.54</v>
+        <v>-3.63</v>
       </c>
       <c r="L39" s="21" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C40" s="21" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>60.37</v>
+        <v>60.48</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>7.54</v>
+        <v>6.16</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="G40" s="21" t="n"/>
+        <v>4.12</v>
+      </c>
+      <c r="G40" s="21" t="n">
+        <v>0.61</v>
+      </c>
       <c r="H40" s="21" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>-8.31</v>
+        <v>14.06</v>
       </c>
       <c r="J40" s="21" t="n">
-        <v>10.03</v>
+        <v>5.23</v>
       </c>
       <c r="K40" s="21" t="n">
-        <v>-0.59</v>
+        <v>-5.54</v>
       </c>
       <c r="L40" s="21" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>38 (C+)</t>
         </is>
       </c>
       <c r="C41" s="21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>64.45</v>
+        <v>69.03</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>0.49</v>
+        <v>0.03</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>7.18</v>
+        <v>7.29</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H41" s="21" t="n"/>
+        <v>2.55</v>
+      </c>
+      <c r="H41" s="21" t="n">
+        <v>33.3</v>
+      </c>
       <c r="I41" s="21" t="n">
-        <v>142.07</v>
+        <v>-22.23</v>
       </c>
       <c r="J41" s="21" t="n">
-        <v>-0.06</v>
+        <v>2.74</v>
       </c>
       <c r="K41" s="21" t="n">
-        <v>-3.63</v>
+        <v>-1.56</v>
       </c>
       <c r="L41" s="21" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>38 (C+)</t>
+          <t>37 (C+)</t>
         </is>
       </c>
       <c r="C42" s="21" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>69.03</v>
+        <v>60.37</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>0.03</v>
+        <v>7.54</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>7.29</v>
+        <v>5.55</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>2.51</v>
+        <v>1.27</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>33.3</v>
+        <v>34.2</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>-22.23</v>
+        <v>-8.31</v>
       </c>
       <c r="J42" s="21" t="n">
-        <v>2.74</v>
+        <v>10.03</v>
       </c>
       <c r="K42" s="21" t="n">
-        <v>-1.56</v>
+        <v>-0.59</v>
       </c>
       <c r="L42" s="21" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -6105,7 +6105,7 @@
         <v>1.05</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H43" s="21" t="n">
         <v>34</v>
@@ -6147,7 +6147,7 @@
         <v>5.6</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H44" s="21" t="n">
         <v>33.7</v>
@@ -6189,7 +6189,7 @@
         <v>6.87</v>
       </c>
       <c r="G45" s="21" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H45" s="21" t="n">
         <v>32.9</v>
@@ -6210,7 +6210,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
@@ -6219,76 +6219,76 @@
         </is>
       </c>
       <c r="C46" s="21" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>62.78</v>
+        <v>66.17</v>
       </c>
       <c r="E46" s="21" t="n">
-        <v>1.78</v>
+        <v>4.78</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>4.84</v>
+        <v>5.25</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>35.1</v>
+        <v>33.9</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>-54.45</v>
+        <v>-16.6</v>
       </c>
       <c r="J46" s="21" t="n">
-        <v>4.55</v>
+        <v>-1.1</v>
       </c>
       <c r="K46" s="21" t="n">
-        <v>-4.07</v>
+        <v>-1.99</v>
       </c>
       <c r="L46" s="21" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>35 (C+)</t>
+          <t>34 (C+)</t>
         </is>
       </c>
       <c r="C47" s="21" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>66.17</v>
+        <v>62.78</v>
       </c>
       <c r="E47" s="21" t="n">
-        <v>4.78</v>
+        <v>1.78</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>5.25</v>
+        <v>4.84</v>
       </c>
       <c r="G47" s="21" t="n">
         <v>1.2</v>
       </c>
       <c r="H47" s="21" t="n">
-        <v>33.9</v>
+        <v>35.1</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>-16.6</v>
+        <v>-54.45</v>
       </c>
       <c r="J47" s="21" t="n">
-        <v>-1.1</v>
+        <v>4.55</v>
       </c>
       <c r="K47" s="21" t="n">
-        <v>-1.99</v>
+        <v>-4.07</v>
       </c>
       <c r="L47" s="21" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
@@ -6315,7 +6315,7 @@
         <v>7.17</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="H48" s="21" t="n">
         <v>32.9</v>
@@ -6357,7 +6357,7 @@
         <v>4.66</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H49" s="21" t="n">
         <v>33.7</v>
@@ -6399,7 +6399,7 @@
         <v>6.04</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H50" s="21" t="n">
         <v>32.7</v>
@@ -6441,7 +6441,7 @@
         <v>7.14</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="H51" s="21" t="n">
         <v>32.6</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>4.5</v>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>4.2</v>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>3.5</v>
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3.8</v>
@@ -6970,7 +6970,7 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>38.9</v>
+        <v>37.2</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>5.1</v>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>38.6</v>
+        <v>39.5</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>4.1</v>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>4.7</v>
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>4.4</v>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>3.6</v>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>3.5</v>
@@ -7426,7 +7426,7 @@
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="F25" s="11" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>3.7</v>
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="G27" s="11" t="n">
         <v>4.9</v>
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>5.2</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>3.6</v>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.5</v>
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>4</v>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>3.6</v>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>4.3</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>3.1</v>
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>2.2</v>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>2.7</v>
@@ -8535,11 +8535,11 @@
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="G3" s="28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" s="28" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="G7" s="28" t="n">
@@ -8705,11 +8705,11 @@
       </c>
       <c r="F8" s="28" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="G8" s="28" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8" s="28" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>67.5</v>
+        <v>69.5</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>68</v>
+        <v>65.8</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -689,20 +689,20 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>65.8</v>
+        <v>64.8</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -751,20 +751,20 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.5</v>
+        <v>64.2</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -782,20 +782,20 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Grand Rapids</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -844,20 +844,20 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Raleigh-Cary</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Raleigh</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>61</v>
+        <v>61.7</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>60.5</v>
+        <v>61.6</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -906,20 +906,20 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Raleigh-Cary</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Raleigh</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>59.7</v>
+        <v>59.3</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>55.7</v>
+        <v>57.9</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -999,20 +999,20 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>54.8</v>
+        <v>57.5</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1030,20 +1030,20 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>54.4</v>
+        <v>57.2</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>53.6</v>
+        <v>54.1</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -1185,16 +1185,16 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -1247,20 +1247,20 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>51.9</v>
+        <v>53</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1308,48 +1308,48 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="A24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth-Arlington</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -1402,20 +1402,20 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -1433,20 +1433,20 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>48.7</v>
+        <v>45.9</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -1464,20 +1464,20 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>46.7</v>
+        <v>46</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -1495,20 +1495,20 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -1526,20 +1526,20 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>45.3</v>
+        <v>46.1</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -1588,20 +1588,20 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>45.2</v>
+        <v>43.1</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -1619,16 +1619,16 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
@@ -1650,20 +1650,20 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -1712,16 +1712,16 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>40.6</v>
+        <v>41.3</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -1773,52 +1773,52 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco-Oakland-Fremont</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="n">
+      <c r="A39" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>39.8</v>
+        <v>38.8</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -1836,20 +1836,20 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="F41" s="11" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -1867,16 +1867,16 @@
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D42" s="13" t="n">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="F42" s="11" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -1898,20 +1898,20 @@
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>37.4</v>
+        <v>36.1</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -1929,16 +1929,16 @@
     </row>
     <row r="44">
       <c r="A44" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D44" s="13" t="n">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="F44" s="11" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -1960,16 +1960,16 @@
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D45" s="13" t="n">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F45" s="11" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="D46" s="13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="F46" s="11" t="n">
-        <v>34.9</v>
+        <v>34.1</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="F47" s="11" t="n">
-        <v>34.5</v>
+        <v>33.1</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2053,16 +2053,16 @@
     </row>
     <row r="48">
       <c r="A48" s="11" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="D48" s="13" t="n">
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="F48" s="11" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2084,20 +2084,20 @@
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="F49" s="11" t="n">
-        <v>31.7</v>
+        <v>30.5</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2115,20 +2115,20 @@
     </row>
     <row r="50">
       <c r="A50" s="14" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>27.6</v>
+        <v>26.3</v>
       </c>
       <c r="G50" s="15" t="inlineStr">
         <is>
@@ -2146,20 +2146,20 @@
     </row>
     <row r="51">
       <c r="A51" s="14" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>22.1</v>
+        <v>24.2</v>
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="18" t="n">
         <v>96</v>
@@ -2303,7 +2303,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="19" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J2" s="18" t="n">
         <v>76</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" s="18" t="n">
         <v>76</v>
@@ -2342,8 +2342,8 @@
       <c r="H3" s="18" t="n">
         <v>90</v>
       </c>
-      <c r="I3" s="18" t="n">
-        <v>86</v>
+      <c r="I3" s="20" t="n">
+        <v>64</v>
       </c>
       <c r="J3" s="20" t="n">
         <v>52</v>
@@ -2358,41 +2358,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>66</v>
-      </c>
-      <c r="C4" s="18" t="n">
-        <v>90</v>
+        <v>65</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>68</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="E4" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="H4" s="18" t="n">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>36</v>
       </c>
       <c r="I4" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="J4" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="K4" s="20" t="n">
-        <v>60</v>
+      <c r="J4" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>74</v>
       </c>
       <c r="L4" s="19" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -2417,13 +2417,13 @@
         <v>60</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>96</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J5" s="20" t="n">
         <v>66</v>
@@ -2438,241 +2438,241 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>63</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>68</v>
+        <v>64</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>90</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>37</v>
+        <v>98</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>92</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>80</v>
       </c>
       <c r="I6" s="19" t="n">
         <v>44</v>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>74</v>
+      <c r="J6" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>60</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>63</v>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>80</v>
+        <v>64</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>34</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>67</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="I7" s="19" t="n">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>86</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="L7" s="20" t="n">
-        <v>68</v>
+        <v>94</v>
+      </c>
+      <c r="L7" s="19" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B8" s="17" t="n">
         <v>63</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="D8" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="D8" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="F8" s="18" t="n">
+      <c r="E8" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="J8" s="18" t="n">
         <v>94</v>
       </c>
-      <c r="G8" s="18" t="n">
-        <v>71</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <v>65</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>90</v>
-      </c>
       <c r="K8" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="L8" s="19" t="n">
-        <v>26</v>
+        <v>88</v>
+      </c>
+      <c r="L8" s="18" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Raleigh-Cary</t>
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="D9" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>76</v>
+      <c r="E9" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>50</v>
       </c>
       <c r="G9" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="18" t="n">
         <v>82</v>
       </c>
-      <c r="H9" s="18" t="n">
-        <v>71</v>
-      </c>
-      <c r="I9" s="19" t="n">
+      <c r="J9" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="L9" s="19" t="n">
         <v>28</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="L9" s="19" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>56</v>
+        <v>48</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>74</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>44</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="L10" s="18" t="n">
-        <v>86</v>
+        <v>78</v>
+      </c>
+      <c r="L10" s="20" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raleigh-Cary</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B11" s="17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="D11" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="E11" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>50</v>
+      <c r="D11" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>76</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>48</v>
+        <v>82</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>56</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>68</v>
@@ -2737,13 +2737,13 @@
         <v>92</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H13" s="19" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J13" s="18" t="n">
         <v>84</v>
@@ -2758,81 +2758,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="D14" s="20" t="n">
         <v>58</v>
       </c>
+      <c r="C14" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>32</v>
+      </c>
       <c r="E14" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>88</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="K14" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="L14" s="18" t="n">
-        <v>70</v>
+        <v>92</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="L14" s="20" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>54</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="D15" s="18" t="n">
+        <v>57</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="J15" s="18" t="n">
         <v>74</v>
       </c>
-      <c r="E15" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>38</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="L15" s="19" t="n">
-        <v>44</v>
+      <c r="K15" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="L15" s="20" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" s="19" t="n">
         <v>6</v>
@@ -2862,8 +2862,8 @@
       <c r="H16" s="18" t="n">
         <v>76</v>
       </c>
-      <c r="I16" s="19" t="n">
-        <v>46</v>
+      <c r="I16" s="20" t="n">
+        <v>52</v>
       </c>
       <c r="J16" s="19" t="n">
         <v>16</v>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" s="20" t="n">
         <v>50</v>
@@ -2900,10 +2900,10 @@
         <v>80</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>80</v>
@@ -2918,41 +2918,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
         <v>54</v>
       </c>
       <c r="C18" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="E18" s="19" t="n">
+        <v>68</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="F18" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="L18" s="20" t="n">
-        <v>60</v>
+      <c r="L18" s="19" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -2977,7 +2977,7 @@
         <v>84</v>
       </c>
       <c r="G19" s="20" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H19" s="19" t="n">
         <v>12</v>
@@ -2998,207 +2998,207 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
         <v>54</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="E20" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="F20" s="20" t="n">
+        <v>94</v>
+      </c>
+      <c r="D20" s="20" t="n">
         <v>58</v>
       </c>
+      <c r="E20" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>2</v>
+      </c>
       <c r="G20" s="19" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>70</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="L20" s="20" t="n">
-        <v>62</v>
+        <v>98</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="L20" s="18" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
         <v>53</v>
       </c>
-      <c r="C21" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" s="20" t="n">
-        <v>68</v>
+      <c r="C21" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>42</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="H21" s="20" t="n">
-        <v>63</v>
+        <v>86</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>80</v>
       </c>
       <c r="I21" s="20" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="K21" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="L21" s="19" t="n">
-        <v>44</v>
+        <v>72</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>52</v>
-      </c>
-      <c r="C22" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D22" s="20" t="n">
+        <v>68</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G22" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="I22" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="J22" s="18" t="n">
         <v>86</v>
       </c>
-      <c r="H22" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>72</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="L22" s="20" t="n">
-        <v>54</v>
+      <c r="K22" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
         <v>52</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="E23" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="D23" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="E23" s="18" t="n">
+      <c r="F23" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="F23" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>27</v>
-      </c>
       <c r="I23" s="19" t="n">
-        <v>42</v>
-      </c>
-      <c r="J23" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K23" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="L23" s="18" t="n">
-        <v>88</v>
+      <c r="J23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="19" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="F24" s="20" t="n">
         <v>52</v>
       </c>
-      <c r="C24" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>72</v>
-      </c>
       <c r="G24" s="19" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I24" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="J24" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="21" t="n">
-        <v>0</v>
+      <c r="J24" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>34</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B25" s="17" t="n">
@@ -3208,31 +3208,31 @@
         <v>50</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="E25" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="G25" s="19" t="n">
-        <v>41</v>
-      </c>
-      <c r="H25" s="18" t="n">
         <v>92</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>26</v>
       </c>
       <c r="I25" s="19" t="n">
         <v>22</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="L25" s="19" t="n">
-        <v>36</v>
+        <v>12</v>
+      </c>
+      <c r="L25" s="18" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="26">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="18" t="n">
         <v>76</v>
@@ -3257,13 +3257,13 @@
         <v>50</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H26" s="20" t="n">
-        <v>67</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>72</v>
+        <v>68</v>
+      </c>
+      <c r="I26" s="20" t="n">
+        <v>66</v>
       </c>
       <c r="J26" s="19" t="n">
         <v>36</v>
@@ -3278,441 +3278,441 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B27" s="17" t="n">
-        <v>49</v>
-      </c>
-      <c r="C27" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="E27" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="F27" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="G27" s="18" t="n">
-        <v>76</v>
+        <v>48</v>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>36</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="I27" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K27" s="20" t="n">
-        <v>62</v>
+        <v>12</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>80</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>49</v>
-      </c>
-      <c r="C28" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="J28" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="D28" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="G28" s="19" t="n">
-        <v>35</v>
-      </c>
-      <c r="H28" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="L28" s="18" t="n">
-        <v>80</v>
+      <c r="K28" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="L28" s="20" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>47</v>
-      </c>
-      <c r="C29" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="E29" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>64</v>
+        <v>46</v>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>22</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="J29" s="20" t="n">
-        <v>50</v>
+        <v>88</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="L29" s="20" t="n">
-        <v>52</v>
+        <v>16</v>
+      </c>
+      <c r="L29" s="19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="C30" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="H30" s="20" t="n">
         <v>68</v>
       </c>
-      <c r="D30" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="F30" s="19" t="n">
+      <c r="I30" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J30" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="G30" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="H30" s="18" t="n">
+      <c r="K30" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" s="18" t="n">
         <v>88</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="L30" s="19" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B31" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="C31" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D31" s="19" t="n">
         <v>46</v>
       </c>
+      <c r="C31" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>86</v>
+      </c>
       <c r="E31" s="19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>61</v>
+        <v>18</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>76</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="J31" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="K31" s="18" t="n">
-        <v>72</v>
+        <v>28</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="K31" s="20" t="n">
+        <v>62</v>
       </c>
       <c r="L31" s="18" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B32" s="17" t="n">
         <v>45</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D32" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>82</v>
-      </c>
-      <c r="F32" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>74</v>
       </c>
       <c r="I32" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>14</v>
+        <v>98</v>
+      </c>
+      <c r="J32" s="20" t="n">
+        <v>54</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="L32" s="20" t="n">
-        <v>54</v>
+        <v>20</v>
+      </c>
+      <c r="L32" s="18" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B33" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="C33" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="D33" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="C33" s="20" t="n">
         <v>50</v>
       </c>
+      <c r="D33" s="19" t="n">
+        <v>46</v>
+      </c>
       <c r="E33" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="F33" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="19" t="n">
-        <v>31</v>
-      </c>
-      <c r="H33" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="I33" s="18" t="n">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>32</v>
       </c>
       <c r="J33" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="K33" s="19" t="n">
-        <v>20</v>
+        <v>68</v>
+      </c>
+      <c r="K33" s="18" t="n">
+        <v>72</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B34" s="17" t="n">
         <v>42</v>
       </c>
       <c r="C34" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="F34" s="19" t="n">
         <v>46</v>
       </c>
-      <c r="D34" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="F34" s="19" t="n">
-        <v>40</v>
-      </c>
       <c r="G34" s="19" t="n">
-        <v>37</v>
-      </c>
-      <c r="H34" s="20" t="n">
-        <v>67</v>
+        <v>44</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>4</v>
+        <v>44</v>
+      </c>
+      <c r="K34" s="18" t="n">
+        <v>76</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B35" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="C35" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D35" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="E35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="G35" s="18" t="n">
-        <v>94</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="I35" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="K35" s="19" t="n">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="J35" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="K35" s="20" t="n">
+        <v>52</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B36" s="17" t="n">
         <v>41</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="L36" s="19" t="n">
         <v>20</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="E36" s="19" t="n">
-        <v>42</v>
-      </c>
-      <c r="F36" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="G36" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="H36" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="I36" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="L36" s="18" t="n">
-        <v>80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C37" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>68</v>
+        <v>2</v>
+      </c>
+      <c r="D37" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>82</v>
       </c>
       <c r="F37" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="G37" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="H37" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="I37" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="G37" s="18" t="n">
-        <v>73</v>
-      </c>
-      <c r="H37" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="I37" s="18" t="n">
-        <v>92</v>
-      </c>
       <c r="J37" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="L37" s="20" t="n">
         <v>54</v>
-      </c>
-      <c r="L37" s="19" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -3740,10 +3740,10 @@
         <v>4</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J38" s="20" t="n">
         <v>64</v>
@@ -3758,281 +3758,281 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
         <v>40</v>
       </c>
       <c r="C39" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="H39" s="20" t="n">
-        <v>50</v>
+        <v>34</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>44</v>
       </c>
       <c r="I39" s="18" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" s="18" t="n">
-        <v>96</v>
+        <v>2</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="D40" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="F40" s="18" t="n">
+      <c r="D40" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="L40" s="18" t="n">
         <v>80</v>
-      </c>
-      <c r="G40" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="I40" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>42</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="19" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="D41" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="E41" s="19" t="n">
+      <c r="H41" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>94</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="K41" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="F41" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>36</v>
-      </c>
       <c r="L41" s="18" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
         <v>37</v>
       </c>
       <c r="C42" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="E42" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="F42" s="19" t="n">
-        <v>30</v>
+      <c r="F42" s="18" t="n">
+        <v>90</v>
       </c>
       <c r="G42" s="19" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H42" s="20" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I42" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="K42" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="L42" s="19" t="n">
         <v>40</v>
-      </c>
-      <c r="J42" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="K42" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="L42" s="19" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C43" s="19" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D43" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K43" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="L43" s="19" t="n">
         <v>22</v>
-      </c>
-      <c r="E43" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="G43" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="H43" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="I43" s="19" t="n">
-        <v>38</v>
-      </c>
-      <c r="J43" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="K43" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="L43" s="19" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
         <v>36</v>
       </c>
       <c r="C44" s="19" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D44" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="E44" s="19" t="n">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>68</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>65</v>
-      </c>
-      <c r="H44" s="19" t="n">
-        <v>39</v>
-      </c>
-      <c r="I44" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="J44" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="K44" s="19" t="n">
-        <v>22</v>
+        <v>42</v>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="H44" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="I44" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="20" t="n">
+        <v>54</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
         <v>35</v>
       </c>
       <c r="C45" s="19" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D45" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="F45" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="G45" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="H45" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H45" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="I45" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I45" s="20" t="n">
-        <v>56</v>
-      </c>
       <c r="J45" s="19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" s="19" t="n">
         <v>8</v>
@@ -4057,13 +4057,13 @@
         <v>34</v>
       </c>
       <c r="G46" s="19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I46" s="19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J46" s="19" t="n">
         <v>12</v>
@@ -4078,201 +4078,201 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C47" s="19" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D47" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="E47" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>56</v>
+        <v>38</v>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="G47" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="H47" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="I47" s="21" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" s="18" t="n">
+        <v>80</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="L47" s="19" t="n">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="L47" s="18" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
         <v>32</v>
       </c>
       <c r="C48" s="19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D48" s="19" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>76</v>
-      </c>
-      <c r="F48" s="19" t="n">
-        <v>12</v>
+        <v>70</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>66</v>
       </c>
       <c r="G48" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="I48" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="H48" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I48" s="20" t="n">
-        <v>68</v>
-      </c>
       <c r="J48" s="19" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="L48" s="18" t="n">
-        <v>74</v>
+        <v>14</v>
+      </c>
+      <c r="L48" s="19" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C49" s="19" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D49" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="F49" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="G49" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="G49" s="19" t="n">
-        <v>37</v>
-      </c>
       <c r="H49" s="19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I49" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J49" s="19" t="n">
-        <v>46</v>
+        <v>6</v>
+      </c>
+      <c r="J49" s="20" t="n">
+        <v>60</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C50" s="19" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D50" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="H50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="J50" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="K50" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="E50" s="19" t="n">
-        <v>38</v>
-      </c>
-      <c r="F50" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="G50" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="J50" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="K50" s="19" t="n">
-        <v>44</v>
-      </c>
       <c r="L50" s="18" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C51" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="D51" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="E51" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="F51" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="G51" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="H51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="19" t="n">
-        <v>12</v>
-      </c>
       <c r="J51" s="19" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>68 (B+)</t>
+          <t>70 (B+)</t>
         </is>
       </c>
       <c r="C2" s="21" t="n">
@@ -4389,13 +4389,13 @@
         <v>0.17</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>33.1</v>
       </c>
       <c r="I2" s="21" t="n">
-        <v>-21.04</v>
+        <v>-10.26</v>
       </c>
       <c r="J2" s="21" t="n">
         <v>16.78</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>68 (B+)</t>
+          <t>66 (B+)</t>
         </is>
       </c>
       <c r="C3" s="21" t="n">
@@ -4437,7 +4437,7 @@
         <v>35.4</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>41.99</v>
+        <v>14.73</v>
       </c>
       <c r="J3" s="21" t="n">
         <v>9.890000000000001</v>
@@ -4452,43 +4452,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>66 (B+)</t>
+          <t>65 (B+)</t>
         </is>
       </c>
       <c r="C4" s="21" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>76.27</v>
+        <v>67.91</v>
       </c>
       <c r="E4" s="21" t="n">
-        <v>1.62</v>
+        <v>6.8</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>5.71</v>
+        <v>4.64</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>3.92</v>
+        <v>1.2</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>34.9</v>
+        <v>33.6</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>6.15</v>
+        <v>5.41</v>
       </c>
       <c r="J4" s="21" t="n">
-        <v>10.88</v>
+        <v>17.56</v>
       </c>
       <c r="K4" s="21" t="n">
-        <v>-0.13</v>
+        <v>1.38</v>
       </c>
       <c r="L4" s="21" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -4515,13 +4515,13 @@
         <v>4.82</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="H5" s="21" t="n">
         <v>35.8</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>22.35</v>
+        <v>20.14</v>
       </c>
       <c r="J5" s="21" t="n">
         <v>12.7</v>
@@ -4536,91 +4536,91 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>63 (B+)</t>
+          <t>64 (B+)</t>
         </is>
       </c>
       <c r="C6" s="21" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>67.91</v>
+        <v>76.27</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>6.8</v>
+        <v>1.62</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>4.64</v>
+        <v>5.71</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>1.22</v>
+        <v>3.9</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>33.6</v>
+        <v>34.9</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>-5.01</v>
+        <v>-8.94</v>
       </c>
       <c r="J6" s="21" t="n">
-        <v>17.56</v>
+        <v>10.88</v>
       </c>
       <c r="K6" s="21" t="n">
-        <v>1.38</v>
+        <v>-0.13</v>
       </c>
       <c r="L6" s="21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>63 (B+)</t>
+          <t>64 (B+)</t>
         </is>
       </c>
       <c r="C7" s="21" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>64.23999999999999</v>
+        <v>63.89</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>5.12</v>
+        <v>3.13</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>4.87</v>
+        <v>0.63</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>-10.9</v>
+        <v>55.17</v>
       </c>
       <c r="J7" s="21" t="n">
-        <v>19.85</v>
+        <v>21.27</v>
       </c>
       <c r="K7" s="21" t="n">
-        <v>1.78</v>
+        <v>8.1</v>
       </c>
       <c r="L7" s="21" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
@@ -4629,160 +4629,160 @@
         </is>
       </c>
       <c r="C8" s="21" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>63.89</v>
+        <v>63.19</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>3.13</v>
+        <v>3.73</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>0.63</v>
+        <v>4.8</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>3.06</v>
+        <v>1.56</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>39.86</v>
+        <v>-10.47</v>
       </c>
       <c r="J8" s="21" t="n">
-        <v>21.27</v>
+        <v>23.89</v>
       </c>
       <c r="K8" s="21" t="n">
-        <v>8.1</v>
+        <v>4.37</v>
       </c>
       <c r="L8" s="21" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Raleigh-Cary</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>61 (B+)</t>
+          <t>62 (B+)</t>
         </is>
       </c>
       <c r="C9" s="21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>64.56999999999999</v>
+        <v>67.67</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>8.27</v>
+        <v>4.51</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>4.43</v>
+        <v>4.95</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>3.53</v>
+        <v>4.4</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>34.6</v>
+        <v>32.9</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>-17.49</v>
+        <v>38.82</v>
       </c>
       <c r="J9" s="21" t="n">
-        <v>0.16</v>
+        <v>10.4</v>
       </c>
       <c r="K9" s="21" t="n">
-        <v>-0.34</v>
+        <v>-0.91</v>
       </c>
       <c r="L9" s="21" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>61 (B+)</t>
+          <t>62 (B+)</t>
         </is>
       </c>
       <c r="C10" s="21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>63.19</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>3.73</v>
+        <v>5.12</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>4.8</v>
+        <v>4.87</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>1.53</v>
+        <v>3.02</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>-23.05</v>
+        <v>-20.27</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>23.89</v>
+        <v>19.85</v>
       </c>
       <c r="K10" s="21" t="n">
-        <v>4.37</v>
+        <v>1.78</v>
       </c>
       <c r="L10" s="21" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raleigh-Cary</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>60 (B)</t>
+          <t>59 (B)</t>
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>67.67</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>4.51</v>
+        <v>8.27</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>4.95</v>
+        <v>4.43</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>4.43</v>
+        <v>3.52</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>32.9</v>
+        <v>34.6</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>9.02</v>
+        <v>-30.9</v>
       </c>
       <c r="J11" s="21" t="n">
-        <v>10.4</v>
+        <v>0.16</v>
       </c>
       <c r="K11" s="21" t="n">
-        <v>-0.91</v>
+        <v>-0.34</v>
       </c>
       <c r="L11" s="21" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -4809,13 +4809,13 @@
         <v>3.13</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>35.5</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>43.07</v>
+        <v>55.25</v>
       </c>
       <c r="J12" s="21" t="n">
         <v>14.39</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>56 (B)</t>
+          <t>58 (B)</t>
         </is>
       </c>
       <c r="C13" s="21" t="n">
@@ -4851,13 +4851,13 @@
         <v>0.73</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>32.9</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>-18.7</v>
+        <v>-6.99</v>
       </c>
       <c r="J13" s="21" t="n">
         <v>18.78</v>
@@ -4872,85 +4872,85 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>55 (B)</t>
+          <t>58 (B)</t>
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>64.7</v>
+        <v>63.08</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>-0.36</v>
+        <v>1.53</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>7.56</v>
+        <v>1.09</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>16.13</v>
+        <v>57.47</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>28.29</v>
+        <v>21.54</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.52</v>
       </c>
       <c r="L14" s="21" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>57 (B)</t>
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>66.34</v>
+        <v>62.74</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>4.52</v>
+        <v>3.37</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>5.18</v>
+        <v>4.82</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>3.59</v>
+        <v>2.38</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>34.2</v>
+        <v>33.3</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>16.78</v>
+        <v>2.98</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>-1.53</v>
+        <v>15.66</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>-2.18</v>
+        <v>3.26</v>
       </c>
       <c r="L15" s="21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C16" s="21" t="n">
@@ -4977,13 +4977,13 @@
         <v>5.62</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>34.8</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>-1.35</v>
+        <v>-0.7</v>
       </c>
       <c r="J16" s="21" t="n">
         <v>-0.13</v>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C17" s="21" t="n">
@@ -5019,13 +5019,13 @@
         <v>4.18</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>33.9</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>-13.83</v>
+        <v>-10.55</v>
       </c>
       <c r="J17" s="21" t="n">
         <v>17.94</v>
@@ -5040,7 +5040,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
@@ -5049,34 +5049,34 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>63.08</v>
+        <v>66.34</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>1.53</v>
+        <v>4.52</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>1.09</v>
+        <v>5.18</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>33.5</v>
+        <v>34.2</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>-0.44</v>
+        <v>16.86</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>21.54</v>
+        <v>-1.53</v>
       </c>
       <c r="K18" s="21" t="n">
-        <v>2.52</v>
+        <v>-2.18</v>
       </c>
       <c r="L18" s="21" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5124,7 +5124,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
@@ -5133,40 +5133,40 @@
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>62.74</v>
+        <v>64.7</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>3.37</v>
+        <v>-0.36</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>4.82</v>
+        <v>7.56</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>33.3</v>
+        <v>33.9</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>-19.57</v>
+        <v>16.13</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>15.66</v>
+        <v>28.29</v>
       </c>
       <c r="K20" s="21" t="n">
-        <v>3.26</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L20" s="21" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B21" s="22" t="inlineStr">
@@ -5175,82 +5175,82 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>65.61</v>
+        <v>63.96</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.86</v>
+        <v>2.21</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>7.49</v>
+        <v>5.4</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>34.3</v>
+        <v>34.9</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>9.82</v>
+        <v>4.14</v>
       </c>
       <c r="J21" s="21" t="n">
-        <v>19.38</v>
+        <v>14.69</v>
       </c>
       <c r="K21" s="21" t="n">
-        <v>-0.82</v>
+        <v>0.44</v>
       </c>
       <c r="L21" s="21" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>63.96</v>
+        <v>65.61</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>2.21</v>
+        <v>0.86</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>5.4</v>
+        <v>7.49</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>3.57</v>
+        <v>3.76</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>-0.99</v>
+        <v>8.67</v>
       </c>
       <c r="J22" s="21" t="n">
-        <v>14.69</v>
+        <v>19.38</v>
       </c>
       <c r="K22" s="21" t="n">
-        <v>0.44</v>
+        <v>-0.82</v>
       </c>
       <c r="L22" s="21" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B23" s="22" t="inlineStr">
@@ -5259,82 +5259,82 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>70.39</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>6.57</v>
+        <v>3.18</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>2.71</v>
+        <v>2.44</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>33.4</v>
+        <v>34.9</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>-6.75</v>
+        <v>-29.44</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>-2.07</v>
+        <v>-5.6</v>
       </c>
       <c r="K23" s="21" t="n">
-        <v>-3.36</v>
+        <v>-6.22</v>
       </c>
       <c r="L23" s="21" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>73.98999999999999</v>
+        <v>69.61</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>4.63</v>
+        <v>4.88</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>34.9</v>
+        <v>35.5</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>-22.9</v>
+        <v>-20.96</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>-5.6</v>
+        <v>-1.52</v>
       </c>
       <c r="K24" s="21" t="n">
-        <v>-6.22</v>
+        <v>-1.8</v>
       </c>
       <c r="L24" s="21" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B25" s="22" t="inlineStr">
@@ -5346,31 +5346,31 @@
         <v>3.6</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>69.61</v>
+        <v>70.39</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>3.1</v>
+        <v>6.57</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>4.88</v>
+        <v>4.64</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>2.24</v>
+        <v>2.76</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>35.5</v>
+        <v>33.4</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>-20.74</v>
+        <v>-15.96</v>
       </c>
       <c r="J25" s="21" t="n">
-        <v>-1.52</v>
+        <v>-2.07</v>
       </c>
       <c r="K25" s="21" t="n">
-        <v>-1.8</v>
+        <v>-3.36</v>
       </c>
       <c r="L25" s="21" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>50 (B-)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C26" s="21" t="n">
@@ -5416,217 +5416,217 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C27" s="21" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>68.47</v>
+        <v>58.99</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>1.42</v>
+        <v>10.22</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>6.61</v>
+        <v>4.53</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>1.05</v>
+        <v>-46.79</v>
       </c>
       <c r="J27" s="21" t="n">
-        <v>0.96</v>
+        <v>18.41</v>
       </c>
       <c r="K27" s="21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="L27" s="21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>58.99</v>
+        <v>64.52</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>10.22</v>
+        <v>2.61</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>4.53</v>
+        <v>4.72</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>2.18</v>
+        <v>0.82</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>33.1</v>
+        <v>36.5</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>-42.41</v>
+        <v>-12.89</v>
       </c>
       <c r="J28" s="21" t="n">
-        <v>18.41</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="K28" s="21" t="n">
-        <v>2.02</v>
+        <v>-2.29</v>
       </c>
       <c r="L28" s="21" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>64.52</v>
+        <v>62.53</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>2.61</v>
+        <v>7.12</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>4.72</v>
+        <v>5.79</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>0.84</v>
+        <v>1.86</v>
       </c>
       <c r="H29" s="21" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>-10.61</v>
+        <v>41.11</v>
       </c>
       <c r="J29" s="21" t="n">
-        <v>8.710000000000001</v>
+        <v>-1.47</v>
       </c>
       <c r="K29" s="21" t="n">
-        <v>-2.29</v>
+        <v>-2.43</v>
       </c>
       <c r="L29" s="21" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C30" s="21" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>62.53</v>
+        <v>67.37</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>7.12</v>
+        <v>1.37</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>5.79</v>
+        <v>5.11</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>35.2</v>
+        <v>34.5</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>20.94</v>
+        <v>-3.97</v>
       </c>
       <c r="J30" s="21" t="n">
-        <v>-1.47</v>
+        <v>0.29</v>
       </c>
       <c r="K30" s="21" t="n">
-        <v>-2.43</v>
+        <v>-5.52</v>
       </c>
       <c r="L30" s="21" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>64.19</v>
+        <v>68.47</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>7.44</v>
+        <v>6.61</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>1.86</v>
+        <v>-14.97</v>
       </c>
       <c r="J31" s="21" t="n">
-        <v>14.35</v>
+        <v>0.96</v>
       </c>
       <c r="K31" s="21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="L31" s="21" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
@@ -5635,82 +5635,82 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>65.02</v>
+        <v>64.34</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>6.71</v>
+        <v>0.59</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>5.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>2.49</v>
+        <v>2.02</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>34.1</v>
+        <v>34.7</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>40.95</v>
+        <v>195.09</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>-0.88</v>
+        <v>9.98</v>
       </c>
       <c r="K32" s="21" t="n">
-        <v>-2.22</v>
+        <v>-2.36</v>
       </c>
       <c r="L32" s="21" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>43 (B-)</t>
         </is>
       </c>
       <c r="C33" s="21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>64.34</v>
+        <v>64.19</v>
       </c>
       <c r="E33" s="21" t="n">
-        <v>0.59</v>
+        <v>1.22</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>9.800000000000001</v>
+        <v>7.44</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="H33" s="21" t="n">
-        <v>34.7</v>
+        <v>33.2</v>
       </c>
       <c r="I33" s="21" t="n">
-        <v>157.99</v>
+        <v>-11.14</v>
       </c>
       <c r="J33" s="21" t="n">
-        <v>9.98</v>
+        <v>14.35</v>
       </c>
       <c r="K33" s="21" t="n">
-        <v>-2.36</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L33" s="21" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
@@ -5719,82 +5719,82 @@
         </is>
       </c>
       <c r="C34" s="21" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>67.37</v>
+        <v>64.75</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>1.37</v>
+        <v>2.84</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>34.5</v>
+        <v>33.1</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>-23.94</v>
+        <v>-27.41</v>
       </c>
       <c r="J34" s="21" t="n">
-        <v>0.29</v>
+        <v>5.37</v>
       </c>
       <c r="K34" s="21" t="n">
-        <v>-5.52</v>
+        <v>1.63</v>
       </c>
       <c r="L34" s="21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>42 (B-)</t>
+          <t>41 (B-)</t>
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>65.43000000000001</v>
+        <v>60.37</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>-1.52</v>
+        <v>7.54</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>1.25</v>
+        <v>5.55</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>4.16</v>
+        <v>1.3</v>
       </c>
       <c r="H35" s="21" t="n">
-        <v>33.5</v>
+        <v>34.2</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>-26.68</v>
+        <v>18.04</v>
       </c>
       <c r="J35" s="21" t="n">
-        <v>0.64</v>
+        <v>10.03</v>
       </c>
       <c r="K35" s="21" t="n">
-        <v>-1.51</v>
+        <v>-0.59</v>
       </c>
       <c r="L35" s="21" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
@@ -5803,40 +5803,40 @@
         </is>
       </c>
       <c r="C36" s="21" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>64.75</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>2.84</v>
+        <v>-1.52</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>5.07</v>
+        <v>1.25</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>2.29</v>
+        <v>4.14</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>-27.01</v>
+        <v>-39.5</v>
       </c>
       <c r="J36" s="21" t="n">
-        <v>5.37</v>
+        <v>0.64</v>
       </c>
       <c r="K36" s="21" t="n">
-        <v>1.63</v>
+        <v>-1.51</v>
       </c>
       <c r="L36" s="21" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
@@ -5845,34 +5845,34 @@
         </is>
       </c>
       <c r="C37" s="21" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>59.95</v>
+        <v>65.02</v>
       </c>
       <c r="E37" s="21" t="n">
-        <v>4.86</v>
+        <v>6.71</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>5.1</v>
+        <v>5.08</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="H37" s="21" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>66.26000000000001</v>
+        <v>-9.83</v>
       </c>
       <c r="J37" s="21" t="n">
-        <v>-2.83</v>
+        <v>-0.88</v>
       </c>
       <c r="K37" s="21" t="n">
-        <v>-0.41</v>
+        <v>-2.22</v>
       </c>
       <c r="L37" s="21" t="n">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -5899,7 +5899,7 @@
         <v>5.05</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="H38" s="21" t="n">
         <v>33.5</v>
@@ -5920,129 +5920,133 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>40 (B-)</t>
         </is>
       </c>
       <c r="C39" s="21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>64.45</v>
+        <v>60.48</v>
       </c>
       <c r="E39" s="21" t="n">
-        <v>0.49</v>
+        <v>6.16</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
+        <v>4.12</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H39" s="21" t="n">
+        <v>33.9</v>
+      </c>
       <c r="I39" s="21" t="n">
-        <v>142.07</v>
+        <v>19.69</v>
       </c>
       <c r="J39" s="21" t="n">
-        <v>-0.06</v>
+        <v>5.23</v>
       </c>
       <c r="K39" s="21" t="n">
-        <v>-3.63</v>
+        <v>-5.54</v>
       </c>
       <c r="L39" s="21" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C40" s="21" t="n">
         <v>4</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>60.48</v>
+        <v>69.03</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>6.16</v>
+        <v>0.03</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>4.12</v>
+        <v>7.29</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>0.61</v>
+        <v>2.56</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>14.06</v>
+        <v>-12.25</v>
       </c>
       <c r="J40" s="21" t="n">
-        <v>5.23</v>
+        <v>2.74</v>
       </c>
       <c r="K40" s="21" t="n">
-        <v>-5.54</v>
+        <v>-1.56</v>
       </c>
       <c r="L40" s="21" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>38 (C+)</t>
+          <t>37 (C+)</t>
         </is>
       </c>
       <c r="C41" s="21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>69.03</v>
+        <v>64.45</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>0.03</v>
+        <v>0.49</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>7.29</v>
+        <v>7.18</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="H41" s="21" t="n">
-        <v>33.3</v>
+        <v>33.6</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>-22.23</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="J41" s="21" t="n">
-        <v>2.74</v>
+        <v>-0.06</v>
       </c>
       <c r="K41" s="21" t="n">
-        <v>-1.56</v>
+        <v>-3.63</v>
       </c>
       <c r="L41" s="21" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
@@ -6051,82 +6055,82 @@
         </is>
       </c>
       <c r="C42" s="21" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>60.37</v>
+        <v>61.27</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>7.54</v>
+        <v>-1.13</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>5.55</v>
+        <v>1.05</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>1.27</v>
+        <v>1.96</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>-8.31</v>
+        <v>-10.94</v>
       </c>
       <c r="J42" s="21" t="n">
-        <v>10.03</v>
+        <v>3.8</v>
       </c>
       <c r="K42" s="21" t="n">
-        <v>-0.59</v>
+        <v>0.2</v>
       </c>
       <c r="L42" s="21" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>37 (C+)</t>
+          <t>36 (C+)</t>
         </is>
       </c>
       <c r="C43" s="21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>61.27</v>
+        <v>63.3</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>-1.13</v>
+        <v>4.84</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>1.05</v>
+        <v>6.87</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>1.94</v>
+        <v>2.98</v>
       </c>
       <c r="H43" s="21" t="n">
-        <v>34</v>
+        <v>32.9</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>-8.4</v>
+        <v>14.97</v>
       </c>
       <c r="J43" s="21" t="n">
-        <v>3.8</v>
+        <v>5.14</v>
       </c>
       <c r="K43" s="21" t="n">
-        <v>0.2</v>
+        <v>-1.43</v>
       </c>
       <c r="L43" s="21" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
@@ -6135,40 +6139,40 @@
         </is>
       </c>
       <c r="C44" s="21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>63.98</v>
+        <v>59.95</v>
       </c>
       <c r="E44" s="21" t="n">
-        <v>0.37</v>
+        <v>4.86</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>33.7</v>
+        <v>34.8</v>
       </c>
       <c r="I44" s="21" t="n">
-        <v>9.83</v>
+        <v>-8.56</v>
       </c>
       <c r="J44" s="21" t="n">
-        <v>10.79</v>
+        <v>-2.83</v>
       </c>
       <c r="K44" s="21" t="n">
-        <v>-2.31</v>
+        <v>-0.41</v>
       </c>
       <c r="L44" s="21" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B45" s="22" t="inlineStr">
@@ -6177,34 +6181,34 @@
         </is>
       </c>
       <c r="C45" s="21" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D45" s="21" t="n">
-        <v>63.3</v>
+        <v>62.78</v>
       </c>
       <c r="E45" s="21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F45" s="21" t="n">
         <v>4.84</v>
       </c>
-      <c r="F45" s="21" t="n">
-        <v>6.87</v>
-      </c>
       <c r="G45" s="21" t="n">
-        <v>2.98</v>
+        <v>1.24</v>
       </c>
       <c r="H45" s="21" t="n">
-        <v>32.9</v>
+        <v>35.1</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>4.77</v>
+        <v>-37.55</v>
       </c>
       <c r="J45" s="21" t="n">
-        <v>5.14</v>
+        <v>4.55</v>
       </c>
       <c r="K45" s="21" t="n">
-        <v>-1.43</v>
+        <v>-4.07</v>
       </c>
       <c r="L45" s="21" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46">
@@ -6215,7 +6219,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>35 (C+)</t>
+          <t>34 (C+)</t>
         </is>
       </c>
       <c r="C46" s="21" t="n">
@@ -6231,13 +6235,13 @@
         <v>5.25</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="H46" s="21" t="n">
         <v>33.9</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>-16.6</v>
+        <v>-18.14</v>
       </c>
       <c r="J46" s="21" t="n">
         <v>-1.1</v>
@@ -6252,49 +6256,49 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>34 (C+)</t>
+          <t>33 (C+)</t>
         </is>
       </c>
       <c r="C47" s="21" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>62.78</v>
+        <v>63.61</v>
       </c>
       <c r="E47" s="21" t="n">
-        <v>1.78</v>
+        <v>5.33</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>4.84</v>
+        <v>7.17</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="H47" s="21" t="n">
-        <v>35.1</v>
+        <v>32.9</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>-54.45</v>
+        <v>20.24</v>
       </c>
       <c r="J47" s="21" t="n">
-        <v>4.55</v>
+        <v>0.86</v>
       </c>
       <c r="K47" s="21" t="n">
-        <v>-4.07</v>
+        <v>-2.37</v>
       </c>
       <c r="L47" s="21" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
@@ -6303,160 +6307,160 @@
         </is>
       </c>
       <c r="C48" s="21" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>63.61</v>
+        <v>60.38</v>
       </c>
       <c r="E48" s="21" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>7.17</v>
+        <v>4.66</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>0.98</v>
+        <v>2.24</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>32.9</v>
+        <v>33.7</v>
       </c>
       <c r="I48" s="21" t="n">
-        <v>10.45</v>
+        <v>-32.7</v>
       </c>
       <c r="J48" s="21" t="n">
-        <v>0.86</v>
+        <v>7.27</v>
       </c>
       <c r="K48" s="21" t="n">
-        <v>-2.37</v>
+        <v>-2.58</v>
       </c>
       <c r="L48" s="21" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>32 (C+)</t>
+          <t>30 (C+)</t>
         </is>
       </c>
       <c r="C49" s="21" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>60.38</v>
+        <v>63.98</v>
       </c>
       <c r="E49" s="21" t="n">
-        <v>5</v>
+        <v>0.37</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>4.66</v>
+        <v>5.6</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="H49" s="21" t="n">
         <v>33.7</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>-25.81</v>
+        <v>-35.64</v>
       </c>
       <c r="J49" s="21" t="n">
-        <v>7.27</v>
+        <v>10.79</v>
       </c>
       <c r="K49" s="21" t="n">
-        <v>-2.58</v>
+        <v>-2.31</v>
       </c>
       <c r="L49" s="21" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>28 (C)</t>
+          <t>26 (C)</t>
         </is>
       </c>
       <c r="C50" s="21" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="D50" s="21" t="n">
-        <v>60.12</v>
+        <v>62.01</v>
       </c>
       <c r="E50" s="21" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>6.04</v>
+        <v>7.14</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>0.12</v>
+        <v>1.34</v>
       </c>
       <c r="H50" s="21" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="I50" s="21" t="n">
-        <v>5.58</v>
+        <v>-0.37</v>
       </c>
       <c r="J50" s="21" t="n">
-        <v>8.43</v>
+        <v>0.78</v>
       </c>
       <c r="K50" s="21" t="n">
-        <v>-1.07</v>
+        <v>-3.69</v>
       </c>
       <c r="L50" s="21" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>22 (C)</t>
+          <t>24 (C)</t>
         </is>
       </c>
       <c r="C51" s="21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="D51" s="21" t="n">
-        <v>62.01</v>
+        <v>60.12</v>
       </c>
       <c r="E51" s="21" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>7.14</v>
+        <v>6.04</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>1.37</v>
+        <v>0.12</v>
       </c>
       <c r="H51" s="21" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="I51" s="21" t="n">
-        <v>-23.13</v>
+        <v>-15.51</v>
       </c>
       <c r="J51" s="21" t="n">
-        <v>0.78</v>
+        <v>8.43</v>
       </c>
       <c r="K51" s="21" t="n">
-        <v>-3.69</v>
+        <v>-1.07</v>
       </c>
       <c r="L51" s="21" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -6552,7 +6556,7 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
@@ -6560,7 +6564,7 @@
         </is>
       </c>
       <c r="F2" s="11" t="n">
-        <v>34.9</v>
+        <v>36.1</v>
       </c>
       <c r="G2" s="11" t="n">
         <v>4.5</v>
@@ -6590,7 +6594,7 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
@@ -6598,7 +6602,7 @@
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>31.9</v>
+        <v>33.1</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>4.8</v>
@@ -6628,7 +6632,7 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
@@ -6636,7 +6640,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>40.6</v>
+        <v>41.6</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>4.5</v>
@@ -6652,40 +6656,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G5" s="8" t="n">
         <v>3.6</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="8" t="n">
         <v>69.61</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="8" t="n">
         <v>3.1</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="8" t="n">
         <v>4.88</v>
       </c>
     </row>
@@ -6704,7 +6708,7 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
@@ -6712,7 +6716,7 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46.7</v>
+        <v>45.9</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>4.2</v>
@@ -6742,7 +6746,7 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
@@ -6750,7 +6754,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>45.4</v>
+        <v>46</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>3.5</v>
@@ -6780,7 +6784,7 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -6788,7 +6792,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>41.6</v>
+        <v>45.7</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3.8</v>
@@ -6804,40 +6808,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="G9" s="2" t="n">
+      <c r="D9" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="5" t="n">
         <v>64.56999999999999</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="5" t="n">
         <v>8.27</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="5" t="n">
         <v>4.43</v>
       </c>
     </row>
@@ -6856,7 +6860,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -6864,7 +6868,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>51.9</v>
+        <v>53</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>4</v>
@@ -6902,7 +6906,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>54.4</v>
+        <v>54.1</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>3.5</v>
@@ -6932,7 +6936,7 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -6940,7 +6944,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>48.7</v>
+        <v>46.1</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>3.9</v>
@@ -6956,40 +6960,40 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="G13" s="11" t="n">
+      <c r="D13" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="G13" s="8" t="n">
         <v>5.1</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="8" t="n">
         <v>60.37</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="I13" s="8" t="n">
         <v>7.54</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J13" s="8" t="n">
         <v>5.55</v>
       </c>
     </row>
@@ -7008,7 +7012,7 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -7016,7 +7020,7 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>39.5</v>
+        <v>37.3</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>4.1</v>
@@ -7054,7 +7058,7 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>4.7</v>
@@ -7084,7 +7088,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
@@ -7092,7 +7096,7 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>5</v>
@@ -7122,7 +7126,7 @@
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -7130,7 +7134,7 @@
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>37.6</v>
+        <v>38.8</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>4</v>
@@ -7146,40 +7150,40 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="G18" s="8" t="n">
+      <c r="D18" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="G18" s="11" t="n">
         <v>4.6</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="11" t="n">
         <v>59.95</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="11" t="n">
         <v>4.86</v>
       </c>
-      <c r="J18" s="8" t="n">
+      <c r="J18" s="11" t="n">
         <v>5.1</v>
       </c>
     </row>
@@ -7198,7 +7202,7 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
@@ -7206,7 +7210,7 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>22.1</v>
+        <v>26.3</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>4.4</v>
@@ -7236,7 +7240,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
@@ -7244,7 +7248,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>3.6</v>
@@ -7274,7 +7278,7 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -7282,7 +7286,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>36.3</v>
+        <v>30.5</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>4.4</v>
@@ -7312,7 +7316,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
@@ -7320,7 +7324,7 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>41.6</v>
+        <v>41.1</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>3.6</v>
@@ -7350,7 +7354,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
@@ -7358,7 +7362,7 @@
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>45.3</v>
+        <v>43.1</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>3.6</v>
@@ -7388,7 +7392,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
@@ -7396,7 +7400,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>55.7</v>
+        <v>57.9</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>3.5</v>
@@ -7426,7 +7430,7 @@
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -7434,7 +7438,7 @@
         </is>
       </c>
       <c r="F25" s="11" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>3.7</v>
@@ -7472,7 +7476,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>3.2</v>
@@ -7502,7 +7506,7 @@
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -7510,7 +7514,7 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>34.9</v>
+        <v>34.1</v>
       </c>
       <c r="G27" s="11" t="n">
         <v>4.9</v>
@@ -7540,7 +7544,7 @@
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -7548,7 +7552,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>27.6</v>
+        <v>24.2</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>4.8</v>
@@ -7578,7 +7582,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
@@ -7586,7 +7590,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>3.6</v>
@@ -7616,7 +7620,7 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
@@ -7624,7 +7628,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>45.4</v>
+        <v>41.3</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>5.2</v>
@@ -7654,7 +7658,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
@@ -7662,7 +7666,7 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>53.6</v>
+        <v>57.5</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>3.6</v>
@@ -7692,7 +7696,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -7700,7 +7704,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>63.5</v>
+        <v>64.8</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.5</v>
@@ -7738,7 +7742,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>3.6</v>
@@ -7768,7 +7772,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -7776,7 +7780,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>67.5</v>
+        <v>69.5</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>2.5</v>
@@ -7806,7 +7810,7 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
@@ -7814,7 +7818,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>3.4</v>
@@ -7842,7 +7846,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -7850,7 +7854,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>65.8</v>
+        <v>64.2</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>3</v>
@@ -7888,7 +7892,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>4</v>
@@ -7918,7 +7922,7 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
@@ -7926,7 +7930,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>3.6</v>
@@ -7964,7 +7968,7 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>4.6</v>
@@ -8032,7 +8036,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -8040,7 +8044,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>60.5</v>
+        <v>63</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>3.1</v>
@@ -8056,40 +8060,40 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Raleigh-Cary</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Raleigh</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G42" s="5" t="n">
+      <c r="D42" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="2" t="n">
         <v>67.67</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="I42" s="2" t="n">
         <v>4.51</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="J42" s="2" t="n">
         <v>4.95</v>
       </c>
     </row>
@@ -8116,7 +8120,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>3.6</v>
@@ -8146,7 +8150,7 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
@@ -8154,7 +8158,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>54</v>
+        <v>57.2</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>3.1</v>
@@ -8184,7 +8188,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -8192,7 +8196,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>63.1</v>
+        <v>61.6</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>3.3</v>
@@ -8208,40 +8212,40 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n">
+      <c r="A46" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="G46" s="11" t="n">
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G46" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H46" s="11" t="n">
+      <c r="H46" s="8" t="n">
         <v>60.48</v>
       </c>
-      <c r="I46" s="11" t="n">
+      <c r="I46" s="8" t="n">
         <v>6.16</v>
       </c>
-      <c r="J46" s="11" t="n">
+      <c r="J46" s="8" t="n">
         <v>4.12</v>
       </c>
     </row>
@@ -8260,7 +8264,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -8268,7 +8272,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>68</v>
+        <v>65.8</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.4</v>
@@ -8344,7 +8348,7 @@
         </is>
       </c>
       <c r="F49" s="8" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>8.199999999999999</v>
@@ -8374,7 +8378,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -8382,7 +8386,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>4</v>
@@ -8412,7 +8416,7 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
@@ -8420,7 +8424,7 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>54.8</v>
+        <v>54.5</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>2.7</v>
@@ -8523,7 +8527,7 @@
         </is>
       </c>
       <c r="C3" s="27" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
@@ -8535,7 +8539,7 @@
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="G3" s="28" t="n">
@@ -8557,7 +8561,7 @@
         </is>
       </c>
       <c r="C4" s="27" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
@@ -8569,11 +8573,11 @@
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="G4" s="28" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H4" s="28" t="inlineStr">
         <is>
@@ -8587,11 +8591,11 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C5" s="27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
@@ -8603,7 +8607,7 @@
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="G5" s="28" t="n">
@@ -8637,7 +8641,7 @@
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="G6" s="28" t="n">
@@ -8655,11 +8659,11 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
@@ -8675,7 +8679,7 @@
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
@@ -8689,11 +8693,11 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C8" s="27" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
@@ -8705,11 +8709,11 @@
       </c>
       <c r="F8" s="28" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="G8" s="28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H8" s="28" t="inlineStr">
         <is>
@@ -8723,7 +8727,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C9" s="27" t="n">
@@ -8739,7 +8743,7 @@
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="G9" s="28" t="n">
@@ -8757,11 +8761,11 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Raleigh-Cary</t>
         </is>
       </c>
       <c r="C10" s="27" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
@@ -8773,11 +8777,11 @@
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="G10" s="28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H10" s="28" t="inlineStr">
         <is>
@@ -8791,11 +8795,11 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
@@ -8807,11 +8811,11 @@
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H11" s="28" t="inlineStr">
         <is>
@@ -8825,11 +8829,11 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>Raleigh-Cary</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C12" s="27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
@@ -8841,11 +8845,11 @@
       </c>
       <c r="F12" s="28" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="G12" s="28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H12" s="28" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>70.8</v>
+        <v>71.2</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -814,33 +814,33 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="D7" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>63.2</v>
+        <v>63.8</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>61.9</v>
+        <v>62.7</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>59.7</v>
+        <v>59.9</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>56.8</v>
+        <v>55.8</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1001,16 +1001,16 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1031,48 +1031,48 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A14" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth-Arlington</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D15" s="13" t="n">
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1094,20 +1094,20 @@
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>53.3</v>
+        <v>54</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1125,20 +1125,20 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>52.6</v>
+        <v>54.5</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1156,20 +1156,20 @@
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="F18" s="11" t="n">
-        <v>52.4</v>
+        <v>53.7</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1187,16 +1187,16 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1231,96 +1231,96 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="F21" s="11" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Seattle-Tacoma-Bellevue</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="F22" s="14" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Philadelphia-Camden-Wilmington</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
@@ -1342,16 +1342,16 @@
     </row>
     <row r="24">
       <c r="A24" s="14" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -1373,20 +1373,20 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>47.3</v>
+        <v>48</v>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
@@ -1404,20 +1404,20 @@
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>46.6</v>
+        <v>47.6</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1435,16 +1435,16 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1466,16 +1466,16 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Grand Rapids</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1497,20 +1497,20 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>45.8</v>
+        <v>47</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1528,16 +1528,16 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1559,20 +1559,20 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>44.1</v>
+        <v>44.8</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1590,20 +1590,20 @@
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>44</v>
+        <v>44.9</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -1621,16 +1621,16 @@
     </row>
     <row r="33">
       <c r="A33" s="17" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D33" s="19" t="n">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
@@ -1652,20 +1652,20 @@
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F34" s="17" t="n">
-        <v>42.8</v>
+        <v>43.7</v>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
@@ -1745,20 +1745,20 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>43.3</v>
+        <v>42.1</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1776,20 +1776,20 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>41.7</v>
+        <v>40.8</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1807,20 +1807,20 @@
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>41.9</v>
+        <v>41</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
@@ -1838,20 +1838,20 @@
     </row>
     <row r="40">
       <c r="A40" s="17" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="F40" s="17" t="n">
-        <v>39.8</v>
+        <v>40.9</v>
       </c>
       <c r="G40" s="18" t="inlineStr">
         <is>
@@ -1869,16 +1869,16 @@
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D41" s="19" t="n">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>40.2</v>
+        <v>40.5</v>
       </c>
       <c r="G41" s="18" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="D42" s="19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F42" s="17" t="n">
-        <v>38.6</v>
+        <v>39.6</v>
       </c>
       <c r="G42" s="18" t="inlineStr">
         <is>
@@ -1930,95 +1930,95 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="n">
+      <c r="A43" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
-      <c r="D43" s="19" t="n">
-        <v>38</v>
-      </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>38</v>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="D43" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>Virginia Beach</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D44" s="22" t="n">
-        <v>38</v>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
+      <c r="D45" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F44" s="20" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G44" s="21" t="inlineStr">
+      <c r="F45" s="20" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
         <is>
           <t>Very Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="n">
-        <v>37</v>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>Virginia Beach</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="n">
-        <v>38</v>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="G45" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="D46" s="22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="D47" s="22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" s="21" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D48" s="22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>35.2</v>
+        <v>34.2</v>
       </c>
       <c r="G48" s="21" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="D50" s="25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="F50" s="23" t="n">
-        <v>24.2</v>
+        <v>25.2</v>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D51" s="25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="F51" s="23" t="n">
-        <v>23.4</v>
+        <v>21.6</v>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="27" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G2" s="27" t="n">
         <v>96</v>
@@ -2357,7 +2357,7 @@
         <v>48</v>
       </c>
       <c r="F3" s="28" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G3" s="27" t="n">
         <v>98</v>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="B4" s="26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="27" t="n">
         <v>84</v>
@@ -2394,7 +2394,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G4" s="28" t="n">
         <v>50</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B5" s="26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>90</v>
@@ -2431,7 +2431,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G5" s="27" t="n">
         <v>92</v>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>50</v>
@@ -2505,7 +2505,7 @@
         <v>62</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G7" s="28" t="n">
         <v>56</v>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="B8" s="26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>94</v>
@@ -2542,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G8" s="29" t="n">
         <v>32</v>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>96</v>
@@ -2579,7 +2579,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G9" s="27" t="n">
         <v>84</v>
@@ -2615,8 +2615,8 @@
       <c r="E10" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="F10" s="29" t="n">
-        <v>48</v>
+      <c r="F10" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>90</v>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="B12" s="26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="28" t="n">
         <v>50</v>
@@ -2690,7 +2690,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G12" s="28" t="n">
         <v>58</v>
@@ -2711,7 +2711,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B13" s="26" t="n">
@@ -2720,251 +2720,251 @@
       <c r="C13" s="28" t="n">
         <v>68</v>
       </c>
-      <c r="D13" s="29" t="n">
-        <v>26</v>
+      <c r="D13" s="27" t="n">
+        <v>82</v>
       </c>
       <c r="E13" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>54</v>
+        <v>84</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>80</v>
       </c>
       <c r="G13" s="29" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H13" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="J13" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="K13" s="28" t="n">
-        <v>62</v>
+        <v>14</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B14" s="26" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" s="28" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="E14" s="27" t="n">
-        <v>84</v>
+        <v>90</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>44</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H14" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="K14" s="29" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B15" s="26" t="n">
         <v>54</v>
       </c>
-      <c r="C15" s="27" t="n">
-        <v>80</v>
+      <c r="C15" s="28" t="n">
+        <v>68</v>
       </c>
       <c r="D15" s="29" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="E15" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="F15" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>68</v>
+        <v>86</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>24</v>
       </c>
       <c r="H15" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>20</v>
+        <v>44</v>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B16" s="26" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="D16" s="27" t="n">
-        <v>90</v>
-      </c>
-      <c r="E16" s="29" t="n">
-        <v>44</v>
+      <c r="D16" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>96</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="G16" s="29" t="n">
-        <v>42</v>
+        <v>72</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>80</v>
       </c>
       <c r="H16" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I16" s="29" t="n">
-        <v>48</v>
+      <c r="I16" s="27" t="n">
+        <v>82</v>
       </c>
       <c r="J16" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="K16" s="29" t="n">
         <v>16</v>
-      </c>
-      <c r="K16" s="29" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B17" s="26" t="n">
-        <v>53</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="D17" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>76</v>
+        <v>54</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>74</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>68</v>
       </c>
       <c r="H17" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I17" s="27" t="n">
-        <v>72</v>
+      <c r="I17" s="29" t="n">
+        <v>46</v>
       </c>
       <c r="J17" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>98</v>
+        <v>18</v>
+      </c>
+      <c r="K17" s="29" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B18" s="26" t="n">
-        <v>52</v>
-      </c>
-      <c r="C18" s="28" t="n">
-        <v>50</v>
+        <v>54</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <v>98</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>80</v>
+        <v>20</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="H18" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I18" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>36</v>
+      <c r="I18" s="28" t="n">
+        <v>68</v>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>88</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B19" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="C19" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>20</v>
+      <c r="C19" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="D19" s="27" t="n">
+        <v>86</v>
       </c>
       <c r="E19" s="29" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F19" s="29" t="n">
-        <v>24</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>76</v>
       </c>
       <c r="H19" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I19" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="J19" s="27" t="n">
-        <v>88</v>
-      </c>
-      <c r="K19" s="29" t="n">
+      <c r="I19" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="J19" s="29" t="n">
         <v>26</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="20">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="B20" s="26" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>50</v>
@@ -2986,7 +2986,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>94</v>
@@ -3007,266 +3007,266 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B21" s="26" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D21" s="29" t="n">
-        <v>38</v>
-      </c>
-      <c r="E21" s="27" t="n">
-        <v>76</v>
+        <v>42</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>34</v>
       </c>
       <c r="F21" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="G21" s="29" t="n">
-        <v>8</v>
+        <v>44</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>86</v>
       </c>
       <c r="H21" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I21" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="J21" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="K21" s="27" t="n">
-        <v>80</v>
+        <v>86</v>
+      </c>
+      <c r="J21" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="K21" s="29" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B22" s="26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="D22" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="E22" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="F22" s="29" t="n">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="D22" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="E22" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>54</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H22" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I22" s="27" t="n">
-        <v>86</v>
+      <c r="I22" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="J22" s="28" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K22" s="29" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B23" s="26" t="n">
         <v>48</v>
       </c>
       <c r="C23" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="D23" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="E23" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="F23" s="28" t="n">
-        <v>58</v>
+      <c r="E23" s="28" t="n">
+        <v>68</v>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H23" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I23" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="J23" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="K23" s="29" t="n">
-        <v>40</v>
+      <c r="I23" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="J23" s="29" t="n">
+        <v>46</v>
+      </c>
+      <c r="K23" s="27" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B24" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="C24" s="29" t="n">
-        <v>34</v>
+      <c r="C24" s="27" t="n">
+        <v>86</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="E24" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>98</v>
+        <v>28</v>
+      </c>
+      <c r="E24" s="28" t="n">
+        <v>52</v>
+      </c>
+      <c r="F24" s="29" t="n">
+        <v>36</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="H24" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="J24" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="K24" s="28" t="n">
-        <v>68</v>
+        <v>24</v>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="K24" s="29" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B25" s="26" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D25" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="F25" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>74</v>
+        <v>18</v>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>98</v>
+      </c>
+      <c r="G25" s="29" t="n">
+        <v>2</v>
       </c>
       <c r="H25" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I25" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="J25" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="K25" s="27" t="n">
-        <v>92</v>
+      <c r="I25" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="J25" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="K25" s="28" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B26" s="26" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" s="29" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D26" s="29" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E26" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="G26" s="29" t="n">
-        <v>14</v>
+        <v>46</v>
+      </c>
+      <c r="F26" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>72</v>
       </c>
       <c r="H26" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I26" s="27" t="n">
+      <c r="I26" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="J26" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="K26" s="27" t="n">
         <v>84</v>
-      </c>
-      <c r="J26" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="K26" s="29" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B27" s="26" t="n">
         <v>47</v>
       </c>
-      <c r="C27" s="27" t="n">
-        <v>86</v>
+      <c r="C27" s="29" t="n">
+        <v>10</v>
       </c>
       <c r="D27" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="E27" s="28" t="n">
-        <v>52</v>
+        <v>38</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>76</v>
       </c>
       <c r="F27" s="29" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G27" s="29" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H27" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I27" s="29" t="n">
-        <v>24</v>
-      </c>
-      <c r="J27" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="K27" s="29" t="n">
-        <v>22</v>
+      <c r="I27" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="J27" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="K27" s="27" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B28" s="26" t="n">
@@ -3275,137 +3275,137 @@
       <c r="C28" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="D28" s="29" t="n">
-        <v>40</v>
+      <c r="D28" s="27" t="n">
+        <v>88</v>
       </c>
       <c r="E28" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>72</v>
+        <v>10</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>54</v>
       </c>
       <c r="H28" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="J28" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="K28" s="27" t="n">
-        <v>84</v>
+        <v>60</v>
+      </c>
+      <c r="J28" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="K28" s="29" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="D29" s="27" t="n">
-        <v>78</v>
+        <v>48</v>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>30</v>
       </c>
       <c r="E29" s="29" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="G29" s="29" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H29" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="K29" s="27" t="n">
-        <v>72</v>
+      <c r="I29" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="J29" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="29" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B30" s="26" t="n">
         <v>46</v>
       </c>
       <c r="C30" s="29" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E30" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="G30" s="28" t="n">
-        <v>54</v>
+        <v>24</v>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="G30" s="29" t="n">
+        <v>38</v>
       </c>
       <c r="H30" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I30" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="J30" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="K30" s="29" t="n">
-        <v>18</v>
+      <c r="I30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K30" s="27" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B31" s="26" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="D31" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="E31" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="F31" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="G31" s="28" t="n">
-        <v>64</v>
+        <v>30</v>
+      </c>
+      <c r="D31" s="28" t="n">
+        <v>54</v>
+      </c>
+      <c r="E31" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="G31" s="29" t="n">
+        <v>6</v>
       </c>
       <c r="H31" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I31" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="J31" s="28" t="n">
-        <v>68</v>
+        <v>52</v>
+      </c>
+      <c r="J31" s="29" t="n">
+        <v>28</v>
       </c>
       <c r="K31" s="29" t="n">
         <v>28</v>
@@ -3414,112 +3414,112 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B32" s="26" t="n">
-        <v>44</v>
-      </c>
-      <c r="C32" s="29" t="n">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="C32" s="28" t="n">
+        <v>68</v>
       </c>
       <c r="D32" s="28" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E32" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>86</v>
+        <v>18</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>18</v>
       </c>
       <c r="G32" s="29" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="H32" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I32" s="28" t="n">
-        <v>52</v>
+      <c r="I32" s="29" t="n">
+        <v>26</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K32" s="29" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B33" s="26" t="n">
         <v>44</v>
       </c>
-      <c r="C33" s="28" t="n">
+      <c r="C33" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="D33" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G33" s="28" t="n">
         <v>68</v>
-      </c>
-      <c r="D33" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="E33" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="F33" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G33" s="29" t="n">
-        <v>46</v>
       </c>
       <c r="H33" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I33" s="29" t="n">
-        <v>26</v>
-      </c>
-      <c r="J33" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="K33" s="29" t="n">
-        <v>42</v>
+      <c r="I33" s="28" t="n">
+        <v>62</v>
+      </c>
+      <c r="J33" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="K33" s="28" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C34" s="27" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D34" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="30" t="n">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="E34" s="28" t="n">
+        <v>56</v>
       </c>
       <c r="F34" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="28" t="n">
-        <v>68</v>
+        <v>26</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <v>22</v>
       </c>
       <c r="H34" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I34" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="J34" s="28" t="n">
-        <v>66</v>
+      <c r="I34" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" s="29" t="n">
+        <v>38</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
@@ -3541,7 +3541,7 @@
         <v>70</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G35" s="29" t="n">
         <v>40</v>
@@ -3599,186 +3599,186 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B37" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="C37" s="27" t="n">
-        <v>86</v>
+        <v>42</v>
+      </c>
+      <c r="C37" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="D37" s="29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E37" s="28" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F37" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="G37" s="29" t="n">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="H37" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I37" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" s="29" t="n">
-        <v>38</v>
-      </c>
-      <c r="K37" s="28" t="n">
+      <c r="I37" s="28" t="n">
         <v>54</v>
+      </c>
+      <c r="J37" s="28" t="n">
+        <v>68</v>
+      </c>
+      <c r="K37" s="29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="E38" s="29" t="n">
         <v>42</v>
       </c>
-      <c r="C38" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="E38" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>72</v>
-      </c>
-      <c r="G38" s="28" t="n">
-        <v>52</v>
+      <c r="F38" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="G38" s="29" t="n">
+        <v>44</v>
       </c>
       <c r="H38" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I38" s="29" t="n">
-        <v>6</v>
+      <c r="I38" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="K38" s="27" t="n">
-        <v>78</v>
+        <v>14</v>
+      </c>
+      <c r="K38" s="29" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B39" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D39" s="29" t="n">
+        <v>46</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="F39" s="29" t="n">
         <v>42</v>
       </c>
-      <c r="C39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="E39" s="27" t="n">
-        <v>90</v>
-      </c>
-      <c r="F39" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="G39" s="29" t="n">
-        <v>4</v>
+      <c r="G39" s="28" t="n">
+        <v>62</v>
       </c>
       <c r="H39" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="J39" s="27" t="n">
-        <v>92</v>
+        <v>22</v>
+      </c>
+      <c r="J39" s="29" t="n">
+        <v>32</v>
       </c>
       <c r="K39" s="28" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B40" s="26" t="n">
-        <v>40</v>
-      </c>
-      <c r="C40" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="D40" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="E40" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="F40" s="29" t="n">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="E40" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="G40" s="29" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H40" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I40" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="J40" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="K40" s="29" t="n">
-        <v>12</v>
+      <c r="I40" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="J40" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="K40" s="28" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B41" s="26" t="n">
         <v>40</v>
       </c>
-      <c r="C41" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="D41" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="E41" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="F41" s="29" t="n">
-        <v>34</v>
+      <c r="C41" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="28" t="n">
+        <v>62</v>
+      </c>
+      <c r="E41" s="27" t="n">
+        <v>82</v>
+      </c>
+      <c r="F41" s="28" t="n">
+        <v>60</v>
       </c>
       <c r="G41" s="28" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H41" s="28" t="n">
         <v>50</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="K41" s="28" t="n">
-        <v>62</v>
+        <v>42</v>
+      </c>
+      <c r="K41" s="27" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="42">
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="B42" s="26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C42" s="28" t="n">
         <v>50</v>
@@ -3800,7 +3800,7 @@
         <v>28</v>
       </c>
       <c r="F42" s="29" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G42" s="29" t="n">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="B43" s="26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C43" s="29" t="n">
         <v>4</v>
@@ -3837,7 +3837,7 @@
         <v>88</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G43" s="29" t="n">
         <v>16</v>
@@ -3858,75 +3858,75 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B44" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="C44" s="29" t="n">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="C44" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="D44" s="29" t="n">
-        <v>24</v>
-      </c>
-      <c r="E44" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="27" t="n">
+        <v>98</v>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="G44" s="29" t="n">
         <v>36</v>
-      </c>
-      <c r="F44" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="G44" s="29" t="n">
-        <v>18</v>
       </c>
       <c r="H44" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I44" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="J44" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="K44" s="27" t="n">
-        <v>72</v>
+      <c r="I44" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="29" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B45" s="26" t="n">
-        <v>38</v>
-      </c>
-      <c r="C45" s="28" t="n">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="C45" s="29" t="n">
+        <v>24</v>
       </c>
       <c r="D45" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="F45" s="27" t="n">
-        <v>88</v>
+        <v>24</v>
+      </c>
+      <c r="E45" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="F45" s="29" t="n">
+        <v>12</v>
       </c>
       <c r="G45" s="29" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H45" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="I45" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="29" t="n">
-        <v>38</v>
+      <c r="I45" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J45" s="28" t="n">
+        <v>54</v>
+      </c>
+      <c r="K45" s="27" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="46">
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="B46" s="26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C46" s="29" t="n">
         <v>24</v>
@@ -3947,8 +3947,8 @@
       <c r="E46" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="F46" s="28" t="n">
-        <v>50</v>
+      <c r="F46" s="29" t="n">
+        <v>46</v>
       </c>
       <c r="G46" s="28" t="n">
         <v>66</v>
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="B47" s="26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C47" s="29" t="n">
         <v>34</v>
@@ -3985,7 +3985,7 @@
         <v>16</v>
       </c>
       <c r="F47" s="29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G47" s="29" t="n">
         <v>28</v>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="B48" s="26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C48" s="29" t="n">
         <v>32</v>
@@ -4022,7 +4022,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="29" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G48" s="29" t="n">
         <v>34</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B50" s="26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C50" s="29" t="n">
         <v>14</v>
@@ -4096,7 +4096,7 @@
         <v>4</v>
       </c>
       <c r="F50" s="29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G50" s="29" t="n">
         <v>26</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="B51" s="26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" s="29" t="n">
         <v>10</v>
@@ -4133,7 +4133,7 @@
         <v>38</v>
       </c>
       <c r="F51" s="29" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G51" s="30" t="n">
         <v>0</v>
@@ -4268,7 +4268,7 @@
         <v>4.51</v>
       </c>
       <c r="F2" s="30" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="G2" s="30" t="n">
         <v>4.4</v>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>69 (A+)</t>
+          <t>68 (A+)</t>
         </is>
       </c>
       <c r="C4" s="30" t="n">
@@ -4354,7 +4354,7 @@
         <v>3.18</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="G4" s="30" t="n">
         <v>2.44</v>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>69 (A+)</t>
+          <t>68 (A+)</t>
         </is>
       </c>
       <c r="C5" s="30" t="n">
@@ -4397,7 +4397,7 @@
         <v>1.62</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="G5" s="30" t="n">
         <v>3.9</v>
@@ -4440,7 +4440,7 @@
         <v>4.52</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="G6" s="30" t="n">
         <v>3.58</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>63 (A-)</t>
+          <t>64 (A)</t>
         </is>
       </c>
       <c r="C7" s="30" t="n">
@@ -4483,7 +4483,7 @@
         <v>4.7</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="G7" s="30" t="n">
         <v>2.6</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>63 (A)</t>
+          <t>64 (A)</t>
         </is>
       </c>
       <c r="C8" s="30" t="n">
@@ -4526,7 +4526,7 @@
         <v>-0.36</v>
       </c>
       <c r="F8" s="30" t="n">
-        <v>4.21</v>
+        <v>3.5</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>2.12</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>62 (A-)</t>
+          <t>63 (A-)</t>
         </is>
       </c>
       <c r="C9" s="30" t="n">
@@ -4569,7 +4569,7 @@
         <v>5.1</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>5.3</v>
+        <v>3.94</v>
       </c>
       <c r="G9" s="30" t="n">
         <v>3.54</v>
@@ -4612,7 +4612,7 @@
         <v>0.86</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>3.59</v>
+        <v>2.99</v>
       </c>
       <c r="G10" s="30" t="n">
         <v>3.76</v>
@@ -4655,7 +4655,7 @@
         <v>8.27</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="G11" s="30" t="n">
         <v>3.52</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>56 (B+)</t>
         </is>
       </c>
       <c r="C12" s="30" t="n">
@@ -4698,7 +4698,7 @@
         <v>6.57</v>
       </c>
       <c r="F12" s="30" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="G12" s="30" t="n">
         <v>2.76</v>
@@ -4723,7 +4723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B13" s="31" t="inlineStr">
@@ -4735,72 +4735,72 @@
         <v>3.5</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>62.53</v>
+        <v>67.91</v>
       </c>
       <c r="E13" s="30" t="n">
-        <v>7.12</v>
+        <v>6.8</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>2.52</v>
+        <v>1.49</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="H13" s="30" t="n"/>
       <c r="I13" s="30" t="n">
-        <v>0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>41.11</v>
+        <v>5.41</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>7.98</v>
+        <v>4.6</v>
       </c>
       <c r="L13" s="30" t="n">
-        <v>12.16</v>
+        <v>-24</v>
       </c>
       <c r="M13" s="30" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>56 (B+)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C14" s="30" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>67.91</v>
+        <v>69.61</v>
       </c>
       <c r="E14" s="30" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>1.2</v>
+        <v>2.26</v>
       </c>
       <c r="H14" s="30" t="n"/>
       <c r="I14" s="30" t="n">
-        <v>-0.31</v>
+        <v>0.33</v>
       </c>
       <c r="J14" s="30" t="n">
-        <v>5.41</v>
+        <v>-20.96</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>4.6</v>
+        <v>7.18</v>
       </c>
       <c r="L14" s="30" t="n">
-        <v>-24</v>
+        <v>1.79</v>
       </c>
       <c r="M14" s="30" t="n">
         <v>57</v>
@@ -4809,7 +4809,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
@@ -4818,170 +4818,170 @@
         </is>
       </c>
       <c r="C15" s="30" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D15" s="30" t="n">
-        <v>64.23999999999999</v>
+        <v>62.53</v>
       </c>
       <c r="E15" s="30" t="n">
-        <v>5.12</v>
+        <v>7.12</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>3.02</v>
+        <v>1.86</v>
       </c>
       <c r="H15" s="30" t="n"/>
       <c r="I15" s="30" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>-20.27</v>
+        <v>41.11</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>6.8</v>
+        <v>7.98</v>
       </c>
       <c r="L15" s="30" t="n">
-        <v>-2.04</v>
+        <v>12.16</v>
       </c>
       <c r="M15" s="30" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C16" s="30" t="n">
         <v>3.6</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>69.61</v>
+        <v>60.33</v>
       </c>
       <c r="E16" s="30" t="n">
-        <v>3.1</v>
+        <v>8.65</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>2.26</v>
+        <v>3.38</v>
       </c>
       <c r="H16" s="30" t="n"/>
       <c r="I16" s="30" t="n">
-        <v>0.33</v>
+        <v>1.07</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>-20.96</v>
+        <v>-10.55</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>7.18</v>
+        <v>6.67</v>
       </c>
       <c r="L16" s="30" t="n">
-        <v>1.79</v>
+        <v>4.65</v>
       </c>
       <c r="M16" s="30" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C17" s="30" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="D17" s="30" t="n">
-        <v>68.47</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>1.42</v>
+        <v>5.12</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>5.46</v>
+        <v>2.71</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="H17" s="30" t="n"/>
       <c r="I17" s="30" t="n">
-        <v>0.73</v>
+        <v>0.29</v>
       </c>
       <c r="J17" s="30" t="n">
-        <v>-14.97</v>
+        <v>-20.27</v>
       </c>
       <c r="K17" s="30" t="n">
-        <v>9.73</v>
+        <v>6.8</v>
       </c>
       <c r="L17" s="30" t="n">
-        <v>27.27</v>
+        <v>-2.04</v>
       </c>
       <c r="M17" s="30" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C18" s="30" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>60.33</v>
+        <v>60.56</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>8.65</v>
+        <v>-0.12</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>2.47</v>
+        <v>3.17</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>3.38</v>
+        <v>1.44</v>
       </c>
       <c r="H18" s="30" t="n"/>
       <c r="I18" s="30" t="n">
-        <v>1.07</v>
+        <v>0.61</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>-10.55</v>
+        <v>55.25</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>6.67</v>
+        <v>6.86</v>
       </c>
       <c r="L18" s="30" t="n">
-        <v>4.65</v>
+        <v>-1.41</v>
       </c>
       <c r="M18" s="30" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
@@ -4990,35 +4990,35 @@
         </is>
       </c>
       <c r="C19" s="30" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>60.56</v>
+        <v>68.47</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>-0.12</v>
+        <v>1.42</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>4.3</v>
+        <v>5.47</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>1.44</v>
+        <v>3.14</v>
       </c>
       <c r="H19" s="30" t="n"/>
       <c r="I19" s="30" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="J19" s="30" t="n">
-        <v>55.25</v>
+        <v>-14.97</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>6.86</v>
+        <v>9.73</v>
       </c>
       <c r="L19" s="30" t="n">
-        <v>-1.41</v>
+        <v>27.27</v>
       </c>
       <c r="M19" s="30" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>52 (B)</t>
         </is>
       </c>
       <c r="C20" s="30" t="n">
@@ -5042,7 +5042,7 @@
         <v>-1.52</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>4.59</v>
+        <v>3.62</v>
       </c>
       <c r="G20" s="30" t="n">
         <v>4.14</v>
@@ -5067,93 +5067,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>50 (B-)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>63.61</v>
+        <v>63.96</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>5.33</v>
+        <v>2.21</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>3.89</v>
+        <v>3.07</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>0.96</v>
+        <v>3.56</v>
       </c>
       <c r="H21" s="30" t="n"/>
       <c r="I21" s="30" t="n">
-        <v>1.83</v>
+        <v>1.16</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>20.24</v>
+        <v>4.14</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>8.279999999999999</v>
+        <v>7.19</v>
       </c>
       <c r="L21" s="30" t="n">
-        <v>12.82</v>
+        <v>1.92</v>
       </c>
       <c r="M21" s="30" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C22" s="30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>63.96</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>2.21</v>
+        <v>7.63</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>3.67</v>
+        <v>2.92</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>3.56</v>
+        <v>3.26</v>
       </c>
       <c r="H22" s="30" t="n"/>
       <c r="I22" s="30" t="n">
-        <v>1.16</v>
+        <v>-0.15</v>
       </c>
       <c r="J22" s="30" t="n">
-        <v>4.14</v>
+        <v>-0.7</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>7.19</v>
+        <v>7.29</v>
       </c>
       <c r="L22" s="30" t="n">
-        <v>1.92</v>
+        <v>2.86</v>
       </c>
       <c r="M22" s="30" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
@@ -5162,41 +5162,41 @@
         </is>
       </c>
       <c r="C23" s="30" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="D23" s="30" t="n">
-        <v>68.23999999999999</v>
+        <v>59.95</v>
       </c>
       <c r="E23" s="30" t="n">
-        <v>7.63</v>
+        <v>4.86</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="H23" s="30" t="n"/>
       <c r="I23" s="30" t="n">
-        <v>-0.15</v>
+        <v>0.92</v>
       </c>
       <c r="J23" s="30" t="n">
-        <v>-0.7</v>
+        <v>-8.56</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>7.29</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L23" s="30" t="n">
-        <v>2.86</v>
+        <v>21.21</v>
       </c>
       <c r="M23" s="30" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
@@ -5205,127 +5205,127 @@
         </is>
       </c>
       <c r="C24" s="30" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="D24" s="30" t="n">
-        <v>60.48</v>
+        <v>62.74</v>
       </c>
       <c r="E24" s="30" t="n">
-        <v>6.16</v>
+        <v>3.37</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>0.41</v>
+        <v>3.32</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>0.6</v>
+        <v>2.38</v>
       </c>
       <c r="H24" s="30" t="n"/>
       <c r="I24" s="30" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="J24" s="30" t="n">
-        <v>19.69</v>
+        <v>2.98</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>8.130000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="L24" s="30" t="n">
-        <v>11.27</v>
+        <v>-1.96</v>
       </c>
       <c r="M24" s="30" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C25" s="30" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="D25" s="30" t="n">
-        <v>59.95</v>
+        <v>60.48</v>
       </c>
       <c r="E25" s="30" t="n">
-        <v>4.86</v>
+        <v>6.16</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>1.86</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>3.08</v>
+        <v>0.6</v>
       </c>
       <c r="H25" s="30" t="n"/>
       <c r="I25" s="30" t="n">
-        <v>0.92</v>
+        <v>0.06</v>
       </c>
       <c r="J25" s="30" t="n">
-        <v>-8.56</v>
+        <v>19.69</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>9.119999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L25" s="30" t="n">
-        <v>21.21</v>
+        <v>11.27</v>
       </c>
       <c r="M25" s="30" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C26" s="30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D26" s="30" t="n">
-        <v>62.78</v>
+        <v>63.89</v>
       </c>
       <c r="E26" s="30" t="n">
-        <v>1.78</v>
+        <v>3.13</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>1.59</v>
+        <v>5.76</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>1.24</v>
+        <v>3.06</v>
       </c>
       <c r="H26" s="30" t="n"/>
       <c r="I26" s="30" t="n">
-        <v>1.09</v>
+        <v>0.51</v>
       </c>
       <c r="J26" s="30" t="n">
-        <v>-37.55</v>
+        <v>55.17</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>7.4</v>
+        <v>8.43</v>
       </c>
       <c r="L26" s="30" t="n">
-        <v>3.95</v>
+        <v>14.29</v>
       </c>
       <c r="M26" s="30" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
@@ -5334,41 +5334,41 @@
         </is>
       </c>
       <c r="C27" s="30" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="D27" s="30" t="n">
-        <v>62.74</v>
+        <v>63.61</v>
       </c>
       <c r="E27" s="30" t="n">
-        <v>3.37</v>
+        <v>5.33</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>4.2</v>
+        <v>5.59</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>2.38</v>
+        <v>0.96</v>
       </c>
       <c r="H27" s="30" t="n"/>
       <c r="I27" s="30" t="n">
-        <v>-0.06</v>
+        <v>1.83</v>
       </c>
       <c r="J27" s="30" t="n">
-        <v>2.98</v>
+        <v>20.24</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>6.8</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L27" s="30" t="n">
-        <v>-1.96</v>
+        <v>12.82</v>
       </c>
       <c r="M27" s="30" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B28" s="31" t="inlineStr">
@@ -5380,81 +5380,81 @@
         <v>4</v>
       </c>
       <c r="D28" s="30" t="n">
-        <v>63.89</v>
+        <v>69.03</v>
       </c>
       <c r="E28" s="30" t="n">
-        <v>3.13</v>
+        <v>0.03</v>
       </c>
       <c r="F28" s="30" t="n">
-        <v>7.23</v>
+        <v>2.83</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>3.06</v>
+        <v>2.56</v>
       </c>
       <c r="H28" s="30" t="n"/>
       <c r="I28" s="30" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="J28" s="30" t="n">
-        <v>55.17</v>
+        <v>-12.25</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>8.43</v>
+        <v>6.76</v>
       </c>
       <c r="L28" s="30" t="n">
-        <v>14.29</v>
+        <v>-2.44</v>
       </c>
       <c r="M28" s="30" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D29" s="30" t="n">
-        <v>67.37</v>
+        <v>62.78</v>
       </c>
       <c r="E29" s="30" t="n">
-        <v>1.37</v>
+        <v>1.78</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>1.84</v>
+        <v>1.38</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>2.22</v>
+        <v>1.24</v>
       </c>
       <c r="H29" s="30" t="n"/>
       <c r="I29" s="30" t="n">
-        <v>-1.63</v>
+        <v>1.09</v>
       </c>
       <c r="J29" s="30" t="n">
-        <v>-3.97</v>
+        <v>-37.55</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>8.18</v>
+        <v>7.4</v>
       </c>
       <c r="L29" s="30" t="n">
-        <v>11.76</v>
+        <v>3.95</v>
       </c>
       <c r="M29" s="30" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
@@ -5463,69 +5463,69 @@
         </is>
       </c>
       <c r="C30" s="30" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D30" s="30" t="n">
-        <v>69.03</v>
+        <v>67.37</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>0.03</v>
+        <v>1.37</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>3.62</v>
+        <v>1.9</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="H30" s="30" t="n"/>
       <c r="I30" s="30" t="n">
-        <v>0.55</v>
+        <v>-1.63</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>-12.25</v>
+        <v>-3.97</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>6.76</v>
+        <v>8.18</v>
       </c>
       <c r="L30" s="30" t="n">
-        <v>-2.44</v>
+        <v>11.76</v>
       </c>
       <c r="M30" s="30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="D31" s="30" t="n">
-        <v>63.3</v>
+        <v>64.52</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>4.84</v>
+        <v>2.61</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>3.74</v>
+        <v>1.17</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>2.98</v>
+        <v>0.82</v>
       </c>
       <c r="H31" s="30" t="n"/>
       <c r="I31" s="30" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="J31" s="30" t="n">
-        <v>14.97</v>
+        <v>-12.89</v>
       </c>
       <c r="K31" s="30" t="n">
         <v>7</v>
@@ -5534,56 +5534,56 @@
         <v>0</v>
       </c>
       <c r="M31" s="30" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="D32" s="30" t="n">
-        <v>64.52</v>
+        <v>65.27</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>2.61</v>
+        <v>0.66</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>1.59</v>
+        <v>4.24</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>0.82</v>
+        <v>2.34</v>
       </c>
       <c r="H32" s="30" t="n"/>
       <c r="I32" s="30" t="n">
-        <v>0.43</v>
+        <v>-0.01</v>
       </c>
       <c r="J32" s="30" t="n">
-        <v>-12.89</v>
+        <v>-6.99</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="L32" s="30" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M32" s="30" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B33" s="31" t="inlineStr">
@@ -5592,32 +5592,32 @@
         </is>
       </c>
       <c r="C33" s="30" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D33" s="30" t="n">
-        <v>65.27</v>
+        <v>58.01</v>
       </c>
       <c r="E33" s="30" t="n">
-        <v>0.66</v>
+        <v>-1.79</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>5.87</v>
+        <v>5</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>2.34</v>
+        <v>3.02</v>
       </c>
       <c r="H33" s="30" t="n"/>
       <c r="I33" s="30" t="n">
-        <v>-0.01</v>
+        <v>0.57</v>
       </c>
       <c r="J33" s="30" t="n">
-        <v>-6.99</v>
+        <v>14.96</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>7.38</v>
+        <v>7.78</v>
       </c>
       <c r="L33" s="30" t="n">
-        <v>3.77</v>
+        <v>7.84</v>
       </c>
       <c r="M33" s="30" t="n">
         <v>55</v>
@@ -5626,44 +5626,44 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>43 (C+)</t>
+          <t>44 (C+)</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D34" s="30" t="n">
-        <v>58.01</v>
+        <v>63.19</v>
       </c>
       <c r="E34" s="30" t="n">
-        <v>-1.79</v>
+        <v>3.73</v>
       </c>
       <c r="F34" s="30" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>3.02</v>
+        <v>1.56</v>
       </c>
       <c r="H34" s="30" t="n"/>
       <c r="I34" s="30" t="n">
-        <v>0.57</v>
+        <v>-0.91</v>
       </c>
       <c r="J34" s="30" t="n">
-        <v>14.96</v>
+        <v>-10.47</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>7.78</v>
+        <v>7.83</v>
       </c>
       <c r="L34" s="30" t="n">
-        <v>7.84</v>
+        <v>8.33</v>
       </c>
       <c r="M34" s="30" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35">
@@ -5687,7 +5687,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="30" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="G35" s="30" t="n">
         <v>2.24</v>
@@ -5730,7 +5730,7 @@
         <v>3.63</v>
       </c>
       <c r="F36" s="30" t="n">
-        <v>7.95</v>
+        <v>7.01</v>
       </c>
       <c r="G36" s="30" t="n">
         <v>2.78</v>
@@ -5755,179 +5755,179 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>43 (C+)</t>
+          <t>42 (C+)</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="D37" s="30" t="n">
-        <v>63.19</v>
+        <v>63.3</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>3.73</v>
+        <v>4.84</v>
       </c>
       <c r="F37" s="30" t="n">
-        <v>4.57</v>
+        <v>4.78</v>
       </c>
       <c r="G37" s="30" t="n">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="H37" s="30" t="n"/>
       <c r="I37" s="30" t="n">
-        <v>-0.91</v>
+        <v>0.48</v>
       </c>
       <c r="J37" s="30" t="n">
-        <v>-10.47</v>
+        <v>14.97</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>7.83</v>
+        <v>7</v>
       </c>
       <c r="L37" s="30" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="M37" s="30" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="D38" s="30" t="n">
-        <v>65.02</v>
+        <v>64.75</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>6.71</v>
+        <v>2.84</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H38" s="30" t="n"/>
       <c r="I38" s="30" t="n">
-        <v>-0.76</v>
+        <v>0.6</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>-9.83</v>
+        <v>-27.41</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>8.279999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="L38" s="30" t="n">
-        <v>12.77</v>
+        <v>-6.98</v>
       </c>
       <c r="M38" s="30" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="D39" s="30" t="n">
-        <v>60.33</v>
+        <v>64.19</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>7.6</v>
+        <v>1.22</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>1.78</v>
+        <v>3.16</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>0.78</v>
+        <v>2.88</v>
       </c>
       <c r="H39" s="30" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>0.22</v>
+        <v>-0.14</v>
       </c>
       <c r="J39" s="30" t="n">
-        <v>61.97</v>
+        <v>-11.14</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>8.039999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="L39" s="30" t="n">
-        <v>10.42</v>
+        <v>9.76</v>
       </c>
       <c r="M39" s="30" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D40" s="30" t="n">
-        <v>64.75</v>
+        <v>60.33</v>
       </c>
       <c r="E40" s="30" t="n">
-        <v>2.84</v>
+        <v>7.6</v>
       </c>
       <c r="F40" s="30" t="n">
-        <v>3.74</v>
+        <v>2.08</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>2.3</v>
+        <v>0.78</v>
       </c>
       <c r="H40" s="30" t="n"/>
       <c r="I40" s="30" t="n">
-        <v>0.6</v>
+        <v>0.22</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>-27.41</v>
+        <v>61.97</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>6.3</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L40" s="30" t="n">
-        <v>-6.98</v>
+        <v>10.42</v>
       </c>
       <c r="M40" s="30" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B41" s="31" t="inlineStr">
@@ -5936,35 +5936,35 @@
         </is>
       </c>
       <c r="C41" s="30" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="D41" s="30" t="n">
-        <v>64.19</v>
+        <v>65.02</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>1.22</v>
+        <v>6.71</v>
       </c>
       <c r="F41" s="30" t="n">
-        <v>3.88</v>
+        <v>2.19</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="H41" s="30" t="n"/>
       <c r="I41" s="30" t="n">
-        <v>-0.14</v>
+        <v>-0.76</v>
       </c>
       <c r="J41" s="30" t="n">
-        <v>-11.14</v>
+        <v>-9.83</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>7.98</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L41" s="30" t="n">
-        <v>9.76</v>
+        <v>12.77</v>
       </c>
       <c r="M41" s="30" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
@@ -5988,7 +5988,7 @@
         <v>1.53</v>
       </c>
       <c r="F42" s="30" t="n">
-        <v>4.76</v>
+        <v>3.69</v>
       </c>
       <c r="G42" s="30" t="n">
         <v>2.02</v>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>38 (C+)</t>
+          <t>37 (C)</t>
         </is>
       </c>
       <c r="C43" s="30" t="n">
@@ -6031,7 +6031,7 @@
         <v>7.54</v>
       </c>
       <c r="F43" s="30" t="n">
-        <v>2.29</v>
+        <v>2.93</v>
       </c>
       <c r="G43" s="30" t="n">
         <v>1.3</v>
@@ -6056,87 +6056,87 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>38 (C)</t>
+          <t>37 (C)</t>
         </is>
       </c>
       <c r="C44" s="30" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="D44" s="30" t="n">
-        <v>62.01</v>
+        <v>58.99</v>
       </c>
       <c r="E44" s="30" t="n">
-        <v>2.43</v>
+        <v>10.22</v>
       </c>
       <c r="F44" s="30" t="n">
-        <v>3.89</v>
+        <v>1.57</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="H44" s="30" t="n"/>
       <c r="I44" s="30" t="n">
-        <v>0.35</v>
+        <v>-1.34</v>
       </c>
       <c r="J44" s="30" t="n">
-        <v>-0.37</v>
+        <v>-46.79</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>8.18</v>
+        <v>7.26</v>
       </c>
       <c r="L44" s="30" t="n">
-        <v>11.76</v>
+        <v>2.56</v>
       </c>
       <c r="M44" s="30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B45" s="31" t="inlineStr">
         <is>
-          <t>38 (C+)</t>
+          <t>36 (C)</t>
         </is>
       </c>
       <c r="C45" s="30" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="D45" s="30" t="n">
-        <v>58.99</v>
+        <v>62.01</v>
       </c>
       <c r="E45" s="30" t="n">
-        <v>10.22</v>
+        <v>2.43</v>
       </c>
       <c r="F45" s="30" t="n">
-        <v>1.56</v>
+        <v>5.24</v>
       </c>
       <c r="G45" s="30" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="H45" s="30" t="n"/>
       <c r="I45" s="30" t="n">
-        <v>-1.34</v>
+        <v>0.35</v>
       </c>
       <c r="J45" s="30" t="n">
-        <v>-46.79</v>
+        <v>-0.37</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>7.26</v>
+        <v>8.18</v>
       </c>
       <c r="L45" s="30" t="n">
-        <v>2.56</v>
+        <v>11.76</v>
       </c>
       <c r="M45" s="30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>35 (C)</t>
         </is>
       </c>
       <c r="C46" s="30" t="n">
@@ -6160,7 +6160,7 @@
         <v>0.37</v>
       </c>
       <c r="F46" s="30" t="n">
-        <v>3.42</v>
+        <v>3.06</v>
       </c>
       <c r="G46" s="30" t="n">
         <v>3</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>35 (C)</t>
         </is>
       </c>
       <c r="C47" s="30" t="n">
@@ -6203,7 +6203,7 @@
         <v>0.59</v>
       </c>
       <c r="F47" s="30" t="n">
-        <v>6.07</v>
+        <v>6.96</v>
       </c>
       <c r="G47" s="30" t="n">
         <v>2.02</v>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>35 (C)</t>
+          <t>34 (C)</t>
         </is>
       </c>
       <c r="C48" s="30" t="n">
@@ -6246,7 +6246,7 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="30" t="n">
-        <v>4.82</v>
+        <v>5.62</v>
       </c>
       <c r="G48" s="30" t="n">
         <v>2.14</v>
@@ -6289,7 +6289,7 @@
         <v>4.78</v>
       </c>
       <c r="F49" s="30" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G49" s="30" t="n">
         <v>1.22</v>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>24 (D)</t>
+          <t>25 (D)</t>
         </is>
       </c>
       <c r="C50" s="30" t="n">
@@ -6332,7 +6332,7 @@
         <v>-1.13</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>5.52</v>
+        <v>4.06</v>
       </c>
       <c r="G50" s="30" t="n">
         <v>1.96</v>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>23 (D)</t>
+          <t>22 (D)</t>
         </is>
       </c>
       <c r="C51" s="30" t="n">
@@ -6375,7 +6375,7 @@
         <v>2.48</v>
       </c>
       <c r="F51" s="30" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="G51" s="30" t="n">
         <v>0.12</v>
@@ -6476,41 +6476,41 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="n">
+      <c r="A2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="G2" s="14" t="n">
+      <c r="D2" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="G2" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="17" t="n">
         <v>63.3</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="17" t="n">
         <v>4.84</v>
       </c>
-      <c r="J2" s="14" t="n">
-        <v>3.74</v>
+      <c r="J2" s="17" t="n">
+        <v>4.78</v>
       </c>
     </row>
     <row r="3">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="D3" s="14" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="F3" s="14" t="n">
-        <v>49.5</v>
+        <v>47.3</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>4.8</v>
@@ -6548,7 +6548,7 @@
         <v>5.33</v>
       </c>
       <c r="J3" s="14" t="n">
-        <v>3.89</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="4">
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="F4" s="17" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>4.5</v>
@@ -6586,7 +6586,7 @@
         <v>2.84</v>
       </c>
       <c r="J4" s="17" t="n">
-        <v>3.74</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>3.6</v>
@@ -6624,7 +6624,7 @@
         <v>3.1</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="6">
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>44</v>
+        <v>44.8</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>4.2</v>
@@ -6662,45 +6662,45 @@
         <v>2.61</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>1.59</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="G7" s="8" t="n">
+      <c r="D7" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>3.5</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="11" t="n">
         <v>62.53</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="11" t="n">
         <v>7.12</v>
       </c>
-      <c r="J7" s="8" t="n">
-        <v>2.52</v>
+      <c r="J7" s="11" t="n">
+        <v>3.36</v>
       </c>
     </row>
     <row r="8">
@@ -6738,7 +6738,7 @@
         <v>1.37</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="9">
@@ -6776,7 +6776,7 @@
         <v>8.27</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="F10" s="11" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>4</v>
@@ -6814,7 +6814,7 @@
         <v>2.21</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>3.67</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="11">
@@ -6852,7 +6852,7 @@
         <v>4.52</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="12">
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="F12" s="11" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>3.9</v>
@@ -6890,45 +6890,45 @@
         <v>1.42</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>5.46</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n">
+      <c r="A13" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>38</v>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>38</v>
-      </c>
-      <c r="G13" s="17" t="n">
+      <c r="D13" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G13" s="20" t="n">
         <v>5.1</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="20" t="n">
         <v>60.37</v>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="20" t="n">
         <v>7.54</v>
       </c>
-      <c r="J13" s="17" t="n">
-        <v>2.29</v>
+      <c r="J13" s="20" t="n">
+        <v>2.93</v>
       </c>
     </row>
     <row r="14">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
       <c r="F14" s="20" t="n">
-        <v>35.2</v>
+        <v>34.2</v>
       </c>
       <c r="G14" s="20" t="n">
         <v>4.1</v>
@@ -6966,7 +6966,7 @@
         <v>0.49</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>4.82</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="15">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="D15" s="23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>24.2</v>
+        <v>25.2</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>4.7</v>
@@ -7004,7 +7004,7 @@
         <v>-1.13</v>
       </c>
       <c r="J15" s="23" t="n">
-        <v>5.52</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="16">
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>5</v>
@@ -7042,7 +7042,7 @@
         <v>7.63</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="17">
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>46</v>
+        <v>47.2</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>4</v>
@@ -7080,7 +7080,7 @@
         <v>0.03</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>3.62</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="18">
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>4.6</v>
@@ -7118,7 +7118,7 @@
         <v>4.86</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="19">
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="D19" s="20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="F19" s="20" t="n">
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="G19" s="20" t="n">
         <v>4.4</v>
@@ -7156,7 +7156,7 @@
         <v>2.43</v>
       </c>
       <c r="J19" s="20" t="n">
-        <v>3.89</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="20">
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>56.8</v>
+        <v>55.8</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>3.6</v>
@@ -7194,7 +7194,7 @@
         <v>6.57</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="21">
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="D21" s="20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="G21" s="20" t="n">
         <v>4.4</v>
@@ -7232,7 +7232,7 @@
         <v>0.37</v>
       </c>
       <c r="J21" s="20" t="n">
-        <v>3.42</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="22">
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         </is>
       </c>
       <c r="F22" s="11" t="n">
-        <v>51.4</v>
+        <v>52.4</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>3.6</v>
@@ -7270,7 +7270,7 @@
         <v>-1.52</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>4.59</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="23">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>40.2</v>
+        <v>41</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>3.6</v>
@@ -7308,45 +7308,45 @@
         <v>1.22</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>3.88</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n">
+      <c r="A24" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>St. Louis</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>St. Louis</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="G24" s="17" t="n">
+      <c r="D24" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G24" s="14" t="n">
         <v>3.5</v>
       </c>
-      <c r="H24" s="17" t="n">
+      <c r="H24" s="14" t="n">
         <v>65.27</v>
       </c>
-      <c r="I24" s="17" t="n">
+      <c r="I24" s="14" t="n">
         <v>0.66</v>
       </c>
-      <c r="J24" s="17" t="n">
-        <v>5.87</v>
+      <c r="J24" s="14" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="25">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>3.7</v>
@@ -7384,7 +7384,7 @@
         <v>1.78</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="26">
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3.2</v>
@@ -7422,7 +7422,7 @@
         <v>3.18</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="27">
@@ -7460,7 +7460,7 @@
         <v>4.78</v>
       </c>
       <c r="J27" s="20" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="28">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="D28" s="23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="F28" s="23" t="n">
-        <v>23.4</v>
+        <v>21.6</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>4.8</v>
@@ -7498,7 +7498,7 @@
         <v>2.48</v>
       </c>
       <c r="J28" s="23" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="29">
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="F29" s="11" t="n">
-        <v>52.4</v>
+        <v>54</v>
       </c>
       <c r="G29" s="11" t="n">
         <v>3.6</v>
@@ -7536,7 +7536,7 @@
         <v>8.65</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>2.47</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="30">
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="D30" s="17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="F30" s="17" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="G30" s="17" t="n">
         <v>5.2</v>
@@ -7574,7 +7574,7 @@
         <v>6.71</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="31">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>38.6</v>
+        <v>39.6</v>
       </c>
       <c r="G31" s="17" t="n">
         <v>3.6</v>
@@ -7612,7 +7612,7 @@
         <v>1.53</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>4.76</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="32">
@@ -7650,7 +7650,7 @@
         <v>6.8</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="33">
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>59.7</v>
+        <v>59.9</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>3.6</v>
@@ -7688,7 +7688,7 @@
         <v>0.86</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>3.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="34">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>61.9</v>
+        <v>62.7</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>2.5</v>
@@ -7726,7 +7726,7 @@
         <v>5.1</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>5.3</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="35">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>42.8</v>
+        <v>43.8</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>3.4</v>
@@ -7764,7 +7764,7 @@
         <v>-1.79</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>3</v>
@@ -7802,7 +7802,7 @@
         <v>1.62</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="37">
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="F37" s="20" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="G37" s="20" t="n">
         <v>4</v>
@@ -7840,45 +7840,45 @@
         <v>0.59</v>
       </c>
       <c r="J37" s="20" t="n">
-        <v>6.07</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
-        <v>38</v>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="G38" s="17" t="n">
+      <c r="D38" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="G38" s="20" t="n">
         <v>3.6</v>
       </c>
-      <c r="H38" s="17" t="n">
+      <c r="H38" s="20" t="n">
         <v>58.99</v>
       </c>
-      <c r="I38" s="17" t="n">
+      <c r="I38" s="20" t="n">
         <v>10.22</v>
       </c>
-      <c r="J38" s="17" t="n">
-        <v>1.56</v>
+      <c r="J38" s="20" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="39">
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="G39" s="17" t="n">
         <v>4.6</v>
@@ -7916,7 +7916,7 @@
         <v>5</v>
       </c>
       <c r="J39" s="17" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="40">
@@ -7954,7 +7954,7 @@
         <v>3.63</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>7.95</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="41">
@@ -7972,7 +7972,7 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>43.3</v>
+        <v>43.7</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>3.1</v>
@@ -7992,7 +7992,7 @@
         <v>3.73</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>4.57</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="42">
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3</v>
@@ -8030,45 +8030,45 @@
         <v>4.51</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="G43" s="5" t="n">
+      <c r="D43" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H43" s="2" t="n">
         <v>65.65000000000001</v>
       </c>
-      <c r="I43" s="5" t="n">
+      <c r="I43" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="J43" s="5" t="n">
-        <v>1.6</v>
+      <c r="J43" s="2" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="44">
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>47.1</v>
+        <v>47.9</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>3.1</v>
@@ -8106,7 +8106,7 @@
         <v>3.37</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="45">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="F45" s="11" t="n">
-        <v>53.9</v>
+        <v>54.5</v>
       </c>
       <c r="G45" s="11" t="n">
         <v>3.3</v>
@@ -8144,7 +8144,7 @@
         <v>5.12</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>3.13</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="46">
@@ -8182,7 +8182,7 @@
         <v>6.16</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="47">
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>70.8</v>
+        <v>71.2</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.4</v>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="F48" s="11" t="n">
-        <v>52.1</v>
+        <v>53.7</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>2.2</v>
@@ -8258,7 +8258,7 @@
         <v>-0.12</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>4.3</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="49">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="D49" s="17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>41.9</v>
+        <v>40.9</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>8.199999999999999</v>
@@ -8296,7 +8296,7 @@
         <v>7.6</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="50">
@@ -8314,7 +8314,7 @@
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>4</v>
@@ -8334,7 +8334,7 @@
         <v>3.13</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>7.23</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="51">
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>63.2</v>
+        <v>63.8</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8372,7 +8372,7 @@
         <v>-0.36</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.21</v>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="G3" s="37" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" s="37" t="inlineStr">
         <is>
@@ -8513,11 +8513,11 @@
         </is>
       </c>
       <c r="G4" s="37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="C5" s="36" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
@@ -8543,11 +8543,11 @@
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="G5" s="37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
@@ -8577,15 +8577,15 @@
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="G6" s="37" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="G7" s="37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7" s="37" t="inlineStr">
         <is>
@@ -8633,11 +8633,11 @@
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E8" s="37" t="n">
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="G8" s="37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="37" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="G9" s="37" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9" s="37" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="G11" s="37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H11" s="37" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="G12" s="37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" s="37" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Scores" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Values" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Rank" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top vs Bottom" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metric Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Raw Values" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="By Rank" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Top vs Bottom" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>69.8</v>
+        <v>70</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -773,38 +773,38 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>65.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -822,20 +822,20 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>64.3</v>
+        <v>66.3</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -852,48 +852,48 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="A8" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Austin-Round Rock-San Marcos</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>61.5</v>
+        <v>62.3</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -915,20 +915,20 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>61.7</v>
+        <v>60.5</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -976,79 +976,79 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Phoenix-Mesa-Chandler</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="D13" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>56.6</v>
+        <v>57.1</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>55.9</v>
+        <v>56.1</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1131,83 +1131,83 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A17" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Philadelphia-Camden-Wilmington</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A18" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth-Arlington</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>53.6</v>
+        <v>52.6</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1225,16 +1225,16 @@
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>51.5</v>
+        <v>53.3</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1287,16 +1287,16 @@
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D22" s="13" t="n">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="F22" s="11" t="n">
-        <v>51.5</v>
+        <v>52.2</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1349,16 +1349,16 @@
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D24" s="13" t="n">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="F24" s="11" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1380,16 +1380,16 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>48.7</v>
+        <v>49.4</v>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
@@ -1411,20 +1411,20 @@
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1442,16 +1442,16 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1473,16 +1473,16 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1535,20 +1535,20 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>46</v>
+        <v>47.1</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1566,16 +1566,16 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>44.5</v>
+        <v>45.3</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1597,16 +1597,16 @@
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Grand Rapids</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -1627,33 +1627,33 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="n">
+      <c r="A33" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1721,28 +1721,28 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Washington-Arlington-Alexandria</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>Milwaukee-Waukesha</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="n">
-        <v>42</v>
-      </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>41.6</v>
+        <v>39.7</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>39.9</v>
+        <v>39</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1783,20 +1783,20 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>39.9</v>
+        <v>39</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>39.7</v>
+        <v>39</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
@@ -1845,16 +1845,16 @@
     </row>
     <row r="40">
       <c r="A40" s="17" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F40" s="17" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="G40" s="18" t="inlineStr">
         <is>
@@ -1876,16 +1876,16 @@
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="D41" s="19" t="n">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>38.8</v>
+        <v>39.4</v>
       </c>
       <c r="G41" s="18" t="inlineStr">
         <is>
@@ -1906,48 +1906,48 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="n">
+      <c r="A42" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>Virginia Beach</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="n">
-        <v>39</v>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -1969,20 +1969,20 @@
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D44" s="22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>36.2</v>
+        <v>35.3</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="D45" s="22" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>35.4</v>
+        <v>33.5</v>
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="D46" s="22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -2062,20 +2062,20 @@
     </row>
     <row r="47">
       <c r="A47" s="23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F47" s="23" t="n">
-        <v>31.7</v>
+        <v>30.4</v>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
@@ -2093,20 +2093,20 @@
     </row>
     <row r="48">
       <c r="A48" s="23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="F48" s="23" t="n">
-        <v>30.9</v>
+        <v>29.4</v>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F49" s="23" t="n">
-        <v>29.3</v>
+        <v>27.7</v>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="D50" s="28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F51" s="26" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>76</v>
       </c>
       <c r="C2" s="30" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D2" s="30" t="n">
         <v>80</v>
@@ -2327,7 +2327,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="30" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G2" s="30" t="n">
         <v>96</v>
@@ -2340,7 +2340,7 @@
         <v>82</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -2353,7 +2353,7 @@
         <v>74</v>
       </c>
       <c r="C3" s="30" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3" s="30" t="n">
         <v>94</v>
@@ -2362,7 +2362,7 @@
         <v>48</v>
       </c>
       <c r="F3" s="31" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G3" s="30" t="n">
         <v>98</v>
@@ -2372,10 +2372,10 @@
         <v>96</v>
       </c>
       <c r="J3" s="31" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2400,7 +2400,7 @@
         <v>90</v>
       </c>
       <c r="G4" s="31" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="30" t="n">
@@ -2410,7 +2410,7 @@
         <v>78</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5" s="30" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" s="30" t="n">
         <v>98</v>
@@ -2432,7 +2432,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" s="30" t="n">
         <v>92</v>
@@ -2442,185 +2442,185 @@
         <v>80</v>
       </c>
       <c r="J5" s="33" t="n">
-        <v>43</v>
-      </c>
-      <c r="K5" s="33" t="n">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>65</v>
-      </c>
-      <c r="C6" s="30" t="n">
+        <v>67</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="F6" s="30" t="n">
         <v>94</v>
       </c>
-      <c r="D6" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="G6" s="33" t="n">
-        <v>35</v>
+      <c r="G6" s="30" t="n">
+        <v>82</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="J6" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="K6" s="30" t="n">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="J6" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" s="33" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>64</v>
-      </c>
-      <c r="C7" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="30" t="n">
+        <v>66</v>
+      </c>
+      <c r="C7" s="30" t="n">
         <v>96</v>
       </c>
-      <c r="F7" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="G7" s="30" t="n">
-        <v>82</v>
+      <c r="D7" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>35</v>
       </c>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="K7" s="33" t="n">
-        <v>22</v>
+        <v>94</v>
+      </c>
+      <c r="J7" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="F8" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="G8" s="30" t="n">
-        <v>73</v>
+        <v>86</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <v>51</v>
       </c>
       <c r="H8" s="32" t="n"/>
-      <c r="I8" s="30" t="n">
-        <v>74</v>
+      <c r="I8" s="33" t="n">
+        <v>44</v>
       </c>
       <c r="J8" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" s="33" t="n">
-        <v>42</v>
+        <v>12</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B9" s="29" t="n">
         <v>62</v>
       </c>
       <c r="C9" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>56</v>
+        <v>82</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>48</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="F9" s="30" t="n">
-        <v>96</v>
+        <v>74</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>60</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="J9" s="31" t="n">
-        <v>50</v>
+      <c r="I9" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="K9" s="33" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="30" t="n">
         <v>98</v>
       </c>
-      <c r="D10" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="33" t="n">
-        <v>8</v>
+      <c r="D10" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>72</v>
       </c>
       <c r="F10" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="J10" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="J10" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>54</v>
+      <c r="K10" s="30" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -2642,7 +2642,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="31" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G11" s="30" t="n">
         <v>90</v>
@@ -2652,45 +2652,45 @@
         <v>84</v>
       </c>
       <c r="J11" s="31" t="n">
-        <v>61</v>
-      </c>
-      <c r="K11" s="30" t="n">
-        <v>88</v>
+        <v>62</v>
+      </c>
+      <c r="K11" s="31" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>58</v>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>84</v>
+        <v>59</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>69</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E12" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="F12" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>51</v>
+        <v>60</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="J12" s="33" t="n">
-        <v>10</v>
+        <v>38</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>72</v>
       </c>
       <c r="K12" s="33" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C13" s="31" t="n">
         <v>51</v>
@@ -2712,7 +2712,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G13" s="31" t="n">
         <v>59</v>
@@ -2722,45 +2722,45 @@
         <v>46</v>
       </c>
       <c r="J13" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K13" s="33" t="n">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="K13" s="31" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B14" s="29" t="n">
         <v>57</v>
       </c>
-      <c r="C14" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="D14" s="33" t="n">
-        <v>18</v>
+      <c r="C14" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>56</v>
       </c>
       <c r="E14" s="30" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="G14" s="33" t="n">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>84</v>
       </c>
       <c r="H14" s="32" t="n"/>
-      <c r="I14" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="J14" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="K14" s="33" t="n">
-        <v>26</v>
+      <c r="I14" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="J14" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2782,7 +2782,7 @@
         <v>86</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>24</v>
@@ -2795,252 +2795,252 @@
         <v>84</v>
       </c>
       <c r="K15" s="33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B16" s="29" t="n">
         <v>56</v>
       </c>
-      <c r="C16" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>66</v>
-      </c>
-      <c r="G16" s="30" t="n">
-        <v>88</v>
+      <c r="C16" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="G16" s="33" t="n">
+        <v>2</v>
       </c>
       <c r="H16" s="32" t="n"/>
-      <c r="I16" s="33" t="n">
-        <v>38</v>
+      <c r="I16" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K16" s="33" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>56</v>
-      </c>
-      <c r="C17" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="D17" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="E17" s="30" t="n">
-        <v>72</v>
+        <v>54</v>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>34</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="G17" s="30" t="n">
-        <v>84</v>
+        <v>42</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H17" s="32" t="n"/>
-      <c r="I17" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="J17" s="33" t="n">
-        <v>39</v>
-      </c>
-      <c r="K17" s="33" t="n">
-        <v>8</v>
+      <c r="I17" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="J17" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="K17" s="31" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>55</v>
-      </c>
-      <c r="C18" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="D18" s="33" t="n">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>90</v>
       </c>
       <c r="E18" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="F18" s="33" t="n">
         <v>44</v>
       </c>
-      <c r="G18" s="30" t="n">
-        <v>86</v>
+      <c r="F18" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="G18" s="33" t="n">
+        <v>41</v>
       </c>
       <c r="H18" s="32" t="n"/>
-      <c r="I18" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="J18" s="31" t="n">
-        <v>57</v>
-      </c>
-      <c r="K18" s="31" t="n">
-        <v>58</v>
+      <c r="I18" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="J18" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="K18" s="33" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B19" s="29" t="n">
+        <v>53</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="D19" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="C19" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="D19" s="30" t="n">
-        <v>90</v>
-      </c>
       <c r="E19" s="33" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G19" s="33" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H19" s="32" t="n"/>
-      <c r="I19" s="33" t="n">
-        <v>48</v>
+      <c r="I19" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="K19" s="31" t="n">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B20" s="29" t="n">
         <v>53</v>
       </c>
-      <c r="C20" s="33" t="n">
+      <c r="C20" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="G20" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="F20" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" s="33" t="n">
-        <v>8</v>
-      </c>
       <c r="H20" s="32" t="n"/>
-      <c r="I20" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="J20" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="K20" s="30" t="n">
-        <v>92</v>
+      <c r="I20" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" s="33" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B21" s="29" t="n">
+        <v>53</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>88</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C21" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="D21" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="F21" s="30" t="n">
-        <v>94</v>
+      <c r="F21" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="G21" s="33" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="H21" s="32" t="n"/>
-      <c r="I21" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="J21" s="33" t="n">
-        <v>27</v>
-      </c>
-      <c r="K21" s="33" t="n">
-        <v>48</v>
+      <c r="I21" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="J21" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="K21" s="31" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B22" s="29" t="n">
         <v>52</v>
       </c>
       <c r="C22" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="D22" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="E22" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="F22" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="G22" s="33" t="n">
-        <v>10</v>
+        <v>51</v>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>66</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>94</v>
       </c>
       <c r="H22" s="32" t="n"/>
-      <c r="I22" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="31" t="n">
-        <v>59</v>
-      </c>
-      <c r="K22" s="32" t="n">
-        <v>0</v>
+      <c r="I22" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="J22" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="30" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -3075,188 +3075,188 @@
         <v>4</v>
       </c>
       <c r="K23" s="33" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B24" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="F24" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="32" t="n"/>
+      <c r="I24" s="30" t="n">
         <v>86</v>
       </c>
-      <c r="D24" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="E24" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="F24" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="G24" s="33" t="n">
+      <c r="J24" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="K24" s="33" t="n">
         <v>47</v>
-      </c>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="J24" s="31" t="n">
-        <v>55</v>
-      </c>
-      <c r="K24" s="33" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B25" s="29" t="n">
         <v>49</v>
       </c>
-      <c r="C25" s="33" t="n">
+      <c r="C25" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="E25" s="31" t="n">
-        <v>66</v>
+      <c r="E25" s="33" t="n">
+        <v>8</v>
       </c>
       <c r="F25" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="G25" s="31" t="n">
-        <v>69</v>
+        <v>26</v>
+      </c>
+      <c r="G25" s="33" t="n">
+        <v>20</v>
       </c>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="J25" s="31" t="n">
-        <v>67</v>
+        <v>88</v>
+      </c>
+      <c r="J25" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="K25" s="33" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B26" s="29" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="D26" s="30" t="n">
-        <v>86</v>
+        <v>35</v>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>40</v>
       </c>
       <c r="E26" s="33" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F26" s="33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="J26" s="33" t="n">
-        <v>24</v>
+        <v>60</v>
+      </c>
+      <c r="J26" s="30" t="n">
+        <v>86</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B27" s="29" t="n">
         <v>48</v>
       </c>
-      <c r="C27" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="D27" s="31" t="n">
+      <c r="C27" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="E27" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="E27" s="33" t="n">
-        <v>2</v>
-      </c>
       <c r="F27" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="G27" s="30" t="n">
-        <v>94</v>
+        <v>14</v>
+      </c>
+      <c r="G27" s="31" t="n">
+        <v>65</v>
       </c>
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="J27" s="33" t="n">
-        <v>2</v>
+        <v>72</v>
+      </c>
+      <c r="J27" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="K27" s="33" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B28" s="29" t="n">
         <v>47</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="D28" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="F28" s="30" t="n">
-        <v>74</v>
+        <v>45</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="E28" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="31" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J28" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="K28" s="33" t="n">
-        <v>4</v>
+        <v>26</v>
+      </c>
+      <c r="K28" s="31" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B29" s="29" t="n">
@@ -3266,131 +3266,131 @@
         <v>16</v>
       </c>
       <c r="D29" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="E29" s="30" t="n">
-        <v>70</v>
+        <v>6</v>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="G29" s="33" t="n">
-        <v>43</v>
+        <v>72</v>
+      </c>
+      <c r="G29" s="30" t="n">
+        <v>76</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="31" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J29" s="33" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="K29" s="33" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B30" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="C30" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="D30" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="E30" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="F30" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="G30" s="30" t="n">
-        <v>80</v>
+        <v>47</v>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="E30" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="F30" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" s="33" t="n">
+        <v>47</v>
       </c>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="J30" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="K30" s="31" t="n">
-        <v>62</v>
+        <v>40</v>
+      </c>
+      <c r="J30" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="K30" s="30" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B31" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="C31" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="D31" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="E31" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="F31" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="G31" s="33" t="n">
-        <v>49</v>
+      <c r="C31" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <v>80</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="J31" s="33" t="n">
-        <v>47</v>
+        <v>22</v>
+      </c>
+      <c r="J31" s="31" t="n">
+        <v>52</v>
       </c>
       <c r="K31" s="31" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B32" s="29" t="n">
         <v>45</v>
       </c>
       <c r="C32" s="33" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D32" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="E32" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="F32" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="G32" s="30" t="n">
-        <v>71</v>
+        <v>16</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="G32" s="33" t="n">
+        <v>43</v>
       </c>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="J32" s="30" t="n">
-        <v>86</v>
+        <v>66</v>
+      </c>
+      <c r="J32" s="33" t="n">
+        <v>8</v>
       </c>
       <c r="K32" s="33" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
@@ -3412,20 +3412,20 @@
         <v>10</v>
       </c>
       <c r="F33" s="31" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G33" s="31" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H33" s="32" t="n"/>
       <c r="I33" s="31" t="n">
         <v>52</v>
       </c>
       <c r="J33" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="K33" s="33" t="n">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="K33" s="31" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="34">
@@ -3438,7 +3438,7 @@
         <v>44</v>
       </c>
       <c r="C34" s="30" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D34" s="33" t="n">
         <v>2</v>
@@ -3447,20 +3447,20 @@
         <v>0</v>
       </c>
       <c r="F34" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="G34" s="31" t="n">
-        <v>65</v>
+        <v>16</v>
+      </c>
+      <c r="G34" s="30" t="n">
+        <v>73</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="31" t="n">
         <v>58</v>
       </c>
       <c r="J34" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="K34" s="30" t="n">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="K34" s="31" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="35">
@@ -3501,36 +3501,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B36" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="C36" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="D36" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="E36" s="31" t="n">
-        <v>56</v>
-      </c>
-      <c r="F36" s="33" t="n">
-        <v>26</v>
+        <v>40</v>
+      </c>
+      <c r="C36" s="33" t="n">
+        <v>47</v>
+      </c>
+      <c r="D36" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="E36" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="G36" s="33" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="33" t="n">
-        <v>37</v>
+        <v>2</v>
+      </c>
+      <c r="J36" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="B37" s="29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="33" t="n">
         <v>20</v>
@@ -3552,7 +3552,7 @@
         <v>42</v>
       </c>
       <c r="F37" s="33" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G37" s="33" t="n">
         <v>45</v>
@@ -3562,255 +3562,255 @@
         <v>54</v>
       </c>
       <c r="J37" s="33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K37" s="33" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B38" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="C38" s="33" t="n">
-        <v>47</v>
-      </c>
-      <c r="D38" s="30" t="n">
-        <v>78</v>
+        <v>39</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="D38" s="33" t="n">
+        <v>46</v>
       </c>
       <c r="E38" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="F38" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="G38" s="33" t="n">
-        <v>37</v>
+        <v>22</v>
+      </c>
+      <c r="F38" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>63</v>
       </c>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="33" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J38" s="33" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="C39" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="33" t="n">
-        <v>12</v>
+        <v>39</v>
+      </c>
+      <c r="C39" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F39" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="G39" s="33" t="n">
-        <v>4</v>
+        <v>62</v>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>53</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="J39" s="30" t="n">
-        <v>92</v>
+        <v>10</v>
+      </c>
+      <c r="J39" s="33" t="n">
+        <v>42</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B40" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="C40" s="31" t="n">
-        <v>51</v>
+      <c r="C40" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="D40" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="E40" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="F40" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="G40" s="33" t="n">
         <v>22</v>
-      </c>
-      <c r="F40" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="G40" s="31" t="n">
-        <v>63</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="33" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J40" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="K40" s="33" t="n">
         <v>31</v>
-      </c>
-      <c r="K40" s="30" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B41" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="C41" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" s="31" t="n">
-        <v>62</v>
+      <c r="C41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>12</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F41" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="G41" s="31" t="n">
-        <v>53</v>
+        <v>66</v>
+      </c>
+      <c r="G41" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="J41" s="33" t="n">
-        <v>41</v>
-      </c>
-      <c r="K41" s="30" t="n">
-        <v>90</v>
+        <v>16</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="K41" s="31" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B42" s="29" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C42" s="31" t="n">
         <v>51</v>
       </c>
       <c r="D42" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="F42" s="30" t="n">
-        <v>76</v>
+        <v>32</v>
+      </c>
+      <c r="E42" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="F42" s="33" t="n">
+        <v>24</v>
       </c>
       <c r="G42" s="33" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H42" s="32" t="n"/>
-      <c r="I42" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="31" t="n">
-        <v>60</v>
+      <c r="I42" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="K42" s="30" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B43" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="C43" s="33" t="n">
+      <c r="C43" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="D43" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="33" t="n">
-        <v>14</v>
-      </c>
       <c r="E43" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="F43" s="31" t="n">
-        <v>52</v>
+        <v>98</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <v>74</v>
       </c>
       <c r="G43" s="33" t="n">
+        <v>39</v>
+      </c>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="33" t="n">
         <v>16</v>
-      </c>
-      <c r="H43" s="32" t="n"/>
-      <c r="I43" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="J43" s="30" t="n">
-        <v>73</v>
-      </c>
-      <c r="K43" s="33" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B44" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="C44" s="31" t="n">
-        <v>51</v>
+        <v>35</v>
+      </c>
+      <c r="C44" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="D44" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="E44" s="33" t="n">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="F44" s="33" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G44" s="33" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="33" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J44" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="K44" s="31" t="n">
-        <v>66</v>
+        <v>74</v>
+      </c>
+      <c r="K44" s="33" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="45">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B45" s="29" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C45" s="33" t="n">
         <v>8</v>
@@ -3832,7 +3832,7 @@
         <v>64</v>
       </c>
       <c r="F45" s="31" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G45" s="33" t="n">
         <v>12</v>
@@ -3842,10 +3842,10 @@
         <v>14</v>
       </c>
       <c r="J45" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="K45" s="30" t="n">
-        <v>76</v>
+        <v>20</v>
+      </c>
+      <c r="K45" s="33" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="B46" s="29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C46" s="33" t="n">
         <v>35</v>
@@ -3880,77 +3880,77 @@
         <v>98</v>
       </c>
       <c r="K46" s="33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C47" s="33" t="n">
         <v>24</v>
       </c>
       <c r="D47" s="33" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E47" s="33" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F47" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="G47" s="33" t="n">
-        <v>18</v>
+        <v>48</v>
+      </c>
+      <c r="G47" s="31" t="n">
+        <v>67</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="31" t="n">
-        <v>53</v>
-      </c>
-      <c r="K47" s="30" t="n">
-        <v>84</v>
+        <v>42</v>
+      </c>
+      <c r="J47" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" s="33" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B48" s="29" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C48" s="33" t="n">
         <v>24</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E48" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="F48" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="F48" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="G48" s="31" t="n">
-        <v>65</v>
+      <c r="G48" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="J48" s="33" t="n">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="J48" s="31" t="n">
+        <v>54</v>
       </c>
       <c r="K48" s="33" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="B49" s="29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49" s="33" t="n">
         <v>33</v>
@@ -3972,7 +3972,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G49" s="33" t="n">
         <v>33</v>
@@ -3984,8 +3984,8 @@
       <c r="J49" s="30" t="n">
         <v>94</v>
       </c>
-      <c r="K49" s="33" t="n">
-        <v>28</v>
+      <c r="K49" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="B50" s="29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C50" s="33" t="n">
         <v>14</v>
@@ -4007,7 +4007,7 @@
         <v>4</v>
       </c>
       <c r="F50" s="33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G50" s="33" t="n">
         <v>27</v>
@@ -4017,10 +4017,10 @@
         <v>28</v>
       </c>
       <c r="J50" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="K50" s="30" t="n">
-        <v>70</v>
+        <v>34</v>
+      </c>
+      <c r="K50" s="33" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="51">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="B51" s="29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51" s="33" t="n">
         <v>10</v>
@@ -4042,7 +4042,7 @@
         <v>38</v>
       </c>
       <c r="F51" s="33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G51" s="32" t="n">
         <v>0</v>
@@ -4052,10 +4052,10 @@
         <v>20</v>
       </c>
       <c r="J51" s="33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K51" s="31" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4175,7 +4175,7 @@
         <v>4.51</v>
       </c>
       <c r="F2" s="32" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="G2" s="32" t="n">
         <v>4.39</v>
@@ -4188,13 +4188,13 @@
         <v>38.82</v>
       </c>
       <c r="K2" s="32" t="n">
-        <v>5.68</v>
+        <v>7.46</v>
       </c>
       <c r="L2" s="32" t="n">
-        <v>13.21</v>
+        <v>4.55</v>
       </c>
       <c r="M2" s="32" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -4218,7 +4218,7 @@
         <v>3.15</v>
       </c>
       <c r="F3" s="32" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="G3" s="32" t="n">
         <v>4.76</v>
@@ -4231,13 +4231,13 @@
         <v>14.73</v>
       </c>
       <c r="K3" s="32" t="n">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="L3" s="32" t="n">
-        <v>-15.52</v>
+        <v>0</v>
       </c>
       <c r="M3" s="32" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -4261,10 +4261,10 @@
         <v>4.7</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="32" t="n">
@@ -4274,13 +4274,13 @@
         <v>20.14</v>
       </c>
       <c r="K4" s="32" t="n">
-        <v>8.15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L4" s="32" t="n">
-        <v>11.54</v>
+        <v>17.02</v>
       </c>
       <c r="M4" s="32" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>65 (A)</t>
+          <t>68 (A+)</t>
         </is>
       </c>
       <c r="C5" s="32" t="n">
@@ -4304,10 +4304,10 @@
         <v>1.62</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="H5" s="32" t="n"/>
       <c r="I5" s="32" t="n">
@@ -4317,148 +4317,148 @@
         <v>-8.94</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>6.09</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L5" s="32" t="n">
-        <v>9.09</v>
+        <v>12.77</v>
       </c>
       <c r="M5" s="32" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>65 (A)</t>
+          <t>67 (A)</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>64.7</v>
+        <v>60.33</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>-0.36</v>
+        <v>8.65</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>3.5</v>
+        <v>1.11</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>2.16</v>
+        <v>3.39</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="32" t="n">
-        <v>1.88</v>
+        <v>1.07</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>16.13</v>
+        <v>-10.55</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>9.109999999999999</v>
+        <v>6.52</v>
       </c>
       <c r="L6" s="32" t="n">
-        <v>21.05</v>
+        <v>4.84</v>
       </c>
       <c r="M6" s="32" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>66 (A)</t>
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>60.33</v>
+        <v>64.7</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>8.65</v>
+        <v>-0.36</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>1.88</v>
+        <v>3.37</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>3.39</v>
+        <v>2.16</v>
       </c>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="32" t="n">
-        <v>1.07</v>
+        <v>1.88</v>
       </c>
       <c r="J7" s="32" t="n">
-        <v>-10.55</v>
+        <v>16.13</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>5.74</v>
+        <v>10</v>
       </c>
       <c r="L7" s="32" t="n">
-        <v>4.65</v>
+        <v>30</v>
       </c>
       <c r="M7" s="32" t="n">
-        <v>90</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>63 (A)</t>
+          <t>62 (A-)</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>64.23999999999999</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>5.12</v>
+        <v>3.18</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>2.71</v>
+        <v>1.44</v>
       </c>
       <c r="G8" s="32" t="n">
-        <v>3.08</v>
+        <v>2.45</v>
       </c>
       <c r="H8" s="32" t="n"/>
       <c r="I8" s="32" t="n">
-        <v>0.29</v>
+        <v>0.73</v>
       </c>
       <c r="J8" s="32" t="n">
-        <v>-20.27</v>
+        <v>-29.44</v>
       </c>
       <c r="K8" s="32" t="n">
-        <v>6.8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L8" s="32" t="n">
-        <v>-2.04</v>
+        <v>20.45</v>
       </c>
       <c r="M8" s="32" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
@@ -4470,71 +4470,75 @@
         <v>3.3</v>
       </c>
       <c r="D9" s="32" t="n">
-        <v>64.56999999999999</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>8.27</v>
+        <v>5.12</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="G9" s="32" t="n"/>
+        <v>2.38</v>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>3.04</v>
+      </c>
       <c r="H9" s="32" t="n"/>
       <c r="I9" s="32" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J9" s="32" t="n"/>
+        <v>0.29</v>
+      </c>
+      <c r="J9" s="32" t="n">
+        <v>-20.27</v>
+      </c>
       <c r="K9" s="32" t="n">
-        <v>6.66</v>
+        <v>5.86</v>
       </c>
       <c r="L9" s="32" t="n">
-        <v>-3.45</v>
+        <v>-11.36</v>
       </c>
       <c r="M9" s="32" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>62 (A-)</t>
+          <t>61 (A-)</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>60.56</v>
+        <v>66.86</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>-0.12</v>
+        <v>5.1</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>3.17</v>
+        <v>3.68</v>
       </c>
       <c r="G10" s="32" t="n">
-        <v>1.47</v>
+        <v>3.57</v>
       </c>
       <c r="H10" s="32" t="n"/>
       <c r="I10" s="32" t="n">
-        <v>0.61</v>
+        <v>0.11</v>
       </c>
       <c r="J10" s="32" t="n">
-        <v>55.25</v>
+        <v>-10.26</v>
       </c>
       <c r="K10" s="32" t="n">
-        <v>7.14</v>
+        <v>8.59</v>
       </c>
       <c r="L10" s="32" t="n">
-        <v>-1.41</v>
+        <v>15.91</v>
       </c>
       <c r="M10" s="32" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -4558,10 +4562,10 @@
         <v>0.86</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>2.99</v>
+        <v>2.63</v>
       </c>
       <c r="G11" s="32" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="32" t="n">
@@ -4571,56 +4575,56 @@
         <v>8.67</v>
       </c>
       <c r="K11" s="32" t="n">
-        <v>8.220000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="L11" s="32" t="n">
-        <v>12.24</v>
+        <v>10.81</v>
       </c>
       <c r="M11" s="32" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>59 (A-)</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D12" s="32" t="n">
-        <v>73.98999999999999</v>
+        <v>66.34</v>
       </c>
       <c r="E12" s="32" t="n">
-        <v>3.18</v>
+        <v>4.52</v>
       </c>
       <c r="F12" s="32" t="n">
-        <v>1.44</v>
+        <v>2.19</v>
       </c>
       <c r="G12" s="32" t="n">
-        <v>2.45</v>
+        <v>3.59</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="32" t="n">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="J12" s="32" t="n">
-        <v>-29.44</v>
+        <v>16.86</v>
       </c>
       <c r="K12" s="32" t="n">
-        <v>5.48</v>
+        <v>7.59</v>
       </c>
       <c r="L12" s="32" t="n">
-        <v>15.15</v>
+        <v>5.88</v>
       </c>
       <c r="M12" s="32" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -4631,7 +4635,7 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>59 (A-)</t>
         </is>
       </c>
       <c r="C13" s="32" t="n">
@@ -4644,7 +4648,7 @@
         <v>6.57</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G13" s="32" t="n">
         <v>2.78</v>
@@ -4657,10 +4661,10 @@
         <v>-15.96</v>
       </c>
       <c r="K13" s="32" t="n">
-        <v>5.64</v>
+        <v>7.86</v>
       </c>
       <c r="L13" s="32" t="n">
-        <v>-13.64</v>
+        <v>8.57</v>
       </c>
       <c r="M13" s="32" t="n">
         <v>38</v>
@@ -4669,7 +4673,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
@@ -4678,36 +4682,32 @@
         </is>
       </c>
       <c r="C14" s="32" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="D14" s="32" t="n">
-        <v>60.48</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E14" s="32" t="n">
-        <v>6.16</v>
+        <v>8.27</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>0.4</v>
+        <v>1.03</v>
       </c>
       <c r="G14" s="32" t="n">
-        <v>0.61</v>
+        <v>3.55</v>
       </c>
       <c r="H14" s="32" t="n"/>
       <c r="I14" s="32" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="J14" s="32" t="n">
-        <v>19.69</v>
+        <v>-30.9</v>
       </c>
       <c r="K14" s="32" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="L14" s="32" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="M14" s="32" t="n">
-        <v>79</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L14" s="32" t="n"/>
+      <c r="M14" s="32" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4730,7 +4730,7 @@
         <v>7.12</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="G15" s="32" t="n">
         <v>1.9</v>
@@ -4743,19 +4743,19 @@
         <v>41.11</v>
       </c>
       <c r="K15" s="32" t="n">
-        <v>5.54</v>
+        <v>5.96</v>
       </c>
       <c r="L15" s="32" t="n">
-        <v>12.16</v>
+        <v>10.45</v>
       </c>
       <c r="M15" s="32" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
@@ -4763,169 +4763,169 @@
           <t>56 (B+)</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
+      <c r="C16" s="32" t="n">
+        <v>4</v>
+      </c>
       <c r="D16" s="32" t="n">
-        <v>66.34</v>
+        <v>60.48</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>4.52</v>
+        <v>6.16</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>2.08</v>
+        <v>0.48</v>
       </c>
       <c r="G16" s="32" t="n">
-        <v>3.59</v>
+        <v>0.61</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="32" t="n">
-        <v>0.87</v>
+        <v>0.06</v>
       </c>
       <c r="J16" s="32" t="n">
-        <v>16.86</v>
+        <v>19.69</v>
       </c>
       <c r="K16" s="32" t="n">
-        <v>6.82</v>
+        <v>6.31</v>
       </c>
       <c r="L16" s="32" t="n">
-        <v>-1.79</v>
+        <v>6.9</v>
       </c>
       <c r="M16" s="32" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>56 (B+)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C17" s="32" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="32" t="n">
-        <v>66.86</v>
+        <v>63.96</v>
       </c>
       <c r="E17" s="32" t="n">
-        <v>5.1</v>
+        <v>2.21</v>
       </c>
       <c r="F17" s="32" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="G17" s="32" t="n">
-        <v>3.55</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="G17" s="32" t="n"/>
       <c r="H17" s="32" t="n"/>
       <c r="I17" s="32" t="n">
-        <v>0.11</v>
+        <v>1.16</v>
       </c>
       <c r="J17" s="32" t="n">
-        <v>-10.26</v>
+        <v>4.14</v>
       </c>
       <c r="K17" s="32" t="n">
-        <v>5.41</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L17" s="32" t="n">
-        <v>15.87</v>
+        <v>10.26</v>
       </c>
       <c r="M17" s="32" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>55 (B+)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C18" s="32" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D18" s="32" t="n">
-        <v>63.96</v>
+        <v>69.61</v>
       </c>
       <c r="E18" s="32" t="n">
-        <v>2.21</v>
+        <v>3.1</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>3.07</v>
+        <v>1.43</v>
       </c>
       <c r="G18" s="32" t="n">
-        <v>3.57</v>
+        <v>2.27</v>
       </c>
       <c r="H18" s="32" t="n"/>
       <c r="I18" s="32" t="n">
-        <v>1.16</v>
+        <v>0.33</v>
       </c>
       <c r="J18" s="32" t="n">
-        <v>4.14</v>
+        <v>-20.96</v>
       </c>
       <c r="K18" s="32" t="n">
-        <v>7.19</v>
+        <v>7.67</v>
       </c>
       <c r="L18" s="32" t="n">
-        <v>1.92</v>
+        <v>6.67</v>
       </c>
       <c r="M18" s="32" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C19" s="32" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D19" s="32" t="n">
-        <v>69.61</v>
+        <v>64.52</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="G19" s="32" t="n">
-        <v>2.27</v>
+        <v>0.84</v>
       </c>
       <c r="H19" s="32" t="n"/>
       <c r="I19" s="32" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="J19" s="32" t="n">
-        <v>-20.96</v>
+        <v>-12.89</v>
       </c>
       <c r="K19" s="32" t="n">
-        <v>7.18</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L19" s="32" t="n">
-        <v>1.79</v>
+        <v>11.11</v>
       </c>
       <c r="M19" s="32" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
@@ -4934,84 +4934,84 @@
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>63.61</v>
+        <v>67.91</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>5.33</v>
+        <v>6.8</v>
       </c>
       <c r="F20" s="32" t="n">
-        <v>5.59</v>
+        <v>1.41</v>
       </c>
       <c r="G20" s="32" t="n">
-        <v>0.98</v>
+        <v>1.18</v>
       </c>
       <c r="H20" s="32" t="n"/>
       <c r="I20" s="32" t="n">
-        <v>1.83</v>
+        <v>-0.31</v>
       </c>
       <c r="J20" s="32" t="n">
-        <v>20.24</v>
+        <v>5.41</v>
       </c>
       <c r="K20" s="32" t="n">
-        <v>8.279999999999999</v>
+        <v>5.82</v>
       </c>
       <c r="L20" s="32" t="n">
-        <v>12.82</v>
+        <v>-11.76</v>
       </c>
       <c r="M20" s="32" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C21" s="32" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>64.52</v>
+        <v>62.74</v>
       </c>
       <c r="E21" s="32" t="n">
-        <v>2.61</v>
+        <v>3.37</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>1.17</v>
+        <v>2.87</v>
       </c>
       <c r="G21" s="32" t="n">
-        <v>0.84</v>
+        <v>2.43</v>
       </c>
       <c r="H21" s="32" t="n"/>
       <c r="I21" s="32" t="n">
-        <v>0.43</v>
+        <v>-0.06</v>
       </c>
       <c r="J21" s="32" t="n">
-        <v>-12.89</v>
+        <v>2.98</v>
       </c>
       <c r="K21" s="32" t="n">
-        <v>7</v>
+        <v>7.98</v>
       </c>
       <c r="L21" s="32" t="n">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="M21" s="32" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
@@ -5020,35 +5020,35 @@
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>67.91</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>6.8</v>
+        <v>-1.52</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>1.49</v>
+        <v>3.46</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>1.22</v>
+        <v>4.12</v>
       </c>
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="32" t="n">
-        <v>-0.31</v>
+        <v>2.69</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>5.41</v>
+        <v>-39.5</v>
       </c>
       <c r="K22" s="32" t="n">
-        <v>4.6</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L22" s="32" t="n">
-        <v>-24</v>
+        <v>13.95</v>
       </c>
       <c r="M22" s="32" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -5072,7 +5072,7 @@
         <v>1.78</v>
       </c>
       <c r="F23" s="32" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G23" s="32" t="n">
         <v>1.27</v>
@@ -5085,19 +5085,19 @@
         <v>-37.55</v>
       </c>
       <c r="K23" s="32" t="n">
-        <v>6.61</v>
+        <v>6.83</v>
       </c>
       <c r="L23" s="32" t="n">
-        <v>3.95</v>
+        <v>1.67</v>
       </c>
       <c r="M23" s="32" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
@@ -5106,41 +5106,41 @@
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="D24" s="32" t="n">
-        <v>62.74</v>
+        <v>63.61</v>
       </c>
       <c r="E24" s="32" t="n">
-        <v>3.37</v>
+        <v>5.33</v>
       </c>
       <c r="F24" s="32" t="n">
-        <v>3.32</v>
+        <v>5.59</v>
       </c>
       <c r="G24" s="32" t="n">
-        <v>2.37</v>
+        <v>0.98</v>
       </c>
       <c r="H24" s="32" t="n"/>
       <c r="I24" s="32" t="n">
-        <v>-0.06</v>
+        <v>1.83</v>
       </c>
       <c r="J24" s="32" t="n">
-        <v>2.98</v>
+        <v>20.24</v>
       </c>
       <c r="K24" s="32" t="n">
-        <v>6.8</v>
+        <v>7.71</v>
       </c>
       <c r="L24" s="32" t="n">
-        <v>-1.96</v>
+        <v>7.14</v>
       </c>
       <c r="M24" s="32" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B25" s="34" t="inlineStr">
@@ -5148,85 +5148,83 @@
           <t>49 (B-)</t>
         </is>
       </c>
-      <c r="C25" s="32" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="C25" s="32" t="n"/>
       <c r="D25" s="32" t="n">
-        <v>63.3</v>
+        <v>60.56</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>4.84</v>
+        <v>-0.12</v>
       </c>
       <c r="F25" s="32" t="n">
-        <v>4.78</v>
+        <v>3.72</v>
       </c>
       <c r="G25" s="32" t="n">
-        <v>3.04</v>
+        <v>1.47</v>
       </c>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="32" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="J25" s="32" t="n">
-        <v>14.97</v>
+        <v>55.25</v>
       </c>
       <c r="K25" s="32" t="n">
-        <v>7</v>
+        <v>7.37</v>
       </c>
       <c r="L25" s="32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M25" s="32" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C26" s="32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D26" s="32" t="n">
-        <v>68.47</v>
+        <v>63.89</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>1.42</v>
+        <v>3.13</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>5.47</v>
+        <v>5.56</v>
       </c>
       <c r="G26" s="32" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="32" t="n">
-        <v>0.73</v>
+        <v>0.51</v>
       </c>
       <c r="J26" s="32" t="n">
-        <v>-14.97</v>
+        <v>55.17</v>
       </c>
       <c r="K26" s="32" t="n">
-        <v>9.73</v>
+        <v>8.58</v>
       </c>
       <c r="L26" s="32" t="n">
-        <v>27.27</v>
+        <v>15.79</v>
       </c>
       <c r="M26" s="32" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B27" s="34" t="inlineStr">
@@ -5235,41 +5233,41 @@
         </is>
       </c>
       <c r="C27" s="32" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D27" s="32" t="n">
-        <v>65.43000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="E27" s="32" t="n">
-        <v>-1.52</v>
+        <v>4.84</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>3.62</v>
+        <v>5.01</v>
       </c>
       <c r="G27" s="32" t="n">
-        <v>4.16</v>
+        <v>3</v>
       </c>
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="32" t="n">
-        <v>2.69</v>
+        <v>0.48</v>
       </c>
       <c r="J27" s="32" t="n">
-        <v>-39.5</v>
+        <v>14.97</v>
       </c>
       <c r="K27" s="32" t="n">
-        <v>4.68</v>
+        <v>7.62</v>
       </c>
       <c r="L27" s="32" t="n">
-        <v>23.21</v>
+        <v>6.25</v>
       </c>
       <c r="M27" s="32" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B28" s="34" t="inlineStr">
@@ -5278,41 +5276,41 @@
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="D28" s="32" t="n">
-        <v>59.95</v>
+        <v>68.47</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>4.86</v>
+        <v>1.42</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>1.87</v>
+        <v>5.25</v>
       </c>
       <c r="G28" s="32" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="32" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="J28" s="32" t="n">
-        <v>-8.56</v>
+        <v>-14.97</v>
       </c>
       <c r="K28" s="32" t="n">
-        <v>4.88</v>
+        <v>8</v>
       </c>
       <c r="L28" s="32" t="n">
-        <v>21.21</v>
+        <v>20</v>
       </c>
       <c r="M28" s="32" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B29" s="34" t="inlineStr">
@@ -5324,81 +5322,81 @@
         <v>4.6</v>
       </c>
       <c r="D29" s="32" t="n">
-        <v>60.38</v>
+        <v>59.95</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="G29" s="32" t="n">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="32" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="J29" s="32" t="n">
-        <v>-32.7</v>
+        <v>-8.56</v>
       </c>
       <c r="K29" s="32" t="n">
-        <v>6.09</v>
+        <v>5.42</v>
       </c>
       <c r="L29" s="32" t="n">
-        <v>9.09</v>
+        <v>15.79</v>
       </c>
       <c r="M29" s="32" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D30" s="32" t="n">
-        <v>68.23999999999999</v>
+        <v>65.27</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>7.63</v>
+        <v>0.66</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="G30" s="32" t="n">
-        <v>3.29</v>
+        <v>2.39</v>
       </c>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="32" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="J30" s="32" t="n">
-        <v>-0.7</v>
+        <v>-6.99</v>
       </c>
       <c r="K30" s="32" t="n">
-        <v>7.29</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L30" s="32" t="n">
-        <v>2.86</v>
+        <v>17.95</v>
       </c>
       <c r="M30" s="32" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B31" s="34" t="inlineStr">
@@ -5407,41 +5405,41 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D31" s="32" t="n">
-        <v>65.27</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>0.66</v>
+        <v>7.63</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>4.24</v>
+        <v>2.86</v>
       </c>
       <c r="G31" s="32" t="n">
-        <v>2.39</v>
+        <v>3.29</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="32" t="n">
-        <v>-0.01</v>
+        <v>-0.15</v>
       </c>
       <c r="J31" s="32" t="n">
-        <v>-6.99</v>
+        <v>-0.7</v>
       </c>
       <c r="K31" s="32" t="n">
-        <v>7.38</v>
+        <v>7.77</v>
       </c>
       <c r="L31" s="32" t="n">
-        <v>3.77</v>
+        <v>9.68</v>
       </c>
       <c r="M31" s="32" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
@@ -5450,35 +5448,35 @@
         </is>
       </c>
       <c r="C32" s="32" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="D32" s="32" t="n">
-        <v>63.89</v>
+        <v>60.38</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>3.13</v>
+        <v>5</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>5.76</v>
+        <v>1.44</v>
       </c>
       <c r="G32" s="32" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="32" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="J32" s="32" t="n">
-        <v>55.17</v>
+        <v>-32.7</v>
       </c>
       <c r="K32" s="32" t="n">
-        <v>5.57</v>
+        <v>7.17</v>
       </c>
       <c r="L32" s="32" t="n">
-        <v>14.29</v>
+        <v>1.75</v>
       </c>
       <c r="M32" s="32" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
@@ -5489,7 +5487,7 @@
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>44 (B-)</t>
         </is>
       </c>
       <c r="C33" s="32" t="n">
@@ -5502,7 +5500,7 @@
         <v>0.03</v>
       </c>
       <c r="F33" s="32" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="G33" s="32" t="n">
         <v>2.61</v>
@@ -5515,13 +5513,13 @@
         <v>-12.25</v>
       </c>
       <c r="K33" s="32" t="n">
-        <v>6.76</v>
+        <v>7.91</v>
       </c>
       <c r="L33" s="32" t="n">
-        <v>-2.44</v>
+        <v>9.09</v>
       </c>
       <c r="M33" s="32" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
@@ -5548,7 +5546,7 @@
         <v>5</v>
       </c>
       <c r="G34" s="32" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="32" t="n">
@@ -5588,7 +5586,7 @@
         <v>3.63</v>
       </c>
       <c r="F35" s="32" t="n">
-        <v>7.01</v>
+        <v>7.35</v>
       </c>
       <c r="G35" s="32" t="n">
         <v>2.78</v>
@@ -5601,56 +5599,56 @@
         <v>144.37</v>
       </c>
       <c r="K35" s="32" t="n">
-        <v>9.56</v>
+        <v>10</v>
       </c>
       <c r="L35" s="32" t="n">
-        <v>25.64</v>
+        <v>33.33</v>
       </c>
       <c r="M35" s="32" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C36" s="32" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="D36" s="32" t="n">
-        <v>63.19</v>
+        <v>67.37</v>
       </c>
       <c r="E36" s="32" t="n">
-        <v>3.73</v>
+        <v>1.37</v>
       </c>
       <c r="F36" s="32" t="n">
-        <v>3.7</v>
+        <v>2.06</v>
       </c>
       <c r="G36" s="32" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="n">
-        <v>-0.91</v>
+        <v>-1.63</v>
       </c>
       <c r="J36" s="32" t="n">
-        <v>-10.47</v>
+        <v>-3.97</v>
       </c>
       <c r="K36" s="32" t="n">
-        <v>7.83</v>
+        <v>8.5</v>
       </c>
       <c r="L36" s="32" t="n">
-        <v>8.33</v>
+        <v>25</v>
       </c>
       <c r="M36" s="32" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -5661,7 +5659,7 @@
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C37" s="32" t="n">
@@ -5674,10 +5672,10 @@
         <v>2.84</v>
       </c>
       <c r="F37" s="32" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="G37" s="32" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="32" t="n">
@@ -5687,105 +5685,105 @@
         <v>-27.41</v>
       </c>
       <c r="K37" s="32" t="n">
-        <v>6.3</v>
+        <v>6.72</v>
       </c>
       <c r="L37" s="32" t="n">
-        <v>-6.98</v>
+        <v>-2.78</v>
       </c>
       <c r="M37" s="32" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D38" s="32" t="n">
-        <v>67.37</v>
+        <v>64.19</v>
       </c>
       <c r="E38" s="32" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="F38" s="32" t="n">
-        <v>1.9</v>
+        <v>3.21</v>
       </c>
       <c r="G38" s="32" t="n">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="32" t="n">
-        <v>-1.63</v>
+        <v>-0.14</v>
       </c>
       <c r="J38" s="32" t="n">
-        <v>-3.97</v>
+        <v>-11.14</v>
       </c>
       <c r="K38" s="32" t="n">
-        <v>8.18</v>
+        <v>9.76</v>
       </c>
       <c r="L38" s="32" t="n">
-        <v>11.76</v>
+        <v>27.59</v>
       </c>
       <c r="M38" s="32" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C39" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="D39" s="32" t="n">
-        <v>60.33</v>
+        <v>65.02</v>
       </c>
       <c r="E39" s="32" t="n">
-        <v>7.6</v>
+        <v>6.71</v>
       </c>
       <c r="F39" s="32" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="G39" s="32" t="n">
-        <v>0.8</v>
+        <v>2.55</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="32" t="n">
-        <v>0.22</v>
+        <v>-0.76</v>
       </c>
       <c r="J39" s="32" t="n">
-        <v>61.97</v>
+        <v>-9.83</v>
       </c>
       <c r="K39" s="32" t="n">
-        <v>8.039999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="L39" s="32" t="n">
-        <v>10.42</v>
+        <v>18.18</v>
       </c>
       <c r="M39" s="32" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
@@ -5794,41 +5792,41 @@
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D40" s="32" t="n">
-        <v>64.19</v>
+        <v>63.19</v>
       </c>
       <c r="E40" s="32" t="n">
-        <v>1.22</v>
+        <v>3.73</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>3.16</v>
+        <v>4.27</v>
       </c>
       <c r="G40" s="32" t="n">
-        <v>2.94</v>
+        <v>1.59</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="32" t="n">
-        <v>-0.14</v>
+        <v>-0.91</v>
       </c>
       <c r="J40" s="32" t="n">
-        <v>-11.14</v>
+        <v>-10.47</v>
       </c>
       <c r="K40" s="32" t="n">
-        <v>7.98</v>
+        <v>7.25</v>
       </c>
       <c r="L40" s="32" t="n">
-        <v>9.76</v>
+        <v>6.45</v>
       </c>
       <c r="M40" s="32" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
@@ -5837,84 +5835,84 @@
         </is>
       </c>
       <c r="C41" s="32" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D41" s="32" t="n">
-        <v>65.02</v>
+        <v>60.33</v>
       </c>
       <c r="E41" s="32" t="n">
-        <v>6.71</v>
+        <v>7.6</v>
       </c>
       <c r="F41" s="32" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="G41" s="32" t="n">
-        <v>2.49</v>
+        <v>0.8</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="32" t="n">
-        <v>-0.76</v>
+        <v>0.22</v>
       </c>
       <c r="J41" s="32" t="n">
-        <v>-9.83</v>
+        <v>61.97</v>
       </c>
       <c r="K41" s="32" t="n">
-        <v>8.279999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="L41" s="32" t="n">
-        <v>12.77</v>
+        <v>10.87</v>
       </c>
       <c r="M41" s="32" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>37 (C)</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
         <v>3.6</v>
       </c>
       <c r="D42" s="32" t="n">
-        <v>58.99</v>
+        <v>63.08</v>
       </c>
       <c r="E42" s="32" t="n">
-        <v>10.22</v>
+        <v>1.53</v>
       </c>
       <c r="F42" s="32" t="n">
-        <v>1.57</v>
+        <v>3.72</v>
       </c>
       <c r="G42" s="32" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="32" t="n">
-        <v>-1.34</v>
+        <v>-0.52</v>
       </c>
       <c r="J42" s="32" t="n">
-        <v>-46.79</v>
+        <v>57.47</v>
       </c>
       <c r="K42" s="32" t="n">
-        <v>7.26</v>
+        <v>9.16</v>
       </c>
       <c r="L42" s="32" t="n">
-        <v>2.56</v>
+        <v>21.62</v>
       </c>
       <c r="M42" s="32" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B43" s="34" t="inlineStr">
@@ -5923,78 +5921,78 @@
         </is>
       </c>
       <c r="C43" s="32" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="D43" s="32" t="n">
-        <v>60.37</v>
+        <v>58.99</v>
       </c>
       <c r="E43" s="32" t="n">
-        <v>7.54</v>
+        <v>10.22</v>
       </c>
       <c r="F43" s="32" t="n">
-        <v>2.93</v>
+        <v>1.53</v>
       </c>
       <c r="G43" s="32" t="n">
-        <v>1.33</v>
+        <v>2.24</v>
       </c>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="32" t="n">
-        <v>0.18</v>
+        <v>-1.34</v>
       </c>
       <c r="J43" s="32" t="n">
-        <v>18.04</v>
+        <v>-46.79</v>
       </c>
       <c r="K43" s="32" t="n">
-        <v>7</v>
+        <v>6.47</v>
       </c>
       <c r="L43" s="32" t="n">
-        <v>0</v>
+        <v>-5.26</v>
       </c>
       <c r="M43" s="32" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>35 (C)</t>
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="D44" s="32" t="n">
-        <v>63.08</v>
+        <v>60.37</v>
       </c>
       <c r="E44" s="32" t="n">
-        <v>1.53</v>
+        <v>7.54</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>3.69</v>
+        <v>2.89</v>
       </c>
       <c r="G44" s="32" t="n">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="32" t="n">
-        <v>-0.52</v>
+        <v>0.18</v>
       </c>
       <c r="J44" s="32" t="n">
-        <v>57.47</v>
+        <v>18.04</v>
       </c>
       <c r="K44" s="32" t="n">
-        <v>7.4</v>
+        <v>7.59</v>
       </c>
       <c r="L44" s="32" t="n">
-        <v>4</v>
+        <v>5.88</v>
       </c>
       <c r="M44" s="32" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45">
@@ -6005,7 +6003,7 @@
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>35 (C)</t>
+          <t>33 (C)</t>
         </is>
       </c>
       <c r="C45" s="32" t="n">
@@ -6018,7 +6016,7 @@
         <v>4.78</v>
       </c>
       <c r="F45" s="32" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G45" s="32" t="n">
         <v>1.24</v>
@@ -6031,13 +6029,13 @@
         <v>-18.14</v>
       </c>
       <c r="K45" s="32" t="n">
-        <v>7.93</v>
+        <v>6.61</v>
       </c>
       <c r="L45" s="32" t="n">
-        <v>-9.33</v>
+        <v>-3.92</v>
       </c>
       <c r="M45" s="32" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
@@ -6048,7 +6046,7 @@
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>33 (C)</t>
         </is>
       </c>
       <c r="C46" s="32" t="n">
@@ -6061,7 +6059,7 @@
         <v>0.59</v>
       </c>
       <c r="F46" s="32" t="n">
-        <v>6.96</v>
+        <v>6.03</v>
       </c>
       <c r="G46" s="32" t="n">
         <v>2.02</v>
@@ -6074,99 +6072,99 @@
         <v>195.09</v>
       </c>
       <c r="K46" s="32" t="n">
-        <v>5.05</v>
+        <v>5.71</v>
       </c>
       <c r="L46" s="32" t="n">
-        <v>4.55</v>
+        <v>9.09</v>
       </c>
       <c r="M46" s="32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>32 (C-)</t>
+          <t>30 (C-)</t>
         </is>
       </c>
       <c r="C47" s="32" t="n">
         <v>4.4</v>
       </c>
       <c r="D47" s="32" t="n">
-        <v>62.01</v>
+        <v>63.98</v>
       </c>
       <c r="E47" s="32" t="n">
-        <v>2.43</v>
+        <v>0.37</v>
       </c>
       <c r="F47" s="32" t="n">
-        <v>5.24</v>
+        <v>2.88</v>
       </c>
       <c r="G47" s="32" t="n">
-        <v>1.37</v>
+        <v>3.02</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="32" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="J47" s="32" t="n">
-        <v>-0.37</v>
+        <v>-35.64</v>
       </c>
       <c r="K47" s="32" t="n">
-        <v>8.18</v>
+        <v>5.83</v>
       </c>
       <c r="L47" s="32" t="n">
-        <v>11.76</v>
+        <v>11.67</v>
       </c>
       <c r="M47" s="32" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>31 (C-)</t>
+          <t>29 (C-)</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
         <v>4.4</v>
       </c>
       <c r="D48" s="32" t="n">
-        <v>63.98</v>
+        <v>62.01</v>
       </c>
       <c r="E48" s="32" t="n">
-        <v>0.37</v>
+        <v>2.43</v>
       </c>
       <c r="F48" s="32" t="n">
-        <v>3.06</v>
+        <v>5.21</v>
       </c>
       <c r="G48" s="32" t="n">
-        <v>3.02</v>
+        <v>1.37</v>
       </c>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="32" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="J48" s="32" t="n">
-        <v>-35.64</v>
+        <v>-0.37</v>
       </c>
       <c r="K48" s="32" t="n">
-        <v>5.76</v>
+        <v>7.56</v>
       </c>
       <c r="L48" s="32" t="n">
-        <v>10.81</v>
+        <v>5.56</v>
       </c>
       <c r="M48" s="32" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
@@ -6177,7 +6175,7 @@
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>29 (C-)</t>
+          <t>28 (C-)</t>
         </is>
       </c>
       <c r="C49" s="32" t="n">
@@ -6190,7 +6188,7 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="32" t="n">
-        <v>5.62</v>
+        <v>5.79</v>
       </c>
       <c r="G49" s="32" t="n">
         <v>2.14</v>
@@ -6203,13 +6201,13 @@
         <v>86.01000000000001</v>
       </c>
       <c r="K49" s="32" t="n">
-        <v>6</v>
+        <v>5.15</v>
       </c>
       <c r="L49" s="32" t="n">
-        <v>0</v>
+        <v>-6.45</v>
       </c>
       <c r="M49" s="32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -6220,7 +6218,7 @@
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>23 (D)</t>
+          <t>22 (D)</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
@@ -6233,10 +6231,10 @@
         <v>-1.13</v>
       </c>
       <c r="F50" s="32" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="G50" s="32" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="32" t="n">
@@ -6246,13 +6244,13 @@
         <v>-10.94</v>
       </c>
       <c r="K50" s="32" t="n">
-        <v>7.77</v>
+        <v>7.71</v>
       </c>
       <c r="L50" s="32" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="M50" s="32" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -6263,7 +6261,7 @@
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>22 (D)</t>
+          <t>21 (D)</t>
         </is>
       </c>
       <c r="C51" s="32" t="n">
@@ -6276,7 +6274,7 @@
         <v>2.48</v>
       </c>
       <c r="F51" s="32" t="n">
-        <v>3.72</v>
+        <v>4.08</v>
       </c>
       <c r="G51" s="32" t="n">
         <v>0.12</v>
@@ -6289,13 +6287,13 @@
         <v>-15.51</v>
       </c>
       <c r="K51" s="32" t="n">
-        <v>7.51</v>
+        <v>7.83</v>
       </c>
       <c r="L51" s="32" t="n">
-        <v>5.13</v>
+        <v>8.33</v>
       </c>
       <c r="M51" s="32" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6389,7 @@
         </is>
       </c>
       <c r="D2" s="14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
@@ -6399,7 +6397,7 @@
         </is>
       </c>
       <c r="F2" s="14" t="n">
-        <v>48.7</v>
+        <v>48.2</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>4.5</v>
@@ -6411,7 +6409,7 @@
         <v>4.84</v>
       </c>
       <c r="J2" s="14" t="n">
-        <v>4.78</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="3">
@@ -6429,7 +6427,7 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
@@ -6437,7 +6435,7 @@
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>52.5</v>
+        <v>50.1</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>4.8</v>
@@ -6467,7 +6465,7 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
@@ -6475,7 +6473,7 @@
         </is>
       </c>
       <c r="F4" s="17" t="n">
-        <v>39.9</v>
+        <v>39</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>4.5</v>
@@ -6487,7 +6485,7 @@
         <v>2.84</v>
       </c>
       <c r="J4" s="17" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="5">
@@ -6505,7 +6503,7 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
@@ -6513,7 +6511,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>53.6</v>
+        <v>53</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>3.6</v>
@@ -6525,7 +6523,7 @@
         <v>3.1</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="6">
@@ -6543,7 +6541,7 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
@@ -6551,7 +6549,7 @@
         </is>
       </c>
       <c r="F6" s="11" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>4.2</v>
@@ -6563,7 +6561,7 @@
         <v>2.61</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="7">
@@ -6589,7 +6587,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>3.5</v>
@@ -6601,7 +6599,7 @@
         <v>7.12</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="8">
@@ -6627,7 +6625,7 @@
         </is>
       </c>
       <c r="F8" s="17" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>3.8</v>
@@ -6639,119 +6637,121 @@
         <v>1.37</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Phoenix-Mesa-Chandler</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>64.56999999999999</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Philadelphia-Camden-Wilmington</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>63.96</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Phoenix-Mesa-Chandler</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="F11" s="5" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>66.34</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="5" t="n">
         <v>4.52</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>2.08</v>
+      <c r="J11" s="5" t="n">
+        <v>2.19</v>
       </c>
     </row>
     <row r="12">
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>48.4</v>
+        <v>46.8</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>3.9</v>
@@ -6789,7 +6789,7 @@
         <v>1.42</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="13">
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>36.4</v>
+        <v>35.3</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>5.1</v>
@@ -6827,7 +6827,7 @@
         <v>7.54</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="14">
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="D14" s="23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>29.3</v>
+        <v>27.7</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>4.1</v>
@@ -6865,7 +6865,7 @@
         <v>0.49</v>
       </c>
       <c r="J14" s="23" t="n">
-        <v>5.62</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="15">
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="D15" s="26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="F15" s="26" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="G15" s="26" t="n">
         <v>4.7</v>
@@ -6903,7 +6903,7 @@
         <v>-1.13</v>
       </c>
       <c r="J15" s="26" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="16">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>46</v>
+        <v>45.3</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>5</v>
@@ -6941,45 +6941,45 @@
         <v>7.63</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G17" s="17" t="n">
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G17" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="14" t="n">
         <v>69.03</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="J17" s="17" t="n">
-        <v>2.83</v>
+      <c r="J17" s="14" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="18">
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>4.6</v>
@@ -7017,7 +7017,7 @@
         <v>4.86</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="19">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="D19" s="23" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="F19" s="23" t="n">
-        <v>31.7</v>
+        <v>29.4</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>4.4</v>
@@ -7055,45 +7055,45 @@
         <v>2.43</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="G20" s="8" t="n">
+      <c r="D20" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="5" t="n">
         <v>70.39</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="5" t="n">
         <v>6.57</v>
       </c>
-      <c r="J20" s="8" t="n">
-        <v>1.48</v>
+      <c r="J20" s="5" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="21">
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="D21" s="23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="F21" s="23" t="n">
-        <v>30.9</v>
+        <v>30.4</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>4.4</v>
@@ -7131,45 +7131,45 @@
         <v>0.37</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="G22" s="14" t="n">
+      <c r="D22" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="G22" s="11" t="n">
         <v>3.6</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="11" t="n">
         <v>65.43000000000001</v>
       </c>
-      <c r="I22" s="14" t="n">
+      <c r="I22" s="11" t="n">
         <v>-1.52</v>
       </c>
-      <c r="J22" s="14" t="n">
-        <v>3.62</v>
+      <c r="J22" s="11" t="n">
+        <v>3.46</v>
       </c>
     </row>
     <row r="23">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>3.6</v>
@@ -7207,7 +7207,7 @@
         <v>1.22</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="24">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>44.5</v>
+        <v>47.1</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>3.5</v>
@@ -7245,7 +7245,7 @@
         <v>0.66</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>4.24</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25">
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="F25" s="11" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>3.7</v>
@@ -7283,44 +7283,44 @@
         <v>1.78</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G26" s="8" t="n">
+      <c r="D26" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="5" t="n">
         <v>73.98999999999999</v>
       </c>
-      <c r="I26" s="8" t="n">
+      <c r="I26" s="5" t="n">
         <v>3.18</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="J26" s="5" t="n">
         <v>1.44</v>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="D27" s="20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="F27" s="20" t="n">
-        <v>35.4</v>
+        <v>33.5</v>
       </c>
       <c r="G27" s="20" t="n">
         <v>4.9</v>
@@ -7359,7 +7359,7 @@
         <v>4.78</v>
       </c>
       <c r="J27" s="20" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -7377,7 +7377,7 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="G28" s="26" t="n">
         <v>4.8</v>
@@ -7397,7 +7397,7 @@
         <v>2.48</v>
       </c>
       <c r="J28" s="26" t="n">
-        <v>3.72</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="29">
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>3.6</v>
@@ -7435,7 +7435,7 @@
         <v>8.65</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="30">
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F30" s="17" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="G30" s="17" t="n">
         <v>5.2</v>
@@ -7473,7 +7473,7 @@
         <v>6.71</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="31">
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="F31" s="20" t="n">
-        <v>36.2</v>
+        <v>37</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>3.6</v>
@@ -7511,7 +7511,7 @@
         <v>1.53</v>
       </c>
       <c r="J31" s="20" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="32">
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="D32" s="11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="F32" s="11" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>3.5</v>
@@ -7549,7 +7549,7 @@
         <v>6.8</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="33">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>3.6</v>
@@ -7587,45 +7587,45 @@
         <v>0.86</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>2.99</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="G34" s="8" t="n">
+      <c r="D34" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="G34" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="5" t="n">
         <v>66.86</v>
       </c>
-      <c r="I34" s="8" t="n">
+      <c r="I34" s="5" t="n">
         <v>5.1</v>
       </c>
-      <c r="J34" s="8" t="n">
-        <v>3.94</v>
+      <c r="J34" s="5" t="n">
+        <v>3.68</v>
       </c>
     </row>
     <row r="35">
@@ -7681,15 +7681,15 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>3</v>
@@ -7701,7 +7701,7 @@
         <v>1.62</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="37">
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="F37" s="20" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="G37" s="20" t="n">
         <v>4</v>
@@ -7739,45 +7739,45 @@
         <v>0.59</v>
       </c>
       <c r="J37" s="20" t="n">
-        <v>6.96</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="G38" s="17" t="n">
+      <c r="D38" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G38" s="20" t="n">
         <v>3.6</v>
       </c>
-      <c r="H38" s="17" t="n">
+      <c r="H38" s="20" t="n">
         <v>58.99</v>
       </c>
-      <c r="I38" s="17" t="n">
+      <c r="I38" s="20" t="n">
         <v>10.22</v>
       </c>
-      <c r="J38" s="17" t="n">
-        <v>1.57</v>
+      <c r="J38" s="20" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="39">
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>46.5</v>
+        <v>45</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>4.6</v>
@@ -7815,7 +7815,7 @@
         <v>5</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="40">
@@ -7853,7 +7853,7 @@
         <v>3.63</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>7.01</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="41">
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>41.6</v>
+        <v>39</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>3.1</v>
@@ -7891,7 +7891,7 @@
         <v>3.73</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>3.7</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="42">
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3</v>
@@ -7929,7 +7929,7 @@
         <v>4.51</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="43">
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>69.8</v>
+        <v>70</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>3.6</v>
@@ -7967,7 +7967,7 @@
         <v>4.7</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="44">
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="F44" s="11" t="n">
-        <v>50.2</v>
+        <v>53.3</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>3.1</v>
@@ -8005,45 +8005,45 @@
         <v>3.37</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>3.32</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="G45" s="2" t="n">
+      <c r="D45" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="5" t="n">
         <v>64.23999999999999</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="I45" s="5" t="n">
         <v>5.12</v>
       </c>
-      <c r="J45" s="2" t="n">
-        <v>2.71</v>
+      <c r="J45" s="5" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="46">
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>56.6</v>
+        <v>56.1</v>
       </c>
       <c r="G46" s="8" t="n">
         <v>4</v>
@@ -8081,7 +8081,7 @@
         <v>6.16</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="47">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.4</v>
@@ -8119,45 +8119,43 @@
         <v>3.15</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H48" s="5" t="n">
+      <c r="D48" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n">
         <v>60.56</v>
       </c>
-      <c r="I48" s="5" t="n">
+      <c r="I48" s="14" t="n">
         <v>-0.12</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>3.17</v>
+      <c r="J48" s="14" t="n">
+        <v>3.72</v>
       </c>
     </row>
     <row r="49">
@@ -8175,7 +8173,7 @@
         </is>
       </c>
       <c r="D49" s="17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
@@ -8183,7 +8181,7 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>39.7</v>
+        <v>39.4</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>8.199999999999999</v>
@@ -8195,7 +8193,7 @@
         <v>7.6</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="50">
@@ -8213,7 +8211,7 @@
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
@@ -8221,7 +8219,7 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>44.8</v>
+        <v>48.5</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>4</v>
@@ -8233,7 +8231,7 @@
         <v>3.13</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.76</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="51">
@@ -8251,7 +8249,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -8259,7 +8257,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>65.5</v>
+        <v>66.3</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8271,7 +8269,7 @@
         <v>-0.36</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
     </row>
   </sheetData>
@@ -8374,15 +8372,15 @@
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="G3" s="40" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8406,7 @@
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="G4" s="40" t="n">
@@ -8442,11 +8440,11 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="G5" s="40" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="40" t="inlineStr">
         <is>
@@ -8464,11 +8462,11 @@
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E6" s="40" t="n">
@@ -8480,7 +8478,7 @@
         </is>
       </c>
       <c r="G6" s="40" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H6" s="40" t="inlineStr">
         <is>
@@ -8494,11 +8492,11 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C7" s="39" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" s="39" t="inlineStr">
         <is>
@@ -8514,7 +8512,7 @@
         </is>
       </c>
       <c r="G7" s="40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7" s="40" t="inlineStr">
         <is>
@@ -8528,11 +8526,11 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
@@ -8544,11 +8542,11 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="G8" s="40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H8" s="40" t="inlineStr">
         <is>
@@ -8562,15 +8560,15 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E9" s="40" t="n">
@@ -8578,11 +8576,11 @@
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="G9" s="40" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H9" s="40" t="inlineStr">
         <is>
@@ -8596,7 +8594,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C10" s="39" t="n">
@@ -8616,7 +8614,7 @@
         </is>
       </c>
       <c r="G10" s="40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" s="40" t="inlineStr">
         <is>
@@ -8630,11 +8628,11 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" s="39" t="inlineStr">
         <is>
@@ -8650,7 +8648,7 @@
         </is>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H11" s="40" t="inlineStr">
         <is>
@@ -8684,7 +8682,7 @@
         </is>
       </c>
       <c r="G12" s="40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H12" s="40" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -791,20 +791,20 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>65.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -822,20 +822,20 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>64.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -852,48 +852,48 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
+      <c r="A8" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Austin-Round Rock-San Marcos</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>61.5</v>
+        <v>61.9</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -915,20 +915,20 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>61.7</v>
+        <v>59.8</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -946,16 +946,16 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -976,52 +976,52 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Atlanta-Sandy Springs-Roswell</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>57.5</v>
+        <v>58.8</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1039,20 +1039,20 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>56.6</v>
+        <v>58.9</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1070,20 +1070,20 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>55.8</v>
+        <v>58.7</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
@@ -1132,20 +1132,20 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>55.2</v>
+        <v>55.3</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>53.6</v>
+        <v>52.7</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1225,16 +1225,16 @@
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>51.5</v>
+        <v>52.9</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1287,16 +1287,16 @@
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D22" s="13" t="n">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="F22" s="11" t="n">
-        <v>51.5</v>
+        <v>51.9</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1318,109 +1318,109 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Los Angeles-Long Beach-Anaheim</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
-        <v>51</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="D25" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="F25" s="11" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Louisville-Jefferson County</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>New York Newark-Jersey City</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1442,16 +1442,16 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1473,16 +1473,16 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1535,20 +1535,20 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>46</v>
+        <v>46.7</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1566,16 +1566,16 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>44.5</v>
+        <v>45.2</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1597,16 +1597,16 @@
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Grand Rapids</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
@@ -1627,48 +1627,48 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="n">
+      <c r="A33" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="F34" s="17" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
@@ -1690,20 +1690,20 @@
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>44</v>
+        <v>41.5</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
@@ -1721,28 +1721,28 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Washington-Arlington-Alexandria</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>Milwaukee-Waukesha</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="n">
-        <v>42</v>
-      </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>41.6</v>
+        <v>39.6</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>39.9</v>
+        <v>38.8</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1783,20 +1783,20 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>39.9</v>
+        <v>38.6</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>39.7</v>
+        <v>39</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
@@ -1845,16 +1845,16 @@
     </row>
     <row r="40">
       <c r="A40" s="17" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D40" s="19" t="n">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F40" s="17" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="G40" s="18" t="inlineStr">
         <is>
@@ -1876,16 +1876,16 @@
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="D41" s="19" t="n">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>38.8</v>
+        <v>39.3</v>
       </c>
       <c r="G41" s="18" t="inlineStr">
         <is>
@@ -1906,48 +1906,48 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="n">
+      <c r="A42" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>Virginia Beach</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="n">
-        <v>39</v>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>36.4</v>
+        <v>35.8</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -1969,20 +1969,20 @@
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D44" s="22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>36.2</v>
+        <v>35</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="D45" s="22" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>35.4</v>
+        <v>33.4</v>
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="D46" s="22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -2062,20 +2062,20 @@
     </row>
     <row r="47">
       <c r="A47" s="23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F47" s="23" t="n">
-        <v>31.7</v>
+        <v>30.1</v>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
@@ -2093,20 +2093,20 @@
     </row>
     <row r="48">
       <c r="A48" s="23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="F48" s="23" t="n">
-        <v>30.9</v>
+        <v>29.4</v>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F49" s="23" t="n">
-        <v>29.3</v>
+        <v>27.6</v>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="D50" s="28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="F50" s="26" t="n">
-        <v>22.6</v>
+        <v>25.1</v>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F51" s="26" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="30" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G2" s="30" t="n">
         <v>96</v>
@@ -2340,7 +2340,7 @@
         <v>82</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="B3" s="29" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="30" t="n">
         <v>76</v>
@@ -2362,7 +2362,7 @@
         <v>48</v>
       </c>
       <c r="F3" s="31" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G3" s="30" t="n">
         <v>98</v>
@@ -2372,10 +2372,10 @@
         <v>96</v>
       </c>
       <c r="J3" s="31" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -2388,7 +2388,7 @@
         <v>70</v>
       </c>
       <c r="C4" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>70</v>
@@ -2400,7 +2400,7 @@
         <v>90</v>
       </c>
       <c r="G4" s="31" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="30" t="n">
@@ -2410,7 +2410,7 @@
         <v>78</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5" s="30" t="n">
         <v>90</v>
@@ -2432,7 +2432,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="30" t="n">
         <v>92</v>
@@ -2442,121 +2442,121 @@
         <v>80</v>
       </c>
       <c r="J5" s="33" t="n">
-        <v>43</v>
-      </c>
-      <c r="K5" s="33" t="n">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>65</v>
-      </c>
-      <c r="C6" s="30" t="n">
+        <v>67</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="F6" s="30" t="n">
         <v>94</v>
       </c>
-      <c r="D6" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="G6" s="33" t="n">
-        <v>35</v>
+      <c r="G6" s="30" t="n">
+        <v>80</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="J6" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="K6" s="30" t="n">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="J6" s="33" t="n">
+        <v>37</v>
+      </c>
+      <c r="K6" s="33" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>64</v>
-      </c>
-      <c r="C7" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="F7" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="G7" s="30" t="n">
-        <v>82</v>
+        <v>66</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>33</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>32</v>
       </c>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="K7" s="33" t="n">
-        <v>22</v>
+        <v>94</v>
+      </c>
+      <c r="J7" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="F8" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="G8" s="30" t="n">
-        <v>73</v>
+        <v>84</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H8" s="32" t="n"/>
-      <c r="I8" s="30" t="n">
-        <v>74</v>
+      <c r="I8" s="33" t="n">
+        <v>44</v>
       </c>
       <c r="J8" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" s="33" t="n">
-        <v>42</v>
+        <v>12</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B9" s="29" t="n">
@@ -2565,307 +2565,307 @@
       <c r="C9" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="D9" s="31" t="n">
-        <v>56</v>
+      <c r="D9" s="33" t="n">
+        <v>48</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="F9" s="30" t="n">
-        <v>96</v>
+        <v>74</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>59</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="J9" s="31" t="n">
-        <v>50</v>
+      <c r="I9" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="K9" s="33" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>62</v>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="D10" s="33" t="n">
+        <v>60</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="E10" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="G10" s="33" t="n">
-        <v>20</v>
+      <c r="F10" s="31" t="n">
+        <v>55</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>90</v>
       </c>
       <c r="H10" s="32" t="n"/>
       <c r="I10" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="J10" s="30" t="n">
-        <v>88</v>
+        <v>84</v>
+      </c>
+      <c r="J10" s="31" t="n">
+        <v>63</v>
       </c>
       <c r="K10" s="31" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B11" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="C11" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="E11" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>50</v>
+      <c r="C11" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>27</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H11" s="32" t="n"/>
-      <c r="I11" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="J11" s="31" t="n">
-        <v>61</v>
+      <c r="I11" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="J11" s="33" t="n">
+        <v>41</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="D12" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="F12" s="30" t="n">
         <v>96</v>
       </c>
-      <c r="E12" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="F12" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>51</v>
+      <c r="G12" s="30" t="n">
+        <v>82</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="33" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J12" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="33" t="n">
-        <v>12</v>
+      <c r="K12" s="31" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C13" s="31" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="F13" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="G13" s="31" t="n">
-        <v>59</v>
+        <v>74</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>63</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="H13" s="32" t="n"/>
       <c r="I13" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="J13" s="33" t="n">
-        <v>20</v>
+        <v>38</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>71</v>
       </c>
       <c r="K13" s="33" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>57</v>
-      </c>
-      <c r="C14" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="D14" s="33" t="n">
-        <v>18</v>
+        <v>59</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>92</v>
       </c>
       <c r="E14" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F14" s="30" t="n">
         <v>78</v>
       </c>
-      <c r="F14" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="G14" s="33" t="n">
-        <v>2</v>
+      <c r="G14" s="31" t="n">
+        <v>58</v>
       </c>
       <c r="H14" s="32" t="n"/>
-      <c r="I14" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="J14" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="K14" s="33" t="n">
-        <v>26</v>
+      <c r="I14" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="J14" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="K14" s="31" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>56</v>
-      </c>
-      <c r="C15" s="31" t="n">
-        <v>69</v>
+        <v>59</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>98</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="E15" s="30" t="n">
-        <v>86</v>
+        <v>20</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>8</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H15" s="32" t="n"/>
-      <c r="I15" s="31" t="n">
-        <v>50</v>
+      <c r="I15" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K15" s="33" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B16" s="29" t="n">
         <v>56</v>
       </c>
-      <c r="C16" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>66</v>
-      </c>
-      <c r="G16" s="30" t="n">
-        <v>88</v>
+      <c r="C16" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="G16" s="33" t="n">
+        <v>2</v>
       </c>
       <c r="H16" s="32" t="n"/>
-      <c r="I16" s="33" t="n">
-        <v>38</v>
+      <c r="I16" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K16" s="33" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>56</v>
-      </c>
-      <c r="C17" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="D17" s="30" t="n">
-        <v>76</v>
+        <v>55</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>26</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="G17" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="H17" s="32" t="n"/>
+      <c r="I17" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" s="30" t="n">
         <v>84</v>
       </c>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="J17" s="33" t="n">
-        <v>39</v>
-      </c>
       <c r="K17" s="33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2878,7 +2878,7 @@
         <v>55</v>
       </c>
       <c r="C18" s="33" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>42</v>
@@ -2887,7 +2887,7 @@
         <v>34</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G18" s="30" t="n">
         <v>86</v>
@@ -2897,10 +2897,10 @@
         <v>90</v>
       </c>
       <c r="J18" s="31" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K18" s="31" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="B19" s="29" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="30" t="n">
         <v>90</v>
@@ -2922,341 +2922,341 @@
         <v>44</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G19" s="33" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H19" s="32" t="n"/>
       <c r="I19" s="33" t="n">
         <v>48</v>
       </c>
       <c r="J19" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="K19" s="31" t="n">
-        <v>56</v>
+        <v>16</v>
+      </c>
+      <c r="K19" s="33" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B20" s="29" t="n">
         <v>53</v>
       </c>
       <c r="C20" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="F20" s="33" t="n">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="E20" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>92</v>
       </c>
       <c r="G20" s="33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H20" s="32" t="n"/>
       <c r="I20" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="J20" s="30" t="n">
-        <v>80</v>
+        <v>70</v>
+      </c>
+      <c r="J20" s="33" t="n">
+        <v>29</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B21" s="29" t="n">
+        <v>53</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C21" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="D21" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="F21" s="30" t="n">
-        <v>94</v>
+      <c r="F21" s="33" t="n">
+        <v>49</v>
       </c>
       <c r="G21" s="33" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H21" s="32" t="n"/>
-      <c r="I21" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="J21" s="33" t="n">
-        <v>27</v>
-      </c>
-      <c r="K21" s="33" t="n">
-        <v>48</v>
+      <c r="I21" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="J21" s="31" t="n">
+        <v>57</v>
+      </c>
+      <c r="K21" s="31" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B22" s="29" t="n">
         <v>52</v>
       </c>
       <c r="C22" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="D22" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="E22" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="F22" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="G22" s="33" t="n">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>66</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>94</v>
       </c>
       <c r="H22" s="32" t="n"/>
-      <c r="I22" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="31" t="n">
-        <v>59</v>
-      </c>
-      <c r="K22" s="32" t="n">
-        <v>0</v>
+      <c r="I22" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="J22" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="30" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B23" s="29" t="n">
-        <v>51</v>
-      </c>
-      <c r="C23" s="33" t="n">
-        <v>49</v>
-      </c>
-      <c r="D23" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="E23" s="33" t="n">
-        <v>32</v>
+        <v>52</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>84</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H23" s="32" t="n"/>
-      <c r="I23" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="J23" s="33" t="n">
+      <c r="I23" s="33" t="n">
         <v>4</v>
       </c>
+      <c r="J23" s="31" t="n">
+        <v>61</v>
+      </c>
       <c r="K23" s="33" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B24" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="F24" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="32" t="n"/>
+      <c r="I24" s="30" t="n">
         <v>86</v>
       </c>
-      <c r="D24" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="E24" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="F24" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="G24" s="33" t="n">
-        <v>47</v>
-      </c>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="J24" s="31" t="n">
-        <v>55</v>
+      <c r="J24" s="30" t="n">
+        <v>80</v>
       </c>
       <c r="K24" s="33" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25" s="33" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D25" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="E25" s="31" t="n">
-        <v>66</v>
-      </c>
-      <c r="F25" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="G25" s="31" t="n">
-        <v>69</v>
+        <v>30</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>88</v>
+      </c>
+      <c r="G25" s="33" t="n">
+        <v>14</v>
       </c>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="J25" s="31" t="n">
-        <v>67</v>
+        <v>82</v>
+      </c>
+      <c r="J25" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="K25" s="33" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B26" s="29" t="n">
         <v>48</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="D26" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="E26" s="33" t="n">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="E26" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="F26" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="G26" s="30" t="n">
-        <v>78</v>
+        <v>14</v>
+      </c>
+      <c r="G26" s="31" t="n">
+        <v>64</v>
       </c>
       <c r="H26" s="32" t="n"/>
-      <c r="I26" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="J26" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="K26" s="30" t="n">
-        <v>98</v>
+      <c r="I26" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="J26" s="31" t="n">
+        <v>67</v>
+      </c>
+      <c r="K26" s="33" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B27" s="29" t="n">
         <v>48</v>
       </c>
-      <c r="C27" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="D27" s="31" t="n">
-        <v>66</v>
+      <c r="C27" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="D27" s="33" t="n">
+        <v>40</v>
       </c>
       <c r="E27" s="33" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F27" s="33" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H27" s="32" t="n"/>
-      <c r="I27" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="J27" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" s="33" t="n">
-        <v>2</v>
+      <c r="I27" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="J27" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="K27" s="30" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B28" s="29" t="n">
         <v>47</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="D28" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="F28" s="30" t="n">
-        <v>74</v>
+        <v>44</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="E28" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="G28" s="30" t="n">
         <v>76</v>
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="31" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J28" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="K28" s="33" t="n">
-        <v>4</v>
+        <v>27</v>
+      </c>
+      <c r="K28" s="31" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B29" s="29" t="n">
@@ -3266,131 +3266,131 @@
         <v>16</v>
       </c>
       <c r="D29" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="E29" s="30" t="n">
-        <v>70</v>
+        <v>6</v>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="G29" s="33" t="n">
-        <v>43</v>
+        <v>71</v>
+      </c>
+      <c r="G29" s="30" t="n">
+        <v>74</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="31" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J29" s="33" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="K29" s="33" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B30" s="29" t="n">
+        <v>47</v>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="E30" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="F30" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="G30" s="33" t="n">
         <v>46</v>
-      </c>
-      <c r="C30" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="D30" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="E30" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="F30" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="G30" s="30" t="n">
-        <v>80</v>
       </c>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="J30" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="K30" s="31" t="n">
-        <v>62</v>
+        <v>40</v>
+      </c>
+      <c r="J30" s="33" t="n">
+        <v>49</v>
+      </c>
+      <c r="K30" s="30" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B31" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="C31" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="D31" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="E31" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="F31" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="G31" s="33" t="n">
-        <v>49</v>
+      <c r="C31" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <v>78</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="J31" s="33" t="n">
-        <v>47</v>
+        <v>22</v>
+      </c>
+      <c r="J31" s="31" t="n">
+        <v>53</v>
       </c>
       <c r="K31" s="31" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B32" s="29" t="n">
         <v>45</v>
       </c>
       <c r="C32" s="33" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D32" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="G32" s="33" t="n">
         <v>40</v>
-      </c>
-      <c r="E32" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="F32" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="G32" s="30" t="n">
-        <v>71</v>
       </c>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="J32" s="30" t="n">
-        <v>86</v>
+        <v>66</v>
+      </c>
+      <c r="J32" s="33" t="n">
+        <v>8</v>
       </c>
       <c r="K32" s="33" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
@@ -3403,7 +3403,7 @@
         <v>44</v>
       </c>
       <c r="C33" s="33" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D33" s="30" t="n">
         <v>88</v>
@@ -3412,125 +3412,125 @@
         <v>10</v>
       </c>
       <c r="F33" s="31" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G33" s="31" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H33" s="32" t="n"/>
       <c r="I33" s="31" t="n">
         <v>52</v>
       </c>
       <c r="J33" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="K33" s="33" t="n">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="K33" s="31" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B34" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="C34" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="D34" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="32" t="n">
+      <c r="C34" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="D34" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="33" t="n">
-        <v>14</v>
+      <c r="E34" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="F34" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="G34" s="31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="J34" s="31" t="n">
-        <v>65</v>
+        <v>56</v>
+      </c>
+      <c r="J34" s="30" t="n">
+        <v>96</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B35" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="C35" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="D35" s="32" t="n">
+        <v>41</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="D35" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="F35" s="32" t="n">
-        <v>0</v>
+      <c r="F35" s="33" t="n">
+        <v>16</v>
       </c>
       <c r="G35" s="31" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="31" t="n">
-        <v>56</v>
-      </c>
-      <c r="J35" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="K35" s="30" t="n">
-        <v>96</v>
+        <v>58</v>
+      </c>
+      <c r="J35" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="K35" s="31" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B36" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="C36" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="D36" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="E36" s="31" t="n">
-        <v>56</v>
-      </c>
-      <c r="F36" s="33" t="n">
-        <v>26</v>
+        <v>40</v>
+      </c>
+      <c r="C36" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="D36" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="E36" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" s="31" t="n">
+        <v>69</v>
       </c>
       <c r="G36" s="33" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="33" t="n">
-        <v>37</v>
+        <v>2</v>
+      </c>
+      <c r="J36" s="31" t="n">
+        <v>51</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="B37" s="29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="33" t="n">
         <v>20</v>
@@ -3552,265 +3552,265 @@
         <v>42</v>
       </c>
       <c r="F37" s="33" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G37" s="33" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="31" t="n">
         <v>54</v>
       </c>
       <c r="J37" s="33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K37" s="33" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B38" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="C38" s="33" t="n">
-        <v>47</v>
-      </c>
-      <c r="D38" s="30" t="n">
-        <v>78</v>
+        <v>39</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D38" s="33" t="n">
+        <v>46</v>
       </c>
       <c r="E38" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="F38" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="G38" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="F38" s="33" t="n">
         <v>37</v>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="33" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J38" s="33" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="C39" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="33" t="n">
-        <v>12</v>
+        <v>39</v>
+      </c>
+      <c r="C39" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F39" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="G39" s="33" t="n">
-        <v>4</v>
+        <v>61</v>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>52</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="J39" s="30" t="n">
-        <v>92</v>
+        <v>10</v>
+      </c>
+      <c r="J39" s="33" t="n">
+        <v>43</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B40" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="C40" s="31" t="n">
-        <v>51</v>
+      <c r="C40" s="30" t="n">
+        <v>86</v>
       </c>
       <c r="D40" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="E40" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="F40" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="G40" s="33" t="n">
         <v>22</v>
-      </c>
-      <c r="F40" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="G40" s="31" t="n">
-        <v>63</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="33" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J40" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="K40" s="30" t="n">
-        <v>78</v>
+        <v>39</v>
+      </c>
+      <c r="K40" s="33" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B41" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="C41" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" s="31" t="n">
-        <v>62</v>
+      <c r="C41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>12</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F41" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="G41" s="31" t="n">
-        <v>53</v>
+        <v>65</v>
+      </c>
+      <c r="G41" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="J41" s="33" t="n">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <v>92</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B42" s="29" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C42" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D42" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="F42" s="30" t="n">
-        <v>76</v>
+        <v>32</v>
+      </c>
+      <c r="E42" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="F42" s="33" t="n">
+        <v>22</v>
       </c>
       <c r="G42" s="33" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H42" s="32" t="n"/>
-      <c r="I42" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="31" t="n">
-        <v>60</v>
+      <c r="I42" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="K42" s="30" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B43" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="C43" s="33" t="n">
+      <c r="C43" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D43" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="33" t="n">
-        <v>14</v>
-      </c>
       <c r="E43" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="F43" s="31" t="n">
-        <v>52</v>
+        <v>98</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <v>73</v>
       </c>
       <c r="G43" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="33" t="n">
         <v>16</v>
-      </c>
-      <c r="H43" s="32" t="n"/>
-      <c r="I43" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="J43" s="30" t="n">
-        <v>73</v>
-      </c>
-      <c r="K43" s="33" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B44" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="C44" s="31" t="n">
-        <v>51</v>
+        <v>35</v>
+      </c>
+      <c r="C44" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="D44" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="E44" s="33" t="n">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="F44" s="33" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G44" s="33" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="33" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J44" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="K44" s="31" t="n">
-        <v>66</v>
+        <v>73</v>
+      </c>
+      <c r="K44" s="33" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B45" s="29" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C45" s="33" t="n">
         <v>8</v>
@@ -3832,7 +3832,7 @@
         <v>64</v>
       </c>
       <c r="F45" s="31" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G45" s="33" t="n">
         <v>12</v>
@@ -3842,10 +3842,10 @@
         <v>14</v>
       </c>
       <c r="J45" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="K45" s="30" t="n">
-        <v>76</v>
+        <v>20</v>
+      </c>
+      <c r="K45" s="33" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="B46" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="33" t="n">
         <v>34</v>
-      </c>
-      <c r="C46" s="33" t="n">
-        <v>35</v>
       </c>
       <c r="D46" s="31" t="n">
         <v>50</v>
@@ -3870,7 +3870,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H46" s="32" t="n"/>
       <c r="I46" s="33" t="n">
@@ -3880,77 +3880,77 @@
         <v>98</v>
       </c>
       <c r="K46" s="33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C47" s="33" t="n">
         <v>24</v>
       </c>
       <c r="D47" s="33" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E47" s="33" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F47" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="G47" s="33" t="n">
-        <v>18</v>
+        <v>47</v>
+      </c>
+      <c r="G47" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="31" t="n">
-        <v>53</v>
-      </c>
-      <c r="K47" s="30" t="n">
-        <v>84</v>
+        <v>42</v>
+      </c>
+      <c r="J47" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" s="33" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B48" s="29" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C48" s="33" t="n">
         <v>24</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E48" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="F48" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="F48" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="G48" s="31" t="n">
-        <v>65</v>
+      <c r="G48" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="J48" s="33" t="n">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="J48" s="31" t="n">
+        <v>55</v>
       </c>
       <c r="K48" s="33" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49">
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="B49" s="29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49" s="33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D49" s="31" t="n">
         <v>52</v>
@@ -3972,10 +3972,10 @@
         <v>14</v>
       </c>
       <c r="F49" s="33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G49" s="33" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="33" t="n">
@@ -3984,8 +3984,8 @@
       <c r="J49" s="30" t="n">
         <v>94</v>
       </c>
-      <c r="K49" s="33" t="n">
-        <v>28</v>
+      <c r="K49" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="B50" s="29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C50" s="33" t="n">
         <v>14</v>
@@ -4006,21 +4006,21 @@
       <c r="E50" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="F50" s="33" t="n">
-        <v>20</v>
+      <c r="F50" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="G50" s="33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="33" t="n">
         <v>28</v>
       </c>
       <c r="J50" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="K50" s="30" t="n">
-        <v>70</v>
+        <v>35</v>
+      </c>
+      <c r="K50" s="33" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="B51" s="29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51" s="33" t="n">
         <v>10</v>
@@ -4042,7 +4042,7 @@
         <v>38</v>
       </c>
       <c r="F51" s="33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G51" s="32" t="n">
         <v>0</v>
@@ -4052,10 +4052,10 @@
         <v>20</v>
       </c>
       <c r="J51" s="33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K51" s="31" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -4175,10 +4175,10 @@
         <v>4.51</v>
       </c>
       <c r="F2" s="32" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="G2" s="32" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="H2" s="32" t="n"/>
       <c r="I2" s="32" t="n">
@@ -4188,13 +4188,13 @@
         <v>38.82</v>
       </c>
       <c r="K2" s="32" t="n">
-        <v>5.68</v>
+        <v>7.46</v>
       </c>
       <c r="L2" s="32" t="n">
-        <v>13.21</v>
+        <v>4.55</v>
       </c>
       <c r="M2" s="32" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>74 (A+)</t>
+          <t>73 (A+)</t>
         </is>
       </c>
       <c r="C3" s="32" t="n">
@@ -4218,7 +4218,7 @@
         <v>3.15</v>
       </c>
       <c r="F3" s="32" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="G3" s="32" t="n">
         <v>4.76</v>
@@ -4231,13 +4231,13 @@
         <v>14.73</v>
       </c>
       <c r="K3" s="32" t="n">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="L3" s="32" t="n">
-        <v>-15.52</v>
+        <v>0</v>
       </c>
       <c r="M3" s="32" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -4261,10 +4261,10 @@
         <v>4.7</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="32" t="n">
@@ -4274,13 +4274,13 @@
         <v>20.14</v>
       </c>
       <c r="K4" s="32" t="n">
-        <v>8.15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L4" s="32" t="n">
-        <v>11.54</v>
+        <v>17.02</v>
       </c>
       <c r="M4" s="32" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>65 (A)</t>
+          <t>68 (A)</t>
         </is>
       </c>
       <c r="C5" s="32" t="n">
@@ -4304,10 +4304,10 @@
         <v>1.62</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="H5" s="32" t="n"/>
       <c r="I5" s="32" t="n">
@@ -4317,148 +4317,148 @@
         <v>-8.94</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>6.09</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L5" s="32" t="n">
-        <v>9.09</v>
+        <v>12.77</v>
       </c>
       <c r="M5" s="32" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>65 (A)</t>
+          <t>67 (A)</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>64.7</v>
+        <v>60.33</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>-0.36</v>
+        <v>8.65</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>3.5</v>
+        <v>1.11</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>2.16</v>
+        <v>3.38</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="32" t="n">
-        <v>1.88</v>
+        <v>1.07</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>16.13</v>
+        <v>-10.55</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>9.109999999999999</v>
+        <v>6.52</v>
       </c>
       <c r="L6" s="32" t="n">
-        <v>21.05</v>
+        <v>4.84</v>
       </c>
       <c r="M6" s="32" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>66 (A)</t>
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>60.33</v>
+        <v>64.7</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>8.65</v>
+        <v>-0.36</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>1.88</v>
+        <v>3.37</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>3.39</v>
+        <v>2.12</v>
       </c>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="32" t="n">
-        <v>1.07</v>
+        <v>1.88</v>
       </c>
       <c r="J7" s="32" t="n">
-        <v>-10.55</v>
+        <v>16.13</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>5.74</v>
+        <v>10</v>
       </c>
       <c r="L7" s="32" t="n">
-        <v>4.65</v>
+        <v>30</v>
       </c>
       <c r="M7" s="32" t="n">
-        <v>90</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>63 (A)</t>
+          <t>62 (A-)</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>64.23999999999999</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>5.12</v>
+        <v>3.18</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>2.71</v>
+        <v>1.44</v>
       </c>
       <c r="G8" s="32" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="H8" s="32" t="n"/>
       <c r="I8" s="32" t="n">
-        <v>0.29</v>
+        <v>0.73</v>
       </c>
       <c r="J8" s="32" t="n">
-        <v>-20.27</v>
+        <v>-29.44</v>
       </c>
       <c r="K8" s="32" t="n">
-        <v>6.8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L8" s="32" t="n">
-        <v>-2.04</v>
+        <v>20.45</v>
       </c>
       <c r="M8" s="32" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
@@ -4470,77 +4470,81 @@
         <v>3.3</v>
       </c>
       <c r="D9" s="32" t="n">
-        <v>64.56999999999999</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>8.27</v>
+        <v>5.12</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="G9" s="32" t="n"/>
+        <v>2.38</v>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>3.02</v>
+      </c>
       <c r="H9" s="32" t="n"/>
       <c r="I9" s="32" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J9" s="32" t="n"/>
+        <v>0.29</v>
+      </c>
+      <c r="J9" s="32" t="n">
+        <v>-20.27</v>
+      </c>
       <c r="K9" s="32" t="n">
-        <v>6.66</v>
+        <v>5.86</v>
       </c>
       <c r="L9" s="32" t="n">
-        <v>-3.45</v>
+        <v>-11.36</v>
       </c>
       <c r="M9" s="32" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>62 (A-)</t>
+          <t>60 (A-)</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>60.56</v>
+        <v>65.61</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>-0.12</v>
+        <v>0.86</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>3.17</v>
+        <v>2.63</v>
       </c>
       <c r="G10" s="32" t="n">
-        <v>1.47</v>
+        <v>3.76</v>
       </c>
       <c r="H10" s="32" t="n"/>
       <c r="I10" s="32" t="n">
-        <v>0.61</v>
+        <v>1.17</v>
       </c>
       <c r="J10" s="32" t="n">
-        <v>55.25</v>
+        <v>8.67</v>
       </c>
       <c r="K10" s="32" t="n">
-        <v>7.14</v>
+        <v>8.08</v>
       </c>
       <c r="L10" s="32" t="n">
-        <v>-1.41</v>
+        <v>10.81</v>
       </c>
       <c r="M10" s="32" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
@@ -4549,213 +4553,213 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="D11" s="32" t="n">
-        <v>65.61</v>
+        <v>66.86</v>
       </c>
       <c r="E11" s="32" t="n">
-        <v>0.86</v>
+        <v>5.1</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>2.99</v>
+        <v>3.68</v>
       </c>
       <c r="G11" s="32" t="n">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="32" t="n">
-        <v>1.17</v>
+        <v>0.11</v>
       </c>
       <c r="J11" s="32" t="n">
-        <v>8.67</v>
+        <v>-10.26</v>
       </c>
       <c r="K11" s="32" t="n">
-        <v>8.220000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="L11" s="32" t="n">
-        <v>12.24</v>
+        <v>15.91</v>
       </c>
       <c r="M11" s="32" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>59 (A-)</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D12" s="32" t="n">
-        <v>73.98999999999999</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E12" s="32" t="n">
-        <v>3.18</v>
+        <v>8.27</v>
       </c>
       <c r="F12" s="32" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="G12" s="32" t="n">
-        <v>2.45</v>
+        <v>3.52</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="32" t="n">
-        <v>0.73</v>
+        <v>-0.01</v>
       </c>
       <c r="J12" s="32" t="n">
-        <v>-29.44</v>
+        <v>-30.9</v>
       </c>
       <c r="K12" s="32" t="n">
-        <v>5.48</v>
+        <v>7.85</v>
       </c>
       <c r="L12" s="32" t="n">
-        <v>15.15</v>
+        <v>8.51</v>
       </c>
       <c r="M12" s="32" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>59 (B+)</t>
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D13" s="32" t="n">
-        <v>70.39</v>
+        <v>66.34</v>
       </c>
       <c r="E13" s="32" t="n">
-        <v>6.57</v>
+        <v>4.52</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>1.48</v>
+        <v>2.19</v>
       </c>
       <c r="G13" s="32" t="n">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="H13" s="32" t="n"/>
       <c r="I13" s="32" t="n">
-        <v>0.13</v>
+        <v>0.87</v>
       </c>
       <c r="J13" s="32" t="n">
-        <v>-15.96</v>
+        <v>16.86</v>
       </c>
       <c r="K13" s="32" t="n">
-        <v>5.64</v>
+        <v>7.59</v>
       </c>
       <c r="L13" s="32" t="n">
-        <v>-13.64</v>
+        <v>5.88</v>
       </c>
       <c r="M13" s="32" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>59 (B+)</t>
         </is>
       </c>
       <c r="C14" s="32" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D14" s="32" t="n">
-        <v>60.48</v>
+        <v>70.39</v>
       </c>
       <c r="E14" s="32" t="n">
-        <v>6.16</v>
+        <v>6.57</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>0.4</v>
+        <v>1.46</v>
       </c>
       <c r="G14" s="32" t="n">
-        <v>0.61</v>
+        <v>2.76</v>
       </c>
       <c r="H14" s="32" t="n"/>
       <c r="I14" s="32" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="J14" s="32" t="n">
-        <v>19.69</v>
+        <v>-15.96</v>
       </c>
       <c r="K14" s="32" t="n">
-        <v>5.87</v>
+        <v>7.86</v>
       </c>
       <c r="L14" s="32" t="n">
-        <v>11.27</v>
+        <v>8.57</v>
       </c>
       <c r="M14" s="32" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>56 (B+)</t>
+          <t>59 (B+)</t>
         </is>
       </c>
       <c r="C15" s="32" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="D15" s="32" t="n">
-        <v>62.53</v>
+        <v>60.56</v>
       </c>
       <c r="E15" s="32" t="n">
-        <v>7.12</v>
+        <v>-0.12</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
       <c r="G15" s="32" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="H15" s="32" t="n"/>
       <c r="I15" s="32" t="n">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="J15" s="32" t="n">
-        <v>41.11</v>
+        <v>55.25</v>
       </c>
       <c r="K15" s="32" t="n">
-        <v>5.54</v>
+        <v>7.37</v>
       </c>
       <c r="L15" s="32" t="n">
-        <v>12.16</v>
+        <v>3.7</v>
       </c>
       <c r="M15" s="32" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
@@ -4763,77 +4767,79 @@
           <t>56 (B+)</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
+      <c r="C16" s="32" t="n">
+        <v>4</v>
+      </c>
       <c r="D16" s="32" t="n">
-        <v>66.34</v>
+        <v>60.48</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>4.52</v>
+        <v>6.16</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>2.08</v>
+        <v>0.48</v>
       </c>
       <c r="G16" s="32" t="n">
-        <v>3.59</v>
+        <v>0.6</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="32" t="n">
-        <v>0.87</v>
+        <v>0.06</v>
       </c>
       <c r="J16" s="32" t="n">
-        <v>16.86</v>
+        <v>19.69</v>
       </c>
       <c r="K16" s="32" t="n">
-        <v>6.82</v>
+        <v>6.31</v>
       </c>
       <c r="L16" s="32" t="n">
-        <v>-1.79</v>
+        <v>6.9</v>
       </c>
       <c r="M16" s="32" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>56 (B+)</t>
+          <t>55 (B+)</t>
         </is>
       </c>
       <c r="C17" s="32" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D17" s="32" t="n">
-        <v>66.86</v>
+        <v>62.53</v>
       </c>
       <c r="E17" s="32" t="n">
-        <v>5.1</v>
+        <v>7.12</v>
       </c>
       <c r="F17" s="32" t="n">
-        <v>3.94</v>
+        <v>3.31</v>
       </c>
       <c r="G17" s="32" t="n">
-        <v>3.55</v>
+        <v>1.86</v>
       </c>
       <c r="H17" s="32" t="n"/>
       <c r="I17" s="32" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="J17" s="32" t="n">
-        <v>-10.26</v>
+        <v>41.11</v>
       </c>
       <c r="K17" s="32" t="n">
-        <v>5.41</v>
+        <v>5.96</v>
       </c>
       <c r="L17" s="32" t="n">
-        <v>15.87</v>
+        <v>10.45</v>
       </c>
       <c r="M17" s="32" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -4857,10 +4863,10 @@
         <v>2.21</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="G18" s="32" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="H18" s="32" t="n"/>
       <c r="I18" s="32" t="n">
@@ -4870,13 +4876,13 @@
         <v>4.14</v>
       </c>
       <c r="K18" s="32" t="n">
-        <v>7.19</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L18" s="32" t="n">
-        <v>1.92</v>
+        <v>10.26</v>
       </c>
       <c r="M18" s="32" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -4887,7 +4893,7 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C19" s="32" t="n">
@@ -4900,10 +4906,10 @@
         <v>3.1</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G19" s="32" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="H19" s="32" t="n"/>
       <c r="I19" s="32" t="n">
@@ -4913,19 +4919,19 @@
         <v>-20.96</v>
       </c>
       <c r="K19" s="32" t="n">
-        <v>7.18</v>
+        <v>7.67</v>
       </c>
       <c r="L19" s="32" t="n">
-        <v>1.79</v>
+        <v>6.67</v>
       </c>
       <c r="M19" s="32" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
@@ -4934,84 +4940,84 @@
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>63.61</v>
+        <v>64.52</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>5.33</v>
+        <v>2.61</v>
       </c>
       <c r="F20" s="32" t="n">
-        <v>5.59</v>
+        <v>1.19</v>
       </c>
       <c r="G20" s="32" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H20" s="32" t="n"/>
       <c r="I20" s="32" t="n">
-        <v>1.83</v>
+        <v>0.43</v>
       </c>
       <c r="J20" s="32" t="n">
-        <v>20.24</v>
+        <v>-12.89</v>
       </c>
       <c r="K20" s="32" t="n">
-        <v>8.279999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L20" s="32" t="n">
-        <v>12.82</v>
+        <v>11.11</v>
       </c>
       <c r="M20" s="32" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C21" s="32" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>64.52</v>
+        <v>62.74</v>
       </c>
       <c r="E21" s="32" t="n">
-        <v>2.61</v>
+        <v>3.37</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>1.17</v>
+        <v>2.87</v>
       </c>
       <c r="G21" s="32" t="n">
-        <v>0.84</v>
+        <v>2.38</v>
       </c>
       <c r="H21" s="32" t="n"/>
       <c r="I21" s="32" t="n">
-        <v>0.43</v>
+        <v>-0.06</v>
       </c>
       <c r="J21" s="32" t="n">
-        <v>-12.89</v>
+        <v>2.98</v>
       </c>
       <c r="K21" s="32" t="n">
-        <v>7</v>
+        <v>7.98</v>
       </c>
       <c r="L21" s="32" t="n">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="M21" s="32" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
@@ -5020,170 +5026,170 @@
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>67.91</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>6.8</v>
+        <v>-1.52</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>1.49</v>
+        <v>3.46</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>1.22</v>
+        <v>4.14</v>
       </c>
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="32" t="n">
-        <v>-0.31</v>
+        <v>2.69</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>5.41</v>
+        <v>-39.5</v>
       </c>
       <c r="K22" s="32" t="n">
-        <v>4.6</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L22" s="32" t="n">
-        <v>-24</v>
+        <v>13.95</v>
       </c>
       <c r="M22" s="32" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>52 (B)</t>
         </is>
       </c>
       <c r="C23" s="32" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D23" s="32" t="n">
-        <v>62.78</v>
+        <v>67.91</v>
       </c>
       <c r="E23" s="32" t="n">
-        <v>1.78</v>
+        <v>6.8</v>
       </c>
       <c r="F23" s="32" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="G23" s="32" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="H23" s="32" t="n"/>
       <c r="I23" s="32" t="n">
-        <v>1.09</v>
+        <v>-0.31</v>
       </c>
       <c r="J23" s="32" t="n">
-        <v>-37.55</v>
+        <v>5.41</v>
       </c>
       <c r="K23" s="32" t="n">
-        <v>6.61</v>
+        <v>5.82</v>
       </c>
       <c r="L23" s="32" t="n">
-        <v>3.95</v>
+        <v>-11.76</v>
       </c>
       <c r="M23" s="32" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="D24" s="32" t="n">
-        <v>62.74</v>
+        <v>63.61</v>
       </c>
       <c r="E24" s="32" t="n">
-        <v>3.37</v>
+        <v>5.33</v>
       </c>
       <c r="F24" s="32" t="n">
-        <v>3.32</v>
+        <v>5.59</v>
       </c>
       <c r="G24" s="32" t="n">
-        <v>2.37</v>
+        <v>0.96</v>
       </c>
       <c r="H24" s="32" t="n"/>
       <c r="I24" s="32" t="n">
-        <v>-0.06</v>
+        <v>1.83</v>
       </c>
       <c r="J24" s="32" t="n">
-        <v>2.98</v>
+        <v>20.24</v>
       </c>
       <c r="K24" s="32" t="n">
-        <v>6.8</v>
+        <v>7.71</v>
       </c>
       <c r="L24" s="32" t="n">
-        <v>-1.96</v>
+        <v>7.14</v>
       </c>
       <c r="M24" s="32" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C25" s="32" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D25" s="32" t="n">
-        <v>63.3</v>
+        <v>62.78</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>4.84</v>
+        <v>1.78</v>
       </c>
       <c r="F25" s="32" t="n">
-        <v>4.78</v>
+        <v>1.33</v>
       </c>
       <c r="G25" s="32" t="n">
-        <v>3.04</v>
+        <v>1.24</v>
       </c>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="32" t="n">
-        <v>0.48</v>
+        <v>1.09</v>
       </c>
       <c r="J25" s="32" t="n">
-        <v>14.97</v>
+        <v>-37.55</v>
       </c>
       <c r="K25" s="32" t="n">
-        <v>7</v>
+        <v>6.83</v>
       </c>
       <c r="L25" s="32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M25" s="32" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B26" s="34" t="inlineStr">
@@ -5192,41 +5198,41 @@
         </is>
       </c>
       <c r="C26" s="32" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="D26" s="32" t="n">
-        <v>68.47</v>
+        <v>63.3</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>1.42</v>
+        <v>4.84</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>5.47</v>
+        <v>5.01</v>
       </c>
       <c r="G26" s="32" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="32" t="n">
-        <v>0.73</v>
+        <v>0.48</v>
       </c>
       <c r="J26" s="32" t="n">
-        <v>-14.97</v>
+        <v>14.97</v>
       </c>
       <c r="K26" s="32" t="n">
-        <v>9.73</v>
+        <v>7.62</v>
       </c>
       <c r="L26" s="32" t="n">
-        <v>27.27</v>
+        <v>6.25</v>
       </c>
       <c r="M26" s="32" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B27" s="34" t="inlineStr">
@@ -5235,41 +5241,41 @@
         </is>
       </c>
       <c r="C27" s="32" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D27" s="32" t="n">
-        <v>65.43000000000001</v>
+        <v>63.89</v>
       </c>
       <c r="E27" s="32" t="n">
-        <v>-1.52</v>
+        <v>3.13</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>3.62</v>
+        <v>5.56</v>
       </c>
       <c r="G27" s="32" t="n">
-        <v>4.16</v>
+        <v>3.06</v>
       </c>
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="32" t="n">
-        <v>2.69</v>
+        <v>0.51</v>
       </c>
       <c r="J27" s="32" t="n">
-        <v>-39.5</v>
+        <v>55.17</v>
       </c>
       <c r="K27" s="32" t="n">
-        <v>4.68</v>
+        <v>8.58</v>
       </c>
       <c r="L27" s="32" t="n">
-        <v>23.21</v>
+        <v>15.79</v>
       </c>
       <c r="M27" s="32" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B28" s="34" t="inlineStr">
@@ -5278,41 +5284,41 @@
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="D28" s="32" t="n">
-        <v>59.95</v>
+        <v>68.47</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>4.86</v>
+        <v>1.42</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>1.87</v>
+        <v>5.25</v>
       </c>
       <c r="G28" s="32" t="n">
         <v>3.14</v>
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="32" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="J28" s="32" t="n">
-        <v>-8.56</v>
+        <v>-14.97</v>
       </c>
       <c r="K28" s="32" t="n">
-        <v>4.88</v>
+        <v>8</v>
       </c>
       <c r="L28" s="32" t="n">
-        <v>21.21</v>
+        <v>20</v>
       </c>
       <c r="M28" s="32" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B29" s="34" t="inlineStr">
@@ -5324,81 +5330,81 @@
         <v>4.6</v>
       </c>
       <c r="D29" s="32" t="n">
-        <v>60.38</v>
+        <v>59.95</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="G29" s="32" t="n">
-        <v>2.29</v>
+        <v>3.08</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="32" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="J29" s="32" t="n">
-        <v>-32.7</v>
+        <v>-8.56</v>
       </c>
       <c r="K29" s="32" t="n">
-        <v>6.09</v>
+        <v>5.42</v>
       </c>
       <c r="L29" s="32" t="n">
-        <v>9.09</v>
+        <v>15.79</v>
       </c>
       <c r="M29" s="32" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D30" s="32" t="n">
-        <v>68.23999999999999</v>
+        <v>65.27</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>7.63</v>
+        <v>0.66</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="G30" s="32" t="n">
-        <v>3.29</v>
+        <v>2.34</v>
       </c>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="32" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="J30" s="32" t="n">
-        <v>-0.7</v>
+        <v>-6.99</v>
       </c>
       <c r="K30" s="32" t="n">
-        <v>7.29</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L30" s="32" t="n">
-        <v>2.86</v>
+        <v>17.95</v>
       </c>
       <c r="M30" s="32" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B31" s="34" t="inlineStr">
@@ -5407,41 +5413,41 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D31" s="32" t="n">
-        <v>65.27</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>0.66</v>
+        <v>7.63</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>4.24</v>
+        <v>2.86</v>
       </c>
       <c r="G31" s="32" t="n">
-        <v>2.39</v>
+        <v>3.26</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="32" t="n">
-        <v>-0.01</v>
+        <v>-0.15</v>
       </c>
       <c r="J31" s="32" t="n">
-        <v>-6.99</v>
+        <v>-0.7</v>
       </c>
       <c r="K31" s="32" t="n">
-        <v>7.38</v>
+        <v>7.77</v>
       </c>
       <c r="L31" s="32" t="n">
-        <v>3.77</v>
+        <v>9.68</v>
       </c>
       <c r="M31" s="32" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
@@ -5450,35 +5456,35 @@
         </is>
       </c>
       <c r="C32" s="32" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="D32" s="32" t="n">
-        <v>63.89</v>
+        <v>60.38</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>3.13</v>
+        <v>5</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>5.76</v>
+        <v>1.44</v>
       </c>
       <c r="G32" s="32" t="n">
-        <v>3.06</v>
+        <v>2.24</v>
       </c>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="32" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="J32" s="32" t="n">
-        <v>55.17</v>
+        <v>-32.7</v>
       </c>
       <c r="K32" s="32" t="n">
-        <v>5.57</v>
+        <v>7.17</v>
       </c>
       <c r="L32" s="32" t="n">
-        <v>14.29</v>
+        <v>1.75</v>
       </c>
       <c r="M32" s="32" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
@@ -5489,7 +5495,7 @@
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>44 (B-)</t>
         </is>
       </c>
       <c r="C33" s="32" t="n">
@@ -5502,10 +5508,10 @@
         <v>0.03</v>
       </c>
       <c r="F33" s="32" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="G33" s="32" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="H33" s="32" t="n"/>
       <c r="I33" s="32" t="n">
@@ -5515,19 +5521,19 @@
         <v>-12.25</v>
       </c>
       <c r="K33" s="32" t="n">
-        <v>6.76</v>
+        <v>7.91</v>
       </c>
       <c r="L33" s="32" t="n">
-        <v>-2.44</v>
+        <v>9.09</v>
       </c>
       <c r="M33" s="32" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B34" s="34" t="inlineStr">
@@ -5536,121 +5542,119 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="D34" s="32" t="n">
-        <v>58.01</v>
+        <v>50.77</v>
       </c>
       <c r="E34" s="32" t="n">
-        <v>-1.79</v>
+        <v>3.63</v>
       </c>
       <c r="F34" s="32" t="n">
-        <v>5</v>
+        <v>7.35</v>
       </c>
       <c r="G34" s="32" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="32" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="J34" s="32" t="n">
-        <v>14.96</v>
+        <v>144.37</v>
       </c>
       <c r="K34" s="32" t="n">
-        <v>7.78</v>
+        <v>10</v>
       </c>
       <c r="L34" s="32" t="n">
-        <v>7.84</v>
+        <v>33.33</v>
       </c>
       <c r="M34" s="32" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C35" s="32" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="D35" s="32" t="n">
-        <v>50.77</v>
+        <v>58.01</v>
       </c>
       <c r="E35" s="32" t="n">
-        <v>3.63</v>
+        <v>-1.79</v>
       </c>
       <c r="F35" s="32" t="n">
-        <v>7.01</v>
+        <v>5</v>
       </c>
       <c r="G35" s="32" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J35" s="32" t="n">
-        <v>144.37</v>
-      </c>
+        <v>0.57</v>
+      </c>
+      <c r="J35" s="32" t="n"/>
       <c r="K35" s="32" t="n">
-        <v>9.56</v>
+        <v>7.78</v>
       </c>
       <c r="L35" s="32" t="n">
-        <v>25.64</v>
+        <v>7.84</v>
       </c>
       <c r="M35" s="32" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C36" s="32" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="D36" s="32" t="n">
-        <v>63.19</v>
+        <v>67.37</v>
       </c>
       <c r="E36" s="32" t="n">
-        <v>3.73</v>
+        <v>1.37</v>
       </c>
       <c r="F36" s="32" t="n">
-        <v>3.7</v>
+        <v>2.06</v>
       </c>
       <c r="G36" s="32" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="n">
-        <v>-0.91</v>
+        <v>-1.63</v>
       </c>
       <c r="J36" s="32" t="n">
-        <v>-10.47</v>
+        <v>-3.97</v>
       </c>
       <c r="K36" s="32" t="n">
-        <v>7.83</v>
+        <v>8.5</v>
       </c>
       <c r="L36" s="32" t="n">
-        <v>8.33</v>
+        <v>25</v>
       </c>
       <c r="M36" s="32" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -5661,7 +5665,7 @@
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C37" s="32" t="n">
@@ -5674,10 +5678,10 @@
         <v>2.84</v>
       </c>
       <c r="F37" s="32" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="G37" s="32" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="32" t="n">
@@ -5687,105 +5691,105 @@
         <v>-27.41</v>
       </c>
       <c r="K37" s="32" t="n">
-        <v>6.3</v>
+        <v>6.72</v>
       </c>
       <c r="L37" s="32" t="n">
-        <v>-6.98</v>
+        <v>-2.78</v>
       </c>
       <c r="M37" s="32" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D38" s="32" t="n">
-        <v>67.37</v>
+        <v>64.19</v>
       </c>
       <c r="E38" s="32" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="F38" s="32" t="n">
-        <v>1.9</v>
+        <v>3.21</v>
       </c>
       <c r="G38" s="32" t="n">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="32" t="n">
-        <v>-1.63</v>
+        <v>-0.14</v>
       </c>
       <c r="J38" s="32" t="n">
-        <v>-3.97</v>
+        <v>-11.14</v>
       </c>
       <c r="K38" s="32" t="n">
-        <v>8.18</v>
+        <v>9.76</v>
       </c>
       <c r="L38" s="32" t="n">
-        <v>11.76</v>
+        <v>27.59</v>
       </c>
       <c r="M38" s="32" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C39" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="D39" s="32" t="n">
-        <v>60.33</v>
+        <v>65.02</v>
       </c>
       <c r="E39" s="32" t="n">
-        <v>7.6</v>
+        <v>6.71</v>
       </c>
       <c r="F39" s="32" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="G39" s="32" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="32" t="n">
-        <v>0.22</v>
+        <v>-0.76</v>
       </c>
       <c r="J39" s="32" t="n">
-        <v>61.97</v>
+        <v>-9.83</v>
       </c>
       <c r="K39" s="32" t="n">
-        <v>8.039999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="L39" s="32" t="n">
-        <v>10.42</v>
+        <v>18.18</v>
       </c>
       <c r="M39" s="32" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
@@ -5794,41 +5798,41 @@
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D40" s="32" t="n">
-        <v>64.19</v>
+        <v>63.19</v>
       </c>
       <c r="E40" s="32" t="n">
-        <v>1.22</v>
+        <v>3.73</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>3.16</v>
+        <v>4.27</v>
       </c>
       <c r="G40" s="32" t="n">
-        <v>2.94</v>
+        <v>1.56</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="32" t="n">
-        <v>-0.14</v>
+        <v>-0.91</v>
       </c>
       <c r="J40" s="32" t="n">
-        <v>-11.14</v>
+        <v>-10.47</v>
       </c>
       <c r="K40" s="32" t="n">
-        <v>7.98</v>
+        <v>7.25</v>
       </c>
       <c r="L40" s="32" t="n">
-        <v>9.76</v>
+        <v>6.45</v>
       </c>
       <c r="M40" s="32" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
@@ -5837,84 +5841,84 @@
         </is>
       </c>
       <c r="C41" s="32" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D41" s="32" t="n">
-        <v>65.02</v>
+        <v>60.33</v>
       </c>
       <c r="E41" s="32" t="n">
-        <v>6.71</v>
+        <v>7.6</v>
       </c>
       <c r="F41" s="32" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="G41" s="32" t="n">
-        <v>2.49</v>
+        <v>0.78</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="32" t="n">
-        <v>-0.76</v>
+        <v>0.22</v>
       </c>
       <c r="J41" s="32" t="n">
-        <v>-9.83</v>
+        <v>61.97</v>
       </c>
       <c r="K41" s="32" t="n">
-        <v>8.279999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="L41" s="32" t="n">
-        <v>12.77</v>
+        <v>10.87</v>
       </c>
       <c r="M41" s="32" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>37 (C)</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
         <v>3.6</v>
       </c>
       <c r="D42" s="32" t="n">
-        <v>58.99</v>
+        <v>63.08</v>
       </c>
       <c r="E42" s="32" t="n">
-        <v>10.22</v>
+        <v>1.53</v>
       </c>
       <c r="F42" s="32" t="n">
-        <v>1.57</v>
+        <v>3.72</v>
       </c>
       <c r="G42" s="32" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="32" t="n">
-        <v>-1.34</v>
+        <v>-0.52</v>
       </c>
       <c r="J42" s="32" t="n">
-        <v>-46.79</v>
+        <v>57.47</v>
       </c>
       <c r="K42" s="32" t="n">
-        <v>7.26</v>
+        <v>9.16</v>
       </c>
       <c r="L42" s="32" t="n">
-        <v>2.56</v>
+        <v>21.62</v>
       </c>
       <c r="M42" s="32" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B43" s="34" t="inlineStr">
@@ -5923,78 +5927,78 @@
         </is>
       </c>
       <c r="C43" s="32" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="D43" s="32" t="n">
-        <v>60.37</v>
+        <v>58.99</v>
       </c>
       <c r="E43" s="32" t="n">
-        <v>7.54</v>
+        <v>10.22</v>
       </c>
       <c r="F43" s="32" t="n">
-        <v>2.93</v>
+        <v>1.53</v>
       </c>
       <c r="G43" s="32" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="32" t="n">
-        <v>0.18</v>
+        <v>-1.34</v>
       </c>
       <c r="J43" s="32" t="n">
-        <v>18.04</v>
+        <v>-46.79</v>
       </c>
       <c r="K43" s="32" t="n">
-        <v>7</v>
+        <v>6.47</v>
       </c>
       <c r="L43" s="32" t="n">
-        <v>0</v>
+        <v>-5.26</v>
       </c>
       <c r="M43" s="32" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>35 (C)</t>
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="D44" s="32" t="n">
-        <v>63.08</v>
+        <v>60.37</v>
       </c>
       <c r="E44" s="32" t="n">
-        <v>1.53</v>
+        <v>7.54</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>3.69</v>
+        <v>2.89</v>
       </c>
       <c r="G44" s="32" t="n">
-        <v>2.06</v>
+        <v>1.3</v>
       </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="32" t="n">
-        <v>-0.52</v>
+        <v>0.18</v>
       </c>
       <c r="J44" s="32" t="n">
-        <v>57.47</v>
+        <v>18.04</v>
       </c>
       <c r="K44" s="32" t="n">
-        <v>7.4</v>
+        <v>7.59</v>
       </c>
       <c r="L44" s="32" t="n">
-        <v>4</v>
+        <v>5.88</v>
       </c>
       <c r="M44" s="32" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45">
@@ -6005,7 +6009,7 @@
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>35 (C)</t>
+          <t>33 (C)</t>
         </is>
       </c>
       <c r="C45" s="32" t="n">
@@ -6018,10 +6022,10 @@
         <v>4.78</v>
       </c>
       <c r="F45" s="32" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G45" s="32" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="32" t="n">
@@ -6031,13 +6035,13 @@
         <v>-18.14</v>
       </c>
       <c r="K45" s="32" t="n">
-        <v>7.93</v>
+        <v>6.61</v>
       </c>
       <c r="L45" s="32" t="n">
-        <v>-9.33</v>
+        <v>-3.92</v>
       </c>
       <c r="M45" s="32" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
@@ -6048,7 +6052,7 @@
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>33 (C)</t>
         </is>
       </c>
       <c r="C46" s="32" t="n">
@@ -6061,7 +6065,7 @@
         <v>0.59</v>
       </c>
       <c r="F46" s="32" t="n">
-        <v>6.96</v>
+        <v>6.03</v>
       </c>
       <c r="G46" s="32" t="n">
         <v>2.02</v>
@@ -6074,99 +6078,99 @@
         <v>195.09</v>
       </c>
       <c r="K46" s="32" t="n">
-        <v>5.05</v>
+        <v>5.71</v>
       </c>
       <c r="L46" s="32" t="n">
-        <v>4.55</v>
+        <v>9.09</v>
       </c>
       <c r="M46" s="32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>32 (C-)</t>
+          <t>30 (C-)</t>
         </is>
       </c>
       <c r="C47" s="32" t="n">
         <v>4.4</v>
       </c>
       <c r="D47" s="32" t="n">
-        <v>62.01</v>
+        <v>63.98</v>
       </c>
       <c r="E47" s="32" t="n">
-        <v>2.43</v>
+        <v>0.37</v>
       </c>
       <c r="F47" s="32" t="n">
-        <v>5.24</v>
+        <v>2.88</v>
       </c>
       <c r="G47" s="32" t="n">
-        <v>1.37</v>
+        <v>3</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="32" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="J47" s="32" t="n">
-        <v>-0.37</v>
+        <v>-35.64</v>
       </c>
       <c r="K47" s="32" t="n">
-        <v>8.18</v>
+        <v>5.83</v>
       </c>
       <c r="L47" s="32" t="n">
-        <v>11.76</v>
+        <v>11.67</v>
       </c>
       <c r="M47" s="32" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>31 (C-)</t>
+          <t>29 (C-)</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
         <v>4.4</v>
       </c>
       <c r="D48" s="32" t="n">
-        <v>63.98</v>
+        <v>62.01</v>
       </c>
       <c r="E48" s="32" t="n">
-        <v>0.37</v>
+        <v>2.43</v>
       </c>
       <c r="F48" s="32" t="n">
-        <v>3.06</v>
+        <v>5.21</v>
       </c>
       <c r="G48" s="32" t="n">
-        <v>3.02</v>
+        <v>1.34</v>
       </c>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="32" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="J48" s="32" t="n">
-        <v>-35.64</v>
+        <v>-0.37</v>
       </c>
       <c r="K48" s="32" t="n">
-        <v>5.76</v>
+        <v>7.56</v>
       </c>
       <c r="L48" s="32" t="n">
-        <v>10.81</v>
+        <v>5.56</v>
       </c>
       <c r="M48" s="32" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
@@ -6177,7 +6181,7 @@
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>29 (C-)</t>
+          <t>28 (C-)</t>
         </is>
       </c>
       <c r="C49" s="32" t="n">
@@ -6190,7 +6194,7 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="32" t="n">
-        <v>5.62</v>
+        <v>5.79</v>
       </c>
       <c r="G49" s="32" t="n">
         <v>2.14</v>
@@ -6203,13 +6207,13 @@
         <v>86.01000000000001</v>
       </c>
       <c r="K49" s="32" t="n">
-        <v>6</v>
+        <v>5.15</v>
       </c>
       <c r="L49" s="32" t="n">
-        <v>0</v>
+        <v>-6.45</v>
       </c>
       <c r="M49" s="32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -6220,7 +6224,7 @@
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>23 (D)</t>
+          <t>25 (D)</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
@@ -6232,11 +6236,9 @@
       <c r="E50" s="32" t="n">
         <v>-1.13</v>
       </c>
-      <c r="F50" s="32" t="n">
-        <v>4.06</v>
-      </c>
+      <c r="F50" s="32" t="n"/>
       <c r="G50" s="32" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="32" t="n">
@@ -6246,13 +6248,13 @@
         <v>-10.94</v>
       </c>
       <c r="K50" s="32" t="n">
-        <v>7.77</v>
+        <v>7.71</v>
       </c>
       <c r="L50" s="32" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="M50" s="32" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -6263,7 +6265,7 @@
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>22 (D)</t>
+          <t>21 (D)</t>
         </is>
       </c>
       <c r="C51" s="32" t="n">
@@ -6276,7 +6278,7 @@
         <v>2.48</v>
       </c>
       <c r="F51" s="32" t="n">
-        <v>3.72</v>
+        <v>4.08</v>
       </c>
       <c r="G51" s="32" t="n">
         <v>0.12</v>
@@ -6289,13 +6291,13 @@
         <v>-15.51</v>
       </c>
       <c r="K51" s="32" t="n">
-        <v>7.51</v>
+        <v>7.83</v>
       </c>
       <c r="L51" s="32" t="n">
-        <v>5.13</v>
+        <v>8.33</v>
       </c>
       <c r="M51" s="32" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6393,7 @@
         </is>
       </c>
       <c r="D2" s="14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
@@ -6399,7 +6401,7 @@
         </is>
       </c>
       <c r="F2" s="14" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>4.5</v>
@@ -6411,44 +6413,44 @@
         <v>4.84</v>
       </c>
       <c r="J2" s="14" t="n">
-        <v>4.78</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G3" s="11" t="n">
+      <c r="D3" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="G3" s="14" t="n">
         <v>4.8</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H3" s="14" t="n">
         <v>63.61</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" s="14" t="n">
         <v>5.33</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J3" s="14" t="n">
         <v>5.59</v>
       </c>
     </row>
@@ -6467,7 +6469,7 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
@@ -6475,7 +6477,7 @@
         </is>
       </c>
       <c r="F4" s="17" t="n">
-        <v>39.9</v>
+        <v>38.8</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>4.5</v>
@@ -6487,7 +6489,7 @@
         <v>2.84</v>
       </c>
       <c r="J4" s="17" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="5">
@@ -6505,7 +6507,7 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
@@ -6513,7 +6515,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>53.6</v>
+        <v>52.7</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>3.6</v>
@@ -6525,7 +6527,7 @@
         <v>3.1</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="6">
@@ -6543,7 +6545,7 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
@@ -6551,7 +6553,7 @@
         </is>
       </c>
       <c r="F6" s="11" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>4.2</v>
@@ -6563,7 +6565,7 @@
         <v>2.61</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="7">
@@ -6581,7 +6583,7 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
@@ -6589,7 +6591,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>55.8</v>
+        <v>55.5</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>3.5</v>
@@ -6601,7 +6603,7 @@
         <v>7.12</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="8">
@@ -6627,7 +6629,7 @@
         </is>
       </c>
       <c r="F8" s="17" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>3.8</v>
@@ -6639,7 +6641,7 @@
         <v>1.37</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="9">
@@ -6657,7 +6659,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -6665,7 +6667,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>61.5</v>
+        <v>59.5</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>3.3</v>
@@ -6677,7 +6679,7 @@
         <v>8.27</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="10">
@@ -6703,7 +6705,7 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>55.2</v>
+        <v>55.3</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>4</v>
@@ -6715,7 +6717,7 @@
         <v>2.21</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -6733,7 +6735,7 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
@@ -6741,9 +6743,11 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="G11" s="8" t="n"/>
+        <v>58.8</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>3.5</v>
+      </c>
       <c r="H11" s="8" t="n">
         <v>66.34</v>
       </c>
@@ -6751,7 +6755,7 @@
         <v>4.52</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="12">
@@ -6769,7 +6773,7 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
@@ -6777,7 +6781,7 @@
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>48.4</v>
+        <v>46.7</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>3.9</v>
@@ -6789,7 +6793,7 @@
         <v>1.42</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="13">
@@ -6807,7 +6811,7 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
@@ -6815,7 +6819,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>36.4</v>
+        <v>35</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>5.1</v>
@@ -6827,7 +6831,7 @@
         <v>7.54</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="14">
@@ -6845,7 +6849,7 @@
         </is>
       </c>
       <c r="D14" s="23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
@@ -6853,7 +6857,7 @@
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>29.3</v>
+        <v>27.6</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>4.1</v>
@@ -6865,7 +6869,7 @@
         <v>0.49</v>
       </c>
       <c r="J14" s="23" t="n">
-        <v>5.62</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="15">
@@ -6883,7 +6887,7 @@
         </is>
       </c>
       <c r="D15" s="26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
@@ -6891,7 +6895,7 @@
         </is>
       </c>
       <c r="F15" s="26" t="n">
-        <v>22.6</v>
+        <v>25.1</v>
       </c>
       <c r="G15" s="26" t="n">
         <v>4.7</v>
@@ -6902,9 +6906,7 @@
       <c r="I15" s="26" t="n">
         <v>-1.13</v>
       </c>
-      <c r="J15" s="26" t="n">
-        <v>4.06</v>
-      </c>
+      <c r="J15" s="26" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n">
@@ -6921,7 +6923,7 @@
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
@@ -6929,7 +6931,7 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>46</v>
+        <v>45.2</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>5</v>
@@ -6941,45 +6943,45 @@
         <v>7.63</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G17" s="17" t="n">
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G17" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="14" t="n">
         <v>69.03</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="J17" s="17" t="n">
-        <v>2.83</v>
+      <c r="J17" s="14" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="18">
@@ -7005,7 +7007,7 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>4.6</v>
@@ -7017,7 +7019,7 @@
         <v>4.86</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="19">
@@ -7035,7 +7037,7 @@
         </is>
       </c>
       <c r="D19" s="23" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
@@ -7043,7 +7045,7 @@
         </is>
       </c>
       <c r="F19" s="23" t="n">
-        <v>31.7</v>
+        <v>29.4</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>4.4</v>
@@ -7055,7 +7057,7 @@
         <v>2.43</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="20">
@@ -7073,7 +7075,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
@@ -7081,7 +7083,7 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>57.5</v>
+        <v>58.9</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>3.6</v>
@@ -7093,7 +7095,7 @@
         <v>6.57</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="21">
@@ -7111,7 +7113,7 @@
         </is>
       </c>
       <c r="D21" s="23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
@@ -7119,7 +7121,7 @@
         </is>
       </c>
       <c r="F21" s="23" t="n">
-        <v>30.9</v>
+        <v>30.1</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>4.4</v>
@@ -7131,45 +7133,45 @@
         <v>0.37</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="G22" s="14" t="n">
+      <c r="D22" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="G22" s="11" t="n">
         <v>3.6</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="11" t="n">
         <v>65.43000000000001</v>
       </c>
-      <c r="I22" s="14" t="n">
+      <c r="I22" s="11" t="n">
         <v>-1.52</v>
       </c>
-      <c r="J22" s="14" t="n">
-        <v>3.62</v>
+      <c r="J22" s="11" t="n">
+        <v>3.46</v>
       </c>
     </row>
     <row r="23">
@@ -7195,7 +7197,7 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>3.6</v>
@@ -7207,7 +7209,7 @@
         <v>1.22</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="24">
@@ -7225,7 +7227,7 @@
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
@@ -7233,7 +7235,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>44.5</v>
+        <v>46.7</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>3.5</v>
@@ -7245,7 +7247,7 @@
         <v>0.66</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>4.24</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25">
@@ -7263,7 +7265,7 @@
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -7271,7 +7273,7 @@
         </is>
       </c>
       <c r="F25" s="11" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>3.7</v>
@@ -7283,44 +7285,44 @@
         <v>1.78</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G26" s="8" t="n">
+      <c r="D26" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="5" t="n">
         <v>73.98999999999999</v>
       </c>
-      <c r="I26" s="8" t="n">
+      <c r="I26" s="5" t="n">
         <v>3.18</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="J26" s="5" t="n">
         <v>1.44</v>
       </c>
     </row>
@@ -7339,7 +7341,7 @@
         </is>
       </c>
       <c r="D27" s="20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
@@ -7347,7 +7349,7 @@
         </is>
       </c>
       <c r="F27" s="20" t="n">
-        <v>35.4</v>
+        <v>33.4</v>
       </c>
       <c r="G27" s="20" t="n">
         <v>4.9</v>
@@ -7359,7 +7361,7 @@
         <v>4.78</v>
       </c>
       <c r="J27" s="20" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -7377,7 +7379,7 @@
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
@@ -7385,7 +7387,7 @@
         </is>
       </c>
       <c r="F28" s="26" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="G28" s="26" t="n">
         <v>4.8</v>
@@ -7397,7 +7399,7 @@
         <v>2.48</v>
       </c>
       <c r="J28" s="26" t="n">
-        <v>3.72</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="29">
@@ -7415,7 +7417,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -7423,7 +7425,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>64.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>3.6</v>
@@ -7435,7 +7437,7 @@
         <v>8.65</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="30">
@@ -7461,7 +7463,7 @@
         </is>
       </c>
       <c r="F30" s="17" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="G30" s="17" t="n">
         <v>5.2</v>
@@ -7473,7 +7475,7 @@
         <v>6.71</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="31">
@@ -7491,7 +7493,7 @@
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
@@ -7499,7 +7501,7 @@
         </is>
       </c>
       <c r="F31" s="20" t="n">
-        <v>36.2</v>
+        <v>36.5</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>3.6</v>
@@ -7511,7 +7513,7 @@
         <v>1.53</v>
       </c>
       <c r="J31" s="20" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="32">
@@ -7537,7 +7539,7 @@
         </is>
       </c>
       <c r="F32" s="11" t="n">
-        <v>51.5</v>
+        <v>52.4</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>3.5</v>
@@ -7549,7 +7551,7 @@
         <v>6.8</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="33">
@@ -7575,7 +7577,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>3.6</v>
@@ -7587,45 +7589,45 @@
         <v>0.86</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>2.99</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="G34" s="8" t="n">
+      <c r="D34" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G34" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="5" t="n">
         <v>66.86</v>
       </c>
-      <c r="I34" s="8" t="n">
+      <c r="I34" s="5" t="n">
         <v>5.1</v>
       </c>
-      <c r="J34" s="8" t="n">
-        <v>3.94</v>
+      <c r="J34" s="5" t="n">
+        <v>3.68</v>
       </c>
     </row>
     <row r="35">
@@ -7643,7 +7645,7 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
@@ -7651,7 +7653,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>43.6</v>
+        <v>41.5</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>3.4</v>
@@ -7681,7 +7683,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -7689,7 +7691,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>3</v>
@@ -7701,7 +7703,7 @@
         <v>1.62</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="37">
@@ -7719,7 +7721,7 @@
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
@@ -7727,7 +7729,7 @@
         </is>
       </c>
       <c r="F37" s="20" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="G37" s="20" t="n">
         <v>4</v>
@@ -7739,45 +7741,45 @@
         <v>0.59</v>
       </c>
       <c r="J37" s="20" t="n">
-        <v>6.96</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="G38" s="17" t="n">
+      <c r="D38" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="G38" s="20" t="n">
         <v>3.6</v>
       </c>
-      <c r="H38" s="17" t="n">
+      <c r="H38" s="20" t="n">
         <v>58.99</v>
       </c>
-      <c r="I38" s="17" t="n">
+      <c r="I38" s="20" t="n">
         <v>10.22</v>
       </c>
-      <c r="J38" s="17" t="n">
-        <v>1.57</v>
+      <c r="J38" s="20" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="39">
@@ -7795,7 +7797,7 @@
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
@@ -7803,7 +7805,7 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>46.5</v>
+        <v>44.8</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>4.6</v>
@@ -7815,7 +7817,7 @@
         <v>5</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="40">
@@ -7841,7 +7843,7 @@
         </is>
       </c>
       <c r="F40" s="17" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="G40" s="17" t="n">
         <v>4.3</v>
@@ -7853,7 +7855,7 @@
         <v>3.63</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>7.01</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="41">
@@ -7871,7 +7873,7 @@
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
@@ -7879,7 +7881,7 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>41.6</v>
+        <v>38.7</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>3.1</v>
@@ -7891,7 +7893,7 @@
         <v>3.73</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>3.7</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="42">
@@ -7917,7 +7919,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3</v>
@@ -7929,7 +7931,7 @@
         <v>4.51</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="43">
@@ -7955,7 +7957,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>3.6</v>
@@ -7967,7 +7969,7 @@
         <v>4.7</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="44">
@@ -7985,7 +7987,7 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
@@ -7993,7 +7995,7 @@
         </is>
       </c>
       <c r="F44" s="11" t="n">
-        <v>50.2</v>
+        <v>52.9</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>3.1</v>
@@ -8005,45 +8007,45 @@
         <v>3.37</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>3.32</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="G45" s="2" t="n">
+      <c r="D45" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="5" t="n">
         <v>64.23999999999999</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="I45" s="5" t="n">
         <v>5.12</v>
       </c>
-      <c r="J45" s="2" t="n">
-        <v>2.71</v>
+      <c r="J45" s="5" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="46">
@@ -8061,7 +8063,7 @@
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
@@ -8069,7 +8071,7 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>56.6</v>
+        <v>55.9</v>
       </c>
       <c r="G46" s="8" t="n">
         <v>4</v>
@@ -8081,7 +8083,7 @@
         <v>6.16</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="47">
@@ -8099,7 +8101,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -8107,7 +8109,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.4</v>
@@ -8119,45 +8121,45 @@
         <v>3.15</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="G48" s="5" t="n">
+      <c r="D48" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G48" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="H48" s="5" t="n">
+      <c r="H48" s="8" t="n">
         <v>60.56</v>
       </c>
-      <c r="I48" s="5" t="n">
+      <c r="I48" s="8" t="n">
         <v>-0.12</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>3.17</v>
+      <c r="J48" s="8" t="n">
+        <v>3.72</v>
       </c>
     </row>
     <row r="49">
@@ -8175,7 +8177,7 @@
         </is>
       </c>
       <c r="D49" s="17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
@@ -8183,7 +8185,7 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>39.7</v>
+        <v>39.3</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>8.199999999999999</v>
@@ -8195,7 +8197,7 @@
         <v>7.6</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="50">
@@ -8213,7 +8215,7 @@
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
@@ -8221,7 +8223,7 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>44.8</v>
+        <v>48.4</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>4</v>
@@ -8233,7 +8235,7 @@
         <v>3.13</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.76</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="51">
@@ -8251,7 +8253,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -8259,7 +8261,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8271,7 +8273,7 @@
         <v>-0.36</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
     </row>
   </sheetData>
@@ -8374,15 +8376,15 @@
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="G3" s="40" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8398,7 @@
         </is>
       </c>
       <c r="C4" s="39" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" s="39" t="inlineStr">
         <is>
@@ -8408,7 +8410,7 @@
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="G4" s="40" t="n">
@@ -8442,11 +8444,11 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="G5" s="40" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="40" t="inlineStr">
         <is>
@@ -8464,7 +8466,7 @@
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
@@ -8480,7 +8482,7 @@
         </is>
       </c>
       <c r="G6" s="40" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H6" s="40" t="inlineStr">
         <is>
@@ -8494,11 +8496,11 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C7" s="39" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" s="39" t="inlineStr">
         <is>
@@ -8514,7 +8516,7 @@
         </is>
       </c>
       <c r="G7" s="40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7" s="40" t="inlineStr">
         <is>
@@ -8528,11 +8530,11 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
@@ -8544,11 +8546,11 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="G8" s="40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H8" s="40" t="inlineStr">
         <is>
@@ -8562,15 +8564,15 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="E9" s="40" t="n">
@@ -8578,11 +8580,11 @@
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="G9" s="40" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H9" s="40" t="inlineStr">
         <is>
@@ -8596,7 +8598,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C10" s="39" t="n">
@@ -8616,7 +8618,7 @@
         </is>
       </c>
       <c r="G10" s="40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" s="40" t="inlineStr">
         <is>
@@ -8630,11 +8632,11 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D11" s="39" t="inlineStr">
         <is>
@@ -8650,7 +8652,7 @@
         </is>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H11" s="40" t="inlineStr">
         <is>
@@ -8664,7 +8666,7 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C12" s="39" t="n">
@@ -8684,7 +8686,7 @@
         </is>
       </c>
       <c r="G12" s="40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H12" s="40" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -729,16 +729,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>68.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -760,20 +760,20 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>68.8</v>
+        <v>68.2</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>64</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>63.7</v>
+        <v>64.2</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -945,52 +945,52 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="A11" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>57.8</v>
+        <v>55.5</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1007,83 +1007,83 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Houston-Pasadena-The Woodlands</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>San Francisco-Oakland-Fremont</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="F14" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Above Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Denver-Aurora-Centennial</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>55</v>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>53.5</v>
+        <v>54.9</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="D16" s="13" t="n">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1132,16 +1132,16 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>53.6</v>
+        <v>54</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="F18" s="11" t="n">
-        <v>53.5</v>
+        <v>53.2</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1238,96 +1238,96 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>New York Newark-Jersey City</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="F21" s="11" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>New York Newark-Jersey City</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="n">
+    <row r="22">
+      <c r="A22" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>San Diego-Chula Vista-Carlsbad</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1348,79 +1348,79 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Charlotte-Concord-Gastonia</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="A24" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="D25" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1442,20 +1442,20 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>49.3</v>
+        <v>48.3</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1473,20 +1473,20 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1566,20 +1566,20 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>47.4</v>
+        <v>44.8</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>45.8</v>
+        <v>44.2</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -1627,83 +1627,83 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Riverside-San Bernardino-Ontario</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="n">
+      <c r="A33" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>San Antonio-New Braunfels</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n">
         <v>44</v>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Sacramento-Roseville-Folsom</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F33" s="14" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
+      <c r="F34" s="14" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
         <is>
           <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
@@ -1720,60 +1720,60 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>Sacramento-Roseville-Folsom</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="A36" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Indianapolis-Carmel-Greenwood</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>44</v>
-      </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>43.6</v>
+        <v>42</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1783,20 +1783,20 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>42.4</v>
+        <v>41.4</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Grand Rapids</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>41.9</v>
+        <v>40.1</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F40" s="17" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="G40" s="18" t="inlineStr">
         <is>
@@ -1876,16 +1876,16 @@
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D41" s="19" t="n">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="G41" s="18" t="inlineStr">
         <is>
@@ -1907,20 +1907,20 @@
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="D42" s="22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>36.5</v>
+        <v>37.7</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>36.2</v>
+        <v>35.5</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -1969,16 +1969,16 @@
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D44" s="22" t="n">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -2000,20 +2000,20 @@
     </row>
     <row r="45">
       <c r="A45" s="20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>32.9</v>
+        <v>34.6</v>
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
@@ -2031,20 +2031,20 @@
     </row>
     <row r="46">
       <c r="A46" s="20" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D46" s="22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>32.3</v>
+        <v>34.3</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -2062,20 +2062,20 @@
     </row>
     <row r="47">
       <c r="A47" s="23" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F47" s="23" t="n">
-        <v>30.6</v>
+        <v>31.9</v>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="F48" s="23" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
@@ -2124,16 +2124,16 @@
     </row>
     <row r="49">
       <c r="A49" s="23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="D50" s="25" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="F50" s="23" t="n">
-        <v>26.4</v>
+        <v>28.7</v>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F51" s="26" t="n">
-        <v>23.9</v>
+        <v>22.8</v>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
@@ -2318,26 +2318,26 @@
         <v>74</v>
       </c>
       <c r="C2" s="30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" s="31" t="n">
+        <v>89</v>
+      </c>
+      <c r="E2" s="31" t="n">
         <v>85</v>
       </c>
-      <c r="E2" s="31" t="n">
-        <v>86</v>
-      </c>
       <c r="F2" s="31" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G2" s="32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H2" s="33" t="n"/>
       <c r="I2" s="31" t="n">
         <v>96</v>
       </c>
       <c r="J2" s="30" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K2" s="32" t="n">
         <v>4</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="B3" s="29" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="31" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" s="32" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" s="32" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="31" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G3" s="31" t="n">
         <v>98</v>
@@ -2372,80 +2372,80 @@
         <v>92</v>
       </c>
       <c r="J3" s="31" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K3" s="32" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B4" s="29" t="n">
         <v>69</v>
       </c>
-      <c r="C4" s="32" t="n">
-        <v>31</v>
+      <c r="C4" s="31" t="n">
+        <v>94</v>
       </c>
       <c r="D4" s="31" t="n">
-        <v>96</v>
-      </c>
-      <c r="E4" s="31" t="n">
-        <v>82</v>
-      </c>
-      <c r="F4" s="30" t="n">
-        <v>53</v>
-      </c>
-      <c r="G4" s="31" t="n">
-        <v>86</v>
+        <v>94</v>
+      </c>
+      <c r="E4" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="G4" s="32" t="n">
+        <v>43</v>
       </c>
       <c r="H4" s="33" t="n"/>
       <c r="I4" s="31" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J4" s="32" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="K4" s="31" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>69</v>
-      </c>
-      <c r="C5" s="31" t="n">
-        <v>94</v>
+        <v>68</v>
+      </c>
+      <c r="C5" s="32" t="n">
+        <v>30</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>92</v>
-      </c>
-      <c r="E5" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="32" t="n">
-        <v>49</v>
-      </c>
-      <c r="G5" s="32" t="n">
-        <v>42</v>
+        <v>96</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>81</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>52</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <v>85</v>
       </c>
       <c r="H5" s="33" t="n"/>
       <c r="I5" s="31" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K5" s="31" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -2455,32 +2455,32 @@
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" s="31" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E6" s="31" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" s="31" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G6" s="31" t="n">
         <v>96</v>
       </c>
       <c r="H6" s="33" t="n"/>
       <c r="I6" s="30" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K6" s="31" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -2493,16 +2493,16 @@
         <v>64</v>
       </c>
       <c r="C7" s="30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>38</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>50</v>
+        <v>40</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>49</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G7" s="31" t="n">
         <v>94</v>
@@ -2511,11 +2511,11 @@
       <c r="I7" s="31" t="n">
         <v>86</v>
       </c>
-      <c r="J7" s="31" t="n">
-        <v>70</v>
+      <c r="J7" s="30" t="n">
+        <v>68</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -2531,26 +2531,26 @@
         <v>98</v>
       </c>
       <c r="D8" s="30" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H8" s="33" t="n"/>
       <c r="I8" s="31" t="n">
         <v>88</v>
       </c>
       <c r="J8" s="31" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K8" s="32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -2562,30 +2562,30 @@
       <c r="B9" s="29" t="n">
         <v>63</v>
       </c>
-      <c r="C9" s="30" t="n">
-        <v>69</v>
+      <c r="C9" s="31" t="n">
+        <v>70</v>
       </c>
       <c r="D9" s="32" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="31" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" s="33" t="n"/>
       <c r="I9" s="31" t="n">
         <v>78</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -2598,274 +2598,274 @@
         <v>62</v>
       </c>
       <c r="C10" s="31" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" s="31" t="n">
         <v>98</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G10" s="31" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H10" s="33" t="n"/>
       <c r="I10" s="30" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J10" s="32" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="C11" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>55</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>49</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>87</v>
+      </c>
+      <c r="F11" s="31" t="n">
         <v>78</v>
       </c>
-      <c r="D11" s="32" t="n">
-        <v>31</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>80</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>76</v>
-      </c>
       <c r="G11" s="30" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H11" s="33" t="n"/>
       <c r="I11" s="30" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J11" s="32" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="K11" s="32" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>58</v>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>36</v>
       </c>
       <c r="D12" s="32" t="n">
-        <v>46</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>88</v>
-      </c>
-      <c r="F12" s="31" t="n">
+        <v>47</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>66</v>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>79</v>
+      </c>
+      <c r="H12" s="33" t="n"/>
+      <c r="I12" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="G12" s="30" t="n">
-        <v>62</v>
-      </c>
-      <c r="H12" s="33" t="n"/>
-      <c r="I12" s="30" t="n">
-        <v>50</v>
-      </c>
-      <c r="J12" s="32" t="n">
-        <v>40</v>
-      </c>
-      <c r="K12" s="32" t="n">
-        <v>20</v>
+      <c r="J12" s="31" t="n">
+        <v>81</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" s="32" t="n">
-        <v>37</v>
-      </c>
-      <c r="D13" s="32" t="n">
-        <v>44</v>
+        <v>36</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>57</v>
       </c>
       <c r="E13" s="30" t="n">
-        <v>68</v>
-      </c>
-      <c r="F13" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="31" t="n">
-        <v>78</v>
+        <v>51</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>96</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>64</v>
       </c>
       <c r="H13" s="33" t="n"/>
-      <c r="I13" s="31" t="n">
-        <v>80</v>
-      </c>
-      <c r="J13" s="31" t="n">
-        <v>83</v>
+      <c r="I13" s="30" t="n">
+        <v>59</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>30</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B14" s="29" t="n">
         <v>55</v>
       </c>
-      <c r="C14" s="31" t="n">
-        <v>90</v>
+      <c r="C14" s="32" t="n">
+        <v>47</v>
       </c>
       <c r="D14" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>58</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>71</v>
+        <v>32</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>15</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H14" s="33" t="n"/>
-      <c r="I14" s="32" t="n">
-        <v>44</v>
-      </c>
-      <c r="J14" s="32" t="n">
-        <v>26</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>66</v>
+      <c r="I14" s="31" t="n">
+        <v>76</v>
+      </c>
+      <c r="J14" s="31" t="n">
+        <v>96</v>
+      </c>
+      <c r="K14" s="33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>54</v>
-      </c>
-      <c r="C15" s="32" t="n">
-        <v>37</v>
-      </c>
-      <c r="D15" s="30" t="n">
-        <v>54</v>
-      </c>
-      <c r="E15" s="30" t="n">
-        <v>52</v>
-      </c>
-      <c r="F15" s="31" t="n">
-        <v>96</v>
-      </c>
-      <c r="G15" s="30" t="n">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>85</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="G15" s="31" t="n">
+        <v>81</v>
       </c>
       <c r="H15" s="33" t="n"/>
       <c r="I15" s="30" t="n">
-        <v>54</v>
-      </c>
-      <c r="J15" s="32" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" s="30" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="J15" s="31" t="n">
+        <v>94</v>
+      </c>
+      <c r="K15" s="31" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B16" s="29" t="n">
         <v>54</v>
       </c>
-      <c r="C16" s="30" t="n">
-        <v>55</v>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" s="30" t="n">
-        <v>57</v>
-      </c>
-      <c r="G16" s="30" t="n">
-        <v>52</v>
+      <c r="C16" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>79</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>74</v>
+      </c>
+      <c r="G16" s="32" t="n">
+        <v>40</v>
       </c>
       <c r="H16" s="33" t="n"/>
-      <c r="I16" s="32" t="n">
-        <v>32</v>
-      </c>
-      <c r="J16" s="31" t="n">
-        <v>74</v>
+      <c r="I16" s="31" t="n">
+        <v>71</v>
+      </c>
+      <c r="J16" s="30" t="n">
+        <v>50</v>
       </c>
       <c r="K16" s="32" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B17" s="29" t="n">
         <v>54</v>
       </c>
       <c r="C17" s="31" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D17" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" s="32" t="n">
-        <v>27</v>
-      </c>
-      <c r="G17" s="31" t="n">
-        <v>82</v>
+        <v>11</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>57</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>57</v>
       </c>
       <c r="H17" s="33" t="n"/>
-      <c r="I17" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="J17" s="31" t="n">
-        <v>96</v>
-      </c>
-      <c r="K17" s="31" t="n">
-        <v>92</v>
+      <c r="I17" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="J17" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="18">
@@ -2875,29 +2875,29 @@
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="31" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E18" s="31" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>98</v>
       </c>
-      <c r="G18" s="33" t="n">
-        <v>0</v>
+      <c r="G18" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="H18" s="33" t="n"/>
       <c r="I18" s="32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J18" s="31" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K18" s="32" t="n">
         <v>22</v>
@@ -2916,13 +2916,13 @@
         <v>0</v>
       </c>
       <c r="D19" s="31" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E19" s="31" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G19" s="32" t="n">
         <v>4</v>
@@ -2932,10 +2932,10 @@
         <v>82</v>
       </c>
       <c r="J19" s="32" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -2945,22 +2945,22 @@
         </is>
       </c>
       <c r="B20" s="29" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="D20" s="32" t="n">
-        <v>48</v>
+      <c r="D20" s="30" t="n">
+        <v>51</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F20" s="32" t="n">
         <v>2</v>
       </c>
       <c r="G20" s="31" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H20" s="33" t="n"/>
       <c r="I20" s="31" t="n">
@@ -2980,137 +2980,137 @@
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="32" t="n">
-        <v>24</v>
-      </c>
-      <c r="D21" s="30" t="n">
-        <v>67</v>
-      </c>
-      <c r="E21" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="D21" s="31" t="n">
         <v>70</v>
       </c>
+      <c r="E21" s="30" t="n">
+        <v>68</v>
+      </c>
       <c r="F21" s="32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" s="31" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H21" s="33" t="n"/>
       <c r="I21" s="30" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J21" s="31" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K21" s="32" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B22" s="29" t="n">
         <v>50</v>
       </c>
       <c r="C22" s="32" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D22" s="31" t="n">
-        <v>73</v>
-      </c>
-      <c r="E22" s="31" t="n">
-        <v>92</v>
+        <v>81</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>55</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>37</v>
-      </c>
-      <c r="G22" s="30" t="n">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="G22" s="32" t="n">
+        <v>49</v>
       </c>
       <c r="H22" s="33" t="n"/>
-      <c r="I22" s="32" t="n">
-        <v>16</v>
-      </c>
-      <c r="J22" s="31" t="n">
-        <v>89</v>
+      <c r="I22" s="30" t="n">
+        <v>69</v>
+      </c>
+      <c r="J22" s="30" t="n">
+        <v>55</v>
       </c>
       <c r="K22" s="32" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B23" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="C23" s="32" t="n">
-        <v>47</v>
-      </c>
-      <c r="D23" s="30" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" s="31" t="n">
-        <v>72</v>
+      <c r="C23" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="G23" s="32" t="n">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="G23" s="31" t="n">
+        <v>83</v>
       </c>
       <c r="H23" s="33" t="n"/>
       <c r="I23" s="31" t="n">
-        <v>70</v>
-      </c>
-      <c r="J23" s="30" t="n">
-        <v>50</v>
-      </c>
-      <c r="K23" s="33" t="n">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="J23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="31" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B24" s="29" t="n">
-        <v>50</v>
-      </c>
-      <c r="C24" s="30" t="n">
-        <v>59</v>
+        <v>49</v>
+      </c>
+      <c r="C24" s="32" t="n">
+        <v>45</v>
       </c>
       <c r="D24" s="31" t="n">
-        <v>88</v>
-      </c>
-      <c r="E24" s="33" t="n">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="E24" s="31" t="n">
+        <v>91</v>
       </c>
       <c r="F24" s="32" t="n">
-        <v>33</v>
-      </c>
-      <c r="G24" s="31" t="n">
-        <v>84</v>
+        <v>37</v>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>68</v>
       </c>
       <c r="H24" s="33" t="n"/>
-      <c r="I24" s="31" t="n">
-        <v>76</v>
-      </c>
-      <c r="J24" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" s="31" t="n">
-        <v>80</v>
+      <c r="I24" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="J24" s="31" t="n">
+        <v>87</v>
+      </c>
+      <c r="K24" s="32" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -3120,204 +3120,204 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="31" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D25" s="32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G25" s="31" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H25" s="33" t="n"/>
       <c r="I25" s="32" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J25" s="30" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K25" s="31" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B26" s="29" t="n">
         <v>49</v>
       </c>
-      <c r="C26" s="32" t="n">
-        <v>27</v>
+      <c r="C26" s="30" t="n">
+        <v>60</v>
       </c>
       <c r="D26" s="31" t="n">
-        <v>77</v>
-      </c>
-      <c r="E26" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="F26" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="G26" s="32" t="n">
-        <v>46</v>
+        <v>85</v>
+      </c>
+      <c r="E26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" s="30" t="n">
+        <v>50</v>
       </c>
       <c r="H26" s="33" t="n"/>
-      <c r="I26" s="30" t="n">
+      <c r="I26" s="32" t="n">
+        <v>49</v>
+      </c>
+      <c r="J26" s="30" t="n">
         <v>66</v>
       </c>
-      <c r="J26" s="30" t="n">
-        <v>57</v>
-      </c>
       <c r="K26" s="32" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="C27" s="30" t="n">
-        <v>59</v>
-      </c>
-      <c r="D27" s="31" t="n">
-        <v>81</v>
-      </c>
-      <c r="E27" s="32" t="n">
-        <v>2</v>
+        <v>48</v>
+      </c>
+      <c r="C27" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="D27" s="30" t="n">
+        <v>57</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>50</v>
       </c>
       <c r="F27" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="G27" s="31" t="n">
-        <v>76</v>
+      <c r="G27" s="30" t="n">
+        <v>60</v>
       </c>
       <c r="H27" s="33" t="n"/>
-      <c r="I27" s="32" t="n">
-        <v>48</v>
+      <c r="I27" s="30" t="n">
+        <v>53</v>
       </c>
       <c r="J27" s="30" t="n">
-        <v>68</v>
-      </c>
-      <c r="K27" s="32" t="n">
-        <v>38</v>
+        <v>60</v>
+      </c>
+      <c r="K27" s="31" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B28" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="C28" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="D28" s="31" t="n">
-        <v>79</v>
-      </c>
-      <c r="E28" s="32" t="n">
-        <v>28</v>
-      </c>
-      <c r="F28" s="33" t="n">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="C28" s="30" t="n">
+        <v>55</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="30" t="n">
+        <v>50</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H28" s="33" t="n"/>
-      <c r="I28" s="31" t="n">
-        <v>74</v>
+      <c r="I28" s="32" t="n">
+        <v>33</v>
       </c>
       <c r="J28" s="31" t="n">
-        <v>85</v>
-      </c>
-      <c r="K28" s="31" t="n">
-        <v>94</v>
+        <v>72</v>
+      </c>
+      <c r="K28" s="32" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B29" s="29" t="n">
         <v>48</v>
       </c>
       <c r="C29" s="32" t="n">
-        <v>27</v>
-      </c>
-      <c r="D29" s="30" t="n">
-        <v>54</v>
+        <v>15</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>83</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="F29" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="G29" s="30" t="n">
-        <v>54</v>
+        <v>26</v>
+      </c>
+      <c r="F29" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="31" t="n">
+        <v>70</v>
       </c>
       <c r="H29" s="33" t="n"/>
       <c r="I29" s="31" t="n">
-        <v>72</v>
-      </c>
-      <c r="J29" s="30" t="n">
-        <v>62</v>
+        <v>71</v>
+      </c>
+      <c r="J29" s="31" t="n">
+        <v>83</v>
       </c>
       <c r="K29" s="31" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B30" s="29" t="n">
         <v>47</v>
       </c>
-      <c r="C30" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="D30" s="31" t="n">
-        <v>94</v>
+      <c r="C30" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>30</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>16</v>
-      </c>
-      <c r="G30" s="31" t="n">
-        <v>80</v>
+        <v>30</v>
+      </c>
+      <c r="G30" s="32" t="n">
+        <v>21</v>
       </c>
       <c r="H30" s="33" t="n"/>
-      <c r="I30" s="30" t="n">
-        <v>68</v>
-      </c>
-      <c r="J30" s="32" t="n">
-        <v>30</v>
+      <c r="I30" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="J30" s="30" t="n">
+        <v>57</v>
       </c>
       <c r="K30" s="31" t="n">
         <v>78</v>
@@ -3326,36 +3326,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B31" s="29" t="n">
-        <v>47</v>
-      </c>
-      <c r="C31" s="31" t="n">
-        <v>92</v>
-      </c>
-      <c r="D31" s="32" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" s="32" t="n">
-        <v>26</v>
+        <v>45</v>
+      </c>
+      <c r="C31" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>68</v>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>83</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>29</v>
-      </c>
-      <c r="G31" s="32" t="n">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="G31" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="H31" s="33" t="n"/>
       <c r="I31" s="32" t="n">
-        <v>34</v>
-      </c>
-      <c r="J31" s="30" t="n">
-        <v>60</v>
-      </c>
-      <c r="K31" s="31" t="n">
-        <v>76</v>
+        <v>37</v>
+      </c>
+      <c r="J31" s="31" t="n">
+        <v>74</v>
+      </c>
+      <c r="K31" s="32" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -3365,277 +3365,277 @@
         </is>
       </c>
       <c r="B32" s="29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="30" t="n">
-        <v>50</v>
+      <c r="D32" s="32" t="n">
+        <v>17</v>
       </c>
       <c r="E32" s="31" t="n">
         <v>96</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H32" s="33" t="n"/>
       <c r="I32" s="32" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J32" s="30" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B33" s="29" t="n">
         <v>44</v>
       </c>
       <c r="C33" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="D33" s="30" t="n">
-        <v>65</v>
-      </c>
-      <c r="E33" s="31" t="n">
-        <v>84</v>
-      </c>
-      <c r="F33" s="32" t="n">
-        <v>39</v>
+        <v>49</v>
+      </c>
+      <c r="D33" s="31" t="n">
+        <v>79</v>
+      </c>
+      <c r="E33" s="32" t="n">
+        <v>36</v>
+      </c>
+      <c r="F33" s="31" t="n">
+        <v>91</v>
       </c>
       <c r="G33" s="32" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H33" s="33" t="n"/>
       <c r="I33" s="32" t="n">
-        <v>36</v>
-      </c>
-      <c r="J33" s="31" t="n">
-        <v>77</v>
+        <v>29</v>
+      </c>
+      <c r="J33" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="K33" s="32" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B34" s="29" t="n">
         <v>44</v>
       </c>
       <c r="C34" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D34" s="30" t="n">
-        <v>52</v>
-      </c>
-      <c r="E34" s="31" t="n">
-        <v>94</v>
-      </c>
-      <c r="F34" s="31" t="n">
-        <v>84</v>
+        <v>15</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="E34" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="F34" s="32" t="n">
+        <v>20</v>
       </c>
       <c r="G34" s="32" t="n">
         <v>32</v>
       </c>
       <c r="H34" s="33" t="n"/>
-      <c r="I34" s="32" t="n">
+      <c r="I34" s="31" t="n">
+        <v>84</v>
+      </c>
+      <c r="J34" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="J34" s="30" t="n">
-        <v>51</v>
-      </c>
-      <c r="K34" s="32" t="n">
-        <v>10</v>
+      <c r="K34" s="30" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B35" s="29" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="32" t="n">
-        <v>49</v>
-      </c>
-      <c r="D35" s="31" t="n">
-        <v>75</v>
-      </c>
-      <c r="E35" s="32" t="n">
-        <v>38</v>
+        <v>6</v>
+      </c>
+      <c r="D35" s="30" t="n">
+        <v>55</v>
+      </c>
+      <c r="E35" s="31" t="n">
+        <v>94</v>
       </c>
       <c r="F35" s="31" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G35" s="32" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H35" s="33" t="n"/>
       <c r="I35" s="32" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J35" s="32" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="K35" s="32" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B36" s="29" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="D36" s="30" t="n">
-        <v>67</v>
-      </c>
-      <c r="E36" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="F36" s="32" t="n">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="E36" s="30" t="n">
+        <v>64</v>
+      </c>
+      <c r="F36" s="31" t="n">
+        <v>89</v>
       </c>
       <c r="G36" s="32" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H36" s="33" t="n"/>
-      <c r="I36" s="31" t="n">
-        <v>84</v>
-      </c>
-      <c r="J36" s="32" t="n">
-        <v>28</v>
+      <c r="I36" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" s="31" t="n">
+        <v>79</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B37" s="29" t="n">
-        <v>44</v>
-      </c>
-      <c r="C37" s="32" t="n">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>96</v>
       </c>
       <c r="D37" s="32" t="n">
-        <v>25</v>
-      </c>
-      <c r="E37" s="30" t="n">
-        <v>66</v>
-      </c>
-      <c r="F37" s="31" t="n">
-        <v>90</v>
+        <v>21</v>
+      </c>
+      <c r="E37" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="F37" s="32" t="n">
+        <v>7</v>
       </c>
       <c r="G37" s="32" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H37" s="33" t="n"/>
       <c r="I37" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" s="31" t="n">
-        <v>81</v>
-      </c>
-      <c r="K37" s="30" t="n">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="J37" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="K37" s="31" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B38" s="29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="31" t="n">
-        <v>96</v>
-      </c>
-      <c r="D38" s="32" t="n">
-        <v>19</v>
+        <v>70</v>
+      </c>
+      <c r="D38" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E38" s="32" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F38" s="32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G38" s="32" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H38" s="33" t="n"/>
       <c r="I38" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="J38" s="32" t="n">
-        <v>45</v>
+        <v>27</v>
+      </c>
+      <c r="J38" s="31" t="n">
+        <v>89</v>
       </c>
       <c r="K38" s="31" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="C39" s="30" t="n">
-        <v>69</v>
-      </c>
-      <c r="D39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="32" t="n">
-        <v>42</v>
-      </c>
-      <c r="F39" s="32" t="n">
-        <v>8</v>
+        <v>40</v>
+      </c>
+      <c r="C39" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="D39" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E39" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="F39" s="30" t="n">
+        <v>50</v>
       </c>
       <c r="G39" s="32" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H39" s="33" t="n"/>
-      <c r="I39" s="32" t="n">
-        <v>28</v>
-      </c>
-      <c r="J39" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="K39" s="31" t="n">
-        <v>88</v>
+      <c r="I39" s="30" t="n">
+        <v>67</v>
+      </c>
+      <c r="J39" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="32" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -3647,27 +3647,27 @@
       <c r="B40" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="C40" s="30" t="n">
-        <v>69</v>
+      <c r="C40" s="31" t="n">
+        <v>70</v>
       </c>
       <c r="D40" s="30" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E40" s="32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G40" s="32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H40" s="33" t="n"/>
       <c r="I40" s="32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K40" s="31" t="n">
         <v>90</v>
@@ -3676,71 +3676,71 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B41" s="29" t="n">
         <v>38</v>
       </c>
       <c r="C41" s="32" t="n">
-        <v>37</v>
-      </c>
-      <c r="D41" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="31" t="n">
-        <v>98</v>
-      </c>
-      <c r="F41" s="31" t="n">
-        <v>73</v>
-      </c>
-      <c r="G41" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="F41" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="G41" s="30" t="n">
+        <v>51</v>
+      </c>
+      <c r="H41" s="33" t="n"/>
+      <c r="I41" s="30" t="n">
+        <v>55</v>
+      </c>
+      <c r="J41" s="32" t="n">
         <v>28</v>
       </c>
-      <c r="H41" s="33" t="n"/>
-      <c r="I41" s="32" t="n">
-        <v>22</v>
-      </c>
-      <c r="J41" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="32" t="n">
-        <v>14</v>
+      <c r="K41" s="31" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B42" s="29" t="n">
+        <v>38</v>
+      </c>
+      <c r="C42" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="C42" s="32" t="n">
-        <v>18</v>
-      </c>
       <c r="D42" s="32" t="n">
-        <v>40</v>
-      </c>
-      <c r="E42" s="32" t="n">
-        <v>16</v>
-      </c>
-      <c r="F42" s="30" t="n">
-        <v>61</v>
+        <v>4</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>98</v>
+      </c>
+      <c r="F42" s="31" t="n">
+        <v>72</v>
       </c>
       <c r="G42" s="32" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H42" s="33" t="n"/>
       <c r="I42" s="32" t="n">
-        <v>42</v>
-      </c>
-      <c r="J42" s="30" t="n">
-        <v>50</v>
-      </c>
-      <c r="K42" s="30" t="n">
-        <v>68</v>
+        <v>20</v>
+      </c>
+      <c r="J42" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="32" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="43">
@@ -3753,169 +3753,169 @@
         <v>36</v>
       </c>
       <c r="C43" s="31" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D43" s="32" t="n">
         <v>2</v>
       </c>
       <c r="E43" s="32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F43" s="32" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G43" s="32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H43" s="33" t="n"/>
       <c r="I43" s="32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J43" s="32" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K43" s="32" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B44" s="29" t="n">
         <v>35</v>
       </c>
       <c r="C44" s="32" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D44" s="32" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E44" s="32" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G44" s="32" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H44" s="33" t="n"/>
       <c r="I44" s="32" t="n">
-        <v>46</v>
-      </c>
-      <c r="J44" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K44" s="32" t="n">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="J44" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="K44" s="30" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B45" s="29" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C45" s="32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D45" s="32" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E45" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="F45" s="32" t="n">
-        <v>45</v>
+        <v>15</v>
+      </c>
+      <c r="F45" s="30" t="n">
+        <v>59</v>
       </c>
       <c r="G45" s="32" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H45" s="33" t="n"/>
       <c r="I45" s="32" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J45" s="32" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B46" s="29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D46" s="30" t="n">
-        <v>50</v>
-      </c>
-      <c r="E46" s="31" t="n">
-        <v>78</v>
-      </c>
-      <c r="F46" s="31" t="n">
-        <v>86</v>
+        <v>30</v>
+      </c>
+      <c r="D46" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" s="32" t="n">
+        <v>47</v>
+      </c>
+      <c r="F46" s="32" t="n">
+        <v>46</v>
       </c>
       <c r="G46" s="32" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H46" s="33" t="n"/>
       <c r="I46" s="32" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="J46" s="32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K46" s="32" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C47" s="32" t="n">
-        <v>31</v>
-      </c>
-      <c r="D47" s="32" t="n">
-        <v>17</v>
-      </c>
-      <c r="E47" s="32" t="n">
-        <v>32</v>
-      </c>
-      <c r="F47" s="30" t="n">
-        <v>65</v>
+        <v>6</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>53</v>
+      </c>
+      <c r="E47" s="31" t="n">
+        <v>77</v>
+      </c>
+      <c r="F47" s="31" t="n">
+        <v>85</v>
       </c>
       <c r="G47" s="32" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H47" s="33" t="n"/>
       <c r="I47" s="32" t="n">
         <v>4</v>
       </c>
       <c r="J47" s="32" t="n">
-        <v>36</v>
-      </c>
-      <c r="K47" s="31" t="n">
-        <v>96</v>
+        <v>9</v>
+      </c>
+      <c r="K47" s="32" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="48">
@@ -3931,23 +3931,23 @@
         <v>49</v>
       </c>
       <c r="D48" s="32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E48" s="30" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F48" s="32" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G48" s="31" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H48" s="33" t="n"/>
       <c r="I48" s="32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J48" s="32" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K48" s="32" t="n">
         <v>6</v>
@@ -3956,36 +3956,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B49" s="29" t="n">
         <v>30</v>
       </c>
       <c r="C49" s="32" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D49" s="32" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E49" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="F49" s="32" t="n">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="F49" s="30" t="n">
+        <v>63</v>
       </c>
       <c r="G49" s="32" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H49" s="33" t="n"/>
-      <c r="I49" s="30" t="n">
-        <v>64</v>
+      <c r="I49" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="J49" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="K49" s="32" t="n">
-        <v>12</v>
+        <v>36</v>
+      </c>
+      <c r="K49" s="31" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="50">
@@ -3995,32 +3995,32 @@
         </is>
       </c>
       <c r="B50" s="29" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C50" s="32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D50" s="32" t="n">
         <v>6</v>
       </c>
       <c r="E50" s="32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>59</v>
-      </c>
-      <c r="G50" s="32" t="n">
-        <v>34</v>
+        <v>57</v>
+      </c>
+      <c r="G50" s="30" t="n">
+        <v>50</v>
       </c>
       <c r="H50" s="33" t="n"/>
-      <c r="I50" s="33" t="n">
+      <c r="I50" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="J50" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="K50" s="33" t="n">
         <v>0</v>
-      </c>
-      <c r="J50" s="30" t="n">
-        <v>55</v>
-      </c>
-      <c r="K50" s="31" t="n">
-        <v>86</v>
       </c>
     </row>
     <row r="51">
@@ -4030,29 +4030,29 @@
         </is>
       </c>
       <c r="B51" s="29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" s="32" t="n">
         <v>4</v>
       </c>
       <c r="D51" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E51" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="F51" s="30" t="n">
+        <v>61</v>
+      </c>
+      <c r="G51" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="H51" s="33" t="n"/>
+      <c r="I51" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="32" t="n">
         <v>21</v>
-      </c>
-      <c r="E51" s="30" t="n">
-        <v>62</v>
-      </c>
-      <c r="F51" s="30" t="n">
-        <v>63</v>
-      </c>
-      <c r="G51" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="H51" s="33" t="n"/>
-      <c r="I51" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="32" t="n">
-        <v>23</v>
       </c>
       <c r="K51" s="32" t="n">
         <v>16</v>
@@ -4175,10 +4175,10 @@
         <v>6.97</v>
       </c>
       <c r="F2" s="33" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="H2" s="33" t="n"/>
       <c r="I2" s="33" t="n">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>73 (A+)</t>
+          <t>72 (A+)</t>
         </is>
       </c>
       <c r="C3" s="33" t="n">
@@ -4218,10 +4218,10 @@
         <v>3.97</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>4.54</v>
+        <v>4.61</v>
       </c>
       <c r="H3" s="33" t="n"/>
       <c r="I3" s="33" t="n">
@@ -4243,7 +4243,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B4" s="34" t="inlineStr">
@@ -4252,78 +4252,78 @@
         </is>
       </c>
       <c r="C4" s="33" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="D4" s="33" t="n">
-        <v>3.24</v>
+        <v>2.77</v>
       </c>
       <c r="E4" s="33" t="n">
-        <v>6.67</v>
+        <v>0.13</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>3.57</v>
+        <v>2.48</v>
       </c>
       <c r="H4" s="33" t="n"/>
       <c r="I4" s="33" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="J4" s="33" t="n">
-        <v>-9.83</v>
+        <v>-12.7</v>
       </c>
       <c r="K4" s="33" t="n">
-        <v>7.97</v>
+        <v>10</v>
       </c>
       <c r="L4" s="33" t="n">
-        <v>18.18</v>
+        <v>30</v>
       </c>
       <c r="M4" s="33" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>69 (A+)</t>
+          <t>68 (A+)</t>
         </is>
       </c>
       <c r="C5" s="33" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="D5" s="33" t="n">
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
       <c r="E5" s="33" t="n">
-        <v>0.13</v>
+        <v>6.67</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>2.72</v>
+        <v>2.31</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>2.44</v>
+        <v>3.58</v>
       </c>
       <c r="H5" s="33" t="n"/>
       <c r="I5" s="33" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="J5" s="33" t="n">
-        <v>-12.7</v>
+        <v>-9.83</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>10</v>
+        <v>7.97</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>30</v>
+        <v>18.18</v>
       </c>
       <c r="M5" s="33" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>65 (A)</t>
         </is>
       </c>
       <c r="C6" s="33" t="n">
@@ -4347,10 +4347,10 @@
         <v>5.84</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>4.52</v>
+        <v>4.59</v>
       </c>
       <c r="H6" s="33" t="n"/>
       <c r="I6" s="33" t="n">
@@ -4390,10 +4390,10 @@
         <v>4.04</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>4.49</v>
+        <v>4.54</v>
       </c>
       <c r="H7" s="33" t="n"/>
       <c r="I7" s="33" t="n">
@@ -4433,10 +4433,10 @@
         <v>-0.46</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="H8" s="33" t="n"/>
       <c r="I8" s="33" t="n">
@@ -4476,10 +4476,10 @@
         <v>4.36</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="H9" s="33" t="n"/>
       <c r="I9" s="33" t="n">
@@ -4519,10 +4519,10 @@
         <v>2.31</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="H10" s="33" t="n"/>
       <c r="I10" s="33" t="n">
@@ -4544,222 +4544,222 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>60 (A-)</t>
+          <t>58 (B+)</t>
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>0.51</v>
+        <v>0.73</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>6.47</v>
+        <v>7</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="H11" s="33" t="n"/>
       <c r="I11" s="33" t="n">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
       <c r="J11" s="33" t="n">
-        <v>-30.9</v>
+        <v>-10.55</v>
       </c>
       <c r="K11" s="33" t="n">
-        <v>7.51</v>
+        <v>6.84</v>
       </c>
       <c r="L11" s="33" t="n">
-        <v>8.51</v>
+        <v>4.84</v>
       </c>
       <c r="M11" s="33" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>56 (B+)</t>
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>7</v>
+        <v>5.44</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.44</v>
+        <v>5.63</v>
       </c>
       <c r="G12" s="33" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="H12" s="33" t="n"/>
       <c r="I12" s="33" t="n">
-        <v>0.31</v>
+        <v>1.83</v>
       </c>
       <c r="J12" s="33" t="n">
-        <v>-10.55</v>
+        <v>20.24</v>
       </c>
       <c r="K12" s="33" t="n">
-        <v>6.84</v>
+        <v>7.71</v>
       </c>
       <c r="L12" s="33" t="n">
-        <v>4.84</v>
+        <v>7.14</v>
       </c>
       <c r="M12" s="33" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>56 (B+)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>5.44</v>
+        <v>4.13</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>5.65</v>
+        <v>1.01</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>3.37</v>
+        <v>3.03</v>
       </c>
       <c r="H13" s="33" t="n"/>
       <c r="I13" s="33" t="n">
-        <v>1.83</v>
+        <v>0.71</v>
       </c>
       <c r="J13" s="33" t="n">
-        <v>20.24</v>
+        <v>-12.89</v>
       </c>
       <c r="K13" s="33" t="n">
-        <v>7.71</v>
+        <v>7.74</v>
       </c>
       <c r="L13" s="33" t="n">
-        <v>7.14</v>
+        <v>11.11</v>
       </c>
       <c r="M13" s="33" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>55 (B)</t>
+          <t>55 (B+)</t>
         </is>
       </c>
       <c r="C14" s="33" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="D14" s="33" t="n">
-        <v>-1.5</v>
+        <v>0.43</v>
       </c>
       <c r="E14" s="33" t="n">
-        <v>4.74</v>
+        <v>5.54</v>
       </c>
       <c r="F14" s="33" t="n">
-        <v>1.69</v>
+        <v>4.52</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="H14" s="33" t="n"/>
       <c r="I14" s="33" t="n">
-        <v>-0.1</v>
+        <v>0.65</v>
       </c>
       <c r="J14" s="33" t="n">
-        <v>-15.96</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="K14" s="33" t="n">
-        <v>7.86</v>
+        <v>5.15</v>
       </c>
       <c r="L14" s="33" t="n">
-        <v>8.57</v>
+        <v>-6.45</v>
       </c>
       <c r="M14" s="33" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C15" s="33" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>0.93</v>
+        <v>-0.79</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>4.13</v>
+        <v>0.55</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>1.02</v>
+        <v>3.61</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>2.96</v>
+        <v>3.42</v>
       </c>
       <c r="H15" s="33" t="n"/>
       <c r="I15" s="33" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="J15" s="33" t="n">
-        <v>-12.89</v>
+        <v>57.47</v>
       </c>
       <c r="K15" s="33" t="n">
-        <v>7.74</v>
+        <v>9.16</v>
       </c>
       <c r="L15" s="33" t="n">
-        <v>11.11</v>
+        <v>21.62</v>
       </c>
       <c r="M15" s="33" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
@@ -4767,42 +4767,36 @@
           <t>54 (B)</t>
         </is>
       </c>
-      <c r="C16" s="33" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="C16" s="33" t="n"/>
       <c r="D16" s="33" t="n">
-        <v>2.36</v>
+        <v>0.51</v>
       </c>
       <c r="E16" s="33" t="n">
-        <v>4.87</v>
+        <v>6.47</v>
       </c>
       <c r="F16" s="33" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>2.82</v>
+        <v>2.47</v>
       </c>
       <c r="H16" s="33" t="n"/>
-      <c r="I16" s="33" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="J16" s="33" t="n">
-        <v>16.86</v>
-      </c>
+      <c r="I16" s="33" t="n"/>
+      <c r="J16" s="33" t="n"/>
       <c r="K16" s="33" t="n">
-        <v>7.24</v>
+        <v>7.51</v>
       </c>
       <c r="L16" s="33" t="n">
-        <v>5.88</v>
+        <v>8.51</v>
       </c>
       <c r="M16" s="33" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
@@ -4814,32 +4808,32 @@
         <v>3.6</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>-0.79</v>
+        <v>-1.5</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>0.55</v>
+        <v>4.74</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>3.62</v>
+        <v>1.68</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="H17" s="33" t="n"/>
       <c r="I17" s="33" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>57.47</v>
+        <v>-15.96</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>9.16</v>
+        <v>7.86</v>
       </c>
       <c r="L17" s="33" t="n">
-        <v>21.62</v>
+        <v>8.57</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -4850,7 +4844,7 @@
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>53 (B)</t>
         </is>
       </c>
       <c r="C18" s="33" t="n">
@@ -4863,10 +4857,10 @@
         <v>6.12</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="G18" s="33" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H18" s="33" t="n"/>
       <c r="I18" s="33" t="n">
@@ -4906,10 +4900,10 @@
         <v>8.369999999999999</v>
       </c>
       <c r="F19" s="33" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="G19" s="33" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="H19" s="33" t="n"/>
       <c r="I19" s="33" t="n">
@@ -4936,7 +4930,7 @@
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>52 (B)</t>
         </is>
       </c>
       <c r="C20" s="33" t="n">
@@ -4949,10 +4943,10 @@
         <v>0.65</v>
       </c>
       <c r="F20" s="33" t="n">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
       <c r="G20" s="33" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="H20" s="33" t="n"/>
       <c r="I20" s="33" t="n">
@@ -4979,7 +4973,7 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>50 (B-)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C21" s="33" t="n">
@@ -4992,10 +4986,10 @@
         <v>5.47</v>
       </c>
       <c r="F21" s="33" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="G21" s="33" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="H21" s="33" t="n"/>
       <c r="I21" s="33" t="n">
@@ -5017,50 +5011,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>50 (B-)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C22" s="33" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="D22" s="33" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="E22" s="33" t="n">
-        <v>8.390000000000001</v>
+        <v>4.58</v>
       </c>
       <c r="F22" s="33" t="n">
-        <v>3.16</v>
+        <v>4.9</v>
       </c>
       <c r="G22" s="33" t="n">
-        <v>2.99</v>
+        <v>2.58</v>
       </c>
       <c r="H22" s="33" t="n"/>
       <c r="I22" s="33" t="n">
-        <v>-0.7</v>
+        <v>0.7</v>
       </c>
       <c r="J22" s="33" t="n">
-        <v>41.11</v>
+        <v>-0.37</v>
       </c>
       <c r="K22" s="33" t="n">
-        <v>6.02</v>
+        <v>7.56</v>
       </c>
       <c r="L22" s="33" t="n">
-        <v>10.45</v>
+        <v>5.56</v>
       </c>
       <c r="M22" s="33" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
@@ -5069,72 +5063,78 @@
         </is>
       </c>
       <c r="C23" s="33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D23" s="33" t="n"/>
+        <v>3.6</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>2.28</v>
+      </c>
       <c r="E23" s="33" t="n">
-        <v>5.54</v>
+        <v>-1.28</v>
       </c>
       <c r="F23" s="33" t="n">
-        <v>4.53</v>
+        <v>3.26</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>2.08</v>
+        <v>3.58</v>
       </c>
       <c r="H23" s="33" t="n"/>
-      <c r="I23" s="33" t="n"/>
-      <c r="J23" s="33" t="n"/>
+      <c r="I23" s="33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J23" s="33" t="n">
+        <v>-39.5</v>
+      </c>
       <c r="K23" s="33" t="n">
-        <v>5.15</v>
+        <v>8.02</v>
       </c>
       <c r="L23" s="33" t="n">
-        <v>-6.45</v>
+        <v>13.95</v>
       </c>
       <c r="M23" s="33" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C24" s="33" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D24" s="33" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="E24" s="33" t="n">
-        <v>-1.28</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>3.27</v>
+        <v>3.14</v>
       </c>
       <c r="G24" s="33" t="n">
-        <v>3.54</v>
+        <v>3.06</v>
       </c>
       <c r="H24" s="33" t="n"/>
       <c r="I24" s="33" t="n">
-        <v>0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="J24" s="33" t="n">
-        <v>-39.5</v>
+        <v>41.11</v>
       </c>
       <c r="K24" s="33" t="n">
-        <v>8.02</v>
+        <v>6.02</v>
       </c>
       <c r="L24" s="33" t="n">
-        <v>13.95</v>
+        <v>10.45</v>
       </c>
       <c r="M24" s="33" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C25" s="33" t="n">
@@ -5158,10 +5158,10 @@
         <v>3.05</v>
       </c>
       <c r="F25" s="33" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G25" s="33" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="H25" s="33" t="n"/>
       <c r="I25" s="33" t="n">
@@ -5183,7 +5183,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B26" s="34" t="inlineStr">
@@ -5192,125 +5192,109 @@
         </is>
       </c>
       <c r="C26" s="33" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="D26" s="33" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="E26" s="33" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="F26" s="33" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="G26" s="33" t="n">
-        <v>2.54</v>
-      </c>
+        <v>-0.77</v>
+      </c>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
       <c r="H26" s="33" t="n"/>
       <c r="I26" s="33" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="J26" s="33" t="n">
-        <v>-0.37</v>
+        <v>11.14</v>
       </c>
       <c r="K26" s="33" t="n">
-        <v>7.56</v>
+        <v>7.26</v>
       </c>
       <c r="L26" s="33" t="n">
-        <v>5.56</v>
+        <v>7.84</v>
       </c>
       <c r="M26" s="33" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="n">
-        <v>3.4</v>
-      </c>
+          <t>48 (B-)</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="n"/>
       <c r="D27" s="33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E27" s="33" t="n">
-        <v>-0.77</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="E27" s="33" t="n"/>
       <c r="F27" s="33" t="n"/>
       <c r="G27" s="33" t="n">
-        <v>3.29</v>
+        <v>2.96</v>
       </c>
       <c r="H27" s="33" t="n"/>
       <c r="I27" s="33" t="n">
-        <v>0.57</v>
+        <v>0.27</v>
       </c>
       <c r="J27" s="33" t="n">
-        <v>11.14</v>
+        <v>4.14</v>
       </c>
       <c r="K27" s="33" t="n">
-        <v>7.26</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L27" s="33" t="n">
-        <v>7.84</v>
+        <v>10.26</v>
       </c>
       <c r="M27" s="33" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C28" s="33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D28" s="33" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E28" s="33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F28" s="33" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="G28" s="33" t="n">
-        <v>3.06</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
       <c r="H28" s="33" t="n"/>
       <c r="I28" s="33" t="n">
-        <v>0.6</v>
+        <v>-0.28</v>
       </c>
       <c r="J28" s="33" t="n">
-        <v>23.5</v>
+        <v>16.86</v>
       </c>
       <c r="K28" s="33" t="n">
-        <v>9.4</v>
+        <v>7.24</v>
       </c>
       <c r="L28" s="33" t="n">
-        <v>33.33</v>
+        <v>5.88</v>
       </c>
       <c r="M28" s="33" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B29" s="34" t="inlineStr">
@@ -5319,41 +5303,41 @@
         </is>
       </c>
       <c r="C29" s="33" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="D29" s="33" t="n">
-        <v>0.93</v>
+        <v>1.69</v>
       </c>
       <c r="E29" s="33" t="n">
-        <v>1.61</v>
+        <v>2.78</v>
       </c>
       <c r="F29" s="33" t="n">
-        <v>3.26</v>
+        <v>7.36</v>
       </c>
       <c r="G29" s="33" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="H29" s="33" t="n"/>
       <c r="I29" s="33" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="J29" s="33" t="n">
-        <v>4.14</v>
+        <v>23.5</v>
       </c>
       <c r="K29" s="33" t="n">
-        <v>8.029999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L29" s="33" t="n">
-        <v>10.26</v>
+        <v>33.33</v>
       </c>
       <c r="M29" s="33" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B30" s="34" t="inlineStr">
@@ -5362,78 +5346,78 @@
         </is>
       </c>
       <c r="C30" s="33" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="D30" s="33" t="n">
-        <v>2.87</v>
+        <v>0.38</v>
       </c>
       <c r="E30" s="33" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F30" s="33" t="n">
         <v>3.37</v>
       </c>
-      <c r="F30" s="33" t="n">
-        <v>4.38</v>
-      </c>
       <c r="G30" s="33" t="n">
-        <v>3.38</v>
+        <v>1.35</v>
       </c>
       <c r="H30" s="33" t="n"/>
       <c r="I30" s="33" t="n">
-        <v>0.73</v>
+        <v>-0.24</v>
       </c>
       <c r="J30" s="33" t="n">
-        <v>-14.97</v>
+        <v>2.98</v>
       </c>
       <c r="K30" s="33" t="n">
-        <v>8</v>
+        <v>7.98</v>
       </c>
       <c r="L30" s="33" t="n">
-        <v>20</v>
+        <v>9.76</v>
       </c>
       <c r="M30" s="33" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C31" s="33" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="D31" s="33" t="n">
-        <v>0.38</v>
+        <v>1.15</v>
       </c>
       <c r="E31" s="33" t="n">
-        <v>2.36</v>
+        <v>6.68</v>
       </c>
       <c r="F31" s="33" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="G31" s="33" t="n">
-        <v>1.32</v>
+        <v>0.3</v>
       </c>
       <c r="H31" s="33" t="n"/>
       <c r="I31" s="33" t="n">
-        <v>-0.24</v>
+        <v>0.88</v>
       </c>
       <c r="J31" s="33" t="n">
-        <v>2.98</v>
+        <v>18.04</v>
       </c>
       <c r="K31" s="33" t="n">
-        <v>7.98</v>
+        <v>7.24</v>
       </c>
       <c r="L31" s="33" t="n">
-        <v>9.76</v>
+        <v>5.88</v>
       </c>
       <c r="M31" s="33" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32">
@@ -5444,27 +5428,31 @@
       </c>
       <c r="B32" s="34" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>44 (B-)</t>
         </is>
       </c>
       <c r="C32" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="33" t="n"/>
+      <c r="D32" s="33" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="E32" s="33" t="n">
         <v>9.02</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="G32" s="33" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="H32" s="33" t="n"/>
       <c r="I32" s="33" t="n">
         <v>-0.08</v>
       </c>
-      <c r="J32" s="33" t="n"/>
+      <c r="J32" s="33" t="n">
+        <v>-0.7</v>
+      </c>
       <c r="K32" s="33" t="n">
         <v>7.77</v>
       </c>
@@ -5478,302 +5466,296 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>44 (C+)</t>
         </is>
       </c>
       <c r="C33" s="33" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="D33" s="33" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="E33" s="33" t="n">
-        <v>6.68</v>
+        <v>3.43</v>
       </c>
       <c r="F33" s="33" t="n">
-        <v>3.14</v>
+        <v>1.09</v>
       </c>
       <c r="G33" s="33" t="n">
-        <v>0.34</v>
+        <v>1.63</v>
       </c>
       <c r="H33" s="33" t="n"/>
       <c r="I33" s="33" t="n">
-        <v>0.88</v>
+        <v>0.43</v>
       </c>
       <c r="J33" s="33" t="n">
-        <v>18.04</v>
+        <v>-37.55</v>
       </c>
       <c r="K33" s="33" t="n">
-        <v>7.24</v>
+        <v>6.99</v>
       </c>
       <c r="L33" s="33" t="n">
-        <v>5.88</v>
+        <v>1.67</v>
       </c>
       <c r="M33" s="33" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>44 (B-)</t>
         </is>
       </c>
       <c r="C34" s="33" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D34" s="33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E34" s="33" t="n">
-        <v>8.81</v>
+        <v>3.02</v>
       </c>
       <c r="F34" s="33" t="n">
-        <v>1.43</v>
+        <v>4.25</v>
       </c>
       <c r="G34" s="33" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="H34" s="33" t="n"/>
       <c r="I34" s="33" t="n">
-        <v>-0.22</v>
+        <v>1</v>
       </c>
       <c r="J34" s="33" t="n">
-        <v>-8.56</v>
+        <v>-15.51</v>
       </c>
       <c r="K34" s="33" t="n">
-        <v>6.37</v>
+        <v>7.83</v>
       </c>
       <c r="L34" s="33" t="n">
-        <v>15.79</v>
+        <v>8.33</v>
       </c>
       <c r="M34" s="33" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>43 (C+)</t>
         </is>
       </c>
       <c r="C35" s="33" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="D35" s="33" t="n">
-        <v>1.47</v>
+        <v>0.8</v>
       </c>
       <c r="E35" s="33" t="n">
-        <v>3.43</v>
+        <v>8.81</v>
       </c>
       <c r="F35" s="33" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="G35" s="33" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="H35" s="33" t="n"/>
       <c r="I35" s="33" t="n">
-        <v>0.43</v>
+        <v>-0.22</v>
       </c>
       <c r="J35" s="33" t="n">
-        <v>-37.55</v>
+        <v>-8.56</v>
       </c>
       <c r="K35" s="33" t="n">
-        <v>6.99</v>
+        <v>6.37</v>
       </c>
       <c r="L35" s="33" t="n">
-        <v>1.67</v>
+        <v>15.79</v>
       </c>
       <c r="M35" s="33" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>43 (C+)</t>
         </is>
       </c>
       <c r="C36" s="33" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="D36" s="33" t="n">
-        <v>1.2</v>
+        <v>0.23</v>
       </c>
       <c r="E36" s="33" t="n">
-        <v>3.02</v>
+        <v>5.38</v>
       </c>
       <c r="F36" s="33" t="n">
-        <v>4.27</v>
+        <v>1.11</v>
       </c>
       <c r="G36" s="33" t="n">
-        <v>1.76</v>
+        <v>1.17</v>
       </c>
       <c r="H36" s="33" t="n"/>
       <c r="I36" s="33" t="n">
-        <v>1</v>
+        <v>-0.54</v>
       </c>
       <c r="J36" s="33" t="n">
-        <v>-15.51</v>
+        <v>20.14</v>
       </c>
       <c r="K36" s="33" t="n">
-        <v>7.83</v>
+        <v>7.57</v>
       </c>
       <c r="L36" s="33" t="n">
-        <v>8.33</v>
+        <v>17.02</v>
       </c>
       <c r="M36" s="33" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>42 (C+)</t>
         </is>
       </c>
       <c r="C37" s="33" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="D37" s="33" t="n">
-        <v>0.23</v>
+        <v>-0.36</v>
       </c>
       <c r="E37" s="33" t="n">
-        <v>5.38</v>
+        <v>3.99</v>
       </c>
       <c r="F37" s="33" t="n">
-        <v>1.13</v>
+        <v>5.25</v>
       </c>
       <c r="G37" s="33" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="H37" s="33" t="n"/>
       <c r="I37" s="33" t="n">
-        <v>-0.54</v>
+        <v>-0.66</v>
       </c>
       <c r="J37" s="33" t="n">
-        <v>20.14</v>
+        <v>-10.26</v>
       </c>
       <c r="K37" s="33" t="n">
-        <v>7.57</v>
+        <v>7.95</v>
       </c>
       <c r="L37" s="33" t="n">
-        <v>17.02</v>
+        <v>15.91</v>
       </c>
       <c r="M37" s="33" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C38" s="33" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="33" t="n">
-        <v>-0.36</v>
+        <v>-4.96</v>
       </c>
       <c r="E38" s="33" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="F38" s="33" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="G38" s="33" t="n">
-        <v>1.52</v>
+        <v>0.8</v>
       </c>
       <c r="H38" s="33" t="n"/>
       <c r="I38" s="33" t="n">
-        <v>-0.66</v>
+        <v>-0.43</v>
       </c>
       <c r="J38" s="33" t="n">
-        <v>-10.26</v>
+        <v>55.17</v>
       </c>
       <c r="K38" s="33" t="n">
-        <v>7.95</v>
+        <v>8.58</v>
       </c>
       <c r="L38" s="33" t="n">
-        <v>15.91</v>
+        <v>15.79</v>
       </c>
       <c r="M38" s="33" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C39" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" s="33" t="n">
-        <v>-4.96</v>
-      </c>
-      <c r="E39" s="33" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="F39" s="33" t="n">
-        <v>5.1</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="D39" s="33" t="n"/>
+      <c r="E39" s="33" t="n"/>
+      <c r="F39" s="33" t="n"/>
       <c r="G39" s="33" t="n">
-        <v>0.8</v>
+        <v>2.58</v>
       </c>
       <c r="H39" s="33" t="n"/>
       <c r="I39" s="33" t="n">
-        <v>-0.43</v>
+        <v>0.46</v>
       </c>
       <c r="J39" s="33" t="n">
-        <v>55.17</v>
+        <v>-35.64</v>
       </c>
       <c r="K39" s="33" t="n">
-        <v>8.58</v>
+        <v>6.46</v>
       </c>
       <c r="L39" s="33" t="n">
-        <v>15.79</v>
+        <v>11.67</v>
       </c>
       <c r="M39" s="33" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
@@ -5797,10 +5779,10 @@
         <v>1.41</v>
       </c>
       <c r="F40" s="33" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="G40" s="33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H40" s="33" t="n"/>
       <c r="I40" s="33" t="n">
@@ -5822,7 +5804,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
@@ -5831,73 +5813,71 @@
         </is>
       </c>
       <c r="C41" s="33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D41" s="33" t="n">
-        <v>-2.41</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="D41" s="33" t="n"/>
       <c r="E41" s="33" t="n">
-        <v>10.08</v>
+        <v>3.37</v>
       </c>
       <c r="F41" s="33" t="n">
-        <v>1.6</v>
+        <v>4.36</v>
       </c>
       <c r="G41" s="33" t="n">
-        <v>1.67</v>
+        <v>2.66</v>
       </c>
       <c r="H41" s="33" t="n"/>
-      <c r="I41" s="33" t="n">
-        <v>-0.41</v>
-      </c>
+      <c r="I41" s="33" t="n"/>
       <c r="J41" s="33" t="n">
-        <v>-46.79</v>
+        <v>-14.97</v>
       </c>
       <c r="K41" s="33" t="n">
-        <v>6.47</v>
+        <v>8</v>
       </c>
       <c r="L41" s="33" t="n">
-        <v>-5.26</v>
+        <v>20</v>
       </c>
       <c r="M41" s="33" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>38 (C)</t>
         </is>
       </c>
       <c r="C42" s="33" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D42" s="33" t="n">
-        <v>0.64</v>
+        <v>-2.41</v>
       </c>
       <c r="E42" s="33" t="n">
-        <v>1.47</v>
+        <v>10.08</v>
       </c>
       <c r="F42" s="33" t="n">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="G42" s="33" t="n">
-        <v>0.61</v>
+        <v>1.69</v>
       </c>
       <c r="H42" s="33" t="n"/>
       <c r="I42" s="33" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="J42" s="33" t="n"/>
+        <v>-0.41</v>
+      </c>
+      <c r="J42" s="33" t="n">
+        <v>-46.79</v>
+      </c>
       <c r="K42" s="33" t="n">
-        <v>7.91</v>
+        <v>6.47</v>
       </c>
       <c r="L42" s="33" t="n">
-        <v>9.09</v>
+        <v>-5.26</v>
       </c>
       <c r="M42" s="33" t="n">
         <v>36</v>
@@ -5924,10 +5904,10 @@
         <v>3.53</v>
       </c>
       <c r="F43" s="33" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="G43" s="33" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H43" s="33" t="n"/>
       <c r="I43" s="33" t="n">
@@ -5949,7 +5929,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
@@ -5958,162 +5938,160 @@
         </is>
       </c>
       <c r="C44" s="33" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="D44" s="33" t="n">
-        <v>-1.72</v>
+        <v>0.59</v>
       </c>
       <c r="E44" s="33" t="n">
-        <v>4.02</v>
+        <v>1.58</v>
       </c>
       <c r="F44" s="33" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="G44" s="33" t="n">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="H44" s="33" t="n"/>
       <c r="I44" s="33" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J44" s="33" t="n">
-        <v>-27.41</v>
-      </c>
+        <v>-0.16</v>
+      </c>
+      <c r="J44" s="33" t="n"/>
       <c r="K44" s="33" t="n">
-        <v>6.72</v>
+        <v>7.71</v>
       </c>
       <c r="L44" s="33" t="n">
-        <v>-2.78</v>
+        <v>7.14</v>
       </c>
       <c r="M44" s="33" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>35 (C)</t>
         </is>
       </c>
       <c r="C45" s="33" t="n"/>
       <c r="D45" s="33" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="E45" s="33" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="F45" s="33" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="G45" s="33" t="n">
-        <v>2.55</v>
+        <v>0.6</v>
       </c>
       <c r="H45" s="33" t="n"/>
       <c r="I45" s="33" t="n">
-        <v>-0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="J45" s="33" t="n">
-        <v>-10.94</v>
+        <v>-12.25</v>
       </c>
       <c r="K45" s="33" t="n">
-        <v>7.71</v>
+        <v>7.91</v>
       </c>
       <c r="L45" s="33" t="n">
-        <v>7.14</v>
+        <v>9.09</v>
       </c>
       <c r="M45" s="33" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>32 (C)</t>
+          <t>34 (C)</t>
         </is>
       </c>
       <c r="C46" s="33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="D46" s="33" t="n">
-        <v>0.79</v>
+        <v>-1.72</v>
       </c>
       <c r="E46" s="33" t="n">
-        <v>6.38</v>
+        <v>4.02</v>
       </c>
       <c r="F46" s="33" t="n">
-        <v>1.3</v>
+        <v>2.74</v>
       </c>
       <c r="G46" s="33" t="n">
-        <v>0.93</v>
+        <v>2.29</v>
       </c>
       <c r="H46" s="33" t="n"/>
       <c r="I46" s="33" t="n">
-        <v>-0.49</v>
+        <v>0.28</v>
       </c>
       <c r="J46" s="33" t="n">
-        <v>-32.7</v>
+        <v>-27.41</v>
       </c>
       <c r="K46" s="33" t="n">
-        <v>7.02</v>
+        <v>6.72</v>
       </c>
       <c r="L46" s="33" t="n">
-        <v>1.75</v>
+        <v>-2.78</v>
       </c>
       <c r="M46" s="33" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>31 (C-)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C47" s="33" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="D47" s="33" t="n">
-        <v>-0.62</v>
+        <v>0.79</v>
       </c>
       <c r="E47" s="33" t="n">
-        <v>3.05</v>
+        <v>6.38</v>
       </c>
       <c r="F47" s="33" t="n">
-        <v>1.86</v>
+        <v>1.29</v>
       </c>
       <c r="G47" s="33" t="n">
-        <v>1.57</v>
+        <v>0.9</v>
       </c>
       <c r="H47" s="33" t="n"/>
       <c r="I47" s="33" t="n">
-        <v>-1.46</v>
+        <v>-0.49</v>
       </c>
       <c r="J47" s="33" t="n">
-        <v>-11.14</v>
+        <v>-32.7</v>
       </c>
       <c r="K47" s="33" t="n">
-        <v>9.76</v>
+        <v>7.02</v>
       </c>
       <c r="L47" s="33" t="n">
-        <v>27.59</v>
+        <v>1.75</v>
       </c>
       <c r="M47" s="33" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
@@ -6137,10 +6115,10 @@
         <v>5.36</v>
       </c>
       <c r="F48" s="33" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="G48" s="33" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="H48" s="33" t="n"/>
       <c r="I48" s="33" t="n">
@@ -6162,7 +6140,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B49" s="34" t="inlineStr">
@@ -6171,35 +6149,35 @@
         </is>
       </c>
       <c r="C49" s="33" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="D49" s="33" t="n">
-        <v>0.22</v>
+        <v>-0.62</v>
       </c>
       <c r="E49" s="33" t="n">
-        <v>1.36</v>
+        <v>3.05</v>
       </c>
       <c r="F49" s="33" t="n">
-        <v>2.82</v>
+        <v>1.85</v>
       </c>
       <c r="G49" s="33" t="n">
-        <v>2.53</v>
+        <v>1.55</v>
       </c>
       <c r="H49" s="33" t="n"/>
       <c r="I49" s="33" t="n">
-        <v>0.46</v>
+        <v>-1.46</v>
       </c>
       <c r="J49" s="33" t="n">
-        <v>-35.64</v>
+        <v>-11.14</v>
       </c>
       <c r="K49" s="33" t="n">
-        <v>6.46</v>
+        <v>9.76</v>
       </c>
       <c r="L49" s="33" t="n">
-        <v>11.67</v>
+        <v>27.59</v>
       </c>
       <c r="M49" s="33" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
@@ -6210,7 +6188,7 @@
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>26 (C-)</t>
+          <t>29 (C-)</t>
         </is>
       </c>
       <c r="C50" s="33" t="n">
@@ -6223,27 +6201,17 @@
         <v>1.9</v>
       </c>
       <c r="F50" s="33" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="G50" s="33" t="n">
-        <v>1.98</v>
-      </c>
+        <v>2.12</v>
+      </c>
+      <c r="G50" s="33" t="n"/>
       <c r="H50" s="33" t="n"/>
-      <c r="I50" s="33" t="n">
-        <v>-3.09</v>
-      </c>
-      <c r="J50" s="33" t="n">
-        <v>-3.97</v>
-      </c>
+      <c r="I50" s="33" t="n"/>
+      <c r="J50" s="33" t="n"/>
       <c r="K50" s="33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L50" s="33" t="n">
-        <v>25</v>
-      </c>
-      <c r="M50" s="33" t="n">
-        <v>30</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L50" s="33" t="n"/>
+      <c r="M50" s="33" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6253,7 +6221,7 @@
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>24 (D)</t>
+          <t>23 (D)</t>
         </is>
       </c>
       <c r="C51" s="33" t="n">
@@ -6266,10 +6234,10 @@
         <v>4.98</v>
       </c>
       <c r="F51" s="33" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G51" s="33" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="H51" s="33" t="n"/>
       <c r="I51" s="33" t="n">
@@ -6367,41 +6335,41 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="n">
+      <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G2" s="14" t="n">
+      <c r="D2" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G2" s="11" t="n">
         <v>4.5</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="11" t="n">
         <v>1.2</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="11" t="n">
         <v>5.47</v>
       </c>
-      <c r="J2" s="14" t="n">
-        <v>4.95</v>
+      <c r="J2" s="11" t="n">
+        <v>4.93</v>
       </c>
     </row>
     <row r="3">
@@ -6427,7 +6395,7 @@
         </is>
       </c>
       <c r="F3" s="8" t="n">
-        <v>55.8</v>
+        <v>55.5</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>4.8</v>
@@ -6439,7 +6407,7 @@
         <v>5.44</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>5.65</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="4">
@@ -6457,7 +6425,7 @@
         </is>
       </c>
       <c r="D4" s="20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
@@ -6465,7 +6433,7 @@
         </is>
       </c>
       <c r="F4" s="20" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>4.5</v>
@@ -6477,7 +6445,7 @@
         <v>4.02</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="5">
@@ -6515,7 +6483,7 @@
         <v>4.36</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="6">
@@ -6533,7 +6501,7 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
@@ -6541,7 +6509,7 @@
         </is>
       </c>
       <c r="F6" s="11" t="n">
-        <v>53.5</v>
+        <v>54.9</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>4.2</v>
@@ -6553,7 +6521,7 @@
         <v>4.13</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="7">
@@ -6571,7 +6539,7 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
@@ -6579,7 +6547,7 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>3.5</v>
@@ -6591,7 +6559,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="8">
@@ -6609,7 +6577,7 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
@@ -6617,7 +6585,7 @@
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>26.4</v>
+        <v>28.7</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>3.8</v>
@@ -6629,45 +6597,43 @@
         <v>1.9</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="D9" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n">
         <v>0.51</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="11" t="n">
         <v>6.47</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>1.53</v>
+      <c r="J9" s="11" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="10">
@@ -6693,95 +6659,81 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>4</v>
-      </c>
+        <v>48.3</v>
+      </c>
+      <c r="G10" s="14" t="n"/>
       <c r="H10" s="14" t="n">
         <v>0.93</v>
       </c>
-      <c r="I10" s="14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>3.26</v>
-      </c>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="D11" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="G11" s="14" t="n">
         <v>3.5</v>
       </c>
-      <c r="H11" s="11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>2.15</v>
-      </c>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
-        <v>47</v>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="G12" s="14" t="n">
+      <c r="D12" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="G12" s="17" t="n">
         <v>3.9</v>
       </c>
-      <c r="H12" s="14" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I12" s="14" t="n">
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n">
         <v>3.37</v>
       </c>
-      <c r="J12" s="14" t="n">
-        <v>4.38</v>
+      <c r="J12" s="17" t="n">
+        <v>4.36</v>
       </c>
     </row>
     <row r="13">
@@ -6799,7 +6751,7 @@
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
@@ -6807,7 +6759,7 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>5.1</v>
@@ -6819,43 +6771,45 @@
         <v>6.68</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G14" s="11" t="n">
+      <c r="D14" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>4.1</v>
       </c>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n">
+      <c r="H14" s="8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I14" s="8" t="n">
         <v>5.54</v>
       </c>
-      <c r="J14" s="11" t="n">
-        <v>4.53</v>
+      <c r="J14" s="8" t="n">
+        <v>4.52</v>
       </c>
     </row>
     <row r="15">
@@ -6873,7 +6827,7 @@
         </is>
       </c>
       <c r="D15" s="20" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
@@ -6881,9 +6835,11 @@
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G15" s="20" t="n"/>
+        <v>35.2</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>4.7</v>
+      </c>
       <c r="H15" s="20" t="n">
         <v>0.59</v>
       </c>
@@ -6891,7 +6847,7 @@
         <v>1.58</v>
       </c>
       <c r="J15" s="20" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="16">
@@ -6909,7 +6865,7 @@
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
@@ -6917,17 +6873,19 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>45.8</v>
+        <v>44.2</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="14" t="n"/>
+      <c r="H16" s="14" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="I16" s="14" t="n">
         <v>9.02</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="17">
@@ -6945,7 +6903,7 @@
         </is>
       </c>
       <c r="D17" s="20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
@@ -6953,11 +6911,9 @@
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="G17" s="20" t="n">
-        <v>4</v>
-      </c>
+        <v>34.6</v>
+      </c>
+      <c r="G17" s="20" t="n"/>
       <c r="H17" s="20" t="n">
         <v>0.64</v>
       </c>
@@ -6965,7 +6921,7 @@
         <v>1.47</v>
       </c>
       <c r="J17" s="20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -6983,7 +6939,7 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
@@ -6991,7 +6947,7 @@
         </is>
       </c>
       <c r="F18" s="17" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="G18" s="17" t="n">
         <v>4.6</v>
@@ -7003,45 +6959,45 @@
         <v>8.81</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="G19" s="14" t="n">
+      <c r="D19" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G19" s="11" t="n">
         <v>4.4</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H19" s="11" t="n">
         <v>1.66</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="11" t="n">
         <v>4.58</v>
       </c>
-      <c r="J19" s="14" t="n">
-        <v>4.92</v>
+      <c r="J19" s="11" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="20">
@@ -7059,7 +7015,7 @@
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -7067,7 +7023,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>54.8</v>
+        <v>54</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>3.6</v>
@@ -7079,46 +7035,40 @@
         <v>4.74</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="n">
+      <c r="A21" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D21" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="G21" s="23" t="n">
+      <c r="D21" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="G21" s="17" t="n">
         <v>4.4</v>
       </c>
-      <c r="H21" s="23" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I21" s="23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J21" s="23" t="n">
-        <v>2.82</v>
-      </c>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="17" t="n"/>
+      <c r="J21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
@@ -7143,7 +7093,7 @@
         </is>
       </c>
       <c r="F22" s="11" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>3.6</v>
@@ -7155,7 +7105,7 @@
         <v>-1.28</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="23">
@@ -7173,7 +7123,7 @@
         </is>
       </c>
       <c r="D23" s="23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
@@ -7181,7 +7131,7 @@
         </is>
       </c>
       <c r="F23" s="23" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>3.6</v>
@@ -7193,7 +7143,7 @@
         <v>3.05</v>
       </c>
       <c r="J23" s="23" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="24">
@@ -7219,7 +7169,7 @@
         </is>
       </c>
       <c r="F24" s="17" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="G24" s="17" t="n">
         <v>3.5</v>
@@ -7231,7 +7181,7 @@
         <v>1.41</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="25">
@@ -7257,7 +7207,7 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="G25" s="17" t="n">
         <v>3.7</v>
@@ -7269,7 +7219,7 @@
         <v>3.43</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="26">
@@ -7287,7 +7237,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -7295,7 +7245,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>64</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3.2</v>
@@ -7307,7 +7257,7 @@
         <v>5.84</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="27">
@@ -7325,7 +7275,7 @@
         </is>
       </c>
       <c r="D27" s="26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
@@ -7333,7 +7283,7 @@
         </is>
       </c>
       <c r="F27" s="26" t="n">
-        <v>23.9</v>
+        <v>22.8</v>
       </c>
       <c r="G27" s="26" t="n">
         <v>4.9</v>
@@ -7345,7 +7295,7 @@
         <v>4.98</v>
       </c>
       <c r="J27" s="26" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="28">
@@ -7371,7 +7321,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>4.8</v>
@@ -7383,7 +7333,7 @@
         <v>3.02</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="29">
@@ -7409,7 +7359,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>3.6</v>
@@ -7421,7 +7371,7 @@
         <v>7</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="30">
@@ -7439,7 +7389,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -7447,7 +7397,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>68.8</v>
+        <v>68.2</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>5.2</v>
@@ -7459,7 +7409,7 @@
         <v>6.67</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="31">
@@ -7477,7 +7427,7 @@
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -7485,7 +7435,7 @@
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>53.6</v>
+        <v>54.9</v>
       </c>
       <c r="G31" s="11" t="n">
         <v>3.6</v>
@@ -7497,7 +7447,7 @@
         <v>0.55</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="32">
@@ -7523,7 +7473,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.5</v>
@@ -7535,45 +7485,45 @@
         <v>6.97</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="G33" s="11" t="n">
+      <c r="D33" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G33" s="14" t="n">
         <v>3.6</v>
       </c>
-      <c r="H33" s="11" t="n">
+      <c r="H33" s="14" t="n">
         <v>0.35</v>
       </c>
-      <c r="I33" s="11" t="n">
+      <c r="I33" s="14" t="n">
         <v>3.05</v>
       </c>
-      <c r="J33" s="11" t="n">
-        <v>1.85</v>
+      <c r="J33" s="14" t="n">
+        <v>1.84</v>
       </c>
     </row>
     <row r="34">
@@ -7599,7 +7549,7 @@
         </is>
       </c>
       <c r="F34" s="17" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="G34" s="17" t="n">
         <v>2.5</v>
@@ -7637,7 +7587,7 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>3.4</v>
@@ -7673,7 +7623,7 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>3</v>
@@ -7685,7 +7635,7 @@
         <v>2.31</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="37">
@@ -7703,7 +7653,7 @@
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -7711,7 +7661,7 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>4</v>
@@ -7723,83 +7673,83 @@
         <v>0.65</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="20" t="n">
         <v>38</v>
       </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="G38" s="17" t="n">
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G38" s="20" t="n">
         <v>3.6</v>
       </c>
-      <c r="H38" s="17" t="n">
+      <c r="H38" s="20" t="n">
         <v>-2.41</v>
       </c>
-      <c r="I38" s="17" t="n">
+      <c r="I38" s="20" t="n">
         <v>10.08</v>
       </c>
-      <c r="J38" s="17" t="n">
-        <v>1.6</v>
+      <c r="J38" s="20" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n">
+      <c r="A39" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="24" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
       </c>
-      <c r="D39" s="20" t="n">
+      <c r="D39" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="G39" s="20" t="n">
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="G39" s="23" t="n">
         <v>4.6</v>
       </c>
-      <c r="H39" s="20" t="n">
+      <c r="H39" s="23" t="n">
         <v>0.79</v>
       </c>
-      <c r="I39" s="20" t="n">
+      <c r="I39" s="23" t="n">
         <v>6.38</v>
       </c>
-      <c r="J39" s="20" t="n">
-        <v>1.3</v>
+      <c r="J39" s="23" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="40">
@@ -7817,7 +7767,7 @@
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
@@ -7825,7 +7775,7 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>4.3</v>
@@ -7863,7 +7813,7 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>36.2</v>
+        <v>35.5</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>3.1</v>
@@ -7875,7 +7825,7 @@
         <v>3.53</v>
       </c>
       <c r="J41" s="20" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="42">
@@ -7893,7 +7843,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -7901,7 +7851,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3</v>
@@ -7913,7 +7863,7 @@
         <v>3.97</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="43">
@@ -7931,7 +7881,7 @@
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
@@ -7939,7 +7889,7 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
       <c r="G43" s="17" t="n">
         <v>3.6</v>
@@ -7951,7 +7901,7 @@
         <v>5.38</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="44">
@@ -7989,7 +7939,7 @@
         <v>2.36</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="45">
@@ -8015,7 +7965,7 @@
         </is>
       </c>
       <c r="F45" s="23" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>3.3</v>
@@ -8027,7 +7977,7 @@
         <v>5.36</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="46">
@@ -8045,7 +7995,7 @@
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
@@ -8053,7 +8003,7 @@
         </is>
       </c>
       <c r="F46" s="11" t="n">
-        <v>53.5</v>
+        <v>53.2</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>4</v>
@@ -8065,7 +8015,7 @@
         <v>6.12</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="47">
@@ -8091,7 +8041,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.4</v>
@@ -8103,7 +8053,7 @@
         <v>4.04</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="48">
@@ -8129,7 +8079,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>63.7</v>
+        <v>64.2</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>2.2</v>
@@ -8141,7 +8091,7 @@
         <v>-0.46</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="49">
@@ -8167,7 +8117,7 @@
         </is>
       </c>
       <c r="F49" s="11" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="G49" s="11" t="n">
         <v>8.199999999999999</v>
@@ -8179,7 +8129,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="50">
@@ -8197,7 +8147,7 @@
         </is>
       </c>
       <c r="D50" s="17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
@@ -8205,7 +8155,7 @@
         </is>
       </c>
       <c r="F50" s="17" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="G50" s="17" t="n">
         <v>4</v>
@@ -8217,7 +8167,7 @@
         <v>3.86</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>5.1</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="51">
@@ -8243,7 +8193,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>68.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8255,7 +8205,7 @@
         <v>0.13</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -8358,11 +8308,11 @@
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="G3" s="40" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
@@ -8380,7 +8330,7 @@
         </is>
       </c>
       <c r="C4" s="39" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="39" t="inlineStr">
         <is>
@@ -8410,7 +8360,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C5" s="39" t="n">
@@ -8426,7 +8376,7 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="G5" s="40" t="n">
@@ -8444,11 +8394,11 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
@@ -8460,11 +8410,11 @@
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="G6" s="40" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H6" s="40" t="inlineStr">
         <is>
@@ -8482,7 +8432,7 @@
         </is>
       </c>
       <c r="C7" s="39" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="39" t="inlineStr">
         <is>
@@ -8494,11 +8444,11 @@
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="G7" s="40" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" s="40" t="inlineStr">
         <is>
@@ -8528,11 +8478,11 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="G8" s="40" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H8" s="40" t="inlineStr">
         <is>
@@ -8596,7 +8546,7 @@
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="G10" s="40" t="n">
@@ -8634,7 +8584,7 @@
         </is>
       </c>
       <c r="G11" s="40" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H11" s="40" t="inlineStr">
         <is>
@@ -8648,15 +8598,15 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C12" s="39" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D12" s="39" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="E12" s="40" t="n">
@@ -8668,7 +8618,7 @@
         </is>
       </c>
       <c r="G12" s="40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H12" s="40" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -760,32 +760,32 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -822,20 +822,20 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -853,78 +853,78 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Salt Lake City-Murray</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Salt Lake City</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D9" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Very Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>60.1</v>
+        <v>59.6</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>59.7</v>
+        <v>60.2</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1008,16 +1008,16 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>57.6</v>
+        <v>58.4</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1038,114 +1038,114 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A14" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth-Arlington</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Dallas-Fort Worth-Arlington</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="n">
+      <c r="A15" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>San Jose</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n">
+      <c r="A16" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Providence-Warwick</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>54.9</v>
+        <v>54</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1163,20 +1163,20 @@
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="F18" s="11" t="n">
-        <v>52.4</v>
+        <v>53.6</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>51.5</v>
+        <v>53.7</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1225,20 +1225,20 @@
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>51.4</v>
+        <v>52.4</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>51.1</v>
+        <v>50.2</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1317,33 +1317,33 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Seattle-Tacoma-Bellevue</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="A23" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -1380,20 +1380,20 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>49.4</v>
+        <v>48</v>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>49.1</v>
+        <v>47.1</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1442,20 +1442,20 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>48.4</v>
+        <v>46.6</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1473,16 +1473,16 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1504,20 +1504,20 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>47.2</v>
+        <v>45.8</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1535,20 +1535,20 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Grand Rapids</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>47</v>
+        <v>45.1</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1566,20 +1566,20 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1597,16 +1597,16 @@
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
     </row>
     <row r="33">
       <c r="A33" s="14" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
@@ -1659,16 +1659,16 @@
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="F34" s="17" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
@@ -1689,52 +1689,52 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="n">
-        <v>37</v>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Virginia Beach</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="A35" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>41.6</v>
+        <v>42.8</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
@@ -1752,20 +1752,20 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1783,20 +1783,20 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>39</v>
+        <v>41.3</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
@@ -1845,20 +1845,20 @@
     </row>
     <row r="40">
       <c r="A40" s="20" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D40" s="22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>36.3</v>
+        <v>36.8</v>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
@@ -1876,20 +1876,20 @@
     </row>
     <row r="41">
       <c r="A41" s="20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>36.2</v>
+        <v>37.1</v>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
@@ -1907,20 +1907,20 @@
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D42" s="22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>35.5</v>
+        <v>36.1</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -1938,20 +1938,20 @@
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>32.6</v>
+        <v>36</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -1969,20 +1969,20 @@
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D44" s="22" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>32.8</v>
+        <v>36.3</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -2000,20 +2000,20 @@
     </row>
     <row r="45">
       <c r="A45" s="20" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>32.5</v>
+        <v>36.4</v>
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -2061,33 +2061,33 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="B47" s="21" t="inlineStr">
-        <is>
-          <t>Milwaukee-Waukesha</t>
-        </is>
-      </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="D47" s="22" t="n">
+      <c r="A47" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Detroit-Warren-Dearborn</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="E47" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="G47" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="F48" s="23" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
@@ -2124,63 +2124,63 @@
     </row>
     <row r="49">
       <c r="A49" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>Washington-Arlington-Alexandria</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="n">
         <v>38</v>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B50" s="27" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
       </c>
-      <c r="D49" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Washington-Arlington-Alexandria</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>Washington DC</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="n">
-        <v>27</v>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="D50" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G50" s="27" t="inlineStr">
+        <is>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F51" s="26" t="n">
-        <v>22.8</v>
+        <v>24.2</v>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
@@ -2318,16 +2318,16 @@
         <v>79</v>
       </c>
       <c r="C2" s="30" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" s="30" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" s="31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F2" s="30" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" s="30" t="n">
         <v>98</v>
@@ -2337,10 +2337,10 @@
         <v>94</v>
       </c>
       <c r="J2" s="30" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -2350,32 +2350,32 @@
         </is>
       </c>
       <c r="B3" s="29" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="30" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D3" s="30" t="n">
         <v>83</v>
       </c>
       <c r="E3" s="30" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3" s="30" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H3" s="32" t="n"/>
       <c r="I3" s="30" t="n">
         <v>88</v>
       </c>
       <c r="J3" s="31" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2385,67 +2385,67 @@
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4" s="30" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D4" s="30" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" s="30" t="n">
         <v>96</v>
       </c>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="31" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J4" s="33" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" s="31" t="n">
-        <v>67</v>
+        <v>12</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>68</v>
-      </c>
-      <c r="C5" s="30" t="n">
-        <v>79</v>
+        <v>67</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>15</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>85</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>50</v>
+        <v>98</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>83</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H5" s="32" t="n"/>
       <c r="I5" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="J5" s="31" t="n">
-        <v>67</v>
-      </c>
-      <c r="K5" s="33" t="n">
-        <v>35</v>
+        <v>96</v>
+      </c>
+      <c r="J5" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -2467,17 +2467,17 @@
         <v>6</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="G6" s="33" t="n">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="30" t="n">
         <v>98</v>
       </c>
       <c r="J6" s="33" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K6" s="30" t="n">
         <v>98</v>
@@ -2486,141 +2486,141 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>66</v>
-      </c>
-      <c r="C7" s="33" t="n">
-        <v>15</v>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>81</v>
+        <v>64</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>32</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>59</v>
-      </c>
-      <c r="G7" s="30" t="n">
-        <v>85</v>
+        <v>60</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>48</v>
       </c>
       <c r="H7" s="32" t="n"/>
-      <c r="I7" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <v>43</v>
+      <c r="I7" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="J7" s="31" t="n">
+        <v>69</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>64</v>
-      </c>
-      <c r="C8" s="31" t="n">
-        <v>56</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" s="31" t="n">
+        <v>63</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>71</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>89</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>88</v>
+      </c>
+      <c r="G8" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="G8" s="30" t="n">
-        <v>94</v>
-      </c>
       <c r="H8" s="32" t="n"/>
-      <c r="I8" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="J8" s="30" t="n">
-        <v>70</v>
+      <c r="I8" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="J8" s="33" t="n">
+        <v>42</v>
       </c>
       <c r="K8" s="33" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>62</v>
-      </c>
-      <c r="C9" s="30" t="n">
+        <v>63</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>65</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>93</v>
+      </c>
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="J9" s="30" t="n">
         <v>73</v>
       </c>
-      <c r="D9" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="F9" s="30" t="n">
-        <v>87</v>
-      </c>
-      <c r="G9" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="J9" s="33" t="n">
-        <v>37</v>
-      </c>
       <c r="K9" s="33" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B10" s="29" t="n">
         <v>61</v>
       </c>
       <c r="C10" s="30" t="n">
-        <v>79</v>
-      </c>
-      <c r="D10" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>73</v>
-      </c>
-      <c r="F10" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="D10" s="30" t="n">
         <v>89</v>
       </c>
+      <c r="E10" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>35</v>
+      </c>
       <c r="G10" s="30" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H10" s="32" t="n"/>
-      <c r="I10" s="33" t="n">
-        <v>38</v>
+      <c r="I10" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="J10" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="K10" s="33" t="n">
-        <v>41</v>
+      <c r="K10" s="31" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -2633,379 +2633,379 @@
         <v>60</v>
       </c>
       <c r="C11" s="33" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="30" t="n">
         <v>84</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K11" s="31" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B12" s="29" t="n">
         <v>60</v>
       </c>
       <c r="C12" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="E12" s="33" t="n">
-        <v>19</v>
+        <v>94</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>66</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="G12" s="30" t="n">
-        <v>88</v>
+        <v>16</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H12" s="32" t="n"/>
-      <c r="I12" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="J12" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="K12" s="31" t="n">
-        <v>50</v>
+      <c r="I12" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="K12" s="33" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B13" s="29" t="n">
         <v>58</v>
       </c>
-      <c r="C13" s="30" t="n">
-        <v>88</v>
+      <c r="C13" s="31" t="n">
+        <v>60</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="G13" s="30" t="n">
-        <v>73</v>
+        <v>23</v>
+      </c>
+      <c r="G13" s="31" t="n">
+        <v>67</v>
       </c>
       <c r="H13" s="32" t="n"/>
-      <c r="I13" s="31" t="n">
-        <v>50</v>
+      <c r="I13" s="30" t="n">
+        <v>78</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>93</v>
-      </c>
-      <c r="K13" s="30" t="n">
-        <v>91</v>
+        <v>96</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>58</v>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>67</v>
-      </c>
-      <c r="E14" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="33" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" s="31" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>47</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>77</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>85</v>
       </c>
       <c r="H14" s="32" t="n"/>
-      <c r="I14" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="J14" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="K14" s="32" t="n">
-        <v>0</v>
+      <c r="I14" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="J14" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="K14" s="33" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B15" s="29" t="n">
         <v>55</v>
       </c>
       <c r="C15" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>50</v>
+        <v>65</v>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>47</v>
       </c>
       <c r="E15" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="F15" s="30" t="n">
-        <v>76</v>
+        <v>9</v>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>2</v>
       </c>
       <c r="G15" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="H15" s="32" t="n"/>
+      <c r="I15" s="30" t="n">
         <v>92</v>
       </c>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="31" t="n">
-        <v>66</v>
-      </c>
-      <c r="J15" s="33" t="n">
-        <v>13</v>
+      <c r="J15" s="30" t="n">
+        <v>98</v>
       </c>
       <c r="K15" s="33" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B16" s="29" t="n">
         <v>55</v>
       </c>
-      <c r="C16" s="31" t="n">
-        <v>67</v>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>50</v>
+      <c r="C16" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>81</v>
       </c>
       <c r="E16" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="30" t="n">
-        <v>90</v>
+        <v>47</v>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <v>63</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="30" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="K16" s="32" t="n">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>55</v>
-      </c>
-      <c r="C17" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="D17" s="30" t="n">
-        <v>81</v>
-      </c>
-      <c r="E17" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="F17" s="32" t="n">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="G17" s="31" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H17" s="32" t="n"/>
-      <c r="I17" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="J17" s="30" t="n">
-        <v>83</v>
-      </c>
-      <c r="K17" s="30" t="n">
-        <v>93</v>
+      <c r="I17" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="J17" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" s="31" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>52</v>
-      </c>
-      <c r="C18" s="33" t="n">
-        <v>33</v>
+        <v>54</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>85</v>
       </c>
       <c r="D18" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="E18" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="E18" s="30" t="n">
-        <v>71</v>
-      </c>
-      <c r="F18" s="33" t="n">
-        <v>22</v>
+      <c r="F18" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="G18" s="31" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H18" s="32" t="n"/>
-      <c r="I18" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="J18" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="K18" s="32" t="n">
-        <v>0</v>
+      <c r="I18" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="J18" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B19" s="29" t="n">
-        <v>52</v>
-      </c>
-      <c r="C19" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="F19" s="33" t="n">
+        <v>54</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>77</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="G19" s="33" t="n">
-        <v>15</v>
-      </c>
-      <c r="H19" s="32" t="n"/>
-      <c r="I19" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="J19" s="33" t="n">
-        <v>11</v>
-      </c>
-      <c r="K19" s="31" t="n">
-        <v>52</v>
+      <c r="J19" s="30" t="n">
+        <v>71</v>
+      </c>
+      <c r="K19" s="33" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B20" s="29" t="n">
-        <v>51</v>
-      </c>
-      <c r="C20" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="D20" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>77</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="F20" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="E20" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="F20" s="31" t="n">
-        <v>63</v>
-      </c>
-      <c r="G20" s="33" t="n">
+      <c r="G20" s="30" t="n">
+        <v>83</v>
+      </c>
+      <c r="H20" s="32" t="n"/>
+      <c r="I20" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="J20" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" s="33" t="n">
         <v>44</v>
-      </c>
-      <c r="H20" s="32" t="n"/>
-      <c r="I20" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="J20" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="K20" s="30" t="n">
-        <v>83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>51</v>
-      </c>
-      <c r="C21" s="31" t="n">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>2</v>
       </c>
       <c r="D21" s="31" t="n">
+        <v>53</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="F21" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="J21" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="E21" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="F21" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="G21" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="K21" s="33" t="n">
-        <v>20</v>
+      <c r="K21" s="31" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -3018,64 +3018,64 @@
         <v>50</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F22" s="30" t="n">
         <v>93</v>
       </c>
       <c r="G22" s="33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="33" t="n">
         <v>8</v>
       </c>
       <c r="J22" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="K22" s="33" t="n">
-        <v>48</v>
+        <v>81</v>
+      </c>
+      <c r="K22" s="31" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B23" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="C23" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>55</v>
+      </c>
+      <c r="E23" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="G23" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="31" t="n">
-        <v>56</v>
-      </c>
-      <c r="E23" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="F23" s="33" t="n">
-        <v>43</v>
-      </c>
-      <c r="G23" s="31" t="n">
-        <v>65</v>
-      </c>
       <c r="H23" s="32" t="n"/>
-      <c r="I23" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="J23" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="K23" s="31" t="n">
-        <v>61</v>
+      <c r="I23" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="30" t="n">
+        <v>79</v>
+      </c>
+      <c r="K23" s="33" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -3088,64 +3088,64 @@
         <v>49</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D24" s="33" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E24" s="31" t="n">
         <v>62</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>11</v>
-      </c>
-      <c r="G24" s="31" t="n">
-        <v>69</v>
+        <v>12</v>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="H24" s="32" t="n"/>
-      <c r="I24" s="31" t="n">
-        <v>68</v>
+      <c r="I24" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="J24" s="31" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K24" s="33" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="C25" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="D25" s="33" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="C25" s="33" t="n">
         <v>33</v>
       </c>
+      <c r="D25" s="30" t="n">
+        <v>79</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>74</v>
+      </c>
       <c r="F25" s="33" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G25" s="31" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H25" s="32" t="n"/>
-      <c r="I25" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="J25" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K25" s="31" t="n">
-        <v>65</v>
+      <c r="I25" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="J25" s="30" t="n">
+        <v>75</v>
+      </c>
+      <c r="K25" s="33" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="26">
@@ -3155,48 +3155,48 @@
         </is>
       </c>
       <c r="B26" s="29" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C26" s="31" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D26" s="31" t="n">
         <v>62</v>
       </c>
       <c r="E26" s="33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" s="31" t="n">
-        <v>57</v>
-      </c>
-      <c r="G26" s="30" t="n">
-        <v>83</v>
+        <v>53</v>
+      </c>
+      <c r="G26" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="30" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J26" s="33" t="n">
         <v>2</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="C27" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="D27" s="30" t="n">
-        <v>79</v>
+        <v>47</v>
+      </c>
+      <c r="C27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>57</v>
       </c>
       <c r="E27" s="31" t="n">
         <v>50</v>
@@ -3205,402 +3205,402 @@
         <v>50</v>
       </c>
       <c r="G27" s="33" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H27" s="32" t="n"/>
-      <c r="I27" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="J27" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="K27" s="33" t="n">
-        <v>37</v>
+      <c r="I27" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="J27" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="K27" s="31" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B28" s="29" t="n">
         <v>47</v>
       </c>
-      <c r="C28" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="D28" s="30" t="n">
-        <v>77</v>
+      <c r="C28" s="31" t="n">
+        <v>65</v>
+      </c>
+      <c r="D28" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="F28" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="G28" s="31" t="n">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="F28" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" s="33" t="n">
+        <v>9</v>
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="33" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J28" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="K28" s="33" t="n">
-        <v>28</v>
+        <v>92</v>
+      </c>
+      <c r="K28" s="30" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="D29" s="33" t="n">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>64</v>
       </c>
       <c r="E29" s="33" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="G29" s="33" t="n">
-        <v>33</v>
+        <v>72</v>
+      </c>
+      <c r="G29" s="30" t="n">
+        <v>78</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="J29" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="K29" s="31" t="n">
         <v>60</v>
-      </c>
-      <c r="J29" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="K29" s="33" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B30" s="29" t="n">
-        <v>47</v>
-      </c>
-      <c r="C30" s="31" t="n">
-        <v>67</v>
-      </c>
-      <c r="D30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="31" t="n">
+        <v>45</v>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="F30" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" s="31" t="n">
         <v>54</v>
-      </c>
-      <c r="F30" s="33" t="n">
-        <v>9</v>
-      </c>
-      <c r="G30" s="33" t="n">
-        <v>6</v>
       </c>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="33" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>89</v>
-      </c>
-      <c r="K30" s="30" t="n">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="K30" s="33" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B31" s="29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="33" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D31" s="33" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="F31" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="G31" s="31" t="n">
-        <v>52</v>
+        <v>96</v>
+      </c>
+      <c r="F31" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="G31" s="33" t="n">
+        <v>33</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="J31" s="30" t="n">
-        <v>87</v>
+        <v>42</v>
+      </c>
+      <c r="J31" s="31" t="n">
+        <v>52</v>
       </c>
       <c r="K31" s="33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B32" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="C32" s="33" t="n">
-        <v>23</v>
-      </c>
-      <c r="D32" s="31" t="n">
-        <v>65</v>
+      <c r="C32" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>72</v>
       </c>
       <c r="E32" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="F32" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="G32" s="30" t="n">
-        <v>77</v>
+        <v>26</v>
+      </c>
+      <c r="F32" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="G32" s="33" t="n">
+        <v>22</v>
       </c>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="33" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J32" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="K32" s="31" t="n">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="K32" s="30" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B33" s="29" t="n">
         <v>44</v>
       </c>
       <c r="C33" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="D33" s="33" t="n">
-        <v>25</v>
-      </c>
-      <c r="E33" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="F33" s="30" t="n">
-        <v>83</v>
+        <v>21</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="E33" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="F33" s="33" t="n">
+        <v>21</v>
       </c>
       <c r="G33" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="H33" s="32" t="n"/>
+      <c r="I33" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J33" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="H33" s="32" t="n"/>
-      <c r="I33" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="J33" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="K33" s="33" t="n">
-        <v>9</v>
+      <c r="K33" s="31" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B34" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="C34" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="D34" s="30" t="n">
-        <v>71</v>
-      </c>
-      <c r="E34" s="33" t="n">
-        <v>25</v>
-      </c>
-      <c r="F34" s="33" t="n">
-        <v>7</v>
+      <c r="C34" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="D34" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>67</v>
       </c>
       <c r="G34" s="33" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" s="33" t="n">
-        <v>41</v>
-      </c>
-      <c r="K34" s="30" t="n">
-        <v>70</v>
+        <v>22</v>
+      </c>
+      <c r="J34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="33" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B35" s="29" t="n">
+        <v>43</v>
+      </c>
+      <c r="C35" s="33" t="n">
         <v>44</v>
       </c>
-      <c r="C35" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="D35" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="E35" s="30" t="n">
-        <v>98</v>
+      <c r="D35" s="30" t="n">
+        <v>77</v>
+      </c>
+      <c r="E35" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="F35" s="31" t="n">
-        <v>67</v>
-      </c>
-      <c r="G35" s="33" t="n">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="G35" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="J35" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="33" t="n">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="J35" s="31" t="n">
+        <v>65</v>
+      </c>
+      <c r="K35" s="30" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B36" s="29" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="33" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D36" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="E36" s="33" t="n">
-        <v>23</v>
+      <c r="E36" s="30" t="n">
+        <v>79</v>
       </c>
       <c r="F36" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="G36" s="33" t="n">
-        <v>31</v>
+        <v>40</v>
+      </c>
+      <c r="G36" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="H36" s="32" t="n"/>
-      <c r="I36" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="J36" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K36" s="31" t="n">
-        <v>63</v>
+      <c r="I36" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" s="30" t="n">
+        <v>77</v>
+      </c>
+      <c r="K36" s="33" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B37" s="29" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="D37" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="E37" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="F37" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="G37" s="30" t="n">
-        <v>71</v>
+        <v>29</v>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="E37" s="31" t="n">
+        <v>57</v>
+      </c>
+      <c r="F37" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="G37" s="31" t="n">
+        <v>59</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="J37" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="K37" s="30" t="n">
-        <v>76</v>
+        <v>34</v>
+      </c>
+      <c r="J37" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="K37" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B38" s="29" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C38" s="33" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D38" s="33" t="n">
-        <v>17</v>
-      </c>
-      <c r="E38" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="F38" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="G38" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="E38" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="F38" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>57</v>
+      </c>
+      <c r="H38" s="32" t="n"/>
+      <c r="I38" s="33" t="n">
         <v>38</v>
       </c>
-      <c r="H38" s="32" t="n"/>
-      <c r="I38" s="31" t="n">
-        <v>56</v>
-      </c>
-      <c r="J38" s="31" t="n">
-        <v>50</v>
+      <c r="J38" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="K38" s="33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
@@ -3610,242 +3610,242 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C39" s="30" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D39" s="33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E39" s="33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F39" s="33" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G39" s="33" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="33" t="n">
         <v>14</v>
       </c>
       <c r="J39" s="31" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B40" s="29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="D40" s="33" t="n">
-        <v>40</v>
+        <v>12</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>51</v>
       </c>
       <c r="E40" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="F40" s="33" t="n">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="F40" s="31" t="n">
+        <v>58</v>
       </c>
       <c r="G40" s="33" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H40" s="32" t="n"/>
-      <c r="I40" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="J40" s="31" t="n">
+      <c r="I40" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="K40" s="30" t="n">
-        <v>89</v>
+      <c r="J40" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K40" s="31" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B41" s="29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="D41" s="33" t="n">
-        <v>23</v>
+        <v>69</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="E41" s="33" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F41" s="33" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G41" s="33" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="33" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J41" s="33" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="K41" s="33" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B42" s="29" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C42" s="33" t="n">
         <v>15</v>
       </c>
       <c r="D42" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="E42" s="30" t="n">
-        <v>77</v>
+        <v>15</v>
+      </c>
+      <c r="E42" s="33" t="n">
+        <v>49</v>
       </c>
       <c r="F42" s="33" t="n">
+        <v>49</v>
+      </c>
+      <c r="G42" s="33" t="n">
         <v>37</v>
       </c>
-      <c r="G42" s="32" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" s="32" t="n"/>
-      <c r="I42" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="J42" s="31" t="n">
-        <v>50</v>
+      <c r="I42" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="J42" s="33" t="n">
+        <v>15</v>
       </c>
       <c r="K42" s="33" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B43" s="29" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C43" s="33" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D43" s="30" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="E43" s="33" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="F43" s="33" t="n">
-        <v>17</v>
-      </c>
-      <c r="G43" s="31" t="n">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="G43" s="30" t="n">
+        <v>76</v>
       </c>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" s="31" t="n">
-        <v>61</v>
-      </c>
-      <c r="K43" s="30" t="n">
-        <v>80</v>
+        <v>18</v>
+      </c>
+      <c r="J43" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="K43" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B44" s="29" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C44" s="33" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D44" s="33" t="n">
         <v>38</v>
       </c>
       <c r="E44" s="33" t="n">
-        <v>15</v>
-      </c>
-      <c r="F44" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="G44" s="31" t="n">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="F44" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="G44" s="33" t="n">
+        <v>20</v>
       </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="J44" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="K44" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="31" t="n">
         <v>54</v>
+      </c>
+      <c r="K44" s="30" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B45" s="29" t="n">
-        <v>33</v>
-      </c>
-      <c r="C45" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="D45" s="31" t="n">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="C45" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="D45" s="33" t="n">
+        <v>21</v>
       </c>
       <c r="E45" s="33" t="n">
-        <v>17</v>
-      </c>
-      <c r="F45" s="31" t="n">
-        <v>61</v>
+        <v>45</v>
+      </c>
+      <c r="F45" s="33" t="n">
+        <v>37</v>
       </c>
       <c r="G45" s="33" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="33" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="J45" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="K45" s="32" t="n">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="K45" s="33" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -3861,23 +3861,23 @@
         <v>15</v>
       </c>
       <c r="D46" s="33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E46" s="31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F46" s="30" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" s="33" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H46" s="32" t="n"/>
       <c r="I46" s="33" t="n">
         <v>4</v>
       </c>
       <c r="J46" s="33" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K46" s="30" t="n">
         <v>96</v>
@@ -3886,36 +3886,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
         <v>32</v>
       </c>
-      <c r="C47" s="30" t="n">
-        <v>71</v>
+      <c r="C47" s="33" t="n">
+        <v>29</v>
       </c>
       <c r="D47" s="33" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E47" s="33" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F47" s="33" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G47" s="33" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="33" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J47" s="33" t="n">
-        <v>39</v>
-      </c>
-      <c r="K47" s="33" t="n">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="K47" s="31" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="48">
@@ -3925,102 +3925,102 @@
         </is>
       </c>
       <c r="B48" s="29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C48" s="33" t="n">
         <v>10</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" s="33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F48" s="31" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G48" s="33" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="30" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J48" s="33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K48" s="33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B49" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C49" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="D49" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="F49" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="G49" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="C49" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="E49" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="F49" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="G49" s="33" t="n">
-        <v>21</v>
-      </c>
       <c r="H49" s="32" t="n"/>
-      <c r="I49" s="33" t="n">
-        <v>12</v>
+      <c r="I49" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="K49" s="33" t="n">
-        <v>26</v>
+        <v>56</v>
+      </c>
+      <c r="K49" s="30" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B50" s="29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C50" s="33" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D50" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="33" t="n">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="E50" s="31" t="n">
+        <v>64</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G50" s="33" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H50" s="32" t="n"/>
-      <c r="I50" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="K50" s="30" t="n">
-        <v>85</v>
+      <c r="I50" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="J50" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="33" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="51">
@@ -4030,32 +4030,32 @@
         </is>
       </c>
       <c r="B51" s="29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C51" s="33" t="n">
         <v>8</v>
       </c>
       <c r="D51" s="33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E51" s="31" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F51" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="G51" s="31" t="n">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="G51" s="33" t="n">
+        <v>11</v>
       </c>
       <c r="H51" s="32" t="n"/>
       <c r="I51" s="32" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="K51" s="33" t="n">
         <v>17</v>
-      </c>
-      <c r="K51" s="32" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4175,10 +4175,10 @@
         <v>3.63</v>
       </c>
       <c r="F2" s="32" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="G2" s="32" t="n">
-        <v>4.52</v>
+        <v>4.49</v>
       </c>
       <c r="H2" s="32" t="n"/>
       <c r="I2" s="32" t="n">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>75 (A+)</t>
+          <t>76 (A+)</t>
         </is>
       </c>
       <c r="C3" s="32" t="n">
@@ -4218,10 +4218,10 @@
         <v>6.36</v>
       </c>
       <c r="F3" s="32" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="G3" s="32" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="H3" s="32" t="n"/>
       <c r="I3" s="32" t="n">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>70 (A+)</t>
+          <t>72 (A+)</t>
         </is>
       </c>
       <c r="C4" s="32" t="n">
@@ -4264,7 +4264,7 @@
         <v>0.76</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="32" t="n">
@@ -4286,40 +4286,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>68 (A+)</t>
+          <t>67 (A)</t>
         </is>
       </c>
       <c r="C5" s="32" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
+        <v>2.95</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>2.18</v>
+      </c>
       <c r="G5" s="32" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
       <c r="H5" s="32" t="n"/>
       <c r="I5" s="32" t="n">
-        <v>0.57</v>
+        <v>1.96</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>11.14</v>
+        <v>-9.83</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>7.26</v>
+        <v>7.97</v>
       </c>
       <c r="L5" s="32" t="n">
-        <v>7.84</v>
+        <v>18.18</v>
       </c>
       <c r="M5" s="32" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -4343,10 +4347,10 @@
         <v>-0.12</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="32" t="n">
@@ -4368,136 +4372,136 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>66 (A)</t>
+          <t>64 (A)</t>
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>2.95</v>
+        <v>0.48</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>6.16</v>
+        <v>2.51</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="32" t="n">
-        <v>1.96</v>
+        <v>-0.04</v>
       </c>
       <c r="J7" s="32" t="n">
-        <v>-9.83</v>
+        <v>8.67</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>7.97</v>
+        <v>8.08</v>
       </c>
       <c r="L7" s="32" t="n">
-        <v>18.18</v>
+        <v>10.81</v>
       </c>
       <c r="M7" s="32" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>63 (A)</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>-0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>4.34</v>
+        <v>6.81</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="G8" s="32" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="H8" s="32" t="n"/>
       <c r="I8" s="32" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.36</v>
       </c>
       <c r="J8" s="32" t="n">
-        <v>14.73</v>
+        <v>-10.55</v>
       </c>
       <c r="K8" s="32" t="n">
-        <v>7</v>
+        <v>6.84</v>
       </c>
       <c r="L8" s="32" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="M8" s="32" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>62 (A-)</t>
+          <t>63 (A)</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="D9" s="32" t="n">
-        <v>0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>6.81</v>
+        <v>4.34</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="G9" s="32" t="n">
-        <v>2.9</v>
+        <v>4.34</v>
       </c>
       <c r="H9" s="32" t="n"/>
       <c r="I9" s="32" t="n">
-        <v>-0.36</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>-10.55</v>
+        <v>14.73</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>6.84</v>
+        <v>7</v>
       </c>
       <c r="L9" s="32" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="M9" s="32" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
@@ -4506,33 +4510,35 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>0.25</v>
+        <v>1.87</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>5.44</v>
+        <v>1.57</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>1.17</v>
+        <v>3.08</v>
       </c>
       <c r="G10" s="32" t="n">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="H10" s="32" t="n"/>
       <c r="I10" s="32" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="J10" s="32" t="n"/>
+        <v>0.05</v>
+      </c>
+      <c r="J10" s="32" t="n">
+        <v>-8.94</v>
+      </c>
       <c r="K10" s="32" t="n">
-        <v>7.51</v>
+        <v>7.6</v>
       </c>
       <c r="L10" s="32" t="n">
-        <v>8.51</v>
+        <v>12.77</v>
       </c>
       <c r="M10" s="32" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -4556,10 +4562,10 @@
         <v>5.68</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="G11" s="32" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="32" t="n">
@@ -4581,7 +4587,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
@@ -4590,41 +4596,39 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="32" t="n">
-        <v>1.87</v>
+        <v>0.62</v>
       </c>
       <c r="E12" s="32" t="n">
-        <v>1.57</v>
+        <v>-1.63</v>
       </c>
       <c r="F12" s="32" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="G12" s="32" t="n">
-        <v>3.6</v>
-      </c>
+        <v>4.63</v>
+      </c>
+      <c r="G12" s="32" t="n"/>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="32" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="J12" s="32" t="n">
-        <v>-8.94</v>
+        <v>55.25</v>
       </c>
       <c r="K12" s="32" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="L12" s="32" t="n">
-        <v>12.77</v>
+        <v>3.7</v>
       </c>
       <c r="M12" s="32" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
@@ -4633,365 +4637,363 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="D13" s="32" t="n">
-        <v>-0.61</v>
+        <v>-0.98</v>
       </c>
       <c r="E13" s="32" t="n">
-        <v>1.6</v>
+        <v>5.42</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>2.82</v>
+        <v>4.27</v>
       </c>
       <c r="G13" s="32" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="H13" s="32" t="n"/>
       <c r="I13" s="32" t="n">
-        <v>-0.21</v>
+        <v>0.46</v>
       </c>
       <c r="J13" s="32" t="n">
-        <v>57.47</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="K13" s="32" t="n">
-        <v>9.16</v>
+        <v>5.15</v>
       </c>
       <c r="L13" s="32" t="n">
-        <v>21.62</v>
+        <v>-6.45</v>
       </c>
       <c r="M13" s="32" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C14" s="32" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="D14" s="32" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="E14" s="32" t="n">
-        <v>-1.63</v>
+        <v>3.24</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>4.65</v>
+        <v>1.52</v>
       </c>
       <c r="G14" s="32" t="n">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="H14" s="32" t="n"/>
-      <c r="I14" s="32" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="I14" s="32" t="n"/>
       <c r="J14" s="32" t="n">
-        <v>55.25</v>
+        <v>-20.96</v>
       </c>
       <c r="K14" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
+        <v>7.53</v>
+      </c>
+      <c r="L14" s="32" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="M14" s="32" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>55 (B+)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C15" s="32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="D15" s="32" t="n">
         <v>0.31</v>
       </c>
       <c r="E15" s="32" t="n">
-        <v>3.24</v>
+        <v>0.46</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>1.54</v>
+        <v>6.24</v>
       </c>
       <c r="G15" s="32" t="n">
-        <v>4.19</v>
+        <v>3.91</v>
       </c>
       <c r="H15" s="32" t="n"/>
       <c r="I15" s="32" t="n">
-        <v>0.57</v>
+        <v>1.52</v>
       </c>
       <c r="J15" s="32" t="n">
-        <v>-20.96</v>
+        <v>195.09</v>
       </c>
       <c r="K15" s="32" t="n">
-        <v>7.53</v>
+        <v>5.71</v>
       </c>
       <c r="L15" s="32" t="n">
-        <v>6.67</v>
+        <v>9.09</v>
       </c>
       <c r="M15" s="32" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>55 (B+)</t>
+          <t>55 (B)</t>
         </is>
       </c>
       <c r="C16" s="32" t="n">
         <v>4.3</v>
       </c>
       <c r="D16" s="32" t="n">
-        <v>0.31</v>
+        <v>1.69</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>0.46</v>
+        <v>3.42</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>6.26</v>
+        <v>7.32</v>
       </c>
       <c r="G16" s="32" t="n">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="32" t="n">
-        <v>1.52</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="32" t="n">
-        <v>195.09</v>
+        <v>23.5</v>
       </c>
       <c r="K16" s="32" t="n">
-        <v>5.71</v>
+        <v>9.4</v>
       </c>
       <c r="L16" s="32" t="n">
-        <v>9.09</v>
+        <v>33.33</v>
       </c>
       <c r="M16" s="32" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>55 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C17" s="32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="D17" s="32" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E17" s="32" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="F17" s="32" t="n">
-        <v>7.32</v>
-      </c>
+        <v>-1.11</v>
+      </c>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
       <c r="G17" s="32" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="H17" s="32" t="n"/>
       <c r="I17" s="32" t="n">
-        <v>0.6</v>
+        <v>-0.16</v>
       </c>
       <c r="J17" s="32" t="n">
-        <v>23.5</v>
+        <v>-15.96</v>
       </c>
       <c r="K17" s="32" t="n">
-        <v>9.4</v>
+        <v>7.86</v>
       </c>
       <c r="L17" s="32" t="n">
-        <v>33.33</v>
+        <v>8.57</v>
       </c>
       <c r="M17" s="32" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>52 (B)</t>
-        </is>
-      </c>
-      <c r="C18" s="32" t="n"/>
+          <t>54 (B)</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>4.2</v>
+      </c>
       <c r="D18" s="32" t="n">
-        <v>-0.98</v>
+        <v>-0.61</v>
       </c>
       <c r="E18" s="32" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="F18" s="32" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="G18" s="32" t="n">
-        <v>2.98</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="32" t="n"/>
       <c r="H18" s="32" t="n"/>
       <c r="I18" s="32" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J18" s="32" t="n">
-        <v>86.01000000000001</v>
-      </c>
+        <v>-0.21</v>
+      </c>
+      <c r="J18" s="32" t="n"/>
       <c r="K18" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
+        <v>9.16</v>
+      </c>
+      <c r="L18" s="32" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="M18" s="32" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C19" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="D19" s="32" t="n">
-        <v>0.44</v>
+        <v>1.8</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="F19" s="32" t="n">
-        <v>2.81</v>
-      </c>
+        <v>-0.47</v>
+      </c>
+      <c r="F19" s="32" t="n"/>
       <c r="G19" s="32" t="n">
-        <v>1</v>
+        <v>3.24</v>
       </c>
       <c r="H19" s="32" t="n"/>
       <c r="I19" s="32" t="n">
-        <v>2.03</v>
+        <v>0.57</v>
       </c>
       <c r="J19" s="32" t="n">
-        <v>-22.67</v>
+        <v>11.14</v>
       </c>
       <c r="K19" s="32" t="n">
-        <v>7.65</v>
+        <v>7.26</v>
       </c>
       <c r="L19" s="32" t="n">
-        <v>10.87</v>
+        <v>7.84</v>
       </c>
       <c r="M19" s="32" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>51 (B)</t>
-        </is>
-      </c>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
+          <t>52 (B)</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>0.25</v>
+      </c>
       <c r="E20" s="32" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F20" s="32" t="n">
-        <v>2.04</v>
-      </c>
+        <v>5.44</v>
+      </c>
+      <c r="F20" s="32" t="n"/>
       <c r="G20" s="32" t="n">
-        <v>2.38</v>
+        <v>3.48</v>
       </c>
       <c r="H20" s="32" t="n"/>
       <c r="I20" s="32" t="n">
-        <v>-0.04</v>
+        <v>-0.18</v>
       </c>
       <c r="J20" s="32" t="n">
-        <v>8.67</v>
+        <v>-30.9</v>
       </c>
       <c r="K20" s="32" t="n">
-        <v>8.08</v>
+        <v>7.51</v>
       </c>
       <c r="L20" s="32" t="n">
-        <v>10.81</v>
+        <v>8.51</v>
       </c>
       <c r="M20" s="32" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C21" s="32" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="E21" s="32" t="n">
-        <v>5.33</v>
+        <v>8.06</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>0.36</v>
+        <v>2.81</v>
       </c>
       <c r="G21" s="32" t="n">
-        <v>0.35</v>
+        <v>3.22</v>
       </c>
       <c r="H21" s="32" t="n"/>
       <c r="I21" s="32" t="n">
-        <v>-0.6</v>
+        <v>-0.18</v>
       </c>
       <c r="J21" s="32" t="n">
-        <v>19.69</v>
+        <v>-0.7</v>
       </c>
       <c r="K21" s="32" t="n">
-        <v>6.91</v>
+        <v>7.77</v>
       </c>
       <c r="L21" s="32" t="n">
-        <v>6.9</v>
+        <v>9.68</v>
       </c>
       <c r="M21" s="32" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
@@ -5015,10 +5017,10 @@
         <v>6.03</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="32" t="n">
@@ -5040,44 +5042,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C23" s="32" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="D23" s="32" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="E23" s="32" t="n">
-        <v>8.06</v>
+        <v>5.33</v>
       </c>
       <c r="F23" s="32" t="n">
-        <v>2.83</v>
+        <v>0.34</v>
       </c>
       <c r="G23" s="32" t="n">
-        <v>3.06</v>
+        <v>0.45</v>
       </c>
       <c r="H23" s="32" t="n"/>
       <c r="I23" s="32" t="n">
-        <v>-0.18</v>
+        <v>-0.6</v>
       </c>
       <c r="J23" s="32" t="n">
-        <v>-0.7</v>
+        <v>19.69</v>
       </c>
       <c r="K23" s="32" t="n">
-        <v>7.77</v>
+        <v>6.91</v>
       </c>
       <c r="L23" s="32" t="n">
-        <v>9.68</v>
+        <v>6.9</v>
       </c>
       <c r="M23" s="32" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5103,10 @@
         <v>4.61</v>
       </c>
       <c r="F24" s="32" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="G24" s="32" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="H24" s="32" t="n"/>
       <c r="I24" s="32" t="n">
@@ -5126,44 +5128,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C25" s="32" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="D25" s="32" t="n">
-        <v>-1.11</v>
+        <v>1.68</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>2.61</v>
+        <v>5.48</v>
       </c>
       <c r="F25" s="32" t="n">
-        <v>2.95</v>
+        <v>4.56</v>
       </c>
       <c r="G25" s="32" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="32" t="n">
-        <v>-0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="J25" s="32" t="n">
-        <v>-15.96</v>
+        <v>14.97</v>
       </c>
       <c r="K25" s="32" t="n">
-        <v>7.86</v>
+        <v>7.38</v>
       </c>
       <c r="L25" s="32" t="n">
-        <v>8.57</v>
+        <v>6.25</v>
       </c>
       <c r="M25" s="32" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
@@ -5174,7 +5176,7 @@
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C26" s="32" t="n">
@@ -5187,11 +5189,9 @@
         <v>-1.42</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G26" s="32" t="n">
-        <v>3.54</v>
-      </c>
+        <v>2.21</v>
+      </c>
+      <c r="G26" s="32" t="n"/>
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="32" t="n">
         <v>0.68</v>
@@ -5212,37 +5212,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C27" s="32" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D27" s="32" t="n">
-        <v>1.68</v>
+        <v>0.44</v>
       </c>
       <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="32" t="n">
-        <v>2.58</v>
+        <v>1.17</v>
       </c>
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="32" t="n">
-        <v>-0.47</v>
+        <v>2.03</v>
       </c>
       <c r="J27" s="32" t="n">
-        <v>14.97</v>
+        <v>-22.67</v>
       </c>
       <c r="K27" s="32" t="n">
-        <v>7.38</v>
+        <v>7.65</v>
       </c>
       <c r="L27" s="32" t="n">
-        <v>6.25</v>
+        <v>10.87</v>
       </c>
       <c r="M27" s="32" t="n">
         <v>51</v>
@@ -5251,7 +5251,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B28" s="34" t="inlineStr">
@@ -5260,170 +5260,170 @@
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="D28" s="32" t="n">
-        <v>1.27</v>
+        <v>-3.97</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>2.35</v>
+        <v>5.22</v>
       </c>
       <c r="G28" s="32" t="n">
-        <v>2.75</v>
+        <v>0.75</v>
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="32" t="n">
-        <v>0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="J28" s="32" t="n">
-        <v>16.86</v>
+        <v>55.17</v>
       </c>
       <c r="K28" s="32" t="n">
-        <v>7.24</v>
+        <v>8.58</v>
       </c>
       <c r="L28" s="32" t="n">
-        <v>5.88</v>
+        <v>15.79</v>
       </c>
       <c r="M28" s="32" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C29" s="32" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="D29" s="32" t="n">
-        <v>-0.38</v>
+        <v>0.58</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>1.07</v>
+        <v>1.63</v>
       </c>
       <c r="G29" s="32" t="n">
-        <v>2.1</v>
+        <v>3.39</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="32" t="n">
-        <v>-0.05</v>
+        <v>0.22</v>
       </c>
       <c r="J29" s="32" t="n">
-        <v>-37.55</v>
+        <v>-12.89</v>
       </c>
       <c r="K29" s="32" t="n">
-        <v>6.99</v>
+        <v>7.74</v>
       </c>
       <c r="L29" s="32" t="n">
-        <v>1.67</v>
+        <v>11.11</v>
       </c>
       <c r="M29" s="32" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="D30" s="32" t="n">
-        <v>-3.97</v>
+        <v>-1.3</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>3.85</v>
+        <v>7.75</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>5.24</v>
+        <v>3.25</v>
       </c>
       <c r="G30" s="32" t="n">
-        <v>0.65</v>
+        <v>2.8</v>
       </c>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="32" t="n">
-        <v>-0.32</v>
+        <v>-0.7</v>
       </c>
       <c r="J30" s="32" t="n">
-        <v>55.17</v>
+        <v>41.11</v>
       </c>
       <c r="K30" s="32" t="n">
-        <v>8.58</v>
+        <v>6.02</v>
       </c>
       <c r="L30" s="32" t="n">
-        <v>15.79</v>
+        <v>10.45</v>
       </c>
       <c r="M30" s="32" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="D31" s="32" t="n">
-        <v>-1.3</v>
+        <v>-0.72</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>7.75</v>
+        <v>8.26</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>3.27</v>
+        <v>1.34</v>
       </c>
       <c r="G31" s="32" t="n">
-        <v>2.67</v>
+        <v>1.96</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="32" t="n">
-        <v>-0.7</v>
+        <v>-0.28</v>
       </c>
       <c r="J31" s="32" t="n">
-        <v>41.11</v>
+        <v>-8.56</v>
       </c>
       <c r="K31" s="32" t="n">
-        <v>6.02</v>
+        <v>6.37</v>
       </c>
       <c r="L31" s="32" t="n">
-        <v>10.45</v>
+        <v>15.79</v>
       </c>
       <c r="M31" s="32" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
@@ -5432,41 +5432,41 @@
         </is>
       </c>
       <c r="C32" s="32" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="D32" s="32" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>2.68</v>
+        <v>2.01</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>1.65</v>
+        <v>5.24</v>
       </c>
       <c r="G32" s="32" t="n">
-        <v>3.31</v>
+        <v>1.41</v>
       </c>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="32" t="n">
-        <v>0.22</v>
+        <v>-0.95</v>
       </c>
       <c r="J32" s="32" t="n">
-        <v>-12.89</v>
+        <v>-10.26</v>
       </c>
       <c r="K32" s="32" t="n">
-        <v>7.74</v>
+        <v>7.95</v>
       </c>
       <c r="L32" s="32" t="n">
-        <v>11.11</v>
+        <v>15.91</v>
       </c>
       <c r="M32" s="32" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B33" s="34" t="inlineStr">
@@ -5475,41 +5475,41 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="D33" s="32" t="n">
-        <v>-0.72</v>
+        <v>0.84</v>
       </c>
       <c r="E33" s="32" t="n">
-        <v>8.26</v>
+        <v>1.83</v>
       </c>
       <c r="F33" s="32" t="n">
-        <v>1.35</v>
+        <v>4.56</v>
       </c>
       <c r="G33" s="32" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="H33" s="32" t="n"/>
       <c r="I33" s="32" t="n">
-        <v>-0.28</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J33" s="32" t="n">
-        <v>-8.56</v>
+        <v>-15.51</v>
       </c>
       <c r="K33" s="32" t="n">
-        <v>6.37</v>
+        <v>7.83</v>
       </c>
       <c r="L33" s="32" t="n">
-        <v>15.79</v>
+        <v>8.33</v>
       </c>
       <c r="M33" s="32" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B34" s="34" t="inlineStr">
@@ -5518,201 +5518,183 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="D34" s="32" t="n">
-        <v>0.96</v>
+        <v>-0.5</v>
       </c>
       <c r="E34" s="32" t="n">
-        <v>2.01</v>
+        <v>8.49</v>
       </c>
       <c r="F34" s="32" t="n">
-        <v>5.25</v>
+        <v>1.7</v>
       </c>
       <c r="G34" s="32" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="32" t="n">
-        <v>-0.95</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J34" s="32" t="n">
-        <v>-10.26</v>
+        <v>-46.79</v>
       </c>
       <c r="K34" s="32" t="n">
-        <v>7.95</v>
+        <v>6.47</v>
       </c>
       <c r="L34" s="32" t="n">
-        <v>15.91</v>
+        <v>-5.26</v>
       </c>
       <c r="M34" s="32" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>44 (B-)</t>
+          <t>43 (C+)</t>
         </is>
       </c>
       <c r="C35" s="32" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D35" s="32" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="E35" s="32" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="F35" s="32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G35" s="32" t="n">
-        <v>1.69</v>
-      </c>
+        <v>1.05</v>
+      </c>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="32" t="n"/>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="32" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.24</v>
       </c>
       <c r="J35" s="32" t="n">
-        <v>-46.79</v>
+        <v>4.14</v>
       </c>
       <c r="K35" s="32" t="n">
-        <v>6.47</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L35" s="32" t="n">
-        <v>-5.26</v>
+        <v>10.26</v>
       </c>
       <c r="M35" s="32" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
-        </is>
-      </c>
-      <c r="C36" s="32" t="n">
-        <v>5.2</v>
-      </c>
+          <t>43 (C+)</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="n"/>
       <c r="D36" s="32" t="n"/>
       <c r="E36" s="32" t="n">
-        <v>1.83</v>
+        <v>5.73</v>
       </c>
       <c r="F36" s="32" t="n">
-        <v>4.58</v>
+        <v>3.05</v>
       </c>
       <c r="G36" s="32" t="n">
-        <v>2.06</v>
+        <v>0.44</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="J36" s="32" t="n">
-        <v>-15.51</v>
+        <v>18.04</v>
       </c>
       <c r="K36" s="32" t="n">
-        <v>7.83</v>
+        <v>7.24</v>
       </c>
       <c r="L36" s="32" t="n">
-        <v>8.33</v>
+        <v>5.88</v>
       </c>
       <c r="M36" s="32" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
-        </is>
-      </c>
-      <c r="C37" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D37" s="32" t="n">
-        <v>2.87</v>
-      </c>
+          <t>41 (C+)</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="n"/>
       <c r="E37" s="32" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="F37" s="32" t="n">
-        <v>4.2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F37" s="32" t="n"/>
       <c r="G37" s="32" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="32" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="J37" s="32" t="n">
-        <v>-14.97</v>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="J37" s="32" t="n"/>
       <c r="K37" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="L37" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="M37" s="32" t="n">
-        <v>30</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L37" s="32" t="n"/>
+      <c r="M37" s="32" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="D38" s="32" t="n">
-        <v>-1.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E38" s="32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="F38" s="32" t="n"/>
+        <v>2.83</v>
+      </c>
+      <c r="F38" s="32" t="n">
+        <v>1.05</v>
+      </c>
       <c r="G38" s="32" t="n">
-        <v>2.17</v>
+        <v>2.83</v>
       </c>
       <c r="H38" s="32" t="n"/>
-      <c r="I38" s="32" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="J38" s="32" t="n"/>
+      <c r="I38" s="32" t="n"/>
+      <c r="J38" s="32" t="n">
+        <v>-37.55</v>
+      </c>
       <c r="K38" s="32" t="n">
-        <v>6.72</v>
+        <v>6.99</v>
       </c>
       <c r="L38" s="32" t="n">
-        <v>-2.78</v>
+        <v>1.67</v>
       </c>
       <c r="M38" s="32" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39">
@@ -5723,7 +5705,7 @@
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C39" s="32" t="n">
@@ -5736,10 +5718,10 @@
         <v>2.35</v>
       </c>
       <c r="F39" s="32" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="G39" s="32" t="n">
-        <v>0.9</v>
+        <v>1.07</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="32" t="n">
@@ -5761,252 +5743,254 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>37 (C)</t>
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D40" s="32" t="n">
-        <v>-0.14</v>
+        <v>0.33</v>
       </c>
       <c r="E40" s="32" t="n">
-        <v>0.79</v>
+        <v>1.56</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>3.03</v>
+        <v>2.11</v>
       </c>
       <c r="G40" s="32" t="n">
-        <v>1.21</v>
+        <v>0.72</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="32" t="n">
-        <v>-0.74</v>
+        <v>-0.26</v>
       </c>
       <c r="J40" s="32" t="n">
-        <v>-6.99</v>
+        <v>-12.25</v>
       </c>
       <c r="K40" s="32" t="n">
-        <v>8.68</v>
+        <v>7.91</v>
       </c>
       <c r="L40" s="32" t="n">
-        <v>17.95</v>
+        <v>9.09</v>
       </c>
       <c r="M40" s="32" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>37 (C)</t>
         </is>
       </c>
       <c r="C41" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D41" s="32" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="D41" s="32" t="n"/>
       <c r="E41" s="32" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="F41" s="32" t="n">
-        <v>3.09</v>
+        <v>4.69</v>
       </c>
       <c r="G41" s="32" t="n">
-        <v>2.27</v>
+        <v>0.6</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="32" t="n">
-        <v>-0.62</v>
+        <v>-0.99</v>
       </c>
       <c r="J41" s="32" t="n">
-        <v>-20.27</v>
+        <v>-10.47</v>
       </c>
       <c r="K41" s="32" t="n">
-        <v>5.86</v>
+        <v>7.25</v>
       </c>
       <c r="L41" s="32" t="n">
-        <v>-11.36</v>
+        <v>6.45</v>
       </c>
       <c r="M41" s="32" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>35 (C)</t>
+          <t>36 (C)</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="D42" s="32" t="n">
-        <v>-0.12</v>
+        <v>-1.06</v>
       </c>
       <c r="E42" s="32" t="n">
-        <v>5.73</v>
+        <v>3.55</v>
       </c>
       <c r="F42" s="32" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="G42" s="32" t="n">
-        <v>0.35</v>
+        <v>2.27</v>
       </c>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J42" s="32" t="n"/>
+        <v>-0.15</v>
+      </c>
+      <c r="J42" s="32" t="n">
+        <v>-27.41</v>
+      </c>
       <c r="K42" s="32" t="n">
-        <v>7.24</v>
+        <v>6.72</v>
       </c>
       <c r="L42" s="32" t="n">
-        <v>5.88</v>
+        <v>-2.78</v>
       </c>
       <c r="M42" s="32" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>36 (C)</t>
         </is>
       </c>
       <c r="C43" s="32" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="D43" s="32" t="n">
-        <v>1.05</v>
+        <v>2.87</v>
       </c>
       <c r="E43" s="32" t="n">
-        <v>-1.5</v>
+        <v>2.98</v>
       </c>
       <c r="F43" s="32" t="n">
-        <v>4.59</v>
+        <v>4.18</v>
       </c>
       <c r="G43" s="32" t="n">
-        <v>2.58</v>
+        <v>3.31</v>
       </c>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="32" t="n">
-        <v>-0.24</v>
+        <v>-0.96</v>
       </c>
       <c r="J43" s="32" t="n">
-        <v>4.14</v>
+        <v>-14.97</v>
       </c>
       <c r="K43" s="32" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="L43" s="32" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="M43" s="32" t="n">
-        <v>43</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L43" s="32" t="n"/>
+      <c r="M43" s="32" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>36 (C)</t>
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="D44" s="32" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="E44" s="32" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G44" s="32" t="n"/>
+        <v>3.01</v>
+      </c>
+      <c r="G44" s="32" t="n">
+        <v>1.26</v>
+      </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="32" t="n">
-        <v>-0.8</v>
+        <v>-0.74</v>
       </c>
       <c r="J44" s="32" t="n">
-        <v>-10.94</v>
+        <v>-6.99</v>
       </c>
       <c r="K44" s="32" t="n">
-        <v>7.71</v>
+        <v>8.68</v>
       </c>
       <c r="L44" s="32" t="n">
-        <v>7.14</v>
+        <v>17.95</v>
       </c>
       <c r="M44" s="32" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>36 (C)</t>
         </is>
       </c>
       <c r="C45" s="32" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="D45" s="32" t="n">
-        <v>0.33</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E45" s="32" t="n">
-        <v>1.56</v>
+        <v>3.39</v>
       </c>
       <c r="F45" s="32" t="n">
-        <v>2.13</v>
+        <v>3.07</v>
       </c>
       <c r="G45" s="32" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="32" t="n">
-        <v>-0.26</v>
+        <v>-0.62</v>
       </c>
       <c r="J45" s="32" t="n">
-        <v>-12.25</v>
+        <v>-20.27</v>
       </c>
       <c r="K45" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L45" s="32" t="n"/>
-      <c r="M45" s="32" t="n"/>
+        <v>5.86</v>
+      </c>
+      <c r="L45" s="32" t="n">
+        <v>-11.36</v>
+      </c>
+      <c r="M45" s="32" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6029,10 +6013,10 @@
         <v>3.85</v>
       </c>
       <c r="F46" s="32" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G46" s="32" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H46" s="32" t="n"/>
       <c r="I46" s="32" t="n">
@@ -6054,44 +6038,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>32 (C)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C47" s="32" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="D47" s="32" t="n">
-        <v>-2.89</v>
+        <v>-0.19</v>
       </c>
       <c r="E47" s="32" t="n">
-        <v>3.28</v>
+        <v>1.37</v>
       </c>
       <c r="F47" s="32" t="n">
-        <v>4.71</v>
+        <v>2.48</v>
       </c>
       <c r="G47" s="32" t="n">
-        <v>0.58</v>
+        <v>2.42</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="32" t="n">
-        <v>-0.99</v>
+        <v>-0.8</v>
       </c>
       <c r="J47" s="32" t="n">
-        <v>-10.47</v>
+        <v>-10.94</v>
       </c>
       <c r="K47" s="32" t="n">
-        <v>7.25</v>
+        <v>7.71</v>
       </c>
       <c r="L47" s="32" t="n">
-        <v>6.45</v>
+        <v>7.14</v>
       </c>
       <c r="M47" s="32" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -6102,7 +6086,7 @@
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>31 (C-)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
@@ -6115,10 +6099,10 @@
         <v>0.75</v>
       </c>
       <c r="F48" s="32" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G48" s="32" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="32" t="n">
@@ -6140,85 +6124,87 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>30 (C-)</t>
+          <t>28 (C-)</t>
         </is>
       </c>
       <c r="C49" s="32" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="D49" s="32" t="n">
-        <v>-1.64</v>
+        <v>-3.05</v>
       </c>
       <c r="E49" s="32" t="n">
-        <v>4.99</v>
+        <v>2.12</v>
       </c>
       <c r="F49" s="32" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G49" s="32" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="32" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="J49" s="32" t="n"/>
+        <v>-3.52</v>
+      </c>
+      <c r="J49" s="32" t="n">
+        <v>-3.97</v>
+      </c>
       <c r="K49" s="32" t="n">
-        <v>7.02</v>
+        <v>8.5</v>
       </c>
       <c r="L49" s="32" t="n">
-        <v>1.75</v>
+        <v>25</v>
       </c>
       <c r="M49" s="32" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>27 (C-)</t>
+          <t>26 (D)</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="D50" s="32" t="n">
-        <v>-3.05</v>
+        <v>-1.64</v>
       </c>
       <c r="E50" s="32" t="n">
-        <v>2.12</v>
+        <v>4.99</v>
       </c>
       <c r="F50" s="32" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="G50" s="32" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="32" t="n">
-        <v>-3.52</v>
+        <v>-0.44</v>
       </c>
       <c r="J50" s="32" t="n">
-        <v>-3.97</v>
+        <v>-32.7</v>
       </c>
       <c r="K50" s="32" t="n">
-        <v>8.5</v>
+        <v>7.02</v>
       </c>
       <c r="L50" s="32" t="n">
-        <v>25</v>
+        <v>1.75</v>
       </c>
       <c r="M50" s="32" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51">
@@ -6229,7 +6215,7 @@
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>23 (D)</t>
+          <t>24 (D)</t>
         </is>
       </c>
       <c r="C51" s="32" t="n">
@@ -6241,8 +6227,12 @@
       <c r="E51" s="32" t="n">
         <v>5.15</v>
       </c>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
+      <c r="F51" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="32" t="n">
+        <v>0.79</v>
+      </c>
       <c r="H51" s="32" t="n"/>
       <c r="I51" s="32" t="n">
         <v>-2.45</v>
@@ -6251,10 +6241,14 @@
         <v>-18.14</v>
       </c>
       <c r="K51" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L51" s="32" t="n"/>
-      <c r="M51" s="32" t="n"/>
+        <v>6.71</v>
+      </c>
+      <c r="L51" s="32" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="M51" s="32" t="n">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6357,7 +6351,7 @@
         </is>
       </c>
       <c r="F2" s="14" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>4.8</v>
@@ -6365,8 +6359,12 @@
       <c r="H2" s="14" t="n">
         <v>1.68</v>
       </c>
-      <c r="I2" s="14" t="n"/>
-      <c r="J2" s="14" t="n"/>
+      <c r="I2" s="14" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>4.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -6391,7 +6389,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>60.1</v>
+        <v>59.6</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>5.1</v>
@@ -6403,81 +6401,83 @@
         <v>5.68</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="D4" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="G4" s="17" t="n">
+      <c r="D4" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="G4" s="20" t="n">
         <v>5.3</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="20" t="n">
         <v>-1.06</v>
       </c>
-      <c r="I4" s="17" t="n">
+      <c r="I4" s="20" t="n">
         <v>3.55</v>
       </c>
-      <c r="J4" s="17" t="n"/>
+      <c r="J4" s="20" t="n">
+        <v>2.37</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="G5" s="8" t="n">
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="G5" s="11" t="n">
         <v>4.2</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="11" t="n">
         <v>0.31</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="11" t="n">
         <v>3.24</v>
       </c>
-      <c r="J5" s="8" t="n">
-        <v>1.54</v>
+      <c r="J5" s="11" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="6">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>44.8</v>
+        <v>45.8</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>4.9</v>
@@ -6515,7 +6515,7 @@
         <v>2.68</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="7">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>45.5</v>
+        <v>45.1</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>3.9</v>
@@ -6553,7 +6553,7 @@
         <v>7.75</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="8">
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>4.4</v>
@@ -6591,309 +6591,295 @@
         <v>2.12</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="D9" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G9" s="11" t="n">
         <v>3.6</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="11" t="n">
         <v>5.44</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>1.17</v>
-      </c>
+      <c r="J9" s="11" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="D10" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Phoenix-Mesa-Chandler</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="17" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Boston-Cambridge-Newton</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F10" s="20" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Phoenix-Mesa-Chandler</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>47</v>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="G11" s="14" t="n">
+      <c r="F12" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Riverside-San Bernardino-Ontario</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>San Francisco-Oakland-Fremont</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>4.4</v>
       </c>
-      <c r="H11" s="14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Boston-Cambridge-Newton</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>Riverside-San Bernardino-Ontario</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco-Oakland-Fremont</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="H14" s="8" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Detroit-Warren-Dearborn</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I15" s="23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Seattle-Tacoma-Bellevue</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>Detroit-Warren-Dearborn</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Seattle-Tacoma-Bellevue</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="G16" s="14" t="n">
+      <c r="F16" s="11" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="G16" s="11" t="n">
         <v>5.9</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="11" t="n">
         <v>0.36</v>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="I16" s="11" t="n">
         <v>8.06</v>
       </c>
-      <c r="J16" s="14" t="n">
-        <v>2.83</v>
+      <c r="J16" s="11" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="17">
@@ -6911,7 +6897,7 @@
         </is>
       </c>
       <c r="D17" s="20" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
@@ -6919,7 +6905,7 @@
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>32.5</v>
+        <v>36.8</v>
       </c>
       <c r="G17" s="20" t="n">
         <v>4.8</v>
@@ -6931,7 +6917,7 @@
         <v>1.56</v>
       </c>
       <c r="J17" s="20" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="18">
@@ -6949,7 +6935,7 @@
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
@@ -6957,7 +6943,7 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>44.1</v>
+        <v>45.2</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>5.1</v>
@@ -6969,7 +6955,7 @@
         <v>8.26</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="19">
@@ -6995,7 +6981,7 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>4.7</v>
@@ -7007,46 +6993,42 @@
         <v>4.61</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="G20" s="14" t="n">
+      <c r="D20" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="G20" s="11" t="n">
         <v>4.2</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="11" t="n">
         <v>-1.11</v>
       </c>
-      <c r="I20" s="14" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>2.95</v>
-      </c>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="23" t="n">
@@ -7063,7 +7045,7 @@
         </is>
       </c>
       <c r="D21" s="23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
@@ -7071,7 +7053,7 @@
         </is>
       </c>
       <c r="F21" s="23" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>4.9</v>
@@ -7083,7 +7065,7 @@
         <v>0.75</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="22">
@@ -7101,7 +7083,7 @@
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
@@ -7109,7 +7091,7 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>49.1</v>
+        <v>47.1</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>4.3</v>
@@ -7121,7 +7103,7 @@
         <v>-1.42</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="23">
@@ -7147,7 +7129,7 @@
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="G23" s="20" t="n">
         <v>4.5</v>
@@ -7159,7 +7141,7 @@
         <v>3.85</v>
       </c>
       <c r="J23" s="20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="24">
@@ -7197,45 +7179,45 @@
         <v>0.79</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>47</v>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="G25" s="14" t="n">
+      <c r="D25" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="G25" s="17" t="n">
         <v>4.3</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="17" t="n">
         <v>-0.38</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="I25" s="17" t="n">
         <v>2.83</v>
       </c>
-      <c r="J25" s="14" t="n">
-        <v>1.07</v>
+      <c r="J25" s="17" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="26">
@@ -7253,7 +7235,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -7261,7 +7243,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3.7</v>
@@ -7291,7 +7273,7 @@
         </is>
       </c>
       <c r="D27" s="26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
@@ -7299,7 +7281,7 @@
         </is>
       </c>
       <c r="F27" s="26" t="n">
-        <v>22.8</v>
+        <v>24.2</v>
       </c>
       <c r="G27" s="26" t="n">
         <v>5.5</v>
@@ -7310,80 +7292,84 @@
       <c r="I27" s="26" t="n">
         <v>5.15</v>
       </c>
-      <c r="J27" s="26" t="n"/>
+      <c r="J27" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="n">
+      <c r="A28" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>Sacramento</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n">
-        <v>42</v>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="G28" s="17" t="n">
+      <c r="D28" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G28" s="14" t="n">
         <v>5.2</v>
       </c>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="17" t="n">
+      <c r="H28" s="14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I28" s="14" t="n">
         <v>1.83</v>
       </c>
-      <c r="J28" s="17" t="n">
-        <v>4.58</v>
+      <c r="J28" s="14" t="n">
+        <v>4.56</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="G29" s="5" t="n">
+      <c r="D29" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I29" s="2" t="n">
         <v>6.81</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>1.3</v>
+      <c r="J29" s="2" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="30">
@@ -7401,7 +7387,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -7409,7 +7395,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>5.8</v>
@@ -7421,46 +7407,44 @@
         <v>6.16</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Cincinnati</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>Cincinnati</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="G31" s="8" t="n">
+      <c r="D31" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="G31" s="11" t="n">
         <v>4.2</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="11" t="n">
         <v>-0.61</v>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="I31" s="11" t="n">
         <v>1.6</v>
       </c>
-      <c r="J31" s="8" t="n">
-        <v>2.82</v>
-      </c>
+      <c r="J31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -7477,7 +7461,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -7485,7 +7469,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>4.1</v>
@@ -7497,114 +7481,120 @@
         <v>6.36</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="D33" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Indianapolis-Carmel-Greenwood</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="G34" s="17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I34" s="17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="J34" s="17" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="G35" s="2" t="n">
+      <c r="F35" s="11" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="G35" s="11" t="n">
         <v>3.4</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="11" t="n">
         <v>1.8</v>
       </c>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
+      <c r="I35" s="11" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="J35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -7621,7 +7611,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
@@ -7629,7 +7619,7 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>59.7</v>
+        <v>61.1</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>3.1</v>
@@ -7641,121 +7631,121 @@
         <v>1.57</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>San Jose</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="G37" s="8" t="n">
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G37" s="11" t="n">
         <v>4.3</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H37" s="11" t="n">
         <v>0.31</v>
       </c>
-      <c r="I37" s="8" t="n">
+      <c r="I37" s="11" t="n">
         <v>0.46</v>
       </c>
-      <c r="J37" s="8" t="n">
-        <v>6.26</v>
+      <c r="J37" s="11" t="n">
+        <v>6.24</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="17" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="14" t="n">
+      <c r="D38" s="17" t="n">
         <v>44</v>
       </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="G38" s="14" t="n">
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G38" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="H38" s="17" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I38" s="14" t="n">
+      <c r="I38" s="17" t="n">
         <v>8.49</v>
       </c>
-      <c r="J38" s="14" t="n">
-        <v>1.72</v>
+      <c r="J38" s="17" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="n">
+      <c r="A39" s="26" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="27" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
       </c>
-      <c r="D39" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G39" s="23" t="n">
+      <c r="D39" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F39" s="26" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G39" s="26" t="n">
         <v>5.2</v>
       </c>
-      <c r="H39" s="23" t="n">
+      <c r="H39" s="26" t="n">
         <v>-1.64</v>
       </c>
-      <c r="I39" s="23" t="n">
+      <c r="I39" s="26" t="n">
         <v>4.99</v>
       </c>
-      <c r="J39" s="23" t="n">
-        <v>1.62</v>
+      <c r="J39" s="26" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="40">
@@ -7781,7 +7771,7 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>54.9</v>
+        <v>54.6</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>4.3</v>
@@ -7811,7 +7801,7 @@
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
@@ -7819,19 +7809,17 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>32.4</v>
+        <v>37.1</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>3.9</v>
       </c>
-      <c r="H41" s="20" t="n">
-        <v>-2.89</v>
-      </c>
+      <c r="H41" s="20" t="n"/>
       <c r="I41" s="20" t="n">
         <v>3.28</v>
       </c>
       <c r="J41" s="20" t="n">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="42">
@@ -7857,7 +7845,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3.5</v>
@@ -7869,7 +7857,7 @@
         <v>3.63</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="43">
@@ -7907,7 +7895,7 @@
         <v>6.03</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="44">
@@ -7925,7 +7913,7 @@
         </is>
       </c>
       <c r="D44" s="17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
@@ -7933,7 +7921,7 @@
         </is>
       </c>
       <c r="F44" s="17" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="G44" s="17" t="n">
         <v>4.2</v>
@@ -7945,7 +7933,7 @@
         <v>2.35</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="45">
@@ -7971,7 +7959,7 @@
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="G45" s="20" t="n">
         <v>3.8</v>
@@ -7983,7 +7971,7 @@
         <v>3.39</v>
       </c>
       <c r="J45" s="20" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="46">
@@ -8001,7 +7989,7 @@
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
@@ -8009,7 +7997,7 @@
         </is>
       </c>
       <c r="F46" s="11" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>4.5</v>
@@ -8021,7 +8009,7 @@
         <v>5.33</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="47">
@@ -8039,7 +8027,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -8047,7 +8035,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>63.7</v>
+        <v>63.1</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>3.9</v>
@@ -8059,84 +8047,80 @@
         <v>4.34</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n">
+      <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="G48" s="8" t="n">
+      <c r="D48" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="G48" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="H48" s="8" t="n">
+      <c r="H48" s="5" t="n">
         <v>0.62</v>
       </c>
-      <c r="I48" s="8" t="n">
+      <c r="I48" s="5" t="n">
         <v>-1.63</v>
       </c>
-      <c r="J48" s="8" t="n">
-        <v>4.65</v>
+      <c r="J48" s="5" t="n">
+        <v>4.63</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="n">
+      <c r="A49" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G49" s="11" t="n">
+      <c r="D49" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G49" s="14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H49" s="11" t="n">
+      <c r="H49" s="14" t="n">
         <v>0.44</v>
       </c>
-      <c r="I49" s="11" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>2.81</v>
-      </c>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n">
@@ -8161,7 +8145,7 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>4.5</v>
@@ -8173,7 +8157,7 @@
         <v>3.85</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="51">
@@ -8199,7 +8183,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8211,7 +8195,7 @@
         <v>-0.12</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
     </row>
   </sheetData>
@@ -8314,11 +8298,11 @@
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="G3" s="40" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
@@ -8336,7 +8320,7 @@
         </is>
       </c>
       <c r="C4" s="39" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" s="39" t="inlineStr">
         <is>
@@ -8348,11 +8332,11 @@
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="G4" s="40" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H4" s="40" t="inlineStr">
         <is>
@@ -8370,7 +8354,7 @@
         </is>
       </c>
       <c r="C5" s="39" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
@@ -8382,11 +8366,11 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="G5" s="40" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H5" s="40" t="inlineStr">
         <is>
@@ -8400,15 +8384,15 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E6" s="40" t="n">
@@ -8416,11 +8400,11 @@
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="G6" s="40" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H6" s="40" t="inlineStr">
         <is>
@@ -8468,11 +8452,11 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
@@ -8484,7 +8468,7 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="G8" s="40" t="n">
@@ -8492,7 +8476,7 @@
       </c>
       <c r="H8" s="40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8502,11 +8486,11 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
@@ -8522,7 +8506,7 @@
         </is>
       </c>
       <c r="G9" s="40" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9" s="40" t="inlineStr">
         <is>
@@ -8536,15 +8520,15 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="C10" s="39" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" s="39" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E10" s="40" t="n">
@@ -8552,11 +8536,11 @@
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="G10" s="40" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H10" s="40" t="inlineStr">
         <is>
@@ -8570,7 +8554,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C11" s="39" t="n">
@@ -8586,15 +8570,15 @@
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="G11" s="40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11" s="40" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8608,7 @@
         </is>
       </c>
       <c r="G12" s="40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="40" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -685,20 +685,20 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>75.2</v>
+        <v>74.2</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -716,82 +716,82 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>66</v>
+        <v>70.5</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>64.3</v>
+        <v>69.2</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -809,94 +809,94 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Hartford</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D8" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Very Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Austin-Round Rock-San Marcos</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>60.1</v>
+        <v>62.6</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -963,83 +963,83 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco-Oakland-Fremont</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
+      <c r="A12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth-Arlington</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>San Jose</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="A13" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>58.8</v>
+        <v>56.6</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1057,20 +1057,20 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>58.3</v>
+        <v>56</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1088,20 +1088,20 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>57</v>
+        <v>56.3</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1118,33 +1118,33 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Nashville</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A17" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Houston-Pasadena-The Woodlands</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="F18" s="11" t="n">
-        <v>54</v>
+        <v>52.2</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1181,20 +1181,20 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>54.3</v>
+        <v>50.6</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1212,20 +1212,20 @@
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1243,20 +1243,20 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1274,140 +1274,140 @@
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles-Long Beach-Anaheim</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Fresno</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Fresno</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="D23" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>51</v>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="A24" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Grand Rapids</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Providence-Warwick</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Providence</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="A25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Chicago-Naperville-Elgin</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1429,20 +1429,20 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>46.5</v>
+        <v>48.2</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1460,20 +1460,20 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>45.1</v>
+        <v>46.7</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1491,20 +1491,20 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>44.8</v>
+        <v>47.3</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1522,20 +1522,20 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>45</v>
+        <v>46.9</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1583,48 +1583,48 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Phoenix-Mesa-Chandler</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="A32" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="D33" s="19" t="n">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>43.3</v>
+        <v>42.5</v>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
@@ -1646,16 +1646,16 @@
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="F34" s="17" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>40.6</v>
+        <v>42.4</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
@@ -1708,20 +1708,20 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>40.4</v>
+        <v>41</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
@@ -1739,16 +1739,16 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="D37" s="19" t="n">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>39.9</v>
+        <v>40.4</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1770,16 +1770,16 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Grand Rapids</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1801,16 +1801,16 @@
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D39" s="19" t="n">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
@@ -1832,16 +1832,16 @@
     </row>
     <row r="40">
       <c r="A40" s="20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D40" s="22" t="n">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>37.4</v>
+        <v>36.7</v>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
     </row>
     <row r="41">
       <c r="A41" s="20" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>36.2</v>
+        <v>35.7</v>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D42" s="22" t="n">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>36.3</v>
+        <v>35.9</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -1925,20 +1925,20 @@
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -1987,16 +1987,16 @@
     </row>
     <row r="45">
       <c r="A45" s="20" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>34.1</v>
+        <v>33.5</v>
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
@@ -2017,48 +2017,48 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="B46" s="21" t="inlineStr">
-        <is>
-          <t>Orlando-Kissimmee-Sanford</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>Orlando</t>
-        </is>
-      </c>
-      <c r="D46" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="E46" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G46" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="A46" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B47" s="21" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -2080,16 +2080,16 @@
     </row>
     <row r="48">
       <c r="A48" s="23" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="F48" s="23" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
@@ -2111,20 +2111,20 @@
     </row>
     <row r="49">
       <c r="A49" s="23" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="F49" s="23" t="n">
-        <v>27.7</v>
+        <v>31.2</v>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
@@ -2142,20 +2142,20 @@
     </row>
     <row r="50">
       <c r="A50" s="23" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="F50" s="23" t="n">
-        <v>27</v>
+        <v>29.6</v>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
@@ -2173,20 +2173,20 @@
     </row>
     <row r="51">
       <c r="A51" s="23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="F51" s="23" t="n">
-        <v>27.4</v>
+        <v>28.2</v>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
@@ -2302,258 +2302,258 @@
         </is>
       </c>
       <c r="B2" s="26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="27" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D2" s="27" t="n">
         <v>82</v>
       </c>
       <c r="E2" s="28" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F2" s="27" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G2" s="27" t="n">
         <v>98</v>
       </c>
       <c r="H2" s="29" t="n"/>
       <c r="I2" s="27" t="n">
-        <v>94</v>
-      </c>
-      <c r="J2" s="27" t="n">
-        <v>85</v>
+        <v>98</v>
+      </c>
+      <c r="J2" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="K2" s="30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B3" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3" s="27" t="n">
         <v>75</v>
       </c>
-      <c r="C3" s="28" t="n">
-        <v>68</v>
-      </c>
       <c r="D3" s="27" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E3" s="27" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F3" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>93</v>
+      </c>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="28" t="n">
+        <v>61</v>
+      </c>
+      <c r="J3" s="30" t="n">
+        <v>24</v>
+      </c>
+      <c r="K3" s="27" t="n">
         <v>86</v>
-      </c>
-      <c r="G3" s="30" t="n">
-        <v>37</v>
-      </c>
-      <c r="H3" s="29" t="n"/>
-      <c r="I3" s="27" t="n">
-        <v>88</v>
-      </c>
-      <c r="J3" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="K3" s="30" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B4" s="26" t="n">
-        <v>66</v>
-      </c>
-      <c r="C4" s="30" t="n">
-        <v>20</v>
+        <v>71</v>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>77</v>
       </c>
       <c r="D4" s="27" t="n">
-        <v>75</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>83</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>57</v>
+        <v>86</v>
+      </c>
+      <c r="E4" s="28" t="n">
+        <v>56</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H4" s="29" t="n"/>
       <c r="I4" s="27" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J4" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="K4" s="27" t="n">
-        <v>84</v>
+        <v>10</v>
+      </c>
+      <c r="K4" s="28" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B5" s="26" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C5" s="28" t="n">
         <v>68</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>57</v>
-      </c>
-      <c r="E5" s="30" t="n">
-        <v>39</v>
+      <c r="D5" s="27" t="n">
+        <v>89</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>86</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>75</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>50</v>
+        <v>90</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>26</v>
       </c>
       <c r="H5" s="29" t="n"/>
-      <c r="I5" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="J5" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="K5" s="27" t="n">
-        <v>73</v>
+      <c r="I5" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J5" s="27" t="n">
+        <v>81</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>64</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>89</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>77</v>
+        <v>67</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>68</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="G6" s="30" t="n">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>88</v>
       </c>
       <c r="H6" s="29" t="n"/>
-      <c r="I6" s="28" t="n">
-        <v>59</v>
-      </c>
-      <c r="J6" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="K6" s="27" t="n">
+      <c r="I6" s="27" t="n">
         <v>96</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B7" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>32</v>
+      </c>
+      <c r="D7" s="28" t="n">
         <v>64</v>
       </c>
-      <c r="C7" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>93</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>50</v>
+      <c r="E7" s="28" t="n">
+        <v>67</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>97</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H7" s="29" t="n"/>
       <c r="I7" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="J7" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="K7" s="29" t="n">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>88</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B8" s="26" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>59</v>
+        <v>98</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>93</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>73</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>76</v>
+        <v>9</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>38</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>51</v>
       </c>
       <c r="H8" s="29" t="n"/>
-      <c r="I8" s="30" t="n">
-        <v>49</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>94</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>82</v>
+      <c r="I8" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" s="29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>77</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>57</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>50</v>
@@ -2561,15 +2561,15 @@
       <c r="F9" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="G9" s="27" t="n">
-        <v>96</v>
+      <c r="G9" s="28" t="n">
+        <v>63</v>
       </c>
       <c r="H9" s="29" t="n"/>
       <c r="I9" s="28" t="n">
-        <v>55</v>
-      </c>
-      <c r="J9" s="30" t="n">
-        <v>13</v>
+        <v>59</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>84</v>
@@ -2582,32 +2582,32 @@
         </is>
       </c>
       <c r="B10" s="26" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D10" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="E10" s="27" t="n">
-        <v>72</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>91</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>80</v>
+      <c r="E10" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="H10" s="29" t="n"/>
-      <c r="I10" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="J10" s="30" t="n">
-        <v>11</v>
+      <c r="I10" s="28" t="n">
+        <v>67</v>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="K10" s="28" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -2623,236 +2623,236 @@
         <v>95</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>55</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H11" s="29" t="n"/>
       <c r="I11" s="27" t="n">
         <v>82</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B12" s="26" t="n">
         <v>59</v>
       </c>
       <c r="C12" s="28" t="n">
-        <v>59</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="F12" s="30" t="n">
-        <v>23</v>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="H12" s="29" t="n"/>
-      <c r="I12" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="J12" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="K12" s="30" t="n">
-        <v>7</v>
+      <c r="I12" s="28" t="n">
+        <v>69</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K12" s="27" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B13" s="26" t="n">
-        <v>59</v>
-      </c>
-      <c r="C13" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="D13" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>91</v>
+        <v>58</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>23</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>75</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="H13" s="29" t="n"/>
-      <c r="I13" s="27" t="n">
-        <v>92</v>
-      </c>
-      <c r="J13" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="K13" s="30" t="n">
-        <v>47</v>
+      <c r="I13" s="28" t="n">
+        <v>63</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B14" s="26" t="n">
-        <v>59</v>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="D14" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="E14" s="28" t="n">
-        <v>59</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>59</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>93</v>
+        <v>57</v>
+      </c>
+      <c r="C14" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="D14" s="27" t="n">
+        <v>77</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>77</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>35</v>
       </c>
       <c r="H14" s="29" t="n"/>
-      <c r="I14" s="27" t="n">
-        <v>86</v>
-      </c>
-      <c r="J14" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>24</v>
+      <c r="I14" s="30" t="n">
+        <v>47</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C15" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="D15" s="28" t="n">
+        <v>39</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>48</v>
+      </c>
+      <c r="E15" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="E15" s="27" t="n">
-        <v>91</v>
-      </c>
-      <c r="F15" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="G15" s="28" t="n">
+      <c r="F15" s="28" t="n">
         <v>50</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>81</v>
       </c>
       <c r="H15" s="29" t="n"/>
       <c r="I15" s="27" t="n">
-        <v>73</v>
-      </c>
-      <c r="J15" s="27" t="n">
-        <v>87</v>
-      </c>
-      <c r="K15" s="30" t="n">
-        <v>4</v>
+        <v>76</v>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>62</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B16" s="26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="30" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>34</v>
-      </c>
-      <c r="E16" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="F16" s="30" t="n">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>59</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H16" s="29" t="n"/>
       <c r="I16" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="J16" s="27" t="n">
-        <v>81</v>
-      </c>
-      <c r="K16" s="28" t="n">
-        <v>58</v>
+        <v>78</v>
+      </c>
+      <c r="J16" s="30" t="n">
+        <v>48</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B17" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="C17" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="D17" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>39</v>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" s="27" t="n">
         <v>86</v>
-      </c>
-      <c r="E17" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="F17" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>89</v>
       </c>
       <c r="H17" s="29" t="n"/>
       <c r="I17" s="28" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J17" s="30" t="n">
-        <v>47</v>
-      </c>
-      <c r="K17" s="28" t="n">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -2862,783 +2862,783 @@
         </is>
       </c>
       <c r="B18" s="26" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" s="30" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="28" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E18" s="27" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>84</v>
       </c>
       <c r="H18" s="29" t="n"/>
-      <c r="I18" s="28" t="n">
-        <v>69</v>
-      </c>
-      <c r="J18" s="28" t="n">
-        <v>55</v>
+      <c r="I18" s="30" t="n">
+        <v>43</v>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>90</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B19" s="26" t="n">
-        <v>54</v>
-      </c>
-      <c r="C19" s="28" t="n">
-        <v>59</v>
-      </c>
-      <c r="D19" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="E19" s="28" t="n">
+        <v>51</v>
+      </c>
+      <c r="C19" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="D19" s="28" t="n">
         <v>50</v>
       </c>
+      <c r="E19" s="30" t="n">
+        <v>19</v>
+      </c>
       <c r="F19" s="28" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="H19" s="29" t="n"/>
-      <c r="I19" s="27" t="n">
-        <v>71</v>
-      </c>
-      <c r="J19" s="30" t="n">
-        <v>2</v>
+      <c r="I19" s="30" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="K19" s="27" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B20" s="26" t="n">
-        <v>52</v>
-      </c>
-      <c r="C20" s="30" t="n">
-        <v>48</v>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="E20" s="28" t="n">
-        <v>61</v>
+        <v>51</v>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>43</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>7</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H20" s="29" t="n"/>
-      <c r="I20" s="28" t="n">
-        <v>65</v>
-      </c>
-      <c r="J20" s="28" t="n">
-        <v>57</v>
-      </c>
-      <c r="K20" s="30" t="n">
-        <v>49</v>
+      <c r="I20" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>31</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B21" s="26" t="n">
-        <v>52</v>
-      </c>
-      <c r="C21" s="27" t="n">
-        <v>75</v>
+        <v>51</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>36</v>
       </c>
       <c r="D21" s="27" t="n">
-        <v>84</v>
-      </c>
-      <c r="E21" s="30" t="n">
+        <v>77</v>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>51</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H21" s="29" t="n"/>
+      <c r="I21" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J21" s="27" t="n">
+        <v>98</v>
+      </c>
+      <c r="K21" s="30" t="n">
         <v>2</v>
-      </c>
-      <c r="F21" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="H21" s="29" t="n"/>
-      <c r="I21" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="J21" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="K21" s="30" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B22" s="26" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>93</v>
-      </c>
-      <c r="G22" s="30" t="n">
-        <v>11</v>
+        <v>70</v>
+      </c>
+      <c r="F22" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="H22" s="29" t="n"/>
-      <c r="I22" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" s="27" t="n">
-        <v>79</v>
-      </c>
-      <c r="K22" s="27" t="n">
-        <v>89</v>
+      <c r="I22" s="27" t="n">
+        <v>73</v>
+      </c>
+      <c r="J22" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K22" s="28" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B23" s="26" t="n">
-        <v>52</v>
-      </c>
-      <c r="C23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="27" t="n">
-        <v>73</v>
+        <v>50</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>39</v>
       </c>
       <c r="E23" s="27" t="n">
-        <v>87</v>
-      </c>
-      <c r="F23" s="30" t="n">
-        <v>34</v>
+        <v>84</v>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>95</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H23" s="29" t="n"/>
-      <c r="I23" s="27" t="n">
+      <c r="I23" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K23" s="27" t="n">
         <v>90</v>
-      </c>
-      <c r="J23" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="K23" s="28" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B24" s="26" t="n">
-        <v>51</v>
-      </c>
-      <c r="C24" s="30" t="n">
-        <v>27</v>
-      </c>
-      <c r="D24" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="E24" s="27" t="n">
-        <v>89</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>70</v>
-      </c>
-      <c r="G24" s="28" t="n">
-        <v>65</v>
+        <v>50</v>
+      </c>
+      <c r="C24" s="27" t="n">
+        <v>91</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F24" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>12</v>
       </c>
       <c r="H24" s="29" t="n"/>
       <c r="I24" s="30" t="n">
-        <v>41</v>
-      </c>
-      <c r="J24" s="30" t="n">
-        <v>38</v>
-      </c>
-      <c r="K24" s="28" t="n">
-        <v>60</v>
+        <v>49</v>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B25" s="26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="D25" s="27" t="n">
-        <v>77</v>
-      </c>
-      <c r="E25" s="30" t="n">
-        <v>46</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="28" t="n">
-        <v>67</v>
+        <v>25</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>45</v>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>69</v>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>37</v>
       </c>
       <c r="H25" s="29" t="n"/>
-      <c r="I25" s="27" t="n">
+      <c r="I25" s="30" t="n">
+        <v>49</v>
+      </c>
+      <c r="J25" s="27" t="n">
         <v>76</v>
       </c>
-      <c r="J25" s="27" t="n">
-        <v>83</v>
-      </c>
       <c r="K25" s="30" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B26" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="C26" s="27" t="n">
-        <v>89</v>
-      </c>
-      <c r="D26" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="30" t="n">
-        <v>33</v>
+      <c r="C26" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="D26" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" s="27" t="n">
+        <v>79</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G26" s="28" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H26" s="29" t="n"/>
       <c r="I26" s="28" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J26" s="30" t="n">
-        <v>23</v>
-      </c>
-      <c r="K26" s="27" t="n">
-        <v>80</v>
+        <v>12</v>
+      </c>
+      <c r="K26" s="30" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B27" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="C27" s="27" t="n">
+        <v>73</v>
+      </c>
+      <c r="D27" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="H27" s="29" t="n"/>
+      <c r="I27" s="30" t="n">
+        <v>45</v>
+      </c>
+      <c r="J27" s="30" t="n">
+        <v>29</v>
+      </c>
+      <c r="K27" s="30" t="n">
         <v>46</v>
-      </c>
-      <c r="C27" s="30" t="n">
-        <v>48</v>
-      </c>
-      <c r="D27" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="E27" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>95</v>
-      </c>
-      <c r="G27" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="H27" s="29" t="n"/>
-      <c r="I27" s="28" t="n">
-        <v>57</v>
-      </c>
-      <c r="J27" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" s="30" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B28" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="C28" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="D28" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="E28" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="F28" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>78</v>
+        <v>47</v>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>61</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="F28" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>60</v>
       </c>
       <c r="H28" s="29" t="n"/>
       <c r="I28" s="30" t="n">
-        <v>47</v>
-      </c>
-      <c r="J28" s="28" t="n">
-        <v>50</v>
+        <v>27</v>
+      </c>
+      <c r="J28" s="30" t="n">
+        <v>43</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="C29" s="30" t="n">
-        <v>41</v>
-      </c>
-      <c r="D29" s="27" t="n">
-        <v>95</v>
-      </c>
-      <c r="E29" s="30" t="n">
+        <v>47</v>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D29" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G29" s="30" t="n">
+        <v>21</v>
+      </c>
+      <c r="H29" s="29" t="n"/>
+      <c r="I29" s="30" t="n">
         <v>37</v>
       </c>
-      <c r="F29" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="G29" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="H29" s="29" t="n"/>
-      <c r="I29" s="28" t="n">
-        <v>61</v>
-      </c>
-      <c r="J29" s="30" t="n">
-        <v>28</v>
-      </c>
-      <c r="K29" s="30" t="n">
-        <v>4</v>
+      <c r="J29" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K29" s="27" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B30" s="26" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C30" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="D30" s="30" t="n">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="D30" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="E30" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="F30" s="27" t="n">
-        <v>89</v>
+        <v>81</v>
+      </c>
+      <c r="F30" s="28" t="n">
+        <v>62</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H30" s="29" t="n"/>
       <c r="I30" s="30" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>49</v>
-      </c>
-      <c r="K30" s="30" t="n">
-        <v>13</v>
+        <v>45</v>
+      </c>
+      <c r="K30" s="28" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B31" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="C31" s="30" t="n">
-        <v>27</v>
-      </c>
-      <c r="D31" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="E31" s="28" t="n">
+        <v>46</v>
+      </c>
+      <c r="C31" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" s="27" t="n">
+        <v>88</v>
+      </c>
+      <c r="F31" s="28" t="n">
         <v>67</v>
       </c>
-      <c r="F31" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="G31" s="29" t="n">
-        <v>0</v>
+      <c r="G31" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="H31" s="29" t="n"/>
       <c r="I31" s="30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J31" s="27" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B32" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="C32" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="D32" s="30" t="n">
-        <v>11</v>
+        <v>46</v>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="27" t="n">
+        <v>73</v>
       </c>
       <c r="E32" s="28" t="n">
-        <v>57</v>
-      </c>
-      <c r="F32" s="28" t="n">
-        <v>61</v>
-      </c>
-      <c r="G32" s="28" t="n">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>26</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>33</v>
       </c>
       <c r="H32" s="29" t="n"/>
-      <c r="I32" s="30" t="n">
-        <v>31</v>
-      </c>
-      <c r="J32" s="27" t="n">
-        <v>72</v>
-      </c>
-      <c r="K32" s="30" t="n">
-        <v>4</v>
+      <c r="I32" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="J32" s="30" t="n">
+        <v>19</v>
+      </c>
+      <c r="K32" s="28" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B33" s="26" t="n">
         <v>43</v>
       </c>
       <c r="C33" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="D33" s="28" t="n">
-        <v>66</v>
+        <v>20</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>7</v>
       </c>
       <c r="E33" s="30" t="n">
-        <v>22</v>
-      </c>
-      <c r="F33" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="G33" s="30" t="n">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="G33" s="28" t="n">
+        <v>58</v>
       </c>
       <c r="H33" s="29" t="n"/>
       <c r="I33" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="J33" s="30" t="n">
-        <v>26</v>
+        <v>94</v>
+      </c>
+      <c r="J33" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B34" s="26" t="n">
         <v>43</v>
       </c>
-      <c r="C34" s="28" t="n">
-        <v>57</v>
+      <c r="C34" s="27" t="n">
+        <v>93</v>
       </c>
       <c r="D34" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="E34" s="27" t="n">
-        <v>98</v>
-      </c>
-      <c r="F34" s="28" t="n">
-        <v>68</v>
+        <v>36</v>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="30" t="n">
+        <v>8</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H34" s="29" t="n"/>
       <c r="I34" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" s="29" t="n">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="J34" s="27" t="n">
+        <v>79</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B35" s="26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="30" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D35" s="30" t="n">
-        <v>48</v>
-      </c>
-      <c r="E35" s="30" t="n">
-        <v>48</v>
-      </c>
-      <c r="F35" s="28" t="n">
-        <v>55</v>
+        <v>25</v>
+      </c>
+      <c r="E35" s="27" t="n">
+        <v>93</v>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>85</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H35" s="29" t="n"/>
-      <c r="I35" s="28" t="n">
-        <v>53</v>
+      <c r="I35" s="30" t="n">
+        <v>35</v>
       </c>
       <c r="J35" s="30" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B36" s="26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" s="27" t="n">
-        <v>91</v>
-      </c>
-      <c r="E36" s="27" t="n">
-        <v>74</v>
+        <v>45</v>
+      </c>
+      <c r="D36" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E36" s="30" t="n">
+        <v>49</v>
       </c>
       <c r="F36" s="30" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H36" s="29" t="n"/>
       <c r="I36" s="30" t="n">
-        <v>33</v>
-      </c>
-      <c r="J36" s="27" t="n">
-        <v>70</v>
+        <v>41</v>
+      </c>
+      <c r="J36" s="30" t="n">
+        <v>38</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B37" s="26" t="n">
         <v>40</v>
       </c>
       <c r="C37" s="30" t="n">
-        <v>23</v>
-      </c>
-      <c r="D37" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="E37" s="27" t="n">
-        <v>78</v>
+        <v>39</v>
+      </c>
+      <c r="D37" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>16</v>
       </c>
       <c r="F37" s="30" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G37" s="30" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H37" s="29" t="n"/>
-      <c r="I37" s="30" t="n">
-        <v>22</v>
-      </c>
-      <c r="J37" s="27" t="n">
-        <v>74</v>
+      <c r="I37" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="J37" s="30" t="n">
+        <v>21</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
         <v>40</v>
       </c>
       <c r="C38" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="D38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="F38" s="30" t="n">
         <v>7</v>
       </c>
+      <c r="D38" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" s="30" t="n">
+        <v>42</v>
+      </c>
+      <c r="F38" s="28" t="n">
+        <v>54</v>
+      </c>
       <c r="G38" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="H38" s="29" t="n"/>
+      <c r="I38" s="27" t="n">
+        <v>88</v>
+      </c>
+      <c r="J38" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="H38" s="29" t="n"/>
-      <c r="I38" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="J38" s="27" t="n">
-        <v>89</v>
-      </c>
-      <c r="K38" s="27" t="n">
-        <v>93</v>
+      <c r="K38" s="30" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B39" s="26" t="n">
         <v>39</v>
       </c>
-      <c r="C39" s="27" t="n">
-        <v>93</v>
-      </c>
-      <c r="D39" s="30" t="n">
-        <v>39</v>
-      </c>
-      <c r="E39" s="30" t="n">
-        <v>24</v>
+      <c r="C39" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" s="27" t="n">
+        <v>91</v>
+      </c>
+      <c r="E39" s="27" t="n">
+        <v>74</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H39" s="29" t="n"/>
       <c r="I39" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="J39" s="30" t="n">
-        <v>43</v>
+        <v>16</v>
+      </c>
+      <c r="J39" s="27" t="n">
+        <v>93</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B40" s="26" t="n">
         <v>37</v>
       </c>
       <c r="C40" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="D40" s="28" t="n">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <v>41</v>
       </c>
       <c r="E40" s="28" t="n">
         <v>50</v>
@@ -3646,123 +3646,123 @@
       <c r="F40" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="G40" s="28" t="n">
-        <v>50</v>
+      <c r="G40" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="H40" s="29" t="n"/>
       <c r="I40" s="30" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J40" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="K40" s="28" t="n">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="K40" s="30" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B41" s="26" t="n">
         <v>36</v>
       </c>
       <c r="C41" s="30" t="n">
-        <v>48</v>
-      </c>
-      <c r="D41" s="30" t="n">
-        <v>32</v>
+        <v>43</v>
+      </c>
+      <c r="D41" s="27" t="n">
+        <v>95</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F41" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="G41" s="30" t="n">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>77</v>
       </c>
       <c r="H41" s="29" t="n"/>
       <c r="I41" s="30" t="n">
-        <v>29</v>
-      </c>
-      <c r="J41" s="28" t="n">
-        <v>51</v>
-      </c>
-      <c r="K41" s="27" t="n">
-        <v>78</v>
+        <v>20</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <v>17</v>
+      </c>
+      <c r="K41" s="30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B42" s="26" t="n">
         <v>36</v>
       </c>
-      <c r="C42" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="D42" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="F42" s="30" t="n">
-        <v>27</v>
+      <c r="C42" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="D42" s="28" t="n">
+        <v>61</v>
+      </c>
+      <c r="E42" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>82</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H42" s="29" t="n"/>
       <c r="I42" s="30" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J42" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="K42" s="27" t="n">
-        <v>71</v>
+        <v>5</v>
+      </c>
+      <c r="K42" s="28" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B43" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="C43" s="27" t="n">
-        <v>73</v>
+        <v>36</v>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>39</v>
       </c>
       <c r="D43" s="30" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E43" s="30" t="n">
-        <v>28</v>
-      </c>
-      <c r="F43" s="30" t="n">
-        <v>41</v>
+        <v>37</v>
+      </c>
+      <c r="F43" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="G43" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H43" s="29" t="n"/>
       <c r="I43" s="30" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J43" s="28" t="n">
         <v>50</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -3775,26 +3775,26 @@
         <v>34</v>
       </c>
       <c r="C44" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="D44" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>44</v>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>79</v>
+      </c>
+      <c r="G44" s="28" t="n">
         <v>50</v>
-      </c>
-      <c r="E44" s="30" t="n">
-        <v>26</v>
-      </c>
-      <c r="F44" s="27" t="n">
-        <v>77</v>
-      </c>
-      <c r="G44" s="30" t="n">
-        <v>28</v>
       </c>
       <c r="H44" s="29" t="n"/>
       <c r="I44" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="28" t="n">
-        <v>53</v>
+      <c r="J44" s="27" t="n">
+        <v>83</v>
       </c>
       <c r="K44" s="28" t="n">
         <v>56</v>
@@ -3803,246 +3803,246 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B45" s="26" t="n">
         <v>34</v>
       </c>
       <c r="C45" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="D45" s="28" t="n">
-        <v>61</v>
-      </c>
-      <c r="E45" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="D45" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E45" s="30" t="n">
+        <v>21</v>
+      </c>
+      <c r="F45" s="30" t="n">
+        <v>41</v>
+      </c>
+      <c r="G45" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" s="29" t="n"/>
+      <c r="I45" s="28" t="n">
+        <v>53</v>
+      </c>
+      <c r="J45" s="28" t="n">
         <v>52</v>
       </c>
-      <c r="F45" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="G45" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="H45" s="29" t="n"/>
-      <c r="I45" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="30" t="n">
-        <v>34</v>
-      </c>
-      <c r="K45" s="28" t="n">
-        <v>64</v>
+      <c r="K45" s="30" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B46" s="26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C46" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="D46" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E46" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="F46" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="G46" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D46" s="28" t="n">
         <v>50</v>
       </c>
+      <c r="E46" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="G46" s="30" t="n">
+        <v>49</v>
+      </c>
       <c r="H46" s="29" t="n"/>
-      <c r="I46" s="28" t="n">
-        <v>67</v>
-      </c>
-      <c r="J46" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="K46" s="30" t="n">
-        <v>16</v>
+      <c r="I46" s="30" t="n">
+        <v>39</v>
+      </c>
+      <c r="J46" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="K46" s="28" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B47" s="26" t="n">
         <v>32</v>
       </c>
       <c r="C47" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="D47" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="E47" s="28" t="n">
-        <v>65</v>
-      </c>
-      <c r="F47" s="28" t="n">
-        <v>64</v>
+        <v>39</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="E47" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="F47" s="30" t="n">
+        <v>23</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H47" s="29" t="n"/>
-      <c r="I47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="30" t="n">
-        <v>21</v>
-      </c>
-      <c r="K47" s="30" t="n">
-        <v>4</v>
+      <c r="I47" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="J47" s="28" t="n">
+        <v>67</v>
+      </c>
+      <c r="K47" s="27" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B48" s="26" t="n">
         <v>31</v>
       </c>
       <c r="C48" s="30" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D48" s="30" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E48" s="30" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F48" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="G48" s="30" t="n">
-        <v>4</v>
+        <v>44</v>
+      </c>
+      <c r="G48" s="28" t="n">
+        <v>53</v>
       </c>
       <c r="H48" s="29" t="n"/>
       <c r="I48" s="30" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="J48" s="30" t="n">
-        <v>40</v>
-      </c>
-      <c r="K48" s="27" t="n">
-        <v>98</v>
+        <v>36</v>
+      </c>
+      <c r="K48" s="28" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B49" s="26" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C49" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="D49" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="E49" s="28" t="n">
-        <v>63</v>
-      </c>
-      <c r="F49" s="27" t="n">
-        <v>82</v>
+        <v>39</v>
+      </c>
+      <c r="D49" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E49" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>51</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H49" s="29" t="n"/>
       <c r="I49" s="30" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J49" s="30" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B50" s="26" t="n">
-        <v>27</v>
-      </c>
-      <c r="C50" s="30" t="n">
-        <v>11</v>
+        <v>30</v>
+      </c>
+      <c r="C50" s="28" t="n">
+        <v>64</v>
       </c>
       <c r="D50" s="30" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E50" s="30" t="n">
-        <v>13</v>
-      </c>
-      <c r="F50" s="28" t="n">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="F50" s="30" t="n">
+        <v>28</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H50" s="29" t="n"/>
       <c r="I50" s="30" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>36</v>
-      </c>
-      <c r="K50" s="28" t="n">
-        <v>69</v>
+        <v>14</v>
+      </c>
+      <c r="K50" s="27" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B51" s="26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C51" s="30" t="n">
         <v>11</v>
       </c>
       <c r="D51" s="30" t="n">
-        <v>27</v>
-      </c>
-      <c r="E51" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="F51" s="30" t="n">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="E51" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>50</v>
       </c>
       <c r="G51" s="30" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H51" s="29" t="n"/>
-      <c r="I51" s="30" t="n">
-        <v>39</v>
-      </c>
-      <c r="J51" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="K51" s="30" t="n">
-        <v>20</v>
+      <c r="I51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="28" t="n">
+        <v>69</v>
+      </c>
+      <c r="K51" s="27" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>79 (A+)</t>
+          <t>78 (A+)</t>
         </is>
       </c>
       <c r="C2" s="29" t="n">
@@ -4159,20 +4159,20 @@
         <v>1.76</v>
       </c>
       <c r="E2" s="29" t="n">
-        <v>3.63</v>
+        <v>4.32</v>
       </c>
       <c r="F2" s="29" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="G2" s="29" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="H2" s="29" t="n"/>
       <c r="I2" s="29" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="J2" s="29" t="n">
-        <v>38.82</v>
+        <v>-2.03</v>
       </c>
       <c r="K2" s="29" t="n">
         <v>7.23</v>
@@ -4187,290 +4187,294 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>75 (A+)</t>
+          <t>74 (A+)</t>
         </is>
       </c>
       <c r="C3" s="29" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="D3" s="29" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>6.36</v>
+        <v>7.75</v>
       </c>
       <c r="F3" s="29" t="n">
-        <v>1.29</v>
+        <v>0.66</v>
       </c>
       <c r="G3" s="29" t="n">
-        <v>2.3</v>
+        <v>4.41</v>
       </c>
       <c r="H3" s="29" t="n"/>
       <c r="I3" s="29" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="J3" s="29" t="n">
-        <v>5.41</v>
+        <v>-19.65</v>
       </c>
       <c r="K3" s="29" t="n">
-        <v>5.72</v>
+        <v>7.95</v>
       </c>
       <c r="L3" s="29" t="n">
-        <v>-12.77</v>
+        <v>15.91</v>
       </c>
       <c r="M3" s="29" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>66 (A)</t>
+          <t>71 (A+)</t>
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6.16</v>
+        <v>3.94</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>2.13</v>
+        <v>1.58</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>3.57</v>
+        <v>3.73</v>
       </c>
       <c r="H4" s="29" t="n"/>
       <c r="I4" s="29" t="n">
-        <v>1.96</v>
+        <v>0.84</v>
       </c>
       <c r="J4" s="29" t="n">
-        <v>-9.83</v>
+        <v>-31.3</v>
       </c>
       <c r="K4" s="29" t="n">
-        <v>7.95</v>
+        <v>7.43</v>
       </c>
       <c r="L4" s="29" t="n">
-        <v>15.91</v>
+        <v>6.38</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>69 (A+)</t>
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>0.73</v>
+        <v>1.87</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>3.24</v>
+        <v>6.99</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G5" s="29" t="n"/>
+        <v>0.83</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>1.85</v>
+      </c>
       <c r="H5" s="29" t="n"/>
-      <c r="I5" s="29" t="n"/>
-      <c r="J5" s="29" t="n"/>
+      <c r="I5" s="29" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>34.49</v>
+      </c>
       <c r="K5" s="29" t="n">
-        <v>7.65</v>
+        <v>5.72</v>
       </c>
       <c r="L5" s="29" t="n">
-        <v>6.98</v>
+        <v>-12.77</v>
       </c>
       <c r="M5" s="29" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>67 (A)</t>
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>1.69</v>
+        <v>1.06</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>2.22</v>
-      </c>
+        <v>0.76</v>
+      </c>
+      <c r="F6" s="29" t="n"/>
       <c r="G6" s="29" t="n">
-        <v>2.46</v>
+        <v>3.69</v>
       </c>
       <c r="H6" s="29" t="n"/>
       <c r="I6" s="29" t="n">
-        <v>-0.04</v>
+        <v>1.56</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>8.67</v>
+        <v>104.08</v>
       </c>
       <c r="K6" s="29" t="n">
-        <v>8.609999999999999</v>
+        <v>7.27</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>16.13</v>
+        <v>16.67</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>66 (A)</t>
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>2.77</v>
+        <v>0.98</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="F7" s="29" t="n"/>
+        <v>4.99</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>0.33</v>
+      </c>
       <c r="G7" s="29" t="n">
-        <v>2.49</v>
+        <v>1.21</v>
       </c>
       <c r="H7" s="29" t="n"/>
-      <c r="I7" s="29" t="n">
-        <v>1.88</v>
-      </c>
+      <c r="I7" s="29" t="n"/>
       <c r="J7" s="29" t="n">
-        <v>-12.7</v>
+        <v>39.08</v>
       </c>
       <c r="K7" s="29" t="n">
-        <v>3.33</v>
+        <v>6.86</v>
       </c>
       <c r="L7" s="29" t="n">
-        <v>-16.67</v>
+        <v>-3.57</v>
       </c>
       <c r="M7" s="29" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>63 (A-)</t>
+          <t>65 (A)</t>
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>0.82</v>
+        <v>2.77</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>3.26</v>
+        <v>2.5</v>
       </c>
       <c r="H8" s="29" t="n"/>
       <c r="I8" s="29" t="n">
-        <v>-0.21</v>
+        <v>1.88</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>57.47</v>
+        <v>6.72</v>
       </c>
       <c r="K8" s="29" t="n">
-        <v>7.88</v>
+        <v>3.33</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>8.82</v>
+        <v>-16.67</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>61 (A-)</t>
+          <t>64 (A)</t>
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>3</v>
+        <v>0.82</v>
       </c>
       <c r="E9" s="29" t="n"/>
       <c r="F9" s="29" t="n"/>
       <c r="G9" s="29" t="n">
-        <v>4.47</v>
+        <v>2.94</v>
       </c>
       <c r="H9" s="29" t="n"/>
       <c r="I9" s="29" t="n">
-        <v>0.98</v>
+        <v>0.06</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>-29.44</v>
+        <v>19.15</v>
       </c>
       <c r="K9" s="29" t="n">
-        <v>7.95</v>
+        <v>7.88</v>
       </c>
       <c r="L9" s="29" t="n">
-        <v>15.91</v>
+        <v>8.82</v>
       </c>
       <c r="M9" s="29" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -4481,7 +4485,7 @@
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>60 (A-)</t>
+          <t>63 (A-)</t>
         </is>
       </c>
       <c r="C10" s="29" t="n">
@@ -4490,22 +4494,14 @@
       <c r="D10" s="29" t="n">
         <v>1.26</v>
       </c>
-      <c r="E10" s="29" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>3.39</v>
-      </c>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
       <c r="H10" s="29" t="n"/>
       <c r="I10" s="29" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>-30.9</v>
-      </c>
+        <v>0.36</v>
+      </c>
+      <c r="J10" s="29" t="n"/>
       <c r="K10" s="29" t="n">
         <v>7.48</v>
       </c>
@@ -4534,20 +4530,20 @@
         <v>0.72</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>-1.63</v>
+        <v>-0.91</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>4.36</v>
+        <v>3.14</v>
       </c>
       <c r="G11" s="29" t="n">
-        <v>2.79</v>
+        <v>3.12</v>
       </c>
       <c r="H11" s="29" t="n"/>
       <c r="I11" s="29" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>55.25</v>
+        <v>18.48</v>
       </c>
       <c r="K11" s="29" t="n">
         <v>7.21</v>
@@ -4562,247 +4558,231 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>59 (A-)</t>
+          <t>59 (B+)</t>
         </is>
       </c>
       <c r="C12" s="29" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="D12" s="29" t="n">
-        <v>-0.36</v>
+        <v>0.73</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="G12" s="29" t="n">
-        <v>3.07</v>
-      </c>
+        <v>3.13</v>
+      </c>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
       <c r="H12" s="29" t="n"/>
-      <c r="I12" s="29" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J12" s="29" t="n">
-        <v>86.01000000000001</v>
-      </c>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="29" t="n"/>
       <c r="K12" s="29" t="n">
-        <v>5.59</v>
+        <v>7.65</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>-6.06</v>
+        <v>6.98</v>
       </c>
       <c r="M12" s="29" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>59 (A-)</t>
+          <t>58 (B+)</t>
         </is>
       </c>
       <c r="C13" s="29" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>1.06</v>
+        <v>1.52</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>0.46</v>
+        <v>6.16</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>3.78</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="G13" s="29" t="n"/>
       <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>195.09</v>
-      </c>
+      <c r="I13" s="29" t="n"/>
+      <c r="J13" s="29" t="n"/>
       <c r="K13" s="29" t="n">
-        <v>7.27</v>
+        <v>7.95</v>
       </c>
       <c r="L13" s="29" t="n">
-        <v>16.67</v>
+        <v>15.91</v>
       </c>
       <c r="M13" s="29" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>59 (B+)</t>
+          <t>57 (B+)</t>
         </is>
       </c>
       <c r="C14" s="29" t="n">
         <v>4.1</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>-0.73</v>
+        <v>1.69</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>4.34</v>
+        <v>2.79</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>2.09</v>
+        <v>1.38</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>4.42</v>
+        <v>2.19</v>
       </c>
       <c r="H14" s="29" t="n"/>
       <c r="I14" s="29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>14.73</v>
+        <v>-41.29</v>
       </c>
       <c r="K14" s="29" t="n">
-        <v>7</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L14" s="29" t="n">
-        <v>0</v>
+        <v>16.13</v>
       </c>
       <c r="M14" s="29" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>56 (B+)</t>
         </is>
       </c>
       <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="G15" s="29" t="n"/>
+      <c r="D15" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="29" t="n">
+        <v>3.43</v>
+      </c>
       <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
+      <c r="I15" s="29" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J15" s="29" t="n">
-        <v>41.11</v>
+        <v>12.45</v>
       </c>
       <c r="K15" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="29" t="n"/>
+        <v>7.27</v>
+      </c>
+      <c r="L15" s="29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M15" s="29" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>56 (B+)</t>
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>5.68</v>
+        <v>4.93</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>5.55</v>
+        <v>1.96</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>3.45</v>
+        <v>4.48</v>
       </c>
       <c r="H16" s="29" t="n"/>
       <c r="I16" s="29" t="n">
-        <v>1.83</v>
+        <v>1.08</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>20.24</v>
+        <v>-3.28</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>7.42</v>
+        <v>7</v>
       </c>
       <c r="L16" s="29" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="M16" s="29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
-        </is>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>3.09</v>
-      </c>
+          <t>53 (B)</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
       <c r="G17" s="29" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="H17" s="29" t="n"/>
       <c r="I17" s="29" t="n">
-        <v>0.05</v>
+        <v>0.54</v>
       </c>
       <c r="J17" s="29" t="n">
-        <v>-8.94</v>
+        <v>-18.37</v>
       </c>
       <c r="K17" s="29" t="n">
-        <v>7.43</v>
+        <v>7.73</v>
       </c>
       <c r="L17" s="29" t="n">
-        <v>6.38</v>
+        <v>9.09</v>
       </c>
       <c r="M17" s="29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -4813,26 +4793,30 @@
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>52 (B)</t>
         </is>
       </c>
       <c r="C18" s="29" t="n">
         <v>5.7</v>
       </c>
-      <c r="D18" s="29" t="n"/>
+      <c r="D18" s="29" t="n">
+        <v>0.84</v>
+      </c>
       <c r="E18" s="29" t="n">
-        <v>8.06</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>2.63</v>
+        <v>3.45</v>
       </c>
       <c r="H18" s="29" t="n"/>
-      <c r="I18" s="29" t="n"/>
+      <c r="I18" s="29" t="n">
+        <v>-0.09</v>
+      </c>
       <c r="J18" s="29" t="n">
-        <v>-0.7</v>
+        <v>42.78</v>
       </c>
       <c r="K18" s="29" t="n">
         <v>8.130000000000001</v>
@@ -4847,302 +4831,302 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C19" s="29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E19" s="29" t="n"/>
-      <c r="F19" s="29" t="n"/>
+        <v>4.3</v>
+      </c>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F19" s="29" t="n">
+        <v>2.01</v>
+      </c>
       <c r="G19" s="29" t="n">
-        <v>3.61</v>
+        <v>3.2</v>
       </c>
       <c r="H19" s="29" t="n"/>
       <c r="I19" s="29" t="n">
-        <v>0.68</v>
+        <v>-0.44</v>
       </c>
       <c r="J19" s="29" t="n">
-        <v>-39.5</v>
+        <v>12.87</v>
       </c>
       <c r="K19" s="29" t="n">
-        <v>7.71</v>
+        <v>7.83</v>
       </c>
       <c r="L19" s="29" t="n">
-        <v>7.14</v>
+        <v>8.33</v>
       </c>
       <c r="M19" s="29" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="E20" s="29" t="n">
-        <v>4.61</v>
+        <v>-0.04</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>4.74</v>
+        <v>2.22</v>
       </c>
       <c r="G20" s="29" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="H20" s="29" t="n"/>
       <c r="I20" s="29" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>-0.37</v>
+        <v>-14.84</v>
       </c>
       <c r="K20" s="29" t="n">
-        <v>7.27</v>
+        <v>7.71</v>
       </c>
       <c r="L20" s="29" t="n">
-        <v>2.7</v>
+        <v>7.14</v>
       </c>
       <c r="M20" s="29" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C21" s="29" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="D21" s="29" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="E21" s="29" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="F21" s="29" t="n"/>
+        <v>3.77</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>6.35</v>
+      </c>
       <c r="G21" s="29" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="H21" s="29" t="n"/>
       <c r="I21" s="29" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="J21" s="29" t="n">
-        <v>11.14</v>
+        <v>132.32</v>
       </c>
       <c r="K21" s="29" t="n">
-        <v>7.26</v>
+        <v>4.71</v>
       </c>
       <c r="L21" s="29" t="n">
-        <v>7.84</v>
+        <v>-6.9</v>
       </c>
       <c r="M21" s="29" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C22" s="29" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="D22" s="29" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>6.03</v>
+        <v>5.19</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>1.06</v>
+        <v>5.52</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>0.98</v>
+        <v>3.32</v>
       </c>
       <c r="H22" s="29" t="n"/>
       <c r="I22" s="29" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="J22" s="29" t="n">
-        <v>20.14</v>
-      </c>
+        <v>1.83</v>
+      </c>
+      <c r="J22" s="29" t="n"/>
       <c r="K22" s="29" t="n">
-        <v>8.119999999999999</v>
+        <v>7.42</v>
       </c>
       <c r="L22" s="29" t="n">
-        <v>18.6</v>
+        <v>4.55</v>
       </c>
       <c r="M22" s="29" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C23" s="29" t="n">
-        <v>9.1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="29" t="n">
-        <v>1.27</v>
+        <v>-0.08</v>
       </c>
       <c r="E23" s="29" t="n">
-        <v>6.52</v>
+        <v>6.84</v>
       </c>
       <c r="F23" s="29" t="n">
-        <v>3.09</v>
+        <v>0.64</v>
       </c>
       <c r="G23" s="29" t="n">
-        <v>1.11</v>
+        <v>0.72</v>
       </c>
       <c r="H23" s="29" t="n"/>
       <c r="I23" s="29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="J23" s="29" t="n">
-        <v>-22.67</v>
-      </c>
+        <v>-0.87</v>
+      </c>
+      <c r="J23" s="29" t="n"/>
       <c r="K23" s="29" t="n">
-        <v>7.28</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L23" s="29" t="n">
-        <v>4.17</v>
+        <v>18.6</v>
       </c>
       <c r="M23" s="29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C24" s="29" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>0.51</v>
+        <v>-5.05</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>6.81</v>
+        <v>3.79</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>1.75</v>
+        <v>5.16</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>2.97</v>
+        <v>0.91</v>
       </c>
       <c r="H24" s="29" t="n"/>
       <c r="I24" s="29" t="n">
-        <v>-0.36</v>
+        <v>-0.13</v>
       </c>
       <c r="J24" s="29" t="n">
-        <v>-10.55</v>
+        <v>-0.59</v>
       </c>
       <c r="K24" s="29" t="n">
-        <v>7.43</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L24" s="29" t="n">
-        <v>6.38</v>
+        <v>12.12</v>
       </c>
       <c r="M24" s="29" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C25" s="29" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="D25" s="29" t="n">
-        <v>1.69</v>
+        <v>0.16</v>
       </c>
       <c r="E25" s="29" t="n">
-        <v>3.42</v>
+        <v>4.16</v>
       </c>
       <c r="F25" s="29" t="n">
-        <v>7.06</v>
+        <v>1.78</v>
       </c>
       <c r="G25" s="29" t="n">
-        <v>3.04</v>
+        <v>2.23</v>
       </c>
       <c r="H25" s="29" t="n"/>
       <c r="I25" s="29" t="n">
-        <v>0.6</v>
+        <v>-0.13</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>23.5</v>
+        <v>29.19</v>
       </c>
       <c r="K25" s="29" t="n">
-        <v>4.71</v>
+        <v>7.1</v>
       </c>
       <c r="L25" s="29" t="n">
-        <v>-6.9</v>
+        <v>3.03</v>
       </c>
       <c r="M25" s="29" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
@@ -5153,277 +5137,279 @@
       <c r="C26" s="29" t="n">
         <v>4.3</v>
       </c>
-      <c r="D26" s="29" t="n">
-        <v>-2.12</v>
-      </c>
+      <c r="D26" s="29" t="n"/>
       <c r="E26" s="29" t="n">
-        <v>2.61</v>
+        <v>6.2</v>
       </c>
       <c r="F26" s="29" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G26" s="29" t="n">
-        <v>2.96</v>
-      </c>
+        <v>4.04</v>
+      </c>
+      <c r="G26" s="29" t="n"/>
       <c r="H26" s="29" t="n"/>
       <c r="I26" s="29" t="n">
-        <v>-0.16</v>
+        <v>0.2</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>-15.96</v>
+        <v>-25.29</v>
       </c>
       <c r="K26" s="29" t="n">
-        <v>7.83</v>
+        <v>5.59</v>
       </c>
       <c r="L26" s="29" t="n">
-        <v>8.33</v>
+        <v>-6.06</v>
       </c>
       <c r="M26" s="29" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C27" s="29" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="D27" s="29" t="n">
-        <v>-0.11</v>
+        <v>1.8</v>
       </c>
       <c r="E27" s="29" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="F27" s="29" t="n">
-        <v>0.91</v>
-      </c>
+        <v>-0.25</v>
+      </c>
+      <c r="F27" s="29" t="n"/>
       <c r="G27" s="29" t="n">
-        <v>2.11</v>
+        <v>3.29</v>
       </c>
       <c r="H27" s="29" t="n"/>
       <c r="I27" s="29" t="n">
-        <v>-0.05</v>
+        <v>0.57</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>-37.55</v>
+        <v>-18.19</v>
       </c>
       <c r="K27" s="29" t="n">
-        <v>6.6</v>
+        <v>7.26</v>
       </c>
       <c r="L27" s="29" t="n">
-        <v>-8.619999999999999</v>
+        <v>7.84</v>
       </c>
       <c r="M27" s="29" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
-        </is>
-      </c>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="29" t="n"/>
-      <c r="E28" s="29" t="n"/>
-      <c r="F28" s="29" t="n"/>
+          <t>47 (B-)</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>2.99</v>
+      </c>
       <c r="G28" s="29" t="n">
-        <v>3.38</v>
+        <v>2.92</v>
       </c>
       <c r="H28" s="29" t="n"/>
       <c r="I28" s="29" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J28" s="29" t="n"/>
+        <v>-0.63</v>
+      </c>
+      <c r="J28" s="29" t="n">
+        <v>-5.72</v>
+      </c>
       <c r="K28" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L28" s="29" t="n"/>
-      <c r="M28" s="29" t="n"/>
+        <v>6.31</v>
+      </c>
+      <c r="L28" s="29" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="M28" s="29" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C29" s="29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D29" s="29" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E29" s="29" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="F29" s="29" t="n">
-        <v>4.38</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="29" t="n"/>
       <c r="G29" s="29" t="n">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="H29" s="29" t="n"/>
       <c r="I29" s="29" t="n"/>
-      <c r="J29" s="29" t="n">
-        <v>-14.97</v>
-      </c>
+      <c r="J29" s="29" t="n"/>
       <c r="K29" s="29" t="n">
-        <v>5</v>
+        <v>7.77</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="M29" s="29" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C30" s="29" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="D30" s="29" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="E30" s="29" t="n">
-        <v>8.26</v>
+        <v>6.43</v>
       </c>
       <c r="F30" s="29" t="n">
-        <v>1.2</v>
+        <v>1.94</v>
       </c>
       <c r="G30" s="29" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="H30" s="29" t="n"/>
       <c r="I30" s="29" t="n">
-        <v>-0.28</v>
+        <v>-0.61</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>-8.56</v>
+        <v>-4.03</v>
       </c>
       <c r="K30" s="29" t="n">
-        <v>6.28</v>
+        <v>7.43</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>15.52</v>
+        <v>6.38</v>
       </c>
       <c r="M30" s="29" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C31" s="29" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="D31" s="29" t="n">
-        <v>0.98</v>
+        <v>-1.18</v>
       </c>
       <c r="E31" s="29" t="n">
-        <v>5.33</v>
+        <v>7.51</v>
       </c>
       <c r="F31" s="29" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="G31" s="29" t="n">
-        <v>0.41</v>
-      </c>
+        <v>1.89</v>
+      </c>
+      <c r="G31" s="29" t="n"/>
       <c r="H31" s="29" t="n"/>
       <c r="I31" s="29" t="n">
-        <v>-0.6</v>
+        <v>-0.66</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>19.69</v>
+        <v>38.19</v>
       </c>
       <c r="K31" s="29" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="L31" s="29" t="n">
-        <v>-3.57</v>
+        <v>0</v>
       </c>
       <c r="M31" s="29" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>43 (C+)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C32" s="29" t="n">
-        <v>4.2</v>
+        <v>9.1</v>
       </c>
       <c r="D32" s="29" t="n">
-        <v>-1.44</v>
+        <v>1.27</v>
       </c>
       <c r="E32" s="29" t="n">
-        <v>4</v>
+        <v>4.39</v>
       </c>
       <c r="F32" s="29" t="n">
-        <v>2.08</v>
+        <v>3.39</v>
       </c>
       <c r="G32" s="29" t="n">
-        <v>2.81</v>
+        <v>2.16</v>
       </c>
       <c r="H32" s="29" t="n"/>
       <c r="I32" s="29" t="n">
-        <v>0.22</v>
+        <v>2.12</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>16.86</v>
+        <v>-22.67</v>
       </c>
       <c r="K32" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L32" s="29" t="n"/>
-      <c r="M32" s="29" t="n"/>
+        <v>7.28</v>
+      </c>
+      <c r="L32" s="29" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="M32" s="29" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B33" s="31" t="inlineStr">
@@ -5432,41 +5418,41 @@
         </is>
       </c>
       <c r="C33" s="29" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="D33" s="29" t="n">
-        <v>1.05</v>
+        <v>-1.54</v>
       </c>
       <c r="E33" s="29" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="F33" s="29" t="n">
-        <v>4.31</v>
+        <v>1.63</v>
       </c>
       <c r="G33" s="29" t="n">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="H33" s="29" t="n"/>
       <c r="I33" s="29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>-15.51</v>
+        <v>-54.27</v>
       </c>
       <c r="K33" s="29" t="n">
-        <v>7</v>
+        <v>6.48</v>
       </c>
       <c r="L33" s="29" t="n">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="M33" s="29" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
@@ -5475,127 +5461,127 @@
         </is>
       </c>
       <c r="C34" s="29" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D34" s="29" t="n">
-        <v>-1.18</v>
+        <v>-0.09</v>
       </c>
       <c r="E34" s="29" t="n">
-        <v>8.49</v>
+        <v>0.62</v>
       </c>
       <c r="F34" s="29" t="n">
-        <v>1.88</v>
+        <v>4.42</v>
       </c>
       <c r="G34" s="29" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="H34" s="29" t="n"/>
       <c r="I34" s="29" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.47</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>-46.79</v>
+        <v>32.81</v>
       </c>
       <c r="K34" s="29" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="L34" s="29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M34" s="29" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>41 (C+)</t>
+          <t>42 (C+)</t>
         </is>
       </c>
       <c r="C35" s="29" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="D35" s="29" t="n">
-        <v>0.16</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E35" s="29" t="n">
-        <v>3.55</v>
+        <v>7.84</v>
       </c>
       <c r="F35" s="29" t="n">
-        <v>2.2</v>
+        <v>1.12</v>
       </c>
       <c r="G35" s="29" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="H35" s="29" t="n"/>
       <c r="I35" s="29" t="n">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>-27.41</v>
+        <v>-12.9</v>
       </c>
       <c r="K35" s="29" t="n">
-        <v>7.1</v>
+        <v>6.28</v>
       </c>
       <c r="L35" s="29" t="n">
-        <v>3.03</v>
+        <v>15.52</v>
       </c>
       <c r="M35" s="29" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C36" s="29" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="D36" s="29" t="n">
-        <v>2.43</v>
+        <v>-1.44</v>
       </c>
       <c r="E36" s="29" t="n">
-        <v>5.48</v>
+        <v>3.68</v>
       </c>
       <c r="F36" s="29" t="n">
-        <v>4.37</v>
+        <v>2.07</v>
       </c>
       <c r="G36" s="29" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="H36" s="29" t="n"/>
       <c r="I36" s="29" t="n">
-        <v>-0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>14.97</v>
+        <v>-9.77</v>
       </c>
       <c r="K36" s="29" t="n">
-        <v>6.11</v>
+        <v>7.19</v>
       </c>
       <c r="L36" s="29" t="n">
-        <v>-8.890000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M36" s="29" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B37" s="31" t="inlineStr">
@@ -5603,42 +5589,40 @@
           <t>40 (C+)</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
-        <v>5.3</v>
-      </c>
+      <c r="C37" s="29" t="n"/>
       <c r="D37" s="29" t="n">
-        <v>0.08</v>
+        <v>1.05</v>
       </c>
       <c r="E37" s="29" t="n">
-        <v>5.73</v>
+        <v>1.22</v>
       </c>
       <c r="F37" s="29" t="n">
-        <v>2.94</v>
+        <v>4.35</v>
       </c>
       <c r="G37" s="29" t="n">
-        <v>0.44</v>
+        <v>1.89</v>
       </c>
       <c r="H37" s="29" t="n"/>
       <c r="I37" s="29" t="n">
-        <v>0.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J37" s="29" t="n">
-        <v>18.04</v>
+        <v>-21.43</v>
       </c>
       <c r="K37" s="29" t="n">
-        <v>7.15</v>
+        <v>7</v>
       </c>
       <c r="L37" s="29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M37" s="29" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
@@ -5646,40 +5630,40 @@
           <t>40 (C+)</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n"/>
+      <c r="C38" s="29" t="n">
+        <v>5</v>
+      </c>
       <c r="D38" s="29" t="n">
-        <v>-5.05</v>
+        <v>-1.48</v>
       </c>
       <c r="E38" s="29" t="n">
-        <v>3.85</v>
+        <v>3.46</v>
       </c>
       <c r="F38" s="29" t="n">
-        <v>5.2</v>
+        <v>2.04</v>
       </c>
       <c r="G38" s="29" t="n">
-        <v>0.71</v>
+        <v>2.26</v>
       </c>
       <c r="H38" s="29" t="n"/>
-      <c r="I38" s="29" t="n">
-        <v>-0.32</v>
-      </c>
+      <c r="I38" s="29" t="n"/>
       <c r="J38" s="29" t="n">
-        <v>55.17</v>
+        <v>-34.14</v>
       </c>
       <c r="K38" s="29" t="n">
-        <v>8.210000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="L38" s="29" t="n">
-        <v>12.12</v>
+        <v>1.75</v>
       </c>
       <c r="M38" s="29" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B39" s="31" t="inlineStr">
@@ -5688,32 +5672,32 @@
         </is>
       </c>
       <c r="C39" s="29" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="D39" s="29" t="n">
-        <v>-0.09</v>
+        <v>2.43</v>
       </c>
       <c r="E39" s="29" t="n">
-        <v>2.01</v>
+        <v>6.12</v>
       </c>
       <c r="F39" s="29" t="n">
-        <v>5.16</v>
+        <v>4.26</v>
       </c>
       <c r="G39" s="29" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="H39" s="29" t="n"/>
       <c r="I39" s="29" t="n">
-        <v>-0.95</v>
+        <v>-0.63</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>-10.26</v>
+        <v>64.22</v>
       </c>
       <c r="K39" s="29" t="n">
-        <v>7.25</v>
+        <v>6.11</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>2.5</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="M39" s="29" t="n">
         <v>41</v>
@@ -5722,7 +5706,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B40" s="31" t="inlineStr">
@@ -5731,31 +5715,33 @@
         </is>
       </c>
       <c r="C40" s="29" t="n"/>
-      <c r="D40" s="29" t="n"/>
+      <c r="D40" s="29" t="n">
+        <v>0.08</v>
+      </c>
       <c r="E40" s="29" t="n"/>
       <c r="F40" s="29" t="n"/>
-      <c r="G40" s="29" t="n"/>
+      <c r="G40" s="29" t="n">
+        <v>0.12</v>
+      </c>
       <c r="H40" s="29" t="n"/>
       <c r="I40" s="29" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="J40" s="29" t="n">
-        <v>4.14</v>
-      </c>
+        <v>0.23</v>
+      </c>
+      <c r="J40" s="29" t="n"/>
       <c r="K40" s="29" t="n">
-        <v>7.29</v>
+        <v>7.15</v>
       </c>
       <c r="L40" s="29" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M40" s="29" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B41" s="31" t="inlineStr">
@@ -5764,41 +5750,41 @@
         </is>
       </c>
       <c r="C41" s="29" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="D41" s="29" t="n">
-        <v>-0.23</v>
+        <v>2.87</v>
       </c>
       <c r="E41" s="29" t="n">
-        <v>0.79</v>
+        <v>3.59</v>
       </c>
       <c r="F41" s="29" t="n">
-        <v>2.76</v>
+        <v>4.38</v>
       </c>
       <c r="G41" s="29" t="n">
-        <v>1.28</v>
+        <v>3.35</v>
       </c>
       <c r="H41" s="29" t="n"/>
       <c r="I41" s="29" t="n">
-        <v>-0.74</v>
+        <v>-0.8</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>-6.99</v>
+        <v>-22.81</v>
       </c>
       <c r="K41" s="29" t="n">
-        <v>7.77</v>
+        <v>5</v>
       </c>
       <c r="L41" s="29" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="M41" s="29" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B42" s="31" t="inlineStr">
@@ -5807,71 +5793,71 @@
         </is>
       </c>
       <c r="C42" s="29" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="D42" s="29" t="n">
-        <v>-1.8</v>
+        <v>0.85</v>
       </c>
       <c r="E42" s="29" t="n">
-        <v>3.39</v>
+        <v>5.3</v>
       </c>
       <c r="F42" s="29" t="n">
-        <v>3.41</v>
+        <v>1.17</v>
       </c>
       <c r="G42" s="29" t="n">
-        <v>2.44</v>
+        <v>1.54</v>
       </c>
       <c r="H42" s="29" t="n"/>
       <c r="I42" s="29" t="n">
-        <v>-0.62</v>
+        <v>-1.45</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>-20.27</v>
+        <v>-36.97</v>
       </c>
       <c r="K42" s="29" t="n">
-        <v>7.56</v>
+        <v>7.43</v>
       </c>
       <c r="L42" s="29" t="n">
-        <v>5.56</v>
+        <v>10.34</v>
       </c>
       <c r="M42" s="29" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>35 (C)</t>
-        </is>
-      </c>
-      <c r="C43" s="29" t="n">
-        <v>4.6</v>
-      </c>
+          <t>36 (C)</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="n"/>
       <c r="D43" s="29" t="n">
-        <v>-1.24</v>
+        <v>-0.11</v>
       </c>
       <c r="E43" s="29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F43" s="29" t="n">
-        <v>2.84</v>
-      </c>
+        <v>3.05</v>
+      </c>
+      <c r="F43" s="29" t="n"/>
       <c r="G43" s="29" t="n"/>
       <c r="H43" s="29" t="n"/>
       <c r="I43" s="29" t="n">
-        <v>-1.1</v>
+        <v>0.35</v>
       </c>
       <c r="J43" s="29" t="n"/>
       <c r="K43" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L43" s="29" t="n"/>
-      <c r="M43" s="29" t="n"/>
+        <v>6.6</v>
+      </c>
+      <c r="L43" s="29" t="n">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="M43" s="29" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5884,23 +5870,25 @@
           <t>34 (C)</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="29" t="n"/>
+      <c r="C44" s="29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D44" s="29" t="n">
+        <v>-2.79</v>
+      </c>
       <c r="E44" s="29" t="n">
-        <v>2.12</v>
+        <v>3.48</v>
       </c>
       <c r="F44" s="29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G44" s="29" t="n">
-        <v>1.91</v>
-      </c>
+        <v>1.38</v>
+      </c>
+      <c r="G44" s="29" t="n"/>
       <c r="H44" s="29" t="n"/>
       <c r="I44" s="29" t="n">
-        <v>-3.52</v>
+        <v>-3.19</v>
       </c>
       <c r="J44" s="29" t="n">
-        <v>-3.97</v>
+        <v>36.76</v>
       </c>
       <c r="K44" s="29" t="n">
         <v>7.4</v>
@@ -5915,7 +5903,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B45" s="31" t="inlineStr">
@@ -5927,81 +5915,79 @@
         <v>4.8</v>
       </c>
       <c r="D45" s="29" t="n">
-        <v>0.85</v>
+        <v>-0.46</v>
       </c>
       <c r="E45" s="29" t="n">
-        <v>3.85</v>
+        <v>1.64</v>
       </c>
       <c r="F45" s="29" t="n">
-        <v>1.48</v>
+        <v>2.29</v>
       </c>
       <c r="G45" s="29" t="n">
-        <v>1.77</v>
+        <v>0.9</v>
       </c>
       <c r="H45" s="29" t="n"/>
       <c r="I45" s="29" t="n">
-        <v>-1.62</v>
+        <v>-0.1</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>-11.14</v>
+        <v>-1.17</v>
       </c>
       <c r="K45" s="29" t="n">
-        <v>7.43</v>
+        <v>6.6</v>
       </c>
       <c r="L45" s="29" t="n">
-        <v>10.34</v>
+        <v>0</v>
       </c>
       <c r="M45" s="29" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C46" s="29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="D46" s="29" t="n">
-        <v>-1.54</v>
-      </c>
+        <v>4.8</v>
+      </c>
+      <c r="D46" s="29" t="n"/>
       <c r="E46" s="29" t="n">
-        <v>0.75</v>
+        <v>-1.45</v>
       </c>
       <c r="F46" s="29" t="n">
-        <v>1.91</v>
+        <v>4.3</v>
       </c>
       <c r="G46" s="29" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="H46" s="29" t="n"/>
       <c r="I46" s="29" t="n">
-        <v>0.1</v>
+        <v>-0.31</v>
       </c>
       <c r="J46" s="29" t="n">
-        <v>-35.64</v>
+        <v>3.44</v>
       </c>
       <c r="K46" s="29" t="n">
-        <v>6.48</v>
+        <v>7.29</v>
       </c>
       <c r="L46" s="29" t="n">
-        <v>9.68</v>
+        <v>2.86</v>
       </c>
       <c r="M46" s="29" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B47" s="31" t="inlineStr">
@@ -6009,34 +5995,42 @@
           <t>32 (C)</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n"/>
-      <c r="D47" s="29" t="n"/>
+      <c r="C47" s="29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D47" s="29" t="n">
+        <v>-1.07</v>
+      </c>
       <c r="E47" s="29" t="n">
-        <v>5.15</v>
+        <v>2.83</v>
       </c>
       <c r="F47" s="29" t="n">
-        <v>1.94</v>
+        <v>3.98</v>
       </c>
       <c r="G47" s="29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H47" s="29" t="n"/>
       <c r="I47" s="29" t="n">
-        <v>-2.45</v>
+        <v>-0.82</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>-18.14</v>
+        <v>15.03</v>
       </c>
       <c r="K47" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L47" s="29" t="n"/>
-      <c r="M47" s="29" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="L47" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="M47" s="29" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B48" s="31" t="inlineStr">
@@ -6045,162 +6039,156 @@
         </is>
       </c>
       <c r="C48" s="29" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="D48" s="29" t="n">
-        <v>-1.07</v>
+        <v>-0.59</v>
       </c>
       <c r="E48" s="29" t="n">
-        <v>3.28</v>
+        <v>2.04</v>
       </c>
       <c r="F48" s="29" t="n">
-        <v>4.11</v>
+        <v>2.27</v>
       </c>
       <c r="G48" s="29" t="n">
-        <v>0.66</v>
+        <v>2.61</v>
       </c>
       <c r="H48" s="29" t="n"/>
       <c r="I48" s="29" t="n">
-        <v>-0.99</v>
+        <v>-0.43</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>-10.47</v>
+        <v>-12.03</v>
       </c>
       <c r="K48" s="29" t="n">
-        <v>9</v>
+        <v>7.54</v>
       </c>
       <c r="L48" s="29" t="n">
-        <v>20</v>
+        <v>5.41</v>
       </c>
       <c r="M48" s="29" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>28 (C-)</t>
-        </is>
-      </c>
-      <c r="C49" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D49" s="29" t="n">
-        <v>-1.48</v>
-      </c>
+          <t>31 (C-)</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="n"/>
+      <c r="D49" s="29" t="n"/>
       <c r="E49" s="29" t="n">
-        <v>4.99</v>
+        <v>3</v>
       </c>
       <c r="F49" s="29" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="G49" s="29" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H49" s="29" t="n"/>
       <c r="I49" s="29" t="n">
-        <v>-0.44</v>
+        <v>-1.16</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>-32.7</v>
+        <v>-6.07</v>
       </c>
       <c r="K49" s="29" t="n">
-        <v>7.02</v>
+        <v>6.74</v>
       </c>
       <c r="L49" s="29" t="n">
-        <v>1.75</v>
+        <v>-2.56</v>
       </c>
       <c r="M49" s="29" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>27 (C-)</t>
+          <t>30 (C-)</t>
         </is>
       </c>
       <c r="C50" s="29" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="D50" s="29" t="n">
-        <v>-0.59</v>
+        <v>-1.8</v>
       </c>
       <c r="E50" s="29" t="n">
-        <v>1.37</v>
+        <v>2.57</v>
       </c>
       <c r="F50" s="29" t="n">
-        <v>2.27</v>
+        <v>3.22</v>
       </c>
       <c r="G50" s="29" t="n">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="H50" s="29" t="n"/>
       <c r="I50" s="29" t="n">
-        <v>-0.8</v>
+        <v>-0.48</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>-10.94</v>
+        <v>-24.31</v>
       </c>
       <c r="K50" s="29" t="n">
-        <v>7.54</v>
+        <v>7.56</v>
       </c>
       <c r="L50" s="29" t="n">
-        <v>5.41</v>
+        <v>5.56</v>
       </c>
       <c r="M50" s="29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>27 (C-)</t>
+          <t>28 (C-)</t>
         </is>
       </c>
       <c r="C51" s="29" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="D51" s="29" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="E51" s="29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F51" s="29" t="n">
-        <v>2.28</v>
-      </c>
+        <v>-0.86</v>
+      </c>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="29" t="n"/>
       <c r="G51" s="29" t="n">
-        <v>1.26</v>
+        <v>0.6</v>
       </c>
       <c r="H51" s="29" t="n"/>
-      <c r="I51" s="29" t="n"/>
+      <c r="I51" s="29" t="n">
+        <v>-2.64</v>
+      </c>
       <c r="J51" s="29" t="n">
-        <v>-12.25</v>
+        <v>18.23</v>
       </c>
       <c r="K51" s="29" t="n">
-        <v>6.6</v>
+        <v>7.59</v>
       </c>
       <c r="L51" s="29" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="M51" s="29" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -6296,7 +6284,7 @@
         </is>
       </c>
       <c r="D2" s="17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" s="18" t="inlineStr">
         <is>
@@ -6304,7 +6292,7 @@
         </is>
       </c>
       <c r="F2" s="17" t="n">
-        <v>40.4</v>
+        <v>38.5</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>5.3</v>
@@ -6313,188 +6301,190 @@
         <v>2.43</v>
       </c>
       <c r="I2" s="17" t="n">
-        <v>5.48</v>
+        <v>6.12</v>
       </c>
       <c r="J2" s="17" t="n">
-        <v>4.37</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="D3" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Chicago-Naperville-Elgin</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Dallas-Fort Worth-Arlington</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Chicago-Naperville-Elgin</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J4" s="17" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Dallas-Fort Worth-Arlington</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="G5" s="2" t="n">
+      <c r="F5" s="8" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="G5" s="8" t="n">
         <v>4.1</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="8" t="n">
         <v>0.73</v>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>1.72</v>
-      </c>
+      <c r="I5" s="8" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="D6" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="n"/>
-      <c r="I6" s="14" t="n"/>
-      <c r="J6" s="14" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>3.25</v>
+      <c r="F7" s="14" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>2.99</v>
       </c>
     </row>
     <row r="8">
@@ -6520,15 +6510,19 @@
         </is>
       </c>
       <c r="F8" s="20" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
+        <v>34.5</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>-2.79</v>
+      </c>
       <c r="I8" s="20" t="n">
-        <v>2.12</v>
+        <v>3.48</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="9">
@@ -6546,7 +6540,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -6554,7 +6548,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>60.1</v>
+        <v>62.6</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>3.6</v>
@@ -6562,42 +6556,44 @@
       <c r="H9" s="5" t="n">
         <v>1.26</v>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>1.15</v>
-      </c>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
+      <c r="D10" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="23" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n">
@@ -6614,7 +6610,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
@@ -6622,7 +6618,7 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>42.6</v>
+        <v>41</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>4.2</v>
@@ -6631,124 +6627,116 @@
         <v>-1.44</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="D12" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Riverside-San Bernardino-Ontario</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>San Francisco-Oakland-Fremont</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Riverside-San Bernardino-Ontario</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco-Oakland-Fremont</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="G14" s="5" t="n">
+      <c r="F14" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G14" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>4.26</v>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>4.04</v>
       </c>
     </row>
     <row r="15">
@@ -6766,7 +6754,7 @@
         </is>
       </c>
       <c r="D15" s="23" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
@@ -6774,7 +6762,7 @@
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>27</v>
+        <v>30.8</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>5.6</v>
@@ -6783,7 +6771,7 @@
         <v>-0.59</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>1.37</v>
+        <v>2.04</v>
       </c>
       <c r="J15" s="23" t="n">
         <v>2.27</v>
@@ -6804,7 +6792,7 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -6812,207 +6800,201 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>54</v>
+        <v>52.2</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>5.7</v>
       </c>
-      <c r="H16" s="11" t="n"/>
+      <c r="H16" s="11" t="n">
+        <v>0.84</v>
+      </c>
       <c r="I16" s="11" t="n">
-        <v>8.06</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D17" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G17" s="23" t="n">
+      <c r="D17" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G17" s="20" t="n">
         <v>4.8</v>
       </c>
-      <c r="H17" s="23" t="n">
+      <c r="H17" s="20" t="n">
         <v>-0.46</v>
       </c>
-      <c r="I17" s="23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="J17" s="23" t="n">
-        <v>2.28</v>
+      <c r="I17" s="20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="G18" s="14" t="n">
+      <c r="D18" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G18" s="17" t="n">
         <v>4.9</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="17" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="I18" s="14" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>1.2</v>
+      <c r="I18" s="17" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="D19" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Denver-Aurora-Centennial</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>4.74</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Denver-Aurora-Centennial</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G20" s="14" t="n">
+      <c r="F20" s="11" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="G20" s="11" t="n">
         <v>4.3</v>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>2.93</v>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n">
+      <c r="A21" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D21" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G21" s="20" t="n">
+      <c r="D21" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G21" s="17" t="n">
         <v>4.7</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="17" t="n">
         <v>-1.54</v>
       </c>
-      <c r="I21" s="20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J21" s="20" t="n">
-        <v>1.91</v>
+      <c r="I21" s="17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="22">
@@ -7030,7 +7012,7 @@
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -7038,7 +7020,7 @@
         </is>
       </c>
       <c r="F22" s="11" t="n">
-        <v>54.3</v>
+        <v>51.4</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>4.1</v>
@@ -7046,8 +7028,12 @@
       <c r="H22" s="11" t="n">
         <v>0.15</v>
       </c>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="11" t="n"/>
+      <c r="I22" s="11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>2.22</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n">
@@ -7064,7 +7050,7 @@
         </is>
       </c>
       <c r="D23" s="20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
@@ -7072,7 +7058,7 @@
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>34.1</v>
+        <v>35.9</v>
       </c>
       <c r="G23" s="20" t="n">
         <v>4.8</v>
@@ -7081,155 +7067,149 @@
         <v>0.85</v>
       </c>
       <c r="I23" s="20" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="J23" s="20" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>St. Louis</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>St. Louis</t>
         </is>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>San Antonio-New Braunfels</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F24" s="20" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="I24" s="20" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J24" s="20" t="n">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>San Antonio-New Braunfels</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>46</v>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H25" s="14" t="n">
+      <c r="F25" s="20" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="20" t="n">
         <v>-0.11</v>
       </c>
-      <c r="I25" s="14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <v>0.91</v>
-      </c>
+      <c r="I25" s="20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J25" s="20" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="G26" s="5" t="n">
+      <c r="D26" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
+      <c r="I26" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Portland</t>
         </is>
       </c>
-      <c r="D27" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="20" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="J27" s="20" t="n">
-        <v>1.94</v>
-      </c>
+      <c r="D27" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G27" s="23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H27" s="23" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="I27" s="23" t="n"/>
+      <c r="J27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n">
@@ -7246,7 +7226,7 @@
         </is>
       </c>
       <c r="D28" s="17" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
@@ -7254,134 +7234,128 @@
         </is>
       </c>
       <c r="F28" s="17" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="G28" s="17" t="n">
-        <v>5</v>
-      </c>
+        <v>40.4</v>
+      </c>
+      <c r="G28" s="17" t="n"/>
       <c r="H28" s="17" t="n">
         <v>1.05</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G29" s="11" t="n">
+      <c r="D29" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="G29" s="14" t="n">
         <v>4.7</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H29" s="14" t="n">
         <v>0.51</v>
       </c>
-      <c r="I29" s="11" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>1.75</v>
+      <c r="I29" s="14" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="D30" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="G31" s="5" t="n">
+      <c r="F31" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" s="2" t="n">
         <v>0.82</v>
       </c>
-      <c r="I31" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>1.75</v>
-      </c>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -7398,7 +7372,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -7406,7 +7380,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>75.2</v>
+        <v>69.2</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>4.2</v>
@@ -7415,48 +7389,48 @@
         <v>1.87</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6.36</v>
+        <v>6.99</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.29</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="G33" s="2" t="n">
+      <c r="D33" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G33" s="8" t="n">
         <v>4.1</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="8" t="n">
         <v>1.69</v>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>2.22</v>
+      <c r="I33" s="8" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>1.38</v>
       </c>
     </row>
     <row r="34">
@@ -7474,7 +7448,7 @@
         </is>
       </c>
       <c r="D34" s="17" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
@@ -7482,7 +7456,7 @@
         </is>
       </c>
       <c r="F34" s="17" t="n">
-        <v>38.7</v>
+        <v>43.2</v>
       </c>
       <c r="G34" s="17" t="n">
         <v>3.5</v>
@@ -7491,198 +7465,196 @@
         <v>-0.09</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>2.01</v>
+        <v>0.62</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>5.16</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>Cleveland</t>
         </is>
       </c>
-      <c r="D35" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="G35" s="11" t="n">
+      <c r="D35" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="G35" s="14" t="n">
         <v>3.4</v>
       </c>
-      <c r="H35" s="11" t="n">
+      <c r="H35" s="14" t="n">
         <v>1.8</v>
       </c>
-      <c r="I35" s="11" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="J35" s="11" t="n"/>
+      <c r="I35" s="14" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J35" s="14" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="G36" s="8" t="n">
+      <c r="D36" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="I36" s="8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J36" s="8" t="n">
-        <v>3.09</v>
+      <c r="I36" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>San Jose</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="G37" s="5" t="n">
+      <c r="D37" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="G37" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="2" t="n">
         <v>1.06</v>
       </c>
-      <c r="I37" s="5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>6.64</v>
-      </c>
+      <c r="I37" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="D38" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F38" s="17" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" s="17" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="I38" s="17" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="J38" s="17" t="n">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>Jacksonville</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>Jacksonville</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="G39" s="23" t="n">
+      <c r="F39" s="17" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G39" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="23" t="n">
+      <c r="H39" s="17" t="n">
         <v>-1.48</v>
       </c>
-      <c r="I39" s="23" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="J39" s="23" t="n">
-        <v>1.43</v>
+      <c r="I39" s="17" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>2.04</v>
       </c>
     </row>
     <row r="40">
@@ -7700,7 +7672,7 @@
         </is>
       </c>
       <c r="D40" s="11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
@@ -7708,7 +7680,7 @@
         </is>
       </c>
       <c r="F40" s="11" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>4.3</v>
@@ -7717,48 +7689,48 @@
         <v>1.69</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>3.42</v>
+        <v>3.77</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>7.06</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="n">
+      <c r="A41" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>Milwaukee-Waukesha</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="D41" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="G41" s="23" t="n">
+      <c r="D41" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="G41" s="20" t="n">
         <v>4.4</v>
       </c>
-      <c r="H41" s="23" t="n">
+      <c r="H41" s="20" t="n">
         <v>-1.07</v>
       </c>
-      <c r="I41" s="23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="J41" s="23" t="n">
-        <v>4.11</v>
+      <c r="I41" s="20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="J41" s="20" t="n">
+        <v>3.98</v>
       </c>
     </row>
     <row r="42">
@@ -7776,7 +7748,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -7784,7 +7756,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3.3</v>
@@ -7793,162 +7765,158 @@
         <v>1.76</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3.63</v>
+        <v>4.32</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="G43" s="11" t="n">
+      <c r="D43" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G43" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="H43" s="14" t="n">
         <v>-0.08</v>
       </c>
-      <c r="I43" s="11" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>1.06</v>
+      <c r="I43" s="14" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="n">
+      <c r="A44" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>Louisville-Jefferson County</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>Louisville</t>
         </is>
       </c>
-      <c r="D44" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="I44" s="20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="J44" s="20" t="n">
-        <v>2.84</v>
+      <c r="D44" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="23" t="n"/>
+      <c r="I44" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="23" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="n">
+      <c r="A45" s="23" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="24" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
       </c>
-      <c r="D45" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="E45" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="G45" s="20" t="n">
+      <c r="D45" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="G45" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="H45" s="20" t="n">
+      <c r="H45" s="23" t="n">
         <v>-1.8</v>
       </c>
-      <c r="I45" s="20" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="J45" s="20" t="n">
-        <v>3.41</v>
+      <c r="I45" s="23" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J45" s="23" t="n">
+        <v>3.22</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="n">
+      <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D46" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="G46" s="14" t="n">
+      <c r="D46" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="G46" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="H46" s="14" t="n">
+      <c r="H46" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="I46" s="14" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="J46" s="14" t="n">
-        <v>0.34</v>
+      <c r="I46" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="47">
@@ -7966,7 +7934,7 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
@@ -7974,7 +7942,7 @@
         </is>
       </c>
       <c r="F47" s="8" t="n">
-        <v>58.8</v>
+        <v>56.3</v>
       </c>
       <c r="G47" s="8" t="n">
         <v>4.1</v>
@@ -7983,10 +7951,10 @@
         <v>-0.73</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>4.34</v>
+        <v>4.93</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="48">
@@ -8021,84 +7989,86 @@
         <v>0.72</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-1.63</v>
+        <v>-0.91</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>4.36</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="n">
+      <c r="A49" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G49" s="11" t="n">
+      <c r="D49" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G49" s="14" t="n">
         <v>9.1</v>
       </c>
-      <c r="H49" s="11" t="n">
+      <c r="H49" s="14" t="n">
         <v>1.27</v>
       </c>
-      <c r="I49" s="11" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>3.09</v>
+      <c r="I49" s="14" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>3.39</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="n">
+      <c r="A50" s="14" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>Grand Rapids</t>
         </is>
       </c>
-      <c r="D50" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="G50" s="17" t="n"/>
-      <c r="H50" s="17" t="n">
+      <c r="D50" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" s="14" t="n">
         <v>-5.05</v>
       </c>
-      <c r="I50" s="17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J50" s="17" t="n">
-        <v>5.2</v>
+      <c r="I50" s="14" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>5.16</v>
       </c>
     </row>
     <row r="51">
@@ -8116,7 +8086,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -8124,7 +8094,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8133,9 +8103,11 @@
         <v>2.77</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J51" s="2" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8225,7 +8197,7 @@
         </is>
       </c>
       <c r="C3" s="36" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" s="36" t="inlineStr">
         <is>
@@ -8237,7 +8209,7 @@
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="G3" s="37" t="n">
@@ -8255,11 +8227,11 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C4" s="36" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" s="36" t="inlineStr">
         <is>
@@ -8271,11 +8243,11 @@
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="G4" s="37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
@@ -8289,15 +8261,15 @@
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C5" s="36" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E5" s="37" t="n">
@@ -8323,15 +8295,15 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E6" s="37" t="n">
@@ -8339,7 +8311,7 @@
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="G6" s="37" t="n">
@@ -8357,11 +8329,11 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
@@ -8373,15 +8345,15 @@
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="G7" s="37" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8391,11 +8363,11 @@
       </c>
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
@@ -8407,7 +8379,7 @@
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="G8" s="37" t="n">
@@ -8425,15 +8397,15 @@
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E9" s="37" t="n">
@@ -8441,7 +8413,7 @@
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="G9" s="37" t="n">
@@ -8459,15 +8431,15 @@
       </c>
       <c r="B10" s="36" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E10" s="37" t="n">
@@ -8475,11 +8447,11 @@
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="G10" s="37" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H10" s="37" t="inlineStr">
         <is>
@@ -8497,7 +8469,7 @@
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
@@ -8509,11 +8481,11 @@
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="G11" s="37" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H11" s="37" t="inlineStr">
         <is>
@@ -8543,11 +8515,11 @@
       </c>
       <c r="F12" s="37" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="G12" s="37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12" s="37" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>78.5</v>
+        <v>80.7</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -698,20 +698,20 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>75.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -729,20 +729,20 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -791,51 +791,51 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>67.7</v>
+        <v>66.8</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -853,16 +853,16 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -884,20 +884,20 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>65.2</v>
+        <v>63.9</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>60.7</v>
+        <v>61</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -946,20 +946,20 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>61.4</v>
+        <v>60.2</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -977,20 +977,20 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>60.6</v>
+        <v>60.3</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1007,48 +1007,48 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
+      <c r="A13" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Charlotte-Concord-Gastonia</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>56.7</v>
+        <v>58.5</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1101,82 +1101,82 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="F17" s="8" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Above Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Houston-Pasadena-The Woodlands</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>53</v>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="F18" s="11" t="n">
-        <v>52.9</v>
+        <v>54.2</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>52.8</v>
+        <v>50.7</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>51.7</v>
+        <v>50.5</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1286,83 +1286,83 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>51</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="A22" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Houston-Pasadena-The Woodlands</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Grand Rapids</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>51</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>49.7</v>
+        <v>48.4</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -1380,20 +1380,20 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
@@ -1411,20 +1411,20 @@
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>49.2</v>
+        <v>48.4</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1442,20 +1442,20 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>48.6</v>
+        <v>47.8</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1473,20 +1473,20 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>47.8</v>
+        <v>46.7</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1504,20 +1504,20 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>48.4</v>
+        <v>46</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1535,20 +1535,20 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1566,144 +1566,144 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>New York Newark-Jersey City</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Chicago-Naperville-Elgin</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>San Antonio-New Braunfels</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="D34" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="G31" s="15" t="inlineStr">
+      <c r="F34" s="14" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
         <is>
           <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>San Antonio-New Braunfels</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Phoenix-Mesa-Chandler</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>42</v>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>41.2</v>
+        <v>44</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>40.4</v>
+        <v>43.3</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
@@ -1752,20 +1752,20 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1783,16 +1783,16 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
@@ -1813,48 +1813,48 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B39" s="21" t="inlineStr">
-        <is>
-          <t>Boston-Cambridge-Newton</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="G39" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="A39" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="20" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D40" s="22" t="n">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
@@ -1876,20 +1876,20 @@
     </row>
     <row r="41">
       <c r="A41" s="20" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
@@ -1907,20 +1907,20 @@
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="D42" s="22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>34.2</v>
+        <v>35.2</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -1938,16 +1938,16 @@
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -1969,16 +1969,16 @@
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D44" s="22" t="n">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>34.1</v>
+        <v>33.6</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -2000,28 +2000,28 @@
     </row>
     <row r="45">
       <c r="A45" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="n">
-        <v>34</v>
-      </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>34.5</v>
+        <v>33.1</v>
       </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
@@ -2031,20 +2031,20 @@
     </row>
     <row r="46">
       <c r="A46" s="20" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D46" s="22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>34.2</v>
+        <v>33.1</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -2062,16 +2062,16 @@
     </row>
     <row r="47">
       <c r="A47" s="20" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B47" s="21" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
@@ -2092,48 +2092,48 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B48" s="21" t="inlineStr">
-        <is>
-          <t>Detroit-Warren-Dearborn</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="D48" s="22" t="n">
+      <c r="A48" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Portland-Vancouver-Hillsboro</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="E48" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="G48" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="23" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F49" s="23" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
@@ -2155,20 +2155,20 @@
     </row>
     <row r="50">
       <c r="A50" s="23" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="F50" s="23" t="n">
-        <v>27.2</v>
+        <v>29.8</v>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F51" s="26" t="n">
-        <v>19.2</v>
+        <v>22.6</v>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="B2" s="29" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C2" s="30" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D2" s="30" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E2" s="31" t="n">
         <v>58</v>
@@ -2346,71 +2346,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B3" s="29" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="30" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D3" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="E3" s="30" t="n">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="F3" s="30" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G3" s="30" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H3" s="32" t="n"/>
-      <c r="I3" s="31" t="n">
-        <v>62</v>
+      <c r="I3" s="30" t="n">
+        <v>78</v>
       </c>
       <c r="J3" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K3" s="30" t="n">
-        <v>86</v>
+        <v>42</v>
+      </c>
+      <c r="K3" s="31" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" s="30" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>74</v>
       </c>
-      <c r="E4" s="31" t="n">
-        <v>66</v>
+      <c r="E4" s="30" t="n">
+        <v>92</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H4" s="32" t="n"/>
-      <c r="I4" s="30" t="n">
-        <v>78</v>
+      <c r="I4" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="J4" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="K4" s="31" t="n">
-        <v>66</v>
+        <v>22</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -2420,13 +2420,13 @@
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="30" t="n">
-        <v>71</v>
-      </c>
-      <c r="D5" s="30" t="n">
-        <v>90</v>
+        <v>72</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>64</v>
       </c>
       <c r="E5" s="30" t="n">
         <v>88</v>
@@ -2451,316 +2451,316 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C6" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" s="30" t="n">
         <v>82</v>
       </c>
-      <c r="D6" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="F6" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="G6" s="30" t="n">
-        <v>90</v>
+      <c r="G6" s="31" t="n">
+        <v>60</v>
       </c>
       <c r="H6" s="32" t="n"/>
-      <c r="I6" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="J6" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="K6" s="31" t="n">
+      <c r="I6" s="31" t="n">
         <v>60</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="30" t="n">
         <v>88</v>
       </c>
-      <c r="D7" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="F7" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="G7" s="31" t="n">
+      <c r="D7" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="J7" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="31" t="n">
         <v>60</v>
-      </c>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="J7" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="K7" s="30" t="n">
-        <v>84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B8" s="29" t="n">
         <v>65</v>
       </c>
       <c r="C8" s="30" t="n">
-        <v>71</v>
-      </c>
-      <c r="D8" s="31" t="n">
-        <v>56</v>
+        <v>98</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>96</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="G8" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>39</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="30" t="n">
         <v>92</v>
       </c>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="31" t="n">
-        <v>68</v>
-      </c>
       <c r="J8" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="K8" s="30" t="n">
-        <v>74</v>
+        <v>60</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>65</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="D9" s="30" t="n">
-        <v>94</v>
+        <v>64</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>39</v>
-      </c>
-      <c r="G9" s="33" t="n">
-        <v>46</v>
+        <v>38</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>92</v>
       </c>
       <c r="H9" s="32" t="n"/>
-      <c r="I9" s="30" t="n">
-        <v>92</v>
+      <c r="I9" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="J9" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="K9" s="32" t="n">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="K9" s="30" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B10" s="29" t="n">
         <v>61</v>
       </c>
-      <c r="C10" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>61</v>
-      </c>
-      <c r="G10" s="30" t="n">
-        <v>88</v>
+      <c r="C10" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="H10" s="32" t="n"/>
       <c r="I10" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="J10" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="30" t="n">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="K10" s="33" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B11" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C11" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="D11" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="E11" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" s="32" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" s="30" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="J11" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="K11" s="33" t="n">
-        <v>48</v>
+        <v>86</v>
+      </c>
+      <c r="J11" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" s="30" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="D12" s="31" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>62</v>
+        <v>14</v>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>86</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="30" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="K12" s="33" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B13" s="29" t="n">
         <v>59</v>
       </c>
-      <c r="C13" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="D13" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" s="30" t="n">
+      <c r="C13" s="30" t="n">
         <v>76</v>
       </c>
+      <c r="D13" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>6</v>
+      </c>
       <c r="F13" s="33" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H13" s="32" t="n"/>
       <c r="I13" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="J13" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="K13" s="30" t="n">
         <v>76</v>
-      </c>
-      <c r="J13" s="31" t="n">
-        <v>66</v>
-      </c>
-      <c r="K13" s="31" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B14" s="29" t="n">
         <v>58</v>
       </c>
-      <c r="C14" s="30" t="n">
-        <v>90</v>
+      <c r="C14" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="E14" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="F14" s="30" t="n">
-        <v>73</v>
+        <v>82</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>57</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H14" s="32" t="n"/>
-      <c r="I14" s="31" t="n">
-        <v>50</v>
+      <c r="I14" s="33" t="n">
+        <v>34</v>
       </c>
       <c r="J14" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>96</v>
+        <v>48</v>
+      </c>
+      <c r="K14" s="31" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>57</v>
-      </c>
-      <c r="C15" s="33" t="n">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>54</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E15" s="31" t="n">
         <v>62</v>
@@ -2801,141 +2801,141 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B16" s="29" t="n">
-        <v>55</v>
-      </c>
-      <c r="C16" s="33" t="n">
-        <v>39</v>
+        <v>57</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="D16" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>68</v>
+        <v>28</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>76</v>
       </c>
       <c r="F16" s="33" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="J16" s="30" t="n">
-        <v>96</v>
+        <v>76</v>
+      </c>
+      <c r="J16" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="K16" s="31" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>53</v>
-      </c>
-      <c r="C17" s="33" t="n">
-        <v>43</v>
-      </c>
-      <c r="D17" s="31" t="n">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>42</v>
       </c>
       <c r="E17" s="33" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>71</v>
-      </c>
-      <c r="G17" s="30" t="n">
-        <v>84</v>
+        <v>73</v>
+      </c>
+      <c r="G17" s="33" t="n">
+        <v>38</v>
       </c>
       <c r="H17" s="32" t="n"/>
       <c r="I17" s="31" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J17" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="K17" s="30" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E18" s="30" t="n">
-        <v>98</v>
+        <v>36</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H18" s="32" t="n"/>
-      <c r="I18" s="33" t="n">
-        <v>46</v>
+      <c r="I18" s="30" t="n">
+        <v>74</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="K18" s="30" t="n">
-        <v>92</v>
+        <v>96</v>
+      </c>
+      <c r="K18" s="31" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B19" s="29" t="n">
-        <v>53</v>
-      </c>
-      <c r="C19" s="31" t="n">
-        <v>61</v>
+        <v>51</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="D19" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="F19" s="33" t="n">
+        <v>37</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="E19" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="G19" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="H19" s="32" t="n"/>
-      <c r="I19" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="J19" s="33" t="n">
-        <v>30</v>
+      <c r="J19" s="30" t="n">
+        <v>90</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="B20" s="29" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="31" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D20" s="33" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>82</v>
@@ -2976,421 +2976,421 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>51</v>
-      </c>
-      <c r="C21" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="D21" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="E21" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="F21" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="31" t="n">
+      <c r="C21" s="31" t="n">
         <v>64</v>
       </c>
+      <c r="D21" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="G21" s="33" t="n">
+        <v>6</v>
+      </c>
       <c r="H21" s="32" t="n"/>
-      <c r="I21" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="J21" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="K21" s="33" t="n">
-        <v>2</v>
+      <c r="I21" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="J21" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="K21" s="30" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B22" s="29" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="31" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D22" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="E22" s="30" t="n">
-        <v>86</v>
+        <v>24</v>
+      </c>
+      <c r="E22" s="31" t="n">
+        <v>64</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G22" s="33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="J22" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="K22" s="30" t="n">
-        <v>90</v>
+        <v>18</v>
+      </c>
+      <c r="J22" s="30" t="n">
+        <v>88</v>
+      </c>
+      <c r="K22" s="33" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B23" s="29" t="n">
-        <v>51</v>
-      </c>
-      <c r="C23" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="D23" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="F23" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="G23" s="33" t="n">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>71</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <v>84</v>
       </c>
       <c r="H23" s="32" t="n"/>
       <c r="I23" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="J23" s="31" t="n">
-        <v>56</v>
+        <v>66</v>
+      </c>
+      <c r="J23" s="33" t="n">
+        <v>24</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B24" s="29" t="n">
-        <v>50</v>
-      </c>
-      <c r="C24" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="D24" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="E24" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="G24" s="30" t="n">
-        <v>70</v>
+        <v>48</v>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="F24" s="33" t="n">
+        <v>33</v>
+      </c>
+      <c r="G24" s="31" t="n">
+        <v>58</v>
       </c>
       <c r="H24" s="32" t="n"/>
       <c r="I24" s="33" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J24" s="33" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="K24" s="33" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="C25" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="D25" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="E25" s="31" t="n">
-        <v>56</v>
+      <c r="C25" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="F25" s="31" t="n">
-        <v>63</v>
-      </c>
-      <c r="G25" s="33" t="n">
-        <v>36</v>
+        <v>50</v>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="H25" s="32" t="n"/>
-      <c r="I25" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="J25" s="30" t="n">
-        <v>78</v>
+      <c r="I25" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="J25" s="33" t="n">
+        <v>26</v>
       </c>
       <c r="K25" s="33" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B26" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="C26" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="D26" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="E26" s="30" t="n">
-        <v>96</v>
+        <v>48</v>
+      </c>
+      <c r="C26" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="30" t="n">
+        <v>88</v>
+      </c>
+      <c r="E26" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="F26" s="33" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G26" s="31" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H26" s="32" t="n"/>
-      <c r="I26" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="J26" s="33" t="n">
-        <v>46</v>
+      <c r="I26" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="J26" s="30" t="n">
+        <v>98</v>
       </c>
       <c r="K26" s="33" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="C27" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="D27" s="31" t="n">
-        <v>66</v>
+        <v>48</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="D27" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="F27" s="30" t="n">
-        <v>98</v>
+        <v>52</v>
+      </c>
+      <c r="F27" s="33" t="n">
+        <v>6</v>
       </c>
       <c r="G27" s="33" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H27" s="32" t="n"/>
-      <c r="I27" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="J27" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="K27" s="33" t="n">
-        <v>24</v>
+      <c r="I27" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="J27" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="K27" s="30" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B28" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="C28" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="D28" s="33" t="n">
-        <v>4</v>
+        <v>47</v>
+      </c>
+      <c r="C28" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>80</v>
       </c>
       <c r="E28" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F28" s="31" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G28" s="31" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="H28" s="32" t="n"/>
-      <c r="I28" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="K28" s="30" t="n">
-        <v>82</v>
+      <c r="I28" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="J28" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="33" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C29" s="33" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D29" s="31" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E29" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="F29" s="30" t="n">
         <v>84</v>
       </c>
-      <c r="F29" s="31" t="n">
-        <v>57</v>
-      </c>
       <c r="G29" s="33" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="33" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J29" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="K29" s="31" t="n">
-        <v>60</v>
+        <v>32</v>
+      </c>
+      <c r="K29" s="33" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B30" s="29" t="n">
-        <v>47</v>
-      </c>
-      <c r="C30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="E30" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="F30" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="G30" s="33" t="n">
-        <v>34</v>
+        <v>46</v>
+      </c>
+      <c r="C30" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="F30" s="31" t="n">
+        <v>53</v>
+      </c>
+      <c r="G30" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="H30" s="32" t="n"/>
-      <c r="I30" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="J30" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="K30" s="31" t="n">
-        <v>52</v>
+      <c r="I30" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="K30" s="30" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B31" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="C31" s="31" t="n">
-        <v>59</v>
-      </c>
-      <c r="D31" s="33" t="n">
-        <v>16</v>
+        <v>45</v>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="F31" s="31" t="n">
-        <v>59</v>
+        <v>78</v>
+      </c>
+      <c r="F31" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="G31" s="33" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="33" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J31" s="30" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K31" s="33" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B32" s="29" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" s="33" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D32" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="E32" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="F32" s="30" t="n">
-        <v>84</v>
+        <v>20</v>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="F32" s="31" t="n">
+        <v>63</v>
       </c>
       <c r="G32" s="33" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H32" s="32" t="n"/>
-      <c r="I32" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="J32" s="33" t="n">
-        <v>32</v>
+      <c r="I32" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="J32" s="30" t="n">
+        <v>78</v>
       </c>
       <c r="K32" s="33" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -3400,13 +3400,13 @@
         </is>
       </c>
       <c r="B33" s="29" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C33" s="31" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D33" s="33" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E33" s="33" t="n">
         <v>36</v>
@@ -3431,596 +3431,596 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B34" s="29" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C34" s="33" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D34" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="E34" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="F34" s="33" t="n">
-        <v>47</v>
-      </c>
-      <c r="G34" s="31" t="n">
-        <v>56</v>
+        <v>36</v>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>59</v>
+      </c>
+      <c r="G34" s="33" t="n">
+        <v>22</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="J34" s="33" t="n">
-        <v>38</v>
+        <v>4</v>
+      </c>
+      <c r="J34" s="30" t="n">
+        <v>86</v>
       </c>
       <c r="K34" s="33" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B35" s="29" t="n">
-        <v>41</v>
-      </c>
-      <c r="C35" s="33" t="n">
-        <v>18</v>
+        <v>44</v>
+      </c>
+      <c r="C35" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="D35" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="E35" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="F35" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="E35" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="G35" s="33" t="n">
+        <v>34</v>
       </c>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="J35" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="33" t="n">
-        <v>16</v>
+        <v>88</v>
+      </c>
+      <c r="J35" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="K35" s="31" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B36" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="C36" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="E36" s="30" t="n">
-        <v>78</v>
+        <v>43</v>
+      </c>
+      <c r="C36" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="D36" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="E36" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="F36" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="33" t="n">
         <v>18</v>
-      </c>
-      <c r="G36" s="33" t="n">
-        <v>42</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="33" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J36" s="30" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K36" s="33" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B37" s="29" t="n">
-        <v>39</v>
-      </c>
-      <c r="C37" s="31" t="n">
-        <v>51</v>
+        <v>40</v>
+      </c>
+      <c r="C37" s="33" t="n">
+        <v>36</v>
       </c>
       <c r="D37" s="33" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E37" s="33" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F37" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="G37" s="33" t="n">
-        <v>16</v>
+        <v>47</v>
+      </c>
+      <c r="G37" s="31" t="n">
+        <v>56</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="J37" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="K37" s="30" t="n">
-        <v>80</v>
+        <v>44</v>
+      </c>
+      <c r="J37" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="K37" s="33" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B38" s="29" t="n">
         <v>39</v>
       </c>
       <c r="C38" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="D38" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="E38" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="F38" s="33" t="n">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D38" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="E38" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="F38" s="30" t="n">
+        <v>80</v>
       </c>
       <c r="G38" s="33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H38" s="32" t="n"/>
-      <c r="I38" s="30" t="n">
-        <v>70</v>
+      <c r="I38" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="J38" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K38" s="33" t="n">
-        <v>26</v>
+        <v>4</v>
+      </c>
+      <c r="K38" s="31" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C39" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="D39" s="30" t="n">
-        <v>96</v>
+        <v>36</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="E39" s="33" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="F39" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" s="30" t="n">
-        <v>74</v>
+        <v>31</v>
+      </c>
+      <c r="G39" s="33" t="n">
+        <v>16</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="J39" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="K39" s="33" t="n">
-        <v>4</v>
+        <v>36</v>
+      </c>
+      <c r="J39" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="K39" s="30" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B40" s="29" t="n">
         <v>36</v>
       </c>
       <c r="C40" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="D40" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="E40" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="F40" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="G40" s="33" t="n">
-        <v>20</v>
+        <v>4</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="E40" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" s="33" t="n">
+        <v>43</v>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="33" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J40" s="33" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="K40" s="31" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B41" s="29" t="n">
-        <v>35</v>
-      </c>
-      <c r="C41" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="D41" s="33" t="n">
-        <v>14</v>
+        <v>36</v>
+      </c>
+      <c r="C41" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>54</v>
       </c>
       <c r="E41" s="33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F41" s="33" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="G41" s="33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="K41" s="33" t="n">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="K41" s="30" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B42" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="C42" s="33" t="n">
         <v>34</v>
       </c>
-      <c r="C42" s="33" t="n">
-        <v>22</v>
-      </c>
       <c r="D42" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="E42" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E42" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="G42" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="H42" s="32" t="n"/>
+      <c r="I42" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="F42" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="G42" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="32" t="n"/>
-      <c r="I42" s="33" t="n">
-        <v>24</v>
-      </c>
       <c r="J42" s="33" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K42" s="33" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B43" s="29" t="n">
         <v>34</v>
       </c>
       <c r="C43" s="33" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D43" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="G43" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="F43" s="33" t="n">
-        <v>41</v>
-      </c>
-      <c r="G43" s="33" t="n">
-        <v>14</v>
-      </c>
       <c r="H43" s="32" t="n"/>
-      <c r="I43" s="31" t="n">
+      <c r="I43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="K43" s="31" t="n">
         <v>56</v>
-      </c>
-      <c r="J43" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="K43" s="33" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B44" s="29" t="n">
         <v>34</v>
       </c>
       <c r="C44" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="E44" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="F44" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="D44" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="E44" s="30" t="n">
+      <c r="G44" s="30" t="n">
         <v>74</v>
       </c>
-      <c r="F44" s="31" t="n">
-        <v>67</v>
-      </c>
-      <c r="G44" s="33" t="n">
+      <c r="H44" s="32" t="n"/>
+      <c r="I44" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="J44" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="K44" s="33" t="n">
         <v>4</v>
-      </c>
-      <c r="H44" s="32" t="n"/>
-      <c r="I44" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="K44" s="30" t="n">
-        <v>72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B45" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="C45" s="33" t="n">
-        <v>39</v>
-      </c>
-      <c r="D45" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="E45" s="33" t="n">
-        <v>10</v>
+        <v>33</v>
+      </c>
+      <c r="C45" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D45" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="E45" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="33" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G45" s="33" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="J45" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="K45" s="33" t="n">
-        <v>44</v>
+        <v>12</v>
+      </c>
+      <c r="J45" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="K45" s="31" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B46" s="29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C46" s="33" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D46" s="33" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E46" s="33" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F46" s="33" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G46" s="33" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H46" s="32" t="n"/>
-      <c r="I46" s="33" t="n">
+      <c r="I46" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="J46" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="K46" s="33" t="n">
         <v>20</v>
-      </c>
-      <c r="J46" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="K46" s="30" t="n">
-        <v>98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
         <v>33</v>
       </c>
-      <c r="C47" s="33" t="n">
+      <c r="C47" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="D47" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="E47" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="F47" s="33" t="n">
         <v>27</v>
-      </c>
-      <c r="D47" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="F47" s="30" t="n">
-        <v>76</v>
       </c>
       <c r="G47" s="33" t="n">
         <v>30</v>
       </c>
       <c r="H47" s="32" t="n"/>
-      <c r="I47" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="K47" s="31" t="n">
-        <v>56</v>
+      <c r="I47" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="J47" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="K47" s="30" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B48" s="29" t="n">
         <v>32</v>
       </c>
       <c r="C48" s="33" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="E48" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="F48" s="33" t="n">
-        <v>43</v>
-      </c>
-      <c r="G48" s="31" t="n">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="E48" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="F48" s="31" t="n">
+        <v>67</v>
+      </c>
+      <c r="G48" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="H48" s="32" t="n"/>
-      <c r="I48" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="J48" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="K48" s="31" t="n">
-        <v>68</v>
+      <c r="I48" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="K48" s="30" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B49" s="29" t="n">
         <v>31</v>
       </c>
-      <c r="C49" s="31" t="n">
-        <v>67</v>
+      <c r="C49" s="33" t="n">
+        <v>22</v>
       </c>
       <c r="D49" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="E49" s="33" t="n">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="E49" s="30" t="n">
+        <v>70</v>
       </c>
       <c r="F49" s="33" t="n">
-        <v>27</v>
-      </c>
-      <c r="G49" s="33" t="n">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="G49" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="33" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J49" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="K49" s="30" t="n">
-        <v>70</v>
+        <v>28</v>
+      </c>
+      <c r="K49" s="33" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B50" s="29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C50" s="33" t="n">
-        <v>27</v>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="E50" s="32" t="n">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="D50" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E50" s="33" t="n">
+        <v>34</v>
       </c>
       <c r="F50" s="33" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="G50" s="33" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="J50" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="K50" s="31" t="n">
-        <v>54</v>
+        <v>8</v>
+      </c>
+      <c r="J50" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="K50" s="33" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -4030,13 +4030,13 @@
         </is>
       </c>
       <c r="B51" s="29" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C51" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="D51" s="33" t="n">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="D51" s="31" t="n">
+        <v>52</v>
       </c>
       <c r="E51" s="33" t="n">
         <v>42</v>
@@ -4162,14 +4162,14 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>78 (A+)</t>
+          <t>81 (A+)</t>
         </is>
       </c>
       <c r="C2" s="32" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="D2" s="32" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="E2" s="32" t="n">
         <v>4.32</v>
@@ -4200,87 +4200,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>76 (A+)</t>
+          <t>75 (A+)</t>
         </is>
       </c>
       <c r="C3" s="32" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="D3" s="32" t="n">
-        <v>3</v>
+        <v>1.37</v>
       </c>
       <c r="E3" s="32" t="n">
-        <v>7.75</v>
+        <v>5.18</v>
       </c>
       <c r="F3" s="32" t="n">
-        <v>0.75</v>
+        <v>1.34</v>
       </c>
       <c r="G3" s="32" t="n">
-        <v>4.34</v>
+        <v>3.42</v>
       </c>
       <c r="H3" s="32" t="n"/>
       <c r="I3" s="32" t="n">
-        <v>1.13</v>
+        <v>0.36</v>
       </c>
       <c r="J3" s="32" t="n">
-        <v>-19.65</v>
+        <v>-7.48</v>
       </c>
       <c r="K3" s="32" t="n">
-        <v>7.95</v>
+        <v>7.48</v>
       </c>
       <c r="L3" s="32" t="n">
-        <v>15.91</v>
+        <v>6.52</v>
       </c>
       <c r="M3" s="32" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>74 (A+)</t>
+          <t>73 (A+)</t>
         </is>
       </c>
       <c r="C4" s="32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D4" s="32" t="n">
-        <v>1.26</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E4" s="32" t="n">
-        <v>5.18</v>
+        <v>7.75</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>1.34</v>
+        <v>0.75</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>3.42</v>
+        <v>4.34</v>
       </c>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="32" t="n">
-        <v>0.36</v>
+        <v>1.13</v>
       </c>
       <c r="J4" s="32" t="n">
-        <v>-7.48</v>
+        <v>-19.65</v>
       </c>
       <c r="K4" s="32" t="n">
-        <v>7.48</v>
+        <v>7.95</v>
       </c>
       <c r="L4" s="32" t="n">
-        <v>6.52</v>
+        <v>15.91</v>
       </c>
       <c r="M4" s="32" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>71 (A+)</t>
+          <t>69 (A+)</t>
         </is>
       </c>
       <c r="C5" s="32" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>1.87</v>
+        <v>0.37</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>6.99</v>
@@ -4329,93 +4329,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>71 (A+)</t>
+          <t>67 (A)</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>1.86</v>
+        <v>-0.39</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3.94</v>
+        <v>3.26</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>3.68</v>
+        <v>2.96</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="32" t="n">
-        <v>0.84</v>
+        <v>0.06</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>-31.3</v>
+        <v>19.15</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>7.43</v>
+        <v>7.88</v>
       </c>
       <c r="L6" s="32" t="n">
-        <v>6.38</v>
+        <v>8.82</v>
       </c>
       <c r="M6" s="32" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>68 (A)</t>
+          <t>67 (A)</t>
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>0.82</v>
+        <v>-0.4</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>1.41</v>
+        <v>1.81</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>2.96</v>
+        <v>3.68</v>
       </c>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="32" t="n">
-        <v>0.06</v>
+        <v>0.84</v>
       </c>
       <c r="J7" s="32" t="n">
-        <v>19.15</v>
+        <v>-31.3</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>7.88</v>
+        <v>7.43</v>
       </c>
       <c r="L7" s="32" t="n">
-        <v>8.82</v>
+        <v>6.38</v>
       </c>
       <c r="M7" s="32" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
@@ -4424,84 +4424,84 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>0.73</v>
+        <v>2.77</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>3.13</v>
+        <v>0.6</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>1.5</v>
+        <v>2.59</v>
       </c>
       <c r="G8" s="32" t="n">
-        <v>4.34</v>
+        <v>2.44</v>
       </c>
       <c r="H8" s="32" t="n"/>
       <c r="I8" s="32" t="n">
-        <v>0.92</v>
+        <v>1.88</v>
       </c>
       <c r="J8" s="32" t="n">
-        <v>7.46</v>
+        <v>6.72</v>
       </c>
       <c r="K8" s="32" t="n">
-        <v>7.65</v>
+        <v>3.33</v>
       </c>
       <c r="L8" s="32" t="n">
-        <v>6.98</v>
+        <v>-16.67</v>
       </c>
       <c r="M8" s="32" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>65 (A)</t>
+          <t>64 (A)</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="D9" s="32" t="n">
-        <v>2.77</v>
+        <v>0.52</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>0.6</v>
+        <v>3.13</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>2.59</v>
+        <v>1.5</v>
       </c>
       <c r="G9" s="32" t="n">
-        <v>2.44</v>
+        <v>4.34</v>
       </c>
       <c r="H9" s="32" t="n"/>
       <c r="I9" s="32" t="n">
-        <v>1.88</v>
+        <v>0.92</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>6.72</v>
+        <v>7.46</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>3.33</v>
+        <v>7.65</v>
       </c>
       <c r="L9" s="32" t="n">
-        <v>-16.67</v>
+        <v>6.98</v>
       </c>
       <c r="M9" s="32" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
@@ -4510,170 +4510,170 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>1.52</v>
+        <v>0.35</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>6.16</v>
+        <v>-0.91</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>2.13</v>
+        <v>3.4</v>
       </c>
       <c r="G10" s="32" t="n">
-        <v>3.66</v>
+        <v>3.04</v>
       </c>
       <c r="H10" s="32" t="n"/>
       <c r="I10" s="32" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="J10" s="32" t="n">
-        <v>-25.89</v>
+        <v>18.48</v>
       </c>
       <c r="K10" s="32" t="n">
-        <v>7.95</v>
+        <v>7.21</v>
       </c>
       <c r="L10" s="32" t="n">
-        <v>15.91</v>
+        <v>4</v>
       </c>
       <c r="M10" s="32" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>61 (A-)</t>
+          <t>60 (A-)</t>
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="D11" s="32" t="n">
-        <v>1.06</v>
+        <v>2.43</v>
       </c>
       <c r="E11" s="32" t="n">
-        <v>0.76</v>
+        <v>6.16</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>6.66</v>
+        <v>2.13</v>
       </c>
       <c r="G11" s="32" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="32" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="J11" s="32" t="n">
-        <v>104.08</v>
+        <v>-25.89</v>
       </c>
       <c r="K11" s="32" t="n">
-        <v>7.27</v>
+        <v>7.95</v>
       </c>
       <c r="L11" s="32" t="n">
-        <v>16.67</v>
+        <v>15.91</v>
       </c>
       <c r="M11" s="32" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>61 (A-)</t>
+          <t>60 (A-)</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="D12" s="32" t="n">
-        <v>0.72</v>
+        <v>-0.11</v>
       </c>
       <c r="E12" s="32" t="n">
-        <v>-0.91</v>
+        <v>0.76</v>
       </c>
       <c r="F12" s="32" t="n">
-        <v>3.4</v>
+        <v>6.66</v>
       </c>
       <c r="G12" s="32" t="n">
-        <v>3.04</v>
+        <v>3.64</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="32" t="n">
-        <v>0.67</v>
+        <v>1.56</v>
       </c>
       <c r="J12" s="32" t="n">
-        <v>18.48</v>
+        <v>104.08</v>
       </c>
       <c r="K12" s="32" t="n">
-        <v>7.21</v>
+        <v>7.27</v>
       </c>
       <c r="L12" s="32" t="n">
-        <v>4</v>
+        <v>16.67</v>
       </c>
       <c r="M12" s="32" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>59 (A-)</t>
+          <t>59 (B+)</t>
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D13" s="32" t="n">
-        <v>0.35</v>
+        <v>1.13</v>
       </c>
       <c r="E13" s="32" t="n">
-        <v>5.93</v>
+        <v>-0.04</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>4.49</v>
+        <v>2.48</v>
       </c>
       <c r="G13" s="32" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="H13" s="32" t="n"/>
       <c r="I13" s="32" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="J13" s="32" t="n">
-        <v>12.45</v>
+        <v>-14.84</v>
       </c>
       <c r="K13" s="32" t="n">
-        <v>7.27</v>
+        <v>7.71</v>
       </c>
       <c r="L13" s="32" t="n">
-        <v>2.7</v>
+        <v>7.14</v>
       </c>
       <c r="M13" s="32" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
@@ -4682,35 +4682,35 @@
         </is>
       </c>
       <c r="C14" s="32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D14" s="32" t="n">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="E14" s="32" t="n">
-        <v>2.79</v>
+        <v>6.43</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="G14" s="32" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="H14" s="32" t="n"/>
       <c r="I14" s="32" t="n">
-        <v>0.49</v>
+        <v>-0.61</v>
       </c>
       <c r="J14" s="32" t="n">
-        <v>-41.29</v>
+        <v>-4.03</v>
       </c>
       <c r="K14" s="32" t="n">
-        <v>8.609999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="L14" s="32" t="n">
-        <v>16.13</v>
+        <v>6.38</v>
       </c>
       <c r="M14" s="32" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -4721,14 +4721,14 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>57 (B+)</t>
+          <t>58 (B+)</t>
         </is>
       </c>
       <c r="C15" s="32" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="D15" s="32" t="n">
-        <v>-0.73</v>
+        <v>-0.68</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>4.93</v>
@@ -4759,173 +4759,173 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>55 (B+)</t>
+          <t>57 (B+)</t>
         </is>
       </c>
       <c r="C16" s="32" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="D16" s="32" t="n">
-        <v>-0.12</v>
+        <v>-0.65</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>5.19</v>
+        <v>5.93</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>5.67</v>
+        <v>4.49</v>
       </c>
       <c r="G16" s="32" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="32" t="n">
-        <v>1.83</v>
+        <v>0.98</v>
       </c>
       <c r="J16" s="32" t="n">
-        <v>112.64</v>
+        <v>12.45</v>
       </c>
       <c r="K16" s="32" t="n">
-        <v>7.42</v>
+        <v>7.27</v>
       </c>
       <c r="L16" s="32" t="n">
-        <v>4.55</v>
+        <v>2.7</v>
       </c>
       <c r="M16" s="32" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>55 (B+)</t>
         </is>
       </c>
       <c r="C17" s="32" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="D17" s="32" t="n">
-        <v>0.87</v>
+        <v>-0.33</v>
       </c>
       <c r="E17" s="32" t="n">
-        <v>2.05</v>
+        <v>2.79</v>
       </c>
       <c r="F17" s="32" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G17" s="32" t="n">
-        <v>3.46</v>
+        <v>2.18</v>
       </c>
       <c r="H17" s="32" t="n"/>
       <c r="I17" s="32" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="J17" s="32" t="n">
-        <v>-18.37</v>
+        <v>-41.29</v>
       </c>
       <c r="K17" s="32" t="n">
-        <v>7.73</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L17" s="32" t="n">
-        <v>9.09</v>
+        <v>16.13</v>
       </c>
       <c r="M17" s="32" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C18" s="32" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="D18" s="32" t="n">
-        <v>0.84</v>
+        <v>-0.54</v>
       </c>
       <c r="E18" s="32" t="n">
-        <v>8.130000000000001</v>
+        <v>5.19</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>2.62</v>
+        <v>5.67</v>
       </c>
       <c r="G18" s="32" t="n">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="H18" s="32" t="n"/>
       <c r="I18" s="32" t="n">
-        <v>-0.09</v>
+        <v>1.83</v>
       </c>
       <c r="J18" s="32" t="n">
-        <v>42.78</v>
+        <v>112.64</v>
       </c>
       <c r="K18" s="32" t="n">
-        <v>8.130000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="L18" s="32" t="n">
-        <v>13.33</v>
+        <v>4.55</v>
       </c>
       <c r="M18" s="32" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>53 (B)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C19" s="32" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="D19" s="32" t="n">
-        <v>0.15</v>
+        <v>-0.8</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>-0.04</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="G19" s="32" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="H19" s="32" t="n"/>
       <c r="I19" s="32" t="n">
-        <v>0.88</v>
+        <v>-0.09</v>
       </c>
       <c r="J19" s="32" t="n">
-        <v>-14.84</v>
+        <v>42.78</v>
       </c>
       <c r="K19" s="32" t="n">
-        <v>7.71</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L19" s="32" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="M19" s="32" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -4936,14 +4936,14 @@
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>52 (B)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>-0.36</v>
+        <v>-1.4</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>6.2</v>
@@ -4974,515 +4974,515 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>50 (B)</t>
         </is>
       </c>
       <c r="C21" s="32" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>1.69</v>
+        <v>-1.21</v>
       </c>
       <c r="E21" s="32" t="n">
-        <v>3.77</v>
+        <v>6.84</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>6.57</v>
+        <v>0.9</v>
       </c>
       <c r="G21" s="32" t="n">
-        <v>3.06</v>
+        <v>0.7</v>
       </c>
       <c r="H21" s="32" t="n"/>
       <c r="I21" s="32" t="n">
-        <v>0.6</v>
+        <v>-0.87</v>
       </c>
       <c r="J21" s="32" t="n">
-        <v>132.32</v>
+        <v>-9.74</v>
       </c>
       <c r="K21" s="32" t="n">
-        <v>4.71</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L21" s="32" t="n">
-        <v>-6.9</v>
+        <v>18.6</v>
       </c>
       <c r="M21" s="32" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>-0.08</v>
+        <v>-0.76</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>6.84</v>
+        <v>4.99</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="32" t="n">
-        <v>-0.87</v>
+        <v>-0.03</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>-9.74</v>
+        <v>39.08</v>
       </c>
       <c r="K22" s="32" t="n">
-        <v>8.119999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="L22" s="32" t="n">
-        <v>18.6</v>
+        <v>-3.57</v>
       </c>
       <c r="M22" s="32" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C23" s="32" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="D23" s="32" t="n">
-        <v>-5.05</v>
+        <v>0.29</v>
       </c>
       <c r="E23" s="32" t="n">
-        <v>3.79</v>
+        <v>2.05</v>
       </c>
       <c r="F23" s="32" t="n">
-        <v>5.4</v>
+        <v>1.64</v>
       </c>
       <c r="G23" s="32" t="n">
-        <v>0.86</v>
+        <v>3.46</v>
       </c>
       <c r="H23" s="32" t="n"/>
       <c r="I23" s="32" t="n">
-        <v>-0.13</v>
+        <v>0.54</v>
       </c>
       <c r="J23" s="32" t="n">
-        <v>-0.59</v>
+        <v>-18.37</v>
       </c>
       <c r="K23" s="32" t="n">
-        <v>8.210000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="L23" s="32" t="n">
-        <v>12.12</v>
+        <v>9.09</v>
       </c>
       <c r="M23" s="32" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>50 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D24" s="32" t="n">
-        <v>1.8</v>
+        <v>0.15</v>
       </c>
       <c r="E24" s="32" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="F24" s="32" t="n"/>
+        <v>8.02</v>
+      </c>
+      <c r="F24" s="32" t="n">
+        <v>3.2</v>
+      </c>
       <c r="G24" s="32" t="n">
-        <v>3.24</v>
+        <v>2.84</v>
       </c>
       <c r="H24" s="32" t="n"/>
       <c r="I24" s="32" t="n">
-        <v>0.57</v>
+        <v>-0.63</v>
       </c>
       <c r="J24" s="32" t="n">
-        <v>-18.19</v>
+        <v>-5.72</v>
       </c>
       <c r="K24" s="32" t="n">
-        <v>7.26</v>
+        <v>6.31</v>
       </c>
       <c r="L24" s="32" t="n">
-        <v>7.84</v>
+        <v>6.94</v>
       </c>
       <c r="M24" s="32" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C25" s="32" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="D25" s="32" t="n">
-        <v>0.16</v>
+        <v>1.8</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="F25" s="32" t="n">
-        <v>2.03</v>
-      </c>
+        <v>-0.25</v>
+      </c>
+      <c r="F25" s="32" t="n"/>
       <c r="G25" s="32" t="n">
-        <v>2.14</v>
+        <v>3.24</v>
       </c>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="32" t="n">
-        <v>-0.13</v>
+        <v>0.57</v>
       </c>
       <c r="J25" s="32" t="n">
-        <v>29.19</v>
+        <v>-18.19</v>
       </c>
       <c r="K25" s="32" t="n">
-        <v>7.1</v>
+        <v>7.26</v>
       </c>
       <c r="L25" s="32" t="n">
-        <v>3.03</v>
+        <v>7.84</v>
       </c>
       <c r="M25" s="32" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C26" s="32" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="D26" s="32" t="n">
-        <v>-0.5</v>
+        <v>1.69</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>8.02</v>
+        <v>3.77</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>3.2</v>
+        <v>6.57</v>
       </c>
       <c r="G26" s="32" t="n">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="32" t="n">
-        <v>-0.63</v>
+        <v>0.6</v>
       </c>
       <c r="J26" s="32" t="n">
-        <v>-5.72</v>
+        <v>132.32</v>
       </c>
       <c r="K26" s="32" t="n">
-        <v>6.31</v>
+        <v>4.71</v>
       </c>
       <c r="L26" s="32" t="n">
-        <v>6.94</v>
+        <v>-6.9</v>
       </c>
       <c r="M26" s="32" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>48 (B-)</t>
         </is>
       </c>
       <c r="C27" s="32" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="D27" s="32" t="n">
-        <v>0.98</v>
+        <v>-4.53</v>
       </c>
       <c r="E27" s="32" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>0.59</v>
+        <v>5.4</v>
       </c>
       <c r="G27" s="32" t="n">
-        <v>0.44</v>
+        <v>0.86</v>
       </c>
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="32" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="J27" s="32" t="n">
-        <v>39.08</v>
+        <v>-0.59</v>
       </c>
       <c r="K27" s="32" t="n">
-        <v>6.86</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L27" s="32" t="n">
-        <v>-3.57</v>
+        <v>12.12</v>
       </c>
       <c r="M27" s="32" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="D28" s="32" t="n">
-        <v>-2.12</v>
+        <v>1.14</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="G28" s="32" t="n">
-        <v>3.08</v>
+        <v>2.54</v>
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="32" t="n">
-        <v>-0.44</v>
+        <v>0.83</v>
       </c>
       <c r="J28" s="32" t="n">
-        <v>12.87</v>
+        <v>-54.27</v>
       </c>
       <c r="K28" s="32" t="n">
-        <v>7.83</v>
+        <v>6.48</v>
       </c>
       <c r="L28" s="32" t="n">
-        <v>8.33</v>
+        <v>9.68</v>
       </c>
       <c r="M28" s="32" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C29" s="32" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="D29" s="32" t="n">
-        <v>0.51</v>
+        <v>0.14</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>6.43</v>
+        <v>7.84</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="G29" s="32" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="32" t="n">
-        <v>-0.61</v>
+        <v>-0.33</v>
       </c>
       <c r="J29" s="32" t="n">
-        <v>-4.03</v>
+        <v>-12.9</v>
       </c>
       <c r="K29" s="32" t="n">
-        <v>7.43</v>
+        <v>6.28</v>
       </c>
       <c r="L29" s="32" t="n">
-        <v>6.38</v>
+        <v>15.52</v>
       </c>
       <c r="M29" s="32" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>46 (B-)</t>
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>9.1</v>
+        <v>3.7</v>
       </c>
       <c r="D30" s="32" t="n">
-        <v>1.27</v>
+        <v>-2.34</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>4.39</v>
+        <v>1.57</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>3.62</v>
+        <v>2.26</v>
       </c>
       <c r="G30" s="32" t="n">
-        <v>2.1</v>
+        <v>3.08</v>
       </c>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="32" t="n">
-        <v>2.12</v>
+        <v>-0.44</v>
       </c>
       <c r="J30" s="32" t="n">
-        <v>-22.67</v>
+        <v>12.87</v>
       </c>
       <c r="K30" s="32" t="n">
-        <v>7.28</v>
+        <v>7.83</v>
       </c>
       <c r="L30" s="32" t="n">
-        <v>4.17</v>
+        <v>8.33</v>
       </c>
       <c r="M30" s="32" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D31" s="32" t="n">
-        <v>-1.18</v>
+        <v>0.73</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>7.51</v>
+        <v>6.12</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>2.14</v>
+        <v>4.45</v>
       </c>
       <c r="G31" s="32" t="n">
-        <v>1.68</v>
+        <v>2.34</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="32" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="J31" s="32" t="n">
-        <v>38.19</v>
+        <v>64.22</v>
       </c>
       <c r="K31" s="32" t="n">
-        <v>7</v>
+        <v>6.11</v>
       </c>
       <c r="L31" s="32" t="n">
-        <v>0</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="M31" s="32" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
         <is>
-          <t>44 (C+)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C32" s="32" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="D32" s="32" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.92</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>7.84</v>
+        <v>4.16</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>1.37</v>
+        <v>2.03</v>
       </c>
       <c r="G32" s="32" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="32" t="n">
-        <v>-0.33</v>
+        <v>-0.13</v>
       </c>
       <c r="J32" s="32" t="n">
-        <v>-12.9</v>
+        <v>29.19</v>
       </c>
       <c r="K32" s="32" t="n">
-        <v>6.28</v>
+        <v>7.1</v>
       </c>
       <c r="L32" s="32" t="n">
-        <v>15.52</v>
+        <v>3.03</v>
       </c>
       <c r="M32" s="32" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -5493,14 +5493,14 @@
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>43 (C+)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="32" t="n">
-        <v>-0.11</v>
+        <v>-0.16</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>3.05</v>
@@ -5531,127 +5531,127 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>42 (C+)</t>
+          <t>45 (B-)</t>
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="D34" s="32" t="n">
-        <v>-1.44</v>
+        <v>-0.41</v>
       </c>
       <c r="E34" s="32" t="n">
-        <v>3.68</v>
+        <v>7.51</v>
       </c>
       <c r="F34" s="32" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="G34" s="32" t="n">
-        <v>2.64</v>
+        <v>1.68</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="32" t="n">
-        <v>-0.23</v>
+        <v>-0.66</v>
       </c>
       <c r="J34" s="32" t="n">
-        <v>-9.77</v>
+        <v>38.19</v>
       </c>
       <c r="K34" s="32" t="n">
-        <v>7.19</v>
+        <v>7</v>
       </c>
       <c r="L34" s="32" t="n">
-        <v>9.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="M34" s="32" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>41 (C+)</t>
+          <t>44 (C+)</t>
         </is>
       </c>
       <c r="C35" s="32" t="n">
-        <v>4.7</v>
+        <v>8.9</v>
       </c>
       <c r="D35" s="32" t="n">
-        <v>-1.54</v>
+        <v>-0.17</v>
       </c>
       <c r="E35" s="32" t="n">
-        <v>1.64</v>
+        <v>4.39</v>
       </c>
       <c r="F35" s="32" t="n">
-        <v>1.87</v>
+        <v>3.62</v>
       </c>
       <c r="G35" s="32" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="32" t="n">
-        <v>0.83</v>
+        <v>2.12</v>
       </c>
       <c r="J35" s="32" t="n">
-        <v>-54.27</v>
+        <v>-22.67</v>
       </c>
       <c r="K35" s="32" t="n">
-        <v>6.48</v>
+        <v>7.28</v>
       </c>
       <c r="L35" s="32" t="n">
-        <v>9.68</v>
+        <v>4.17</v>
       </c>
       <c r="M35" s="32" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>43 (C+)</t>
         </is>
       </c>
       <c r="C36" s="32" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="D36" s="32" t="n">
-        <v>2.43</v>
+        <v>-0.5</v>
       </c>
       <c r="E36" s="32" t="n">
-        <v>6.12</v>
+        <v>0.62</v>
       </c>
       <c r="F36" s="32" t="n">
-        <v>4.45</v>
+        <v>4.68</v>
       </c>
       <c r="G36" s="32" t="n">
-        <v>2.34</v>
+        <v>1.36</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="n">
-        <v>-0.63</v>
+        <v>-0.47</v>
       </c>
       <c r="J36" s="32" t="n">
-        <v>64.22</v>
+        <v>32.81</v>
       </c>
       <c r="K36" s="32" t="n">
-        <v>6.11</v>
+        <v>7.25</v>
       </c>
       <c r="L36" s="32" t="n">
-        <v>-8.890000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="M36" s="32" t="n">
         <v>41</v>
@@ -5660,50 +5660,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C37" s="32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="D37" s="32" t="n">
-        <v>-0.23</v>
+        <v>-0.96</v>
       </c>
       <c r="E37" s="32" t="n">
-        <v>0.64</v>
+        <v>3.68</v>
       </c>
       <c r="F37" s="32" t="n">
-        <v>3.25</v>
+        <v>2.31</v>
       </c>
       <c r="G37" s="32" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="32" t="n">
-        <v>-0.58</v>
+        <v>-0.23</v>
       </c>
       <c r="J37" s="32" t="n">
-        <v>9.19</v>
+        <v>-9.77</v>
       </c>
       <c r="K37" s="32" t="n">
-        <v>7.77</v>
+        <v>7.19</v>
       </c>
       <c r="L37" s="32" t="n">
-        <v>7.69</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M37" s="32" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="B38" s="34" t="inlineStr">
@@ -5712,84 +5712,84 @@
         </is>
       </c>
       <c r="C38" s="32" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="D38" s="32" t="n">
-        <v>1.05</v>
+        <v>0.78</v>
       </c>
       <c r="E38" s="32" t="n">
-        <v>1.22</v>
+        <v>5.3</v>
       </c>
       <c r="F38" s="32" t="n">
-        <v>4.57</v>
+        <v>1.42</v>
       </c>
       <c r="G38" s="32" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="32" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.45</v>
       </c>
       <c r="J38" s="32" t="n">
-        <v>-21.43</v>
+        <v>-36.97</v>
       </c>
       <c r="K38" s="32" t="n">
-        <v>7</v>
+        <v>7.43</v>
       </c>
       <c r="L38" s="32" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="M38" s="32" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>37 (C)</t>
+          <t>39 (C+)</t>
         </is>
       </c>
       <c r="C39" s="32" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="D39" s="32" t="n">
-        <v>2.87</v>
+        <v>0.39</v>
       </c>
       <c r="E39" s="32" t="n">
-        <v>3.59</v>
+        <v>0.64</v>
       </c>
       <c r="F39" s="32" t="n">
-        <v>4.59</v>
+        <v>3.25</v>
       </c>
       <c r="G39" s="32" t="n">
-        <v>3.28</v>
+        <v>1.04</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="32" t="n">
-        <v>-0.8</v>
+        <v>-0.58</v>
       </c>
       <c r="J39" s="32" t="n">
-        <v>-22.81</v>
+        <v>9.19</v>
       </c>
       <c r="K39" s="32" t="n">
-        <v>5</v>
+        <v>7.77</v>
       </c>
       <c r="L39" s="32" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="M39" s="32" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
@@ -5798,127 +5798,127 @@
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="D40" s="32" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="E40" s="32" t="n">
-        <v>5.3</v>
+        <v>2.04</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>1.42</v>
+        <v>2.53</v>
       </c>
       <c r="G40" s="32" t="n">
-        <v>1.54</v>
+        <v>2.52</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="32" t="n">
-        <v>-1.45</v>
+        <v>-0.43</v>
       </c>
       <c r="J40" s="32" t="n">
-        <v>-36.97</v>
+        <v>-12.03</v>
       </c>
       <c r="K40" s="32" t="n">
-        <v>7.43</v>
+        <v>7.54</v>
       </c>
       <c r="L40" s="32" t="n">
-        <v>10.34</v>
+        <v>5.41</v>
       </c>
       <c r="M40" s="32" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>35 (C)</t>
+          <t>36 (C)</t>
         </is>
       </c>
       <c r="C41" s="32" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="D41" s="32" t="n">
-        <v>-1.24</v>
+        <v>-0.01</v>
       </c>
       <c r="E41" s="32" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="F41" s="32" t="n">
-        <v>2.3</v>
+        <v>4.22</v>
       </c>
       <c r="G41" s="32" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="32" t="n">
-        <v>-1.16</v>
+        <v>-0.82</v>
       </c>
       <c r="J41" s="32" t="n">
-        <v>-6.07</v>
+        <v>15.03</v>
       </c>
       <c r="K41" s="32" t="n">
-        <v>6.74</v>
+        <v>9</v>
       </c>
       <c r="L41" s="32" t="n">
-        <v>-2.56</v>
+        <v>20</v>
       </c>
       <c r="M41" s="32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>35 (C)</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="D42" s="32" t="n">
-        <v>0.08</v>
+        <v>-0.59</v>
       </c>
       <c r="E42" s="32" t="n">
-        <v>5.2</v>
+        <v>1.22</v>
       </c>
       <c r="F42" s="32" t="n">
-        <v>2.97</v>
+        <v>4.57</v>
       </c>
       <c r="G42" s="32" t="n">
-        <v>0.16</v>
+        <v>1.8</v>
       </c>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="32" t="n">
-        <v>0.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J42" s="32" t="n">
-        <v>-15.03</v>
+        <v>-21.43</v>
       </c>
       <c r="K42" s="32" t="n">
-        <v>7.15</v>
+        <v>7</v>
       </c>
       <c r="L42" s="32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M42" s="32" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B43" s="34" t="inlineStr">
@@ -5927,41 +5927,41 @@
         </is>
       </c>
       <c r="C43" s="32" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="D43" s="32" t="n">
-        <v>-0.46</v>
+        <v>-2.11</v>
       </c>
       <c r="E43" s="32" t="n">
-        <v>1.64</v>
+        <v>3.48</v>
       </c>
       <c r="F43" s="32" t="n">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="G43" s="32" t="n">
-        <v>0.88</v>
+        <v>1.98</v>
       </c>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="32" t="n">
-        <v>-0.1</v>
+        <v>-3.19</v>
       </c>
       <c r="J43" s="32" t="n">
-        <v>-1.17</v>
+        <v>36.76</v>
       </c>
       <c r="K43" s="32" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="L43" s="32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M43" s="32" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
@@ -5970,125 +5970,127 @@
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="D44" s="32" t="n">
-        <v>-0.86</v>
+        <v>2.87</v>
       </c>
       <c r="E44" s="32" t="n">
-        <v>5.82</v>
+        <v>3.59</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>1.83</v>
+        <v>4.59</v>
       </c>
       <c r="G44" s="32" t="n">
-        <v>0.68</v>
+        <v>3.28</v>
       </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="32" t="n">
-        <v>-2.64</v>
+        <v>-0.8</v>
       </c>
       <c r="J44" s="32" t="n">
-        <v>18.23</v>
+        <v>-22.81</v>
       </c>
       <c r="K44" s="32" t="n">
-        <v>7.59</v>
+        <v>5</v>
       </c>
       <c r="L44" s="32" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="M44" s="32" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>34 (C)</t>
-        </is>
-      </c>
-      <c r="C45" s="32" t="n"/>
+          <t>33 (C)</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="n">
+        <v>4.3</v>
+      </c>
       <c r="D45" s="32" t="n">
-        <v>-0.09</v>
+        <v>1.25</v>
       </c>
       <c r="E45" s="32" t="n">
-        <v>0.62</v>
+        <v>-1.45</v>
       </c>
       <c r="F45" s="32" t="n">
-        <v>4.68</v>
+        <v>4.54</v>
       </c>
       <c r="G45" s="32" t="n">
-        <v>1.36</v>
+        <v>2.46</v>
       </c>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="32" t="n">
-        <v>-0.47</v>
+        <v>-0.31</v>
       </c>
       <c r="J45" s="32" t="n">
-        <v>32.81</v>
+        <v>3.44</v>
       </c>
       <c r="K45" s="32" t="n">
-        <v>7.25</v>
+        <v>7.29</v>
       </c>
       <c r="L45" s="32" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="M45" s="32" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>33 (C)</t>
         </is>
       </c>
       <c r="C46" s="32" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="D46" s="32" t="n">
-        <v>-1.07</v>
+        <v>-1.13</v>
       </c>
       <c r="E46" s="32" t="n">
-        <v>2.83</v>
+        <v>1.64</v>
       </c>
       <c r="F46" s="32" t="n">
-        <v>4.22</v>
+        <v>2.55</v>
       </c>
       <c r="G46" s="32" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="H46" s="32" t="n"/>
       <c r="I46" s="32" t="n">
-        <v>-0.82</v>
+        <v>-0.1</v>
       </c>
       <c r="J46" s="32" t="n">
-        <v>15.03</v>
+        <v>-1.17</v>
       </c>
       <c r="K46" s="32" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="L46" s="32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M46" s="32" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B47" s="34" t="inlineStr">
@@ -6097,84 +6099,84 @@
         </is>
       </c>
       <c r="C47" s="32" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="D47" s="32" t="n">
-        <v>-2.79</v>
+        <v>-0.33</v>
       </c>
       <c r="E47" s="32" t="n">
-        <v>3.48</v>
+        <v>2.57</v>
       </c>
       <c r="F47" s="32" t="n">
-        <v>1.62</v>
+        <v>3.46</v>
       </c>
       <c r="G47" s="32" t="n">
         <v>1.98</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="32" t="n">
-        <v>-3.19</v>
+        <v>-0.48</v>
       </c>
       <c r="J47" s="32" t="n">
-        <v>36.76</v>
+        <v>-24.31</v>
       </c>
       <c r="K47" s="32" t="n">
-        <v>7.4</v>
+        <v>7.56</v>
       </c>
       <c r="L47" s="32" t="n">
-        <v>16</v>
+        <v>5.56</v>
       </c>
       <c r="M47" s="32" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>32 (C)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="D48" s="32" t="n">
-        <v>-0.59</v>
+        <v>-1.39</v>
       </c>
       <c r="E48" s="32" t="n">
-        <v>2.04</v>
+        <v>5.82</v>
       </c>
       <c r="F48" s="32" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="G48" s="32" t="n">
-        <v>2.52</v>
+        <v>0.68</v>
       </c>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="32" t="n">
-        <v>-0.43</v>
+        <v>-2.64</v>
       </c>
       <c r="J48" s="32" t="n">
-        <v>-12.03</v>
+        <v>18.23</v>
       </c>
       <c r="K48" s="32" t="n">
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
       <c r="L48" s="32" t="n">
-        <v>5.41</v>
+        <v>6.82</v>
       </c>
       <c r="M48" s="32" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B49" s="34" t="inlineStr">
@@ -6183,78 +6185,78 @@
         </is>
       </c>
       <c r="C49" s="32" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="D49" s="32" t="n">
-        <v>-1.8</v>
+        <v>-1.1</v>
       </c>
       <c r="E49" s="32" t="n">
-        <v>2.57</v>
+        <v>5.2</v>
       </c>
       <c r="F49" s="32" t="n">
-        <v>3.46</v>
+        <v>2.97</v>
       </c>
       <c r="G49" s="32" t="n">
-        <v>1.98</v>
+        <v>0.16</v>
       </c>
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="32" t="n">
-        <v>-0.48</v>
+        <v>0.23</v>
       </c>
       <c r="J49" s="32" t="n">
-        <v>-24.31</v>
+        <v>-15.03</v>
       </c>
       <c r="K49" s="32" t="n">
-        <v>7.56</v>
+        <v>7.15</v>
       </c>
       <c r="L49" s="32" t="n">
-        <v>5.56</v>
+        <v>3.85</v>
       </c>
       <c r="M49" s="32" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>27 (C-)</t>
+          <t>30 (C-)</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="D50" s="32" t="n">
-        <v>1.1</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E50" s="32" t="n">
-        <v>-1.45</v>
+        <v>3</v>
       </c>
       <c r="F50" s="32" t="n">
-        <v>4.54</v>
+        <v>2.3</v>
       </c>
       <c r="G50" s="32" t="n">
-        <v>2.46</v>
+        <v>0.86</v>
       </c>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="32" t="n">
-        <v>-0.31</v>
+        <v>-1.16</v>
       </c>
       <c r="J50" s="32" t="n">
-        <v>3.44</v>
+        <v>-6.07</v>
       </c>
       <c r="K50" s="32" t="n">
-        <v>7.29</v>
+        <v>6.74</v>
       </c>
       <c r="L50" s="32" t="n">
-        <v>2.86</v>
+        <v>-2.56</v>
       </c>
       <c r="M50" s="32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
@@ -6265,14 +6267,14 @@
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>19 (D)</t>
+          <t>23 (D)</t>
         </is>
       </c>
       <c r="C51" s="32" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="D51" s="32" t="n">
-        <v>-1.48</v>
+        <v>-0.05</v>
       </c>
       <c r="E51" s="32" t="n">
         <v>3.46</v>
@@ -6379,78 +6381,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F2" s="17" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="G2" s="17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H2" s="17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="I2" s="17" t="n">
+      <c r="D2" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I2" s="14" t="n">
         <v>6.12</v>
       </c>
-      <c r="J2" s="17" t="n">
+      <c r="J2" s="14" t="n">
         <v>4.45</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="I3" s="8" t="n">
+      <c r="D3" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="I3" s="11" t="n">
         <v>5.19</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="11" t="n">
         <v>5.67</v>
       </c>
     </row>
@@ -6469,7 +6471,7 @@
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
@@ -6477,13 +6479,13 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>48.9</v>
+        <v>44.8</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>0.16</v>
+        <v>-0.92</v>
       </c>
       <c r="I4" s="14" t="n">
         <v>4.16</v>
@@ -6507,7 +6509,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -6515,13 +6517,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>3.13</v>
@@ -6531,40 +6533,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I6" s="11" t="n">
+      <c r="D6" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I6" s="14" t="n">
         <v>2.05</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="14" t="n">
         <v>1.64</v>
       </c>
     </row>
@@ -6583,7 +6585,7 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
@@ -6591,13 +6593,13 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>49.2</v>
+        <v>48.4</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>-0.5</v>
+        <v>0.15</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>8.02</v>
@@ -6621,7 +6623,7 @@
         </is>
       </c>
       <c r="D8" s="20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
@@ -6629,13 +6631,13 @@
         </is>
       </c>
       <c r="F8" s="20" t="n">
-        <v>33.3</v>
+        <v>33.8</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>-2.79</v>
+        <v>-2.11</v>
       </c>
       <c r="I8" s="20" t="n">
         <v>3.48</v>
@@ -6659,7 +6661,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -6667,13 +6669,13 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>5.18</v>
@@ -6683,40 +6685,40 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D10" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I10" s="23" t="n">
+      <c r="D10" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I10" s="20" t="n">
         <v>-1.45</v>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="20" t="n">
         <v>4.54</v>
       </c>
     </row>
@@ -6735,7 +6737,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
@@ -6743,13 +6745,13 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>41.8</v>
+        <v>40</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>-1.44</v>
+        <v>-0.96</v>
       </c>
       <c r="I11" s="17" t="n">
         <v>3.68</v>
@@ -6773,7 +6775,7 @@
         </is>
       </c>
       <c r="D12" s="20" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
@@ -6781,7 +6783,7 @@
         </is>
       </c>
       <c r="F12" s="20" t="n">
-        <v>37.2</v>
+        <v>33.6</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>3.9</v>
@@ -6797,40 +6799,40 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Riverside</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I13" s="20" t="n">
+      <c r="D13" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I13" s="23" t="n">
         <v>5.2</v>
       </c>
-      <c r="J13" s="20" t="n">
+      <c r="J13" s="23" t="n">
         <v>2.97</v>
       </c>
     </row>
@@ -6849,7 +6851,7 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -6857,13 +6859,13 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>51.7</v>
+        <v>50.5</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>-0.36</v>
+        <v>-1.4</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>6.2</v>
@@ -6887,7 +6889,7 @@
         </is>
       </c>
       <c r="D15" s="20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
@@ -6895,13 +6897,13 @@
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>32.1</v>
+        <v>35.6</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>-0.59</v>
+        <v>0.92</v>
       </c>
       <c r="I15" s="20" t="n">
         <v>2.04</v>
@@ -6925,7 +6927,7 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -6933,13 +6935,13 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.84</v>
+        <v>-0.8</v>
       </c>
       <c r="I16" s="11" t="n">
         <v>8.130000000000001</v>
@@ -6963,7 +6965,7 @@
         </is>
       </c>
       <c r="D17" s="20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
@@ -6971,13 +6973,13 @@
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>34.2</v>
+        <v>33.1</v>
       </c>
       <c r="G17" s="20" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>-0.46</v>
+        <v>-1.13</v>
       </c>
       <c r="I17" s="20" t="n">
         <v>1.64</v>
@@ -6987,78 +6989,78 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n">
+      <c r="A18" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="I18" s="17" t="n">
+      <c r="D18" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I18" s="14" t="n">
         <v>7.84</v>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="14" t="n">
         <v>1.37</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I19" s="5" t="n">
+      <c r="D19" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="I19" s="8" t="n">
         <v>5.93</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J19" s="8" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -7077,7 +7079,7 @@
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
@@ -7085,13 +7087,13 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>47.8</v>
+        <v>46</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>-2.12</v>
+        <v>-2.34</v>
       </c>
       <c r="I20" s="14" t="n">
         <v>1.57</v>
@@ -7101,116 +7103,116 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n">
+      <c r="A21" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="D21" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Charlotte-Concord-Gastonia</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Baltimore-Columbia-Towson</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F21" s="17" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="J21" s="17" t="n">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Charlotte-Concord-Gastonia</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H22" s="11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>Baltimore-Columbia-Towson</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>Baltimore</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I23" s="20" t="n">
+      <c r="F23" s="17" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I23" s="17" t="n">
         <v>5.3</v>
       </c>
-      <c r="J23" s="20" t="n">
+      <c r="J23" s="17" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -7237,13 +7239,13 @@
         </is>
       </c>
       <c r="F24" s="17" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>-0.23</v>
+        <v>0.39</v>
       </c>
       <c r="I24" s="17" t="n">
         <v>0.64</v>
@@ -7253,40 +7255,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n">
+      <c r="A25" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="G25" s="17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H25" s="17" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I25" s="17" t="n">
+      <c r="D25" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I25" s="14" t="n">
         <v>3.05</v>
       </c>
-      <c r="J25" s="17" t="n">
+      <c r="J25" s="14" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -7305,7 +7307,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -7313,13 +7315,13 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>75.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>7.75</v>
@@ -7329,116 +7331,116 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Portland</t>
         </is>
       </c>
-      <c r="D27" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="D27" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G27" s="23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H27" s="23" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="I27" s="23" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="J27" s="23" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Sacramento-Roseville-Folsom</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F27" s="20" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="I27" s="20" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="J27" s="20" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Sacramento-Roseville-Folsom</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="G28" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" s="17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I28" s="17" t="n">
+      <c r="F28" s="20" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H28" s="20" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="I28" s="20" t="n">
         <v>1.22</v>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="20" t="n">
         <v>4.57</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Pittsburgh</t>
         </is>
       </c>
-      <c r="D29" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H29" s="14" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I29" s="14" t="n">
+      <c r="D29" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I29" s="8" t="n">
         <v>6.43</v>
       </c>
-      <c r="J29" s="14" t="n">
+      <c r="J29" s="8" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -7457,7 +7459,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
@@ -7465,13 +7467,13 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>60.7</v>
+        <v>60.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>1.52</v>
+        <v>2.43</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>6.16</v>
@@ -7495,7 +7497,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -7503,13 +7505,13 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>67.7</v>
+        <v>66.8</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.82</v>
+        <v>-0.39</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>3.26</v>
@@ -7533,7 +7535,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -7541,13 +7543,13 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.87</v>
+        <v>0.37</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>6.99</v>
@@ -7571,7 +7573,7 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
@@ -7579,13 +7581,13 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>57.9</v>
+        <v>55.4</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>1.69</v>
+        <v>-0.33</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>2.79</v>
@@ -7595,38 +7597,40 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="n">
+      <c r="A34" s="17" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D34" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="G34" s="20" t="n"/>
-      <c r="H34" s="20" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I34" s="20" t="n">
+      <c r="D34" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I34" s="17" t="n">
         <v>0.62</v>
       </c>
-      <c r="J34" s="20" t="n">
+      <c r="J34" s="17" t="n">
         <v>4.68</v>
       </c>
     </row>
@@ -7645,7 +7649,7 @@
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
@@ -7653,7 +7657,7 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>49.7</v>
+        <v>48.4</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>3.4</v>
@@ -7681,21 +7685,21 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.86</v>
+        <v>-0.4</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>3.94</v>
@@ -7719,7 +7723,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
@@ -7727,13 +7731,13 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>61.4</v>
+        <v>60.3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>1.06</v>
+        <v>-0.11</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>0.76</v>
@@ -7757,7 +7761,7 @@
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
@@ -7765,13 +7769,13 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>45.6</v>
+        <v>44.6</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H38" s="14" t="n">
-        <v>-1.18</v>
+        <v>-0.41</v>
       </c>
       <c r="I38" s="14" t="n">
         <v>7.51</v>
@@ -7795,7 +7799,7 @@
         </is>
       </c>
       <c r="D39" s="26" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E39" s="27" t="inlineStr">
         <is>
@@ -7803,13 +7807,13 @@
         </is>
       </c>
       <c r="F39" s="26" t="n">
-        <v>19.2</v>
+        <v>22.6</v>
       </c>
       <c r="G39" s="26" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H39" s="26" t="n">
-        <v>-1.48</v>
+        <v>-0.05</v>
       </c>
       <c r="I39" s="26" t="n">
         <v>3.46</v>
@@ -7819,40 +7823,40 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Providence-Warwick</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G40" s="11" t="n">
+      <c r="D40" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G40" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H40" s="11" t="n">
+      <c r="H40" s="14" t="n">
         <v>1.69</v>
       </c>
-      <c r="I40" s="11" t="n">
+      <c r="I40" s="14" t="n">
         <v>3.77</v>
       </c>
-      <c r="J40" s="11" t="n">
+      <c r="J40" s="14" t="n">
         <v>6.57</v>
       </c>
     </row>
@@ -7871,7 +7875,7 @@
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
@@ -7879,13 +7883,13 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>34.2</v>
+        <v>35.6</v>
       </c>
       <c r="G41" s="20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H41" s="20" t="n">
-        <v>-1.07</v>
+        <v>-0.01</v>
       </c>
       <c r="I41" s="20" t="n">
         <v>2.83</v>
@@ -7909,7 +7913,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -7917,13 +7921,13 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>78.5</v>
+        <v>80.7</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>4.32</v>
@@ -7947,7 +7951,7 @@
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
@@ -7955,13 +7959,13 @@
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>-0.08</v>
+        <v>-1.21</v>
       </c>
       <c r="I43" s="11" t="n">
         <v>6.84</v>
@@ -7971,78 +7975,78 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="n">
+      <c r="A44" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>Louisville-Jefferson County</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>Louisville</t>
         </is>
       </c>
-      <c r="D44" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
+      <c r="D44" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="23" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F44" s="20" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="I44" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="20" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H45" s="23" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="I45" s="23" t="n">
+      <c r="F45" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H45" s="20" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="I45" s="20" t="n">
         <v>2.57</v>
       </c>
-      <c r="J45" s="23" t="n">
+      <c r="J45" s="20" t="n">
         <v>3.46</v>
       </c>
     </row>
@@ -8061,7 +8065,7 @@
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
@@ -8069,13 +8073,13 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>48.6</v>
+        <v>49.9</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="H46" s="14" t="n">
-        <v>0.98</v>
+        <v>-0.76</v>
       </c>
       <c r="I46" s="14" t="n">
         <v>4.99</v>
@@ -8099,7 +8103,7 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
@@ -8107,13 +8111,13 @@
         </is>
       </c>
       <c r="F47" s="8" t="n">
-        <v>56.7</v>
+        <v>58.5</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>-0.73</v>
+        <v>-0.68</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>4.93</v>
@@ -8145,13 +8149,13 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>60.6</v>
+        <v>61</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.72</v>
+        <v>0.35</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>-0.91</v>
@@ -8161,78 +8165,78 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="n">
+      <c r="A49" s="17" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="D49" s="14" t="n">
-        <v>47</v>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="D49" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Grand Rapids</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
-      <c r="F49" s="14" t="n">
-        <v>47</v>
-      </c>
-      <c r="G49" s="14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H49" s="14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="J49" s="14" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>Grand Rapids</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="G50" s="11" t="n">
+      <c r="F50" s="14" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G50" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H50" s="11" t="n">
-        <v>-5.05</v>
-      </c>
-      <c r="I50" s="11" t="n">
+      <c r="H50" s="14" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="I50" s="14" t="n">
         <v>3.79</v>
       </c>
-      <c r="J50" s="11" t="n">
+      <c r="J50" s="14" t="n">
         <v>5.4</v>
       </c>
     </row>
@@ -8259,7 +8263,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>65.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8362,7 +8366,7 @@
         </is>
       </c>
       <c r="C3" s="39" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
@@ -8374,11 +8378,11 @@
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="G3" s="40" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
@@ -8392,11 +8396,11 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Atlanta-Sandy Springs-Roswell</t>
         </is>
       </c>
       <c r="C4" s="39" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="39" t="inlineStr">
         <is>
@@ -8408,7 +8412,7 @@
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="G4" s="40" t="n">
@@ -8426,11 +8430,11 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Atlanta-Sandy Springs-Roswell</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C5" s="39" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
@@ -8442,7 +8446,7 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="G5" s="40" t="n">
@@ -8464,7 +8468,7 @@
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
@@ -8476,11 +8480,11 @@
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="G6" s="40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H6" s="40" t="inlineStr">
         <is>
@@ -8494,15 +8498,15 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C7" s="39" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D7" s="39" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" s="40" t="n">
@@ -8510,11 +8514,11 @@
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="G7" s="40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7" s="40" t="inlineStr">
         <is>
@@ -8528,11 +8532,11 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
@@ -8544,7 +8548,7 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="G8" s="40" t="n">
@@ -8562,7 +8566,7 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
@@ -8578,7 +8582,7 @@
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="G9" s="40" t="n">
@@ -8586,7 +8590,7 @@
       </c>
       <c r="H9" s="40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8596,11 +8600,11 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="C10" s="39" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="39" t="inlineStr">
         <is>
@@ -8612,7 +8616,7 @@
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="G10" s="40" t="n">
@@ -8630,7 +8634,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C11" s="39" t="n">
@@ -8646,11 +8650,11 @@
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="G11" s="40" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H11" s="40" t="inlineStr">
         <is>
@@ -8664,11 +8668,11 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="C12" s="39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="39" t="inlineStr">
         <is>
@@ -8684,7 +8688,7 @@
         </is>
       </c>
       <c r="G12" s="40" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H12" s="40" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>80.7</v>
+        <v>79.3</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -729,20 +729,20 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -760,20 +760,20 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -853,20 +853,20 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -884,20 +884,20 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>63.9</v>
+        <v>66.2</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>61</v>
+        <v>61.4</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -945,33 +945,33 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
+      <c r="D11" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>60.3</v>
+        <v>59.2</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1008,16 +1008,16 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>58.5</v>
+        <v>58.2</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1070,20 +1070,20 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>58.5</v>
+        <v>57.1</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>56.6</v>
+        <v>57.1</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1132,82 +1132,82 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Los Angeles-Long Beach-Anaheim</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Above Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Columbus</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="D18" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="F18" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Above Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>54</v>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>50.7</v>
+        <v>53.7</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1225,20 +1225,20 @@
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>50.5</v>
+        <v>54.4</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>50.1</v>
+        <v>51</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1286,114 +1286,114 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco-Oakland-Fremont</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D22" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Houston-Pasadena-The Woodlands</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="D24" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
@@ -1411,20 +1411,20 @@
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>48.4</v>
+        <v>49.9</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1442,28 +1442,28 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Tampa-St. Petersburg-Clearwater</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Grand Rapids</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>48</v>
-      </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
           <t>B-</t>
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>47.8</v>
+        <v>49.2</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1473,20 +1473,20 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>46.7</v>
+        <v>49</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1504,20 +1504,20 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>46</v>
+        <v>47.4</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1566,16 +1566,16 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1597,16 +1597,16 @@
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
     </row>
     <row r="33">
       <c r="A33" s="14" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
@@ -1658,48 +1658,48 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="17" t="n">
         <v>37</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D34" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>Below Average</t>
+      <c r="D34" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D35" s="19" t="n">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
@@ -1721,16 +1721,16 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
@@ -1752,20 +1752,20 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>40</v>
+        <v>40.9</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>39.2</v>
+        <v>39.8</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
@@ -1845,20 +1845,20 @@
     </row>
     <row r="40">
       <c r="A40" s="20" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="D40" s="22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>35.6</v>
+        <v>37.5</v>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
@@ -1876,20 +1876,20 @@
     </row>
     <row r="41">
       <c r="A41" s="20" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>35.6</v>
+        <v>36.5</v>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
@@ -1907,20 +1907,20 @@
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="D42" s="22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>35.2</v>
+        <v>36.1</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -1938,20 +1938,20 @@
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>33.8</v>
+        <v>33.3</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -1969,20 +1969,20 @@
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D44" s="22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>33.6</v>
+        <v>33</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -1999,52 +1999,52 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>Philadelphia-Camden-Wilmington</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="E45" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="G45" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="A45" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Detroit-Warren-Dearborn</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="20" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="D46" s="22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -2061,52 +2061,52 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" s="21" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="D47" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="E47" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="G47" s="21" t="inlineStr">
-        <is>
-          <t>Very Poor</t>
+      <c r="A47" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Riverside-San Bernardino-Ontario</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>31</v>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="F48" s="23" t="n">
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
@@ -2124,20 +2124,20 @@
     </row>
     <row r="49">
       <c r="A49" s="23" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F49" s="23" t="n">
-        <v>31.1</v>
+        <v>26.6</v>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
@@ -2154,33 +2154,33 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Louisville-Jefferson County</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="A50" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Minneapolis-St. Paul-Bloomington</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G50" s="27" t="inlineStr">
+        <is>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F51" s="26" t="n">
-        <v>22.6</v>
+        <v>18.9</v>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B2" s="29" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" s="30" t="n">
         <v>90</v>
@@ -2324,10 +2324,10 @@
         <v>90</v>
       </c>
       <c r="E2" s="31" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F2" s="30" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G2" s="30" t="n">
         <v>98</v>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="B3" s="29" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" s="30" t="n">
         <v>82</v>
@@ -2362,17 +2362,17 @@
         <v>66</v>
       </c>
       <c r="F3" s="30" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G3" s="30" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H3" s="32" t="n"/>
       <c r="I3" s="30" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J3" s="33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K3" s="31" t="n">
         <v>66</v>
@@ -2381,106 +2381,106 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C4" s="30" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D4" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="E4" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="F4" s="30" t="n">
         <v>96</v>
       </c>
-      <c r="G4" s="30" t="n">
-        <v>92</v>
+      <c r="E4" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="31" t="n">
+        <v>63</v>
+      </c>
+      <c r="G4" s="33" t="n">
+        <v>38</v>
       </c>
       <c r="H4" s="32" t="n"/>
-      <c r="I4" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="J4" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K4" s="30" t="n">
-        <v>86</v>
+      <c r="I4" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="J4" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>64</v>
+        <v>78</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>74</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="G5" s="33" t="n">
-        <v>26</v>
+        <v>92</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>92</v>
       </c>
       <c r="H5" s="32" t="n"/>
       <c r="I5" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="J5" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="K5" s="33" t="n">
-        <v>8</v>
+        <v>50</v>
+      </c>
+      <c r="J5" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B6" s="29" t="n">
         <v>67</v>
       </c>
       <c r="C6" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>40</v>
+        <v>76</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>78</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F6" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="G6" s="30" t="n">
         <v>82</v>
       </c>
-      <c r="G6" s="31" t="n">
-        <v>60</v>
-      </c>
       <c r="H6" s="32" t="n"/>
-      <c r="I6" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="J6" s="30" t="n">
+      <c r="I6" s="30" t="n">
+        <v>88</v>
+      </c>
+      <c r="J6" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="K6" s="30" t="n">
         <v>76</v>
-      </c>
-      <c r="K6" s="30" t="n">
-        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -2498,18 +2498,18 @@
       <c r="D7" s="33" t="n">
         <v>38</v>
       </c>
-      <c r="E7" s="31" t="n">
-        <v>54</v>
+      <c r="E7" s="30" t="n">
+        <v>74</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="30" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J7" s="33" t="n">
         <v>8</v>
@@ -2521,106 +2521,106 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="33" t="n">
-        <v>39</v>
+        <v>92</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="G8" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="J8" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="K8" s="32" t="n">
-        <v>0</v>
+      <c r="J8" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B9" s="29" t="n">
+        <v>66</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="D9" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C9" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>38</v>
+      <c r="E9" s="30" t="n">
+        <v>98</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="G9" s="30" t="n">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>28</v>
       </c>
       <c r="H9" s="32" t="n"/>
-      <c r="I9" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="J9" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="K9" s="30" t="n">
-        <v>74</v>
+      <c r="I9" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="K9" s="33" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B10" s="29" t="n">
         <v>61</v>
       </c>
-      <c r="C10" s="30" t="n">
-        <v>94</v>
+      <c r="C10" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="D10" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="J10" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="E10" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="J10" s="30" t="n">
+      <c r="K10" s="30" t="n">
         <v>74</v>
-      </c>
-      <c r="K10" s="33" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="33" t="n">
         <v>10</v>
@@ -2639,17 +2639,17 @@
         <v>94</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>61</v>
+        <v>70</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>47</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="30" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J11" s="33" t="n">
         <v>10</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="30" t="n">
         <v>74</v>
@@ -2674,13 +2674,13 @@
         <v>50</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F12" s="32" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="30" t="n">
@@ -2696,36 +2696,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B13" s="29" t="n">
         <v>59</v>
       </c>
       <c r="C13" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="D13" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <v>6</v>
+        <v>94</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="G13" s="30" t="n">
-        <v>80</v>
+        <v>27</v>
+      </c>
+      <c r="G13" s="31" t="n">
+        <v>58</v>
       </c>
       <c r="H13" s="32" t="n"/>
       <c r="I13" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="J13" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="K13" s="30" t="n">
-        <v>76</v>
+        <v>78</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="K13" s="33" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -2744,13 +2744,13 @@
         <v>82</v>
       </c>
       <c r="E14" s="30" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>57</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H14" s="32" t="n"/>
       <c r="I14" s="33" t="n">
@@ -2766,666 +2766,666 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="31" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="E15" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="F15" s="31" t="n">
-        <v>55</v>
+        <v>28</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>16</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="H15" s="32" t="n"/>
       <c r="I15" s="30" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J15" s="31" t="n">
+        <v>66</v>
+      </c>
+      <c r="K15" s="31" t="n">
         <v>50</v>
-      </c>
-      <c r="K15" s="33" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B16" s="29" t="n">
         <v>57</v>
       </c>
       <c r="C16" s="31" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D16" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>76</v>
+        <v>26</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>58</v>
       </c>
       <c r="F16" s="33" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="30" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J16" s="31" t="n">
-        <v>66</v>
-      </c>
-      <c r="K16" s="31" t="n">
         <v>50</v>
+      </c>
+      <c r="K16" s="33" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>55</v>
-      </c>
-      <c r="C17" s="30" t="n">
+        <v>56</v>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" s="32" t="n"/>
+      <c r="I17" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="J17" s="30" t="n">
         <v>96</v>
       </c>
-      <c r="D17" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="E17" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="F17" s="30" t="n">
-        <v>73</v>
-      </c>
-      <c r="G17" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="J17" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" s="30" t="n">
-        <v>96</v>
+      <c r="K17" s="31" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>54</v>
-      </c>
-      <c r="C18" s="33" t="n">
-        <v>36</v>
+        <v>56</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>96</v>
       </c>
       <c r="D18" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="G18" s="33" t="n">
         <v>32</v>
       </c>
-      <c r="E18" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="F18" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="30" t="n">
-        <v>72</v>
-      </c>
       <c r="H18" s="32" t="n"/>
-      <c r="I18" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="J18" s="30" t="n">
+      <c r="I18" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="J18" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="30" t="n">
         <v>96</v>
-      </c>
-      <c r="K18" s="31" t="n">
-        <v>58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B19" s="29" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C19" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="F19" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="F19" s="33" t="n">
-        <v>37</v>
-      </c>
-      <c r="G19" s="30" t="n">
-        <v>76</v>
+      <c r="G19" s="33" t="n">
+        <v>44</v>
       </c>
       <c r="H19" s="32" t="n"/>
-      <c r="I19" s="33" t="n">
-        <v>46</v>
+      <c r="I19" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="J19" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="K19" s="30" t="n">
         <v>92</v>
+      </c>
+      <c r="K19" s="33" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B20" s="29" t="n">
-        <v>50</v>
-      </c>
-      <c r="C20" s="31" t="n">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="D20" s="33" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F20" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="G20" s="31" t="n">
-        <v>68</v>
+        <v>39</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>84</v>
       </c>
       <c r="H20" s="32" t="n"/>
-      <c r="I20" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="J20" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="K20" s="33" t="n">
-        <v>6</v>
+      <c r="I20" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>50</v>
-      </c>
-      <c r="C21" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="D21" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" s="30" t="n">
-        <v>86</v>
+        <v>51</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="33" t="n">
+        <v>26</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="G21" s="33" t="n">
-        <v>6</v>
+        <v>96</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>80</v>
       </c>
       <c r="H21" s="32" t="n"/>
-      <c r="I21" s="33" t="n">
-        <v>14</v>
+      <c r="I21" s="31" t="n">
+        <v>62</v>
       </c>
       <c r="J21" s="33" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B22" s="29" t="n">
+        <v>51</v>
+      </c>
+      <c r="C22" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="C22" s="31" t="n">
+      <c r="D22" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="G22" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="H22" s="32" t="n"/>
+      <c r="I22" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J22" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="D22" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="E22" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="F22" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="G22" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="32" t="n"/>
-      <c r="I22" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="J22" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="K22" s="33" t="n">
-        <v>24</v>
+      <c r="K22" s="31" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B23" s="29" t="n">
-        <v>49</v>
-      </c>
-      <c r="C23" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="D23" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E23" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="F23" s="30" t="n">
-        <v>71</v>
-      </c>
-      <c r="G23" s="30" t="n">
+        <v>51</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="30" t="n">
         <v>84</v>
       </c>
+      <c r="F23" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" s="31" t="n">
+        <v>66</v>
+      </c>
       <c r="H23" s="32" t="n"/>
-      <c r="I23" s="31" t="n">
-        <v>66</v>
+      <c r="I23" s="30" t="n">
+        <v>74</v>
       </c>
       <c r="J23" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="K23" s="30" t="n">
-        <v>78</v>
+        <v>12</v>
+      </c>
+      <c r="K23" s="33" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B24" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="C24" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="D24" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="C24" s="31" t="n">
         <v>58</v>
       </c>
+      <c r="D24" s="33" t="n">
+        <v>24</v>
+      </c>
       <c r="E24" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="F24" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="G24" s="31" t="n">
-        <v>58</v>
+        <v>76</v>
+      </c>
+      <c r="F24" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="G24" s="33" t="n">
+        <v>6</v>
       </c>
       <c r="H24" s="32" t="n"/>
       <c r="I24" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="J24" s="33" t="n">
-        <v>46</v>
+        <v>14</v>
+      </c>
+      <c r="J24" s="30" t="n">
+        <v>88</v>
       </c>
       <c r="K24" s="33" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="C25" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="D25" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="E25" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="F25" s="31" t="n">
         <v>50</v>
       </c>
+      <c r="C25" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="D25" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="F25" s="33" t="n">
+        <v>33</v>
+      </c>
       <c r="G25" s="30" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="33" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J25" s="33" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="K25" s="33" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B26" s="29" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C26" s="33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D26" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="E26" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="F26" s="33" t="n">
-        <v>2</v>
+        <v>80</v>
+      </c>
+      <c r="E26" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <v>73</v>
       </c>
       <c r="G26" s="31" t="n">
         <v>64</v>
       </c>
       <c r="H26" s="32" t="n"/>
-      <c r="I26" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="J26" s="30" t="n">
-        <v>98</v>
+      <c r="I26" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="J26" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="K26" s="33" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="C27" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="D27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="31" t="n">
+        <v>49</v>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="G27" s="31" t="n">
         <v>52</v>
-      </c>
-      <c r="F27" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="G27" s="33" t="n">
-        <v>12</v>
       </c>
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="J27" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="K27" s="30" t="n">
-        <v>94</v>
+      <c r="J27" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="K27" s="33" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B28" s="29" t="n">
-        <v>47</v>
-      </c>
-      <c r="C28" s="33" t="n">
-        <v>10</v>
+        <v>49</v>
+      </c>
+      <c r="C28" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="D28" s="30" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E28" s="33" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F28" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="G28" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="H28" s="32" t="n"/>
+      <c r="I28" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="H28" s="32" t="n"/>
-      <c r="I28" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="J28" s="32" t="n">
-        <v>0</v>
+      <c r="J28" s="33" t="n">
+        <v>24</v>
       </c>
       <c r="K28" s="33" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="C29" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" s="31" t="n">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="C29" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="D29" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="E29" s="30" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G29" s="33" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="33" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="J29" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="K29" s="33" t="n">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="K29" s="30" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B30" s="29" t="n">
         <v>46</v>
       </c>
-      <c r="C30" s="30" t="n">
-        <v>82</v>
+      <c r="C30" s="33" t="n">
+        <v>36</v>
       </c>
       <c r="D30" s="33" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E30" s="33" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F30" s="31" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G30" s="31" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H30" s="32" t="n"/>
-      <c r="I30" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" s="31" t="n">
+      <c r="I30" s="31" t="n">
         <v>68</v>
       </c>
-      <c r="K30" s="30" t="n">
-        <v>82</v>
+      <c r="J30" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="K30" s="33" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B31" s="29" t="n">
         <v>45</v>
       </c>
       <c r="C31" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="D31" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="E31" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>53</v>
+      </c>
+      <c r="G31" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="H31" s="32" t="n"/>
+      <c r="I31" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="J31" s="30" t="n">
         <v>78</v>
       </c>
-      <c r="F31" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="G31" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="H31" s="32" t="n"/>
-      <c r="I31" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="J31" s="30" t="n">
-        <v>92</v>
-      </c>
       <c r="K31" s="33" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B32" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="C32" s="33" t="n">
-        <v>16</v>
+      <c r="C32" s="30" t="n">
+        <v>82</v>
       </c>
       <c r="D32" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="E32" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="31" t="n">
+        <v>59</v>
+      </c>
+      <c r="G32" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="F32" s="31" t="n">
-        <v>63</v>
-      </c>
-      <c r="G32" s="33" t="n">
-        <v>36</v>
-      </c>
       <c r="H32" s="32" t="n"/>
-      <c r="I32" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="J32" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="K32" s="33" t="n">
-        <v>34</v>
+      <c r="I32" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="J32" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="K32" s="30" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B33" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="C33" s="31" t="n">
-        <v>56</v>
+      <c r="C33" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="D33" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="E33" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="F33" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="G33" s="31" t="n">
-        <v>54</v>
+        <v>46</v>
+      </c>
+      <c r="E33" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="F33" s="33" t="n">
+        <v>49</v>
+      </c>
+      <c r="G33" s="33" t="n">
+        <v>26</v>
       </c>
       <c r="H33" s="32" t="n"/>
-      <c r="I33" s="33" t="n">
-        <v>28</v>
+      <c r="I33" s="30" t="n">
+        <v>76</v>
       </c>
       <c r="J33" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="K33" s="33" t="n">
-        <v>18</v>
+        <v>42</v>
+      </c>
+      <c r="K33" s="31" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="34">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="B34" s="29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" s="33" t="n">
         <v>44</v>
@@ -3444,13 +3444,13 @@
         <v>36</v>
       </c>
       <c r="E34" s="30" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F34" s="31" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G34" s="33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="33" t="n">
@@ -3466,106 +3466,106 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B35" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="C35" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="33" t="n">
+      <c r="C35" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" s="30" t="n">
+        <v>88</v>
+      </c>
+      <c r="E35" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="E35" s="31" t="n">
-        <v>60</v>
-      </c>
       <c r="F35" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="G35" s="33" t="n">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="G35" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="H35" s="32" t="n"/>
-      <c r="I35" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="J35" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="K35" s="31" t="n">
-        <v>52</v>
+      <c r="I35" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="J35" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="K35" s="33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B36" s="29" t="n">
         <v>43</v>
       </c>
       <c r="C36" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="D36" s="33" t="n">
-        <v>34</v>
+        <v>78</v>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="E36" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="F36" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="33" t="n">
         <v>10</v>
-      </c>
-      <c r="F36" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="G36" s="33" t="n">
-        <v>18</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="J36" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="K36" s="33" t="n">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="J36" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="K36" s="30" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B37" s="29" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37" s="33" t="n">
         <v>36</v>
       </c>
-      <c r="D37" s="33" t="n">
-        <v>16</v>
+      <c r="D37" s="31" t="n">
+        <v>66</v>
       </c>
       <c r="E37" s="33" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F37" s="33" t="n">
-        <v>47</v>
-      </c>
-      <c r="G37" s="31" t="n">
-        <v>56</v>
+        <v>43</v>
+      </c>
+      <c r="G37" s="33" t="n">
+        <v>14</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="J37" s="33" t="n">
-        <v>38</v>
-      </c>
-      <c r="K37" s="33" t="n">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="J37" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="K37" s="30" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="38">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="B38" s="29" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C38" s="33" t="n">
         <v>24</v>
@@ -3583,18 +3583,18 @@
       <c r="D38" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="E38" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="F38" s="30" t="n">
-        <v>80</v>
+      <c r="E38" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="F38" s="31" t="n">
+        <v>61</v>
       </c>
       <c r="G38" s="33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="33" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J38" s="33" t="n">
         <v>4</v>
@@ -3606,421 +3606,421 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>39</v>
-      </c>
-      <c r="C39" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="D39" s="31" t="n">
-        <v>66</v>
+        <v>40</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="D39" s="33" t="n">
+        <v>48</v>
       </c>
       <c r="E39" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="F39" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="G39" s="33" t="n">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="F39" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>54</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="J39" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="K39" s="30" t="n">
-        <v>80</v>
+        <v>18</v>
+      </c>
+      <c r="J39" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="K39" s="33" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B40" s="29" t="n">
-        <v>36</v>
-      </c>
-      <c r="C40" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D40" s="30" t="n">
-        <v>76</v>
+        <v>38</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="D40" s="33" t="n">
+        <v>34</v>
       </c>
       <c r="E40" s="33" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F40" s="33" t="n">
-        <v>43</v>
-      </c>
-      <c r="G40" s="31" t="n">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="G40" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="J40" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="K40" s="31" t="n">
-        <v>68</v>
+        <v>16</v>
+      </c>
+      <c r="J40" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="K40" s="33" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B41" s="29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="D41" s="31" t="n">
-        <v>54</v>
+        <v>26</v>
+      </c>
+      <c r="D41" s="30" t="n">
+        <v>98</v>
       </c>
       <c r="E41" s="33" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F41" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="G41" s="33" t="n">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>60</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="J41" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="K41" s="30" t="n">
-        <v>98</v>
+        <v>36</v>
+      </c>
+      <c r="J41" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="K41" s="33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B42" s="29" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C42" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="D42" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>71</v>
+      </c>
+      <c r="G42" s="33" t="n">
         <v>34</v>
       </c>
-      <c r="D42" s="33" t="n">
-        <v>30</v>
-      </c>
-      <c r="E42" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="F42" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="G42" s="33" t="n">
-        <v>24</v>
-      </c>
       <c r="H42" s="32" t="n"/>
-      <c r="I42" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="J42" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K42" s="33" t="n">
-        <v>26</v>
+      <c r="I42" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="K42" s="31" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B43" s="29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43" s="33" t="n">
         <v>28</v>
       </c>
-      <c r="D43" s="33" t="n">
-        <v>4</v>
+      <c r="D43" s="31" t="n">
+        <v>54</v>
       </c>
       <c r="E43" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="F43" s="30" t="n">
-        <v>76</v>
+        <v>20</v>
+      </c>
+      <c r="F43" s="33" t="n">
+        <v>12</v>
       </c>
       <c r="G43" s="33" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H43" s="32" t="n"/>
-      <c r="I43" s="32" t="n">
-        <v>0</v>
+      <c r="I43" s="33" t="n">
+        <v>22</v>
       </c>
       <c r="J43" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="K43" s="31" t="n">
-        <v>56</v>
+        <v>70</v>
+      </c>
+      <c r="K43" s="30" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B44" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="C44" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="D44" s="30" t="n">
-        <v>98</v>
+        <v>33</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="D44" s="33" t="n">
+        <v>42</v>
       </c>
       <c r="E44" s="33" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F44" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="G44" s="30" t="n">
-        <v>74</v>
+        <v>29</v>
+      </c>
+      <c r="G44" s="33" t="n">
+        <v>30</v>
       </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="33" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J44" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="K44" s="33" t="n">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="K44" s="30" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B45" s="29" t="n">
-        <v>33</v>
-      </c>
-      <c r="C45" s="31" t="n">
-        <v>50</v>
+        <v>32</v>
+      </c>
+      <c r="C45" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="D45" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="E45" s="32" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="E45" s="33" t="n">
+        <v>30</v>
       </c>
       <c r="F45" s="33" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="G45" s="33" t="n">
         <v>48</v>
       </c>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="J45" s="31" t="n">
-        <v>58</v>
+        <v>20</v>
+      </c>
+      <c r="J45" s="33" t="n">
+        <v>34</v>
       </c>
       <c r="K45" s="31" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B46" s="29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C46" s="33" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D46" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="E46" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="F46" s="33" t="n">
-        <v>41</v>
+        <v>8</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="F46" s="31" t="n">
+        <v>67</v>
       </c>
       <c r="G46" s="33" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H46" s="32" t="n"/>
-      <c r="I46" s="31" t="n">
-        <v>56</v>
-      </c>
-      <c r="J46" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="K46" s="33" t="n">
-        <v>20</v>
+      <c r="I46" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="K46" s="30" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>33</v>
-      </c>
-      <c r="C47" s="31" t="n">
-        <v>58</v>
+        <v>31</v>
+      </c>
+      <c r="C47" s="33" t="n">
+        <v>22</v>
       </c>
       <c r="D47" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="E47" s="33" t="n">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="E47" s="31" t="n">
+        <v>68</v>
       </c>
       <c r="F47" s="33" t="n">
-        <v>27</v>
-      </c>
-      <c r="G47" s="33" t="n">
-        <v>30</v>
+        <v>37</v>
+      </c>
+      <c r="G47" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="33" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J47" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="K47" s="30" t="n">
-        <v>70</v>
+        <v>26</v>
+      </c>
+      <c r="K47" s="33" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B48" s="29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C48" s="33" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="E48" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="F48" s="31" t="n">
-        <v>67</v>
+        <v>30</v>
+      </c>
+      <c r="E48" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="F48" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="G48" s="33" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H48" s="32" t="n"/>
-      <c r="I48" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="K48" s="30" t="n">
-        <v>72</v>
+      <c r="I48" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="J48" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="K48" s="33" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B49" s="29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C49" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="D49" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E49" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="F49" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="C49" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="D49" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="E49" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F49" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="G49" s="32" t="n">
-        <v>0</v>
+      <c r="G49" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="33" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J49" s="33" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K49" s="33" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B50" s="29" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C50" s="33" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="D50" s="33" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E50" s="33" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F50" s="33" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G50" s="33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="J50" s="33" t="n">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="J50" s="31" t="n">
+        <v>54</v>
       </c>
       <c r="K50" s="33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="B51" s="29" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C51" s="33" t="n">
         <v>2</v>
@@ -4039,17 +4039,17 @@
         <v>52</v>
       </c>
       <c r="E51" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="F51" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="G51" s="33" t="n">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="F51" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="G51" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H51" s="32" t="n"/>
       <c r="I51" s="33" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J51" s="33" t="n">
         <v>6</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>81 (A+)</t>
+          <t>79 (A+)</t>
         </is>
       </c>
       <c r="C2" s="32" t="n">
@@ -4172,17 +4172,17 @@
         <v>1.72</v>
       </c>
       <c r="E2" s="32" t="n">
-        <v>4.32</v>
+        <v>4.09</v>
       </c>
       <c r="F2" s="32" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="G2" s="32" t="n">
-        <v>4.42</v>
+        <v>4.48</v>
       </c>
       <c r="H2" s="32" t="n"/>
       <c r="I2" s="32" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J2" s="32" t="n">
         <v>-2.03</v>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>75 (A+)</t>
+          <t>72 (A+)</t>
         </is>
       </c>
       <c r="C3" s="32" t="n">
@@ -4215,17 +4215,17 @@
         <v>1.37</v>
       </c>
       <c r="E3" s="32" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="F3" s="32" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="G3" s="32" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="H3" s="32" t="n"/>
       <c r="I3" s="32" t="n">
-        <v>0.36</v>
+        <v>0.21</v>
       </c>
       <c r="J3" s="32" t="n">
         <v>-7.48</v>
@@ -4243,93 +4243,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>73 (A+)</t>
+          <t>69 (A+)</t>
         </is>
       </c>
       <c r="C4" s="32" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="D4" s="32" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.77</v>
       </c>
       <c r="E4" s="32" t="n">
-        <v>7.75</v>
+        <v>1.48</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>0.75</v>
+        <v>1.94</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>4.34</v>
+        <v>2.32</v>
       </c>
       <c r="H4" s="32" t="n"/>
       <c r="I4" s="32" t="n">
-        <v>1.13</v>
+        <v>1.88</v>
       </c>
       <c r="J4" s="32" t="n">
-        <v>-19.65</v>
+        <v>6.72</v>
       </c>
       <c r="K4" s="32" t="n">
-        <v>7.95</v>
+        <v>3.33</v>
       </c>
       <c r="L4" s="32" t="n">
-        <v>15.91</v>
+        <v>-16.67</v>
       </c>
       <c r="M4" s="32" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>69 (A+)</t>
+          <t>68 (A+)</t>
         </is>
       </c>
       <c r="C5" s="32" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>0.37</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>6.99</v>
+        <v>6.75</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>1.84</v>
+        <v>4.28</v>
       </c>
       <c r="H5" s="32" t="n"/>
       <c r="I5" s="32" t="n">
-        <v>0.04</v>
+        <v>0.63</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>34.49</v>
+        <v>-19.65</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>5.72</v>
+        <v>7.95</v>
       </c>
       <c r="L5" s="32" t="n">
-        <v>-12.77</v>
+        <v>15.91</v>
       </c>
       <c r="M5" s="32" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
@@ -4341,32 +4341,32 @@
         <v>3.7</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>-0.39</v>
+        <v>1.13</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>3.26</v>
+        <v>2.06</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="32" t="n">
-        <v>0.06</v>
+        <v>1.08</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>19.15</v>
+        <v>-14.84</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>7.88</v>
+        <v>7.71</v>
       </c>
       <c r="L6" s="32" t="n">
-        <v>8.82</v>
+        <v>7.14</v>
       </c>
       <c r="M6" s="32" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -4387,17 +4387,17 @@
         <v>-0.4</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>3.94</v>
+        <v>5.81</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="H7" s="32" t="n"/>
       <c r="I7" s="32" t="n">
-        <v>0.84</v>
+        <v>0.28</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>-31.3</v>
@@ -4415,93 +4415,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>65 (A)</t>
+          <t>66 (A)</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="D8" s="32" t="n">
-        <v>2.77</v>
+        <v>-0.39</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>0.6</v>
+        <v>4.25</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>2.59</v>
+        <v>1.32</v>
       </c>
       <c r="G8" s="32" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H8" s="32" t="n"/>
       <c r="I8" s="32" t="n">
-        <v>1.88</v>
+        <v>0.3</v>
       </c>
       <c r="J8" s="32" t="n">
-        <v>6.72</v>
+        <v>19.15</v>
       </c>
       <c r="K8" s="32" t="n">
-        <v>3.33</v>
+        <v>7.88</v>
       </c>
       <c r="L8" s="32" t="n">
-        <v>-16.67</v>
+        <v>8.82</v>
       </c>
       <c r="M8" s="32" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>64 (A)</t>
+          <t>66 (A)</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
         <v>3.9</v>
       </c>
       <c r="D9" s="32" t="n">
-        <v>0.52</v>
+        <v>0.37</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>3.13</v>
+        <v>7.97</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="G9" s="32" t="n">
-        <v>4.34</v>
+        <v>1.86</v>
       </c>
       <c r="H9" s="32" t="n"/>
       <c r="I9" s="32" t="n">
-        <v>0.92</v>
+        <v>-0.03</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>7.46</v>
+        <v>34.49</v>
       </c>
       <c r="K9" s="32" t="n">
-        <v>7.65</v>
+        <v>5.72</v>
       </c>
       <c r="L9" s="32" t="n">
-        <v>6.98</v>
+        <v>-12.77</v>
       </c>
       <c r="M9" s="32" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
@@ -4510,35 +4510,35 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>-0.91</v>
+        <v>2.44</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="G10" s="32" t="n">
-        <v>3.04</v>
+        <v>4.38</v>
       </c>
       <c r="H10" s="32" t="n"/>
       <c r="I10" s="32" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="J10" s="32" t="n">
-        <v>18.48</v>
+        <v>7.46</v>
       </c>
       <c r="K10" s="32" t="n">
-        <v>7.21</v>
+        <v>7.65</v>
       </c>
       <c r="L10" s="32" t="n">
-        <v>4</v>
+        <v>6.98</v>
       </c>
       <c r="M10" s="32" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>60 (A-)</t>
+          <t>59 (B+)</t>
         </is>
       </c>
       <c r="C11" s="32" t="n">
@@ -4559,17 +4559,17 @@
         <v>2.43</v>
       </c>
       <c r="E11" s="32" t="n">
-        <v>6.16</v>
+        <v>5.63</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="G11" s="32" t="n">
         <v>3.66</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="32" t="n">
-        <v>1.46</v>
+        <v>2.04</v>
       </c>
       <c r="J11" s="32" t="n">
         <v>-25.89</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>60 (A-)</t>
+          <t>59 (A-)</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
@@ -4602,17 +4602,17 @@
         <v>-0.11</v>
       </c>
       <c r="E12" s="32" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="F12" s="32" t="n">
-        <v>6.66</v>
+        <v>7.07</v>
       </c>
       <c r="G12" s="32" t="n">
-        <v>3.64</v>
+        <v>3.88</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="32" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="J12" s="32" t="n">
         <v>104.08</v>
@@ -4630,7 +4630,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
@@ -4639,35 +4639,35 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="D13" s="32" t="n">
-        <v>1.13</v>
+        <v>0.35</v>
       </c>
       <c r="E13" s="32" t="n">
-        <v>-0.04</v>
+        <v>-1.22</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="G13" s="32" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="H13" s="32" t="n"/>
       <c r="I13" s="32" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="J13" s="32" t="n">
-        <v>-14.84</v>
+        <v>18.48</v>
       </c>
       <c r="K13" s="32" t="n">
-        <v>7.71</v>
+        <v>7.21</v>
       </c>
       <c r="L13" s="32" t="n">
-        <v>7.14</v>
+        <v>4</v>
       </c>
       <c r="M13" s="32" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -4688,17 +4688,17 @@
         <v>1.2</v>
       </c>
       <c r="E14" s="32" t="n">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="G14" s="32" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H14" s="32" t="n"/>
       <c r="I14" s="32" t="n">
-        <v>-0.61</v>
+        <v>-0.43</v>
       </c>
       <c r="J14" s="32" t="n">
         <v>-4.03</v>
@@ -4716,50 +4716,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>58 (B+)</t>
+          <t>57 (B+)</t>
         </is>
       </c>
       <c r="C15" s="32" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="D15" s="32" t="n">
-        <v>-0.68</v>
+        <v>-0.65</v>
       </c>
       <c r="E15" s="32" t="n">
-        <v>4.93</v>
+        <v>6.85</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>2.2</v>
+        <v>4.55</v>
       </c>
       <c r="G15" s="32" t="n">
-        <v>4.36</v>
+        <v>3.28</v>
       </c>
       <c r="H15" s="32" t="n"/>
       <c r="I15" s="32" t="n">
-        <v>1.08</v>
+        <v>0.64</v>
       </c>
       <c r="J15" s="32" t="n">
-        <v>-3.28</v>
+        <v>12.45</v>
       </c>
       <c r="K15" s="32" t="n">
-        <v>7</v>
+        <v>7.27</v>
       </c>
       <c r="L15" s="32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M15" s="32" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Diego-Chula Vista-Carlsbad</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
@@ -4768,598 +4768,598 @@
         </is>
       </c>
       <c r="C16" s="32" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="D16" s="32" t="n">
-        <v>-0.65</v>
+        <v>-0.68</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>5.93</v>
+        <v>4.31</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>4.49</v>
+        <v>2.53</v>
       </c>
       <c r="G16" s="32" t="n">
-        <v>3.36</v>
+        <v>4.32</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="32" t="n">
-        <v>0.98</v>
+        <v>1.33</v>
       </c>
       <c r="J16" s="32" t="n">
-        <v>12.45</v>
+        <v>-3.28</v>
       </c>
       <c r="K16" s="32" t="n">
-        <v>7.27</v>
+        <v>7</v>
       </c>
       <c r="L16" s="32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M16" s="32" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>55 (B+)</t>
+          <t>56 (B+)</t>
         </is>
       </c>
       <c r="C17" s="32" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="D17" s="32" t="n">
-        <v>-0.33</v>
+        <v>-0.54</v>
       </c>
       <c r="E17" s="32" t="n">
-        <v>2.79</v>
+        <v>4.84</v>
       </c>
       <c r="F17" s="32" t="n">
-        <v>1.63</v>
+        <v>5.74</v>
       </c>
       <c r="G17" s="32" t="n">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="H17" s="32" t="n"/>
       <c r="I17" s="32" t="n">
-        <v>0.49</v>
+        <v>1.83</v>
       </c>
       <c r="J17" s="32" t="n">
-        <v>-41.29</v>
+        <v>112.64</v>
       </c>
       <c r="K17" s="32" t="n">
-        <v>8.609999999999999</v>
+        <v>7.42</v>
       </c>
       <c r="L17" s="32" t="n">
-        <v>16.13</v>
+        <v>4.55</v>
       </c>
       <c r="M17" s="32" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>54 (B)</t>
+          <t>56 (B+)</t>
         </is>
       </c>
       <c r="C18" s="32" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="D18" s="32" t="n">
-        <v>-0.54</v>
+        <v>-0.33</v>
       </c>
       <c r="E18" s="32" t="n">
-        <v>5.19</v>
+        <v>3.26</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>5.67</v>
+        <v>1.62</v>
       </c>
       <c r="G18" s="32" t="n">
-        <v>3.26</v>
+        <v>1.92</v>
       </c>
       <c r="H18" s="32" t="n"/>
       <c r="I18" s="32" t="n">
-        <v>1.83</v>
+        <v>0.22</v>
       </c>
       <c r="J18" s="32" t="n">
-        <v>112.64</v>
+        <v>-41.29</v>
       </c>
       <c r="K18" s="32" t="n">
-        <v>7.42</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L18" s="32" t="n">
-        <v>4.55</v>
+        <v>16.13</v>
       </c>
       <c r="M18" s="32" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>51 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C19" s="32" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="D19" s="32" t="n">
-        <v>-0.8</v>
+        <v>0.73</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>8.130000000000001</v>
+        <v>5.68</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>2.62</v>
+        <v>4.71</v>
       </c>
       <c r="G19" s="32" t="n">
-        <v>3.36</v>
+        <v>2.4</v>
       </c>
       <c r="H19" s="32" t="n"/>
       <c r="I19" s="32" t="n">
-        <v>-0.09</v>
+        <v>0.39</v>
       </c>
       <c r="J19" s="32" t="n">
-        <v>42.78</v>
+        <v>64.22</v>
       </c>
       <c r="K19" s="32" t="n">
-        <v>8.130000000000001</v>
+        <v>6.11</v>
       </c>
       <c r="L19" s="32" t="n">
-        <v>13.33</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="M19" s="32" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>54 (B)</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>6.2</v>
+        <v>7.37</v>
       </c>
       <c r="F20" s="32" t="n">
-        <v>4.22</v>
+        <v>2.73</v>
       </c>
       <c r="G20" s="32" t="n">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="H20" s="32" t="n"/>
       <c r="I20" s="32" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="J20" s="32" t="n">
-        <v>-25.29</v>
+        <v>42.78</v>
       </c>
       <c r="K20" s="32" t="n">
-        <v>5.59</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L20" s="32" t="n">
-        <v>-6.06</v>
+        <v>13.33</v>
       </c>
       <c r="M20" s="32" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>50 (B)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C21" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" s="32" t="n">
         <v>3.4</v>
-      </c>
-      <c r="D21" s="32" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="E21" s="32" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="F21" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G21" s="32" t="n">
-        <v>0.7</v>
       </c>
       <c r="H21" s="32" t="n"/>
       <c r="I21" s="32" t="n">
-        <v>-0.87</v>
+        <v>0.22</v>
       </c>
       <c r="J21" s="32" t="n">
-        <v>-9.74</v>
+        <v>-18.37</v>
       </c>
       <c r="K21" s="32" t="n">
-        <v>8.119999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="L21" s="32" t="n">
-        <v>18.6</v>
+        <v>9.09</v>
       </c>
       <c r="M21" s="32" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>50 (B-)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>-0.76</v>
+        <v>1.25</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>4.99</v>
+        <v>-0.37</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>0.59</v>
+        <v>3.6</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>0.44</v>
+        <v>2.38</v>
       </c>
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="32" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>39.08</v>
+        <v>3.44</v>
       </c>
       <c r="K22" s="32" t="n">
-        <v>6.86</v>
+        <v>7.29</v>
       </c>
       <c r="L22" s="32" t="n">
-        <v>-3.57</v>
+        <v>2.86</v>
       </c>
       <c r="M22" s="32" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>49 (B-)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C23" s="32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="D23" s="32" t="n">
-        <v>0.29</v>
+        <v>-1.4</v>
       </c>
       <c r="E23" s="32" t="n">
-        <v>2.05</v>
+        <v>6.7</v>
       </c>
       <c r="F23" s="32" t="n">
-        <v>1.64</v>
+        <v>4.27</v>
       </c>
       <c r="G23" s="32" t="n">
-        <v>3.46</v>
+        <v>3.06</v>
       </c>
       <c r="H23" s="32" t="n"/>
       <c r="I23" s="32" t="n">
-        <v>0.54</v>
+        <v>0.34</v>
       </c>
       <c r="J23" s="32" t="n">
-        <v>-18.37</v>
+        <v>-25.29</v>
       </c>
       <c r="K23" s="32" t="n">
-        <v>7.73</v>
+        <v>5.59</v>
       </c>
       <c r="L23" s="32" t="n">
-        <v>9.09</v>
+        <v>-6.06</v>
       </c>
       <c r="M23" s="32" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>51 (B)</t>
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="D24" s="32" t="n">
-        <v>0.15</v>
+        <v>-0.76</v>
       </c>
       <c r="E24" s="32" t="n">
-        <v>8.02</v>
+        <v>6.18</v>
       </c>
       <c r="F24" s="32" t="n">
-        <v>3.2</v>
+        <v>0.31</v>
       </c>
       <c r="G24" s="32" t="n">
-        <v>2.84</v>
+        <v>0.58</v>
       </c>
       <c r="H24" s="32" t="n"/>
       <c r="I24" s="32" t="n">
-        <v>-0.63</v>
+        <v>-0.11</v>
       </c>
       <c r="J24" s="32" t="n">
-        <v>-5.72</v>
+        <v>39.08</v>
       </c>
       <c r="K24" s="32" t="n">
-        <v>6.31</v>
+        <v>6.86</v>
       </c>
       <c r="L24" s="32" t="n">
-        <v>6.94</v>
+        <v>-3.57</v>
       </c>
       <c r="M24" s="32" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C25" s="32" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D25" s="32" t="n">
-        <v>1.8</v>
+        <v>0.15</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="F25" s="32" t="n"/>
+        <v>7.3</v>
+      </c>
+      <c r="F25" s="32" t="n">
+        <v>3.28</v>
+      </c>
       <c r="G25" s="32" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="32" t="n">
-        <v>0.57</v>
+        <v>-0.25</v>
       </c>
       <c r="J25" s="32" t="n">
-        <v>-18.19</v>
+        <v>-5.72</v>
       </c>
       <c r="K25" s="32" t="n">
-        <v>7.26</v>
+        <v>6.31</v>
       </c>
       <c r="L25" s="32" t="n">
-        <v>7.84</v>
+        <v>6.94</v>
       </c>
       <c r="M25" s="32" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>50 (B-)</t>
         </is>
       </c>
       <c r="C26" s="32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="D26" s="32" t="n">
-        <v>1.69</v>
+        <v>1.14</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>3.77</v>
+        <v>2.81</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>6.57</v>
+        <v>1.66</v>
       </c>
       <c r="G26" s="32" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="32" t="n">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="J26" s="32" t="n">
-        <v>132.32</v>
+        <v>-54.27</v>
       </c>
       <c r="K26" s="32" t="n">
-        <v>4.71</v>
+        <v>6.48</v>
       </c>
       <c r="L26" s="32" t="n">
-        <v>-6.9</v>
+        <v>9.68</v>
       </c>
       <c r="M26" s="32" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>48 (B-)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C27" s="32" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D27" s="32" t="n">
-        <v>-4.53</v>
+        <v>0.14</v>
       </c>
       <c r="E27" s="32" t="n">
-        <v>3.79</v>
+        <v>6.9</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>5.4</v>
+        <v>1.52</v>
       </c>
       <c r="G27" s="32" t="n">
-        <v>0.86</v>
+        <v>2.66</v>
       </c>
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="32" t="n">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="J27" s="32" t="n">
-        <v>-0.59</v>
+        <v>-12.9</v>
       </c>
       <c r="K27" s="32" t="n">
-        <v>8.210000000000001</v>
+        <v>6.28</v>
       </c>
       <c r="L27" s="32" t="n">
-        <v>12.12</v>
+        <v>15.52</v>
       </c>
       <c r="M27" s="32" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>47 (B-)</t>
+          <t>49 (B-)</t>
         </is>
       </c>
       <c r="C28" s="32" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="D28" s="32" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="F28" s="32" t="n">
-        <v>1.87</v>
-      </c>
+        <v>-0.55</v>
+      </c>
+      <c r="F28" s="32" t="n"/>
       <c r="G28" s="32" t="n">
-        <v>2.54</v>
+        <v>3.28</v>
       </c>
       <c r="H28" s="32" t="n"/>
       <c r="I28" s="32" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="J28" s="32" t="n">
-        <v>-54.27</v>
+        <v>-18.19</v>
       </c>
       <c r="K28" s="32" t="n">
-        <v>6.48</v>
+        <v>7.26</v>
       </c>
       <c r="L28" s="32" t="n">
-        <v>9.68</v>
+        <v>7.84</v>
       </c>
       <c r="M28" s="32" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>46 (B-)</t>
+          <t>47 (B-)</t>
         </is>
       </c>
       <c r="C29" s="32" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D29" s="32" t="n">
-        <v>0.14</v>
+        <v>-1.21</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>7.84</v>
+        <v>6.23</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="G29" s="32" t="n">
-        <v>2.32</v>
+        <v>0.38</v>
       </c>
       <c r="H29" s="32" t="n"/>
       <c r="I29" s="32" t="n">
-        <v>-0.33</v>
+        <v>-0.96</v>
       </c>
       <c r="J29" s="32" t="n">
-        <v>-12.9</v>
+        <v>-9.74</v>
       </c>
       <c r="K29" s="32" t="n">
-        <v>6.28</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L29" s="32" t="n">
-        <v>15.52</v>
+        <v>18.6</v>
       </c>
       <c r="M29" s="32" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="B30" s="34" t="inlineStr">
@@ -5368,41 +5368,41 @@
         </is>
       </c>
       <c r="C30" s="32" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D30" s="32" t="n">
-        <v>-2.34</v>
+        <v>-0.96</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>1.57</v>
+        <v>3.26</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="G30" s="32" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="32" t="n">
-        <v>-0.44</v>
+        <v>0.62</v>
       </c>
       <c r="J30" s="32" t="n">
-        <v>12.87</v>
+        <v>-9.77</v>
       </c>
       <c r="K30" s="32" t="n">
-        <v>7.83</v>
+        <v>7.19</v>
       </c>
       <c r="L30" s="32" t="n">
-        <v>8.33</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M30" s="32" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="B31" s="34" t="inlineStr">
@@ -5411,41 +5411,41 @@
         </is>
       </c>
       <c r="C31" s="32" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="D31" s="32" t="n">
-        <v>0.73</v>
+        <v>-0.92</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>6.12</v>
+        <v>4.27</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>4.45</v>
+        <v>2.2</v>
       </c>
       <c r="G31" s="32" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="32" t="n">
-        <v>-0.63</v>
+        <v>0.08</v>
       </c>
       <c r="J31" s="32" t="n">
-        <v>64.22</v>
+        <v>29.19</v>
       </c>
       <c r="K31" s="32" t="n">
-        <v>6.11</v>
+        <v>7.1</v>
       </c>
       <c r="L31" s="32" t="n">
-        <v>-8.890000000000001</v>
+        <v>3.03</v>
       </c>
       <c r="M31" s="32" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
@@ -5454,41 +5454,41 @@
         </is>
       </c>
       <c r="C32" s="32" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="D32" s="32" t="n">
-        <v>-0.92</v>
+        <v>-2.34</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>4.16</v>
+        <v>0.74</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="G32" s="32" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="H32" s="32" t="n"/>
       <c r="I32" s="32" t="n">
-        <v>-0.13</v>
+        <v>-0.24</v>
       </c>
       <c r="J32" s="32" t="n">
-        <v>29.19</v>
+        <v>12.87</v>
       </c>
       <c r="K32" s="32" t="n">
-        <v>7.1</v>
+        <v>7.83</v>
       </c>
       <c r="L32" s="32" t="n">
-        <v>3.03</v>
+        <v>8.33</v>
       </c>
       <c r="M32" s="32" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Antonio-New Braunfels</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="B33" s="34" t="inlineStr">
@@ -5497,35 +5497,35 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="D33" s="32" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="E33" s="32" t="n">
-        <v>3.05</v>
+        <v>4.17</v>
       </c>
       <c r="F33" s="32" t="n">
-        <v>0.93</v>
+        <v>2.34</v>
       </c>
       <c r="G33" s="32" t="n">
-        <v>2.58</v>
+        <v>1.74</v>
       </c>
       <c r="H33" s="32" t="n"/>
       <c r="I33" s="32" t="n">
-        <v>0.35</v>
+        <v>1.67</v>
       </c>
       <c r="J33" s="32" t="n">
-        <v>-12.26</v>
+        <v>-6.89</v>
       </c>
       <c r="K33" s="32" t="n">
-        <v>6.6</v>
+        <v>7.28</v>
       </c>
       <c r="L33" s="32" t="n">
-        <v>-8.619999999999999</v>
+        <v>4.17</v>
       </c>
       <c r="M33" s="32" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>45 (B-)</t>
+          <t>44 (C+)</t>
         </is>
       </c>
       <c r="C34" s="32" t="n">
@@ -5546,17 +5546,17 @@
         <v>-0.41</v>
       </c>
       <c r="E34" s="32" t="n">
-        <v>7.51</v>
+        <v>6.78</v>
       </c>
       <c r="F34" s="32" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="G34" s="32" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="H34" s="32" t="n"/>
       <c r="I34" s="32" t="n">
-        <v>-0.66</v>
+        <v>-0.73</v>
       </c>
       <c r="J34" s="32" t="n">
         <v>38.19</v>
@@ -5574,7 +5574,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="B35" s="34" t="inlineStr">
@@ -5583,41 +5583,41 @@
         </is>
       </c>
       <c r="C35" s="32" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="D35" s="32" t="n">
-        <v>-0.17</v>
+        <v>1.69</v>
       </c>
       <c r="E35" s="32" t="n">
-        <v>4.39</v>
+        <v>3.51</v>
       </c>
       <c r="F35" s="32" t="n">
-        <v>3.62</v>
+        <v>6.7</v>
       </c>
       <c r="G35" s="32" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="32" t="n">
-        <v>2.12</v>
+        <v>0.6</v>
       </c>
       <c r="J35" s="32" t="n">
-        <v>-22.67</v>
+        <v>132.32</v>
       </c>
       <c r="K35" s="32" t="n">
-        <v>7.28</v>
+        <v>4.71</v>
       </c>
       <c r="L35" s="32" t="n">
-        <v>4.17</v>
+        <v>-6.9</v>
       </c>
       <c r="M35" s="32" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="B36" s="34" t="inlineStr">
@@ -5626,78 +5626,78 @@
         </is>
       </c>
       <c r="C36" s="32" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="32" t="n">
-        <v>-0.5</v>
+        <v>-4.53</v>
       </c>
       <c r="E36" s="32" t="n">
-        <v>0.62</v>
+        <v>2.97</v>
       </c>
       <c r="F36" s="32" t="n">
-        <v>4.68</v>
+        <v>6.03</v>
       </c>
       <c r="G36" s="32" t="n">
-        <v>1.36</v>
+        <v>0.84</v>
       </c>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="n">
-        <v>-0.47</v>
+        <v>-0.1</v>
       </c>
       <c r="J36" s="32" t="n">
-        <v>32.81</v>
+        <v>-0.59</v>
       </c>
       <c r="K36" s="32" t="n">
-        <v>7.25</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L36" s="32" t="n">
-        <v>2.5</v>
+        <v>12.12</v>
       </c>
       <c r="M36" s="32" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>40 (C+)</t>
+          <t>41 (C+)</t>
         </is>
       </c>
       <c r="C37" s="32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="D37" s="32" t="n">
-        <v>-0.96</v>
+        <v>0.39</v>
       </c>
       <c r="E37" s="32" t="n">
-        <v>3.68</v>
+        <v>1.8</v>
       </c>
       <c r="F37" s="32" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="G37" s="32" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="32" t="n">
-        <v>-0.23</v>
+        <v>-0.48</v>
       </c>
       <c r="J37" s="32" t="n">
-        <v>-9.77</v>
+        <v>9.19</v>
       </c>
       <c r="K37" s="32" t="n">
-        <v>7.19</v>
+        <v>7.77</v>
       </c>
       <c r="L37" s="32" t="n">
-        <v>9.619999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="M37" s="32" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
@@ -5718,17 +5718,17 @@
         <v>0.78</v>
       </c>
       <c r="E38" s="32" t="n">
-        <v>5.3</v>
+        <v>4.92</v>
       </c>
       <c r="F38" s="32" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="G38" s="32" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="32" t="n">
-        <v>-1.45</v>
+        <v>-0.74</v>
       </c>
       <c r="J38" s="32" t="n">
         <v>-36.97</v>
@@ -5746,517 +5746,517 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>39 (C+)</t>
+          <t>40 (C+)</t>
         </is>
       </c>
       <c r="C39" s="32" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="D39" s="32" t="n">
-        <v>0.39</v>
+        <v>-0.16</v>
       </c>
       <c r="E39" s="32" t="n">
-        <v>0.64</v>
+        <v>1.63</v>
       </c>
       <c r="F39" s="32" t="n">
-        <v>3.25</v>
+        <v>1.35</v>
       </c>
       <c r="G39" s="32" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="32" t="n">
-        <v>-0.58</v>
+        <v>0.04</v>
       </c>
       <c r="J39" s="32" t="n">
-        <v>9.19</v>
+        <v>-12.26</v>
       </c>
       <c r="K39" s="32" t="n">
-        <v>7.77</v>
+        <v>6.6</v>
       </c>
       <c r="L39" s="32" t="n">
-        <v>7.69</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="M39" s="32" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Detroit-Warren-Dearborn</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>38 (C)</t>
         </is>
       </c>
       <c r="C40" s="32" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="D40" s="32" t="n">
-        <v>0.92</v>
+        <v>-0.5</v>
       </c>
       <c r="E40" s="32" t="n">
-        <v>2.04</v>
+        <v>0.46</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>2.53</v>
+        <v>5.29</v>
       </c>
       <c r="G40" s="32" t="n">
-        <v>2.52</v>
+        <v>1.4</v>
       </c>
       <c r="H40" s="32" t="n"/>
       <c r="I40" s="32" t="n">
-        <v>-0.43</v>
+        <v>-0.72</v>
       </c>
       <c r="J40" s="32" t="n">
-        <v>-12.03</v>
+        <v>32.81</v>
       </c>
       <c r="K40" s="32" t="n">
-        <v>7.54</v>
+        <v>7.25</v>
       </c>
       <c r="L40" s="32" t="n">
-        <v>5.41</v>
+        <v>2.5</v>
       </c>
       <c r="M40" s="32" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Milwaukee-Waukesha</t>
+          <t>Boston-Cambridge-Newton</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>36 (C)</t>
+          <t>37 (C)</t>
         </is>
       </c>
       <c r="C41" s="32" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="D41" s="32" t="n">
-        <v>-0.01</v>
+        <v>2.87</v>
       </c>
       <c r="E41" s="32" t="n">
-        <v>2.83</v>
+        <v>3.66</v>
       </c>
       <c r="F41" s="32" t="n">
-        <v>4.22</v>
+        <v>4.58</v>
       </c>
       <c r="G41" s="32" t="n">
-        <v>0.74</v>
+        <v>2.96</v>
       </c>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="32" t="n">
-        <v>-0.82</v>
+        <v>-0.41</v>
       </c>
       <c r="J41" s="32" t="n">
-        <v>15.03</v>
+        <v>-22.81</v>
       </c>
       <c r="K41" s="32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L41" s="32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M41" s="32" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>35 (C)</t>
+          <t>36 (C)</t>
         </is>
       </c>
       <c r="C42" s="32" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="D42" s="32" t="n">
-        <v>-0.59</v>
+        <v>-2.11</v>
       </c>
       <c r="E42" s="32" t="n">
-        <v>1.22</v>
+        <v>4.85</v>
       </c>
       <c r="F42" s="32" t="n">
-        <v>4.57</v>
+        <v>1.71</v>
       </c>
       <c r="G42" s="32" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="H42" s="32" t="n"/>
       <c r="I42" s="32" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.86</v>
       </c>
       <c r="J42" s="32" t="n">
-        <v>-21.43</v>
+        <v>36.76</v>
       </c>
       <c r="K42" s="32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L42" s="32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M42" s="32" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>33 (C)</t>
         </is>
       </c>
       <c r="C43" s="32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D43" s="32" t="n">
-        <v>-2.11</v>
+        <v>-0.01</v>
       </c>
       <c r="E43" s="32" t="n">
-        <v>3.48</v>
+        <v>1.49</v>
       </c>
       <c r="F43" s="32" t="n">
-        <v>1.62</v>
+        <v>4.69</v>
       </c>
       <c r="G43" s="32" t="n">
-        <v>1.98</v>
+        <v>1.16</v>
       </c>
       <c r="H43" s="32" t="n"/>
       <c r="I43" s="32" t="n">
-        <v>-3.19</v>
+        <v>-0.91</v>
       </c>
       <c r="J43" s="32" t="n">
-        <v>36.76</v>
+        <v>15.03</v>
       </c>
       <c r="K43" s="32" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="L43" s="32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M43" s="32" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>34 (C)</t>
+          <t>33 (C)</t>
         </is>
       </c>
       <c r="C44" s="32" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="D44" s="32" t="n">
-        <v>2.87</v>
+        <v>-0.33</v>
       </c>
       <c r="E44" s="32" t="n">
-        <v>3.59</v>
+        <v>3.03</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>4.59</v>
+        <v>3.41</v>
       </c>
       <c r="G44" s="32" t="n">
-        <v>3.28</v>
+        <v>1.86</v>
       </c>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="32" t="n">
-        <v>-0.8</v>
+        <v>-0.54</v>
       </c>
       <c r="J44" s="32" t="n">
-        <v>-22.81</v>
+        <v>-24.31</v>
       </c>
       <c r="K44" s="32" t="n">
-        <v>5</v>
+        <v>7.56</v>
       </c>
       <c r="L44" s="32" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="M44" s="32" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>32 (C-)</t>
         </is>
       </c>
       <c r="C45" s="32" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="D45" s="32" t="n">
-        <v>1.25</v>
+        <v>0.92</v>
       </c>
       <c r="E45" s="32" t="n">
-        <v>-1.45</v>
+        <v>2.32</v>
       </c>
       <c r="F45" s="32" t="n">
-        <v>4.54</v>
+        <v>2.39</v>
       </c>
       <c r="G45" s="32" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="32" t="n">
-        <v>-0.31</v>
+        <v>-0.93</v>
       </c>
       <c r="J45" s="32" t="n">
-        <v>3.44</v>
+        <v>-12.03</v>
       </c>
       <c r="K45" s="32" t="n">
-        <v>7.29</v>
+        <v>7.54</v>
       </c>
       <c r="L45" s="32" t="n">
-        <v>2.86</v>
+        <v>5.41</v>
       </c>
       <c r="M45" s="32" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>32 (C)</t>
         </is>
       </c>
       <c r="C46" s="32" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="D46" s="32" t="n">
-        <v>-1.13</v>
+        <v>-1.39</v>
       </c>
       <c r="E46" s="32" t="n">
-        <v>1.64</v>
+        <v>6.21</v>
       </c>
       <c r="F46" s="32" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="G46" s="32" t="n">
-        <v>0.88</v>
+        <v>0.68</v>
       </c>
       <c r="H46" s="32" t="n"/>
       <c r="I46" s="32" t="n">
-        <v>-0.1</v>
+        <v>-2.85</v>
       </c>
       <c r="J46" s="32" t="n">
-        <v>-1.17</v>
+        <v>18.23</v>
       </c>
       <c r="K46" s="32" t="n">
-        <v>6.6</v>
+        <v>7.59</v>
       </c>
       <c r="L46" s="32" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="M46" s="32" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>33 (C)</t>
+          <t>31 (C-)</t>
         </is>
       </c>
       <c r="C47" s="32" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="D47" s="32" t="n">
-        <v>-0.33</v>
+        <v>-1.1</v>
       </c>
       <c r="E47" s="32" t="n">
-        <v>2.57</v>
+        <v>5.4</v>
       </c>
       <c r="F47" s="32" t="n">
-        <v>3.46</v>
+        <v>2.92</v>
       </c>
       <c r="G47" s="32" t="n">
-        <v>1.98</v>
+        <v>0.16</v>
       </c>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="32" t="n">
-        <v>-0.48</v>
+        <v>0.01</v>
       </c>
       <c r="J47" s="32" t="n">
-        <v>-24.31</v>
+        <v>-15.03</v>
       </c>
       <c r="K47" s="32" t="n">
-        <v>7.56</v>
+        <v>7.15</v>
       </c>
       <c r="L47" s="32" t="n">
-        <v>5.56</v>
+        <v>3.85</v>
       </c>
       <c r="M47" s="32" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>32 (C-)</t>
+          <t>31 (C-)</t>
         </is>
       </c>
       <c r="C48" s="32" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="D48" s="32" t="n">
-        <v>-1.39</v>
+        <v>-0.59</v>
       </c>
       <c r="E48" s="32" t="n">
-        <v>5.82</v>
+        <v>1.14</v>
       </c>
       <c r="F48" s="32" t="n">
-        <v>1.83</v>
+        <v>4.36</v>
       </c>
       <c r="G48" s="32" t="n">
-        <v>0.68</v>
+        <v>1.62</v>
       </c>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="32" t="n">
-        <v>-2.64</v>
+        <v>0.44</v>
       </c>
       <c r="J48" s="32" t="n">
-        <v>18.23</v>
+        <v>-21.43</v>
       </c>
       <c r="K48" s="32" t="n">
-        <v>7.59</v>
+        <v>7</v>
       </c>
       <c r="L48" s="32" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="M48" s="32" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>31 (C-)</t>
+          <t>27 (C-)</t>
         </is>
       </c>
       <c r="C49" s="32" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="D49" s="32" t="n">
-        <v>-1.1</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E49" s="32" t="n">
-        <v>5.2</v>
+        <v>2.34</v>
       </c>
       <c r="F49" s="32" t="n">
-        <v>2.97</v>
+        <v>3.31</v>
       </c>
       <c r="G49" s="32" t="n">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="32" t="n">
-        <v>0.23</v>
+        <v>-0.8</v>
       </c>
       <c r="J49" s="32" t="n">
-        <v>-15.03</v>
+        <v>-6.07</v>
       </c>
       <c r="K49" s="32" t="n">
-        <v>7.15</v>
+        <v>6.74</v>
       </c>
       <c r="L49" s="32" t="n">
-        <v>3.85</v>
+        <v>-2.56</v>
       </c>
       <c r="M49" s="32" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>30 (C-)</t>
+          <t>24 (D)</t>
         </is>
       </c>
       <c r="C50" s="32" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="D50" s="32" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="E50" s="32" t="n">
-        <v>3</v>
+        <v>0.51</v>
       </c>
       <c r="F50" s="32" t="n">
-        <v>2.3</v>
+        <v>3.59</v>
       </c>
       <c r="G50" s="32" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="32" t="n">
-        <v>-1.16</v>
+        <v>-0.44</v>
       </c>
       <c r="J50" s="32" t="n">
-        <v>-6.07</v>
+        <v>-1.17</v>
       </c>
       <c r="K50" s="32" t="n">
-        <v>6.74</v>
+        <v>6.6</v>
       </c>
       <c r="L50" s="32" t="n">
-        <v>-2.56</v>
+        <v>0</v>
       </c>
       <c r="M50" s="32" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>23 (D)</t>
+          <t>19 (D)</t>
         </is>
       </c>
       <c r="C51" s="32" t="n">
@@ -6277,17 +6277,17 @@
         <v>-0.05</v>
       </c>
       <c r="E51" s="32" t="n">
-        <v>3.46</v>
+        <v>1.23</v>
       </c>
       <c r="F51" s="32" t="n">
-        <v>2.29</v>
+        <v>3.06</v>
       </c>
       <c r="G51" s="32" t="n">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="H51" s="32" t="n"/>
       <c r="I51" s="32" t="n">
-        <v>-0.77</v>
+        <v>-0.42</v>
       </c>
       <c r="J51" s="32" t="n">
         <v>-34.14</v>
@@ -6381,79 +6381,79 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="n">
+      <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>New York Newark-Jersey City</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="G2" s="14" t="n">
+      <c r="D2" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="G2" s="11" t="n">
         <v>4.5</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="11" t="n">
         <v>0.73</v>
       </c>
-      <c r="I2" s="14" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="J2" s="14" t="n">
-        <v>4.45</v>
+      <c r="I2" s="11" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>4.71</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="G3" s="11" t="n">
+      <c r="D3" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="G3" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H3" s="8" t="n">
         <v>-0.54</v>
       </c>
-      <c r="I3" s="11" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>5.67</v>
+      <c r="I3" s="8" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>5.74</v>
       </c>
     </row>
     <row r="4">
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>5.1</v>
@@ -6488,86 +6488,86 @@
         <v>-0.92</v>
       </c>
       <c r="I4" s="14" t="n">
-        <v>4.16</v>
+        <v>4.27</v>
       </c>
       <c r="J4" s="14" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="G5" s="2" t="n">
+      <c r="D5" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="5" t="n">
         <v>0.52</v>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>1.5</v>
+      <c r="I5" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="D6" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="G6" s="11" t="n">
         <v>4.4</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="11" t="n">
         <v>0.29</v>
       </c>
-      <c r="I6" s="14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>1.64</v>
+      <c r="I6" s="11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="7">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>3.7</v>
@@ -6602,10 +6602,10 @@
         <v>0.15</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>8.02</v>
+        <v>7.3</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="D8" s="20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="F8" s="20" t="n">
-        <v>33.8</v>
+        <v>36.1</v>
       </c>
       <c r="G8" s="20" t="n">
         <v>4.1</v>
@@ -6640,10 +6640,10 @@
         <v>-2.11</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>3.48</v>
+        <v>4.85</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="9">
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3.3</v>
@@ -6678,86 +6678,86 @@
         <v>1.37</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Philadelphia</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="G10" s="20" t="n">
+      <c r="D10" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G10" s="11" t="n">
         <v>4.3</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="11" t="n">
         <v>1.25</v>
       </c>
-      <c r="I10" s="20" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>4.54</v>
+      <c r="I10" s="11" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="G11" s="17" t="n">
+      <c r="D11" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="14" t="n">
         <v>-0.96</v>
       </c>
-      <c r="I11" s="17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>2.31</v>
+      <c r="I11" s="14" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>2.21</v>
       </c>
     </row>
     <row r="12">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="D12" s="20" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="F12" s="20" t="n">
-        <v>33.6</v>
+        <v>36.5</v>
       </c>
       <c r="G12" s="20" t="n">
         <v>3.9</v>
@@ -6792,10 +6792,10 @@
         <v>2.87</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="13">
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="F13" s="23" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>5.1</v>
@@ -6830,10 +6830,10 @@
         <v>-1.1</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J13" s="23" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="14">
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="F14" s="11" t="n">
-        <v>50.5</v>
+        <v>51.2</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>4</v>
@@ -6868,48 +6868,48 @@
         <v>-1.4</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Detroit</t>
         </is>
       </c>
-      <c r="D15" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="G15" s="20" t="n">
+      <c r="D15" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G15" s="23" t="n">
         <v>5.3</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="23" t="n">
         <v>0.92</v>
       </c>
-      <c r="I15" s="20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>2.53</v>
+      <c r="I15" s="23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>2.39</v>
       </c>
     </row>
     <row r="16">
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>50.7</v>
+        <v>54.4</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>4.9</v>
@@ -6944,48 +6944,48 @@
         <v>-0.8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>8.130000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>Minneapolis</t>
         </is>
       </c>
-      <c r="D17" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="G17" s="20" t="n">
+      <c r="D17" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G17" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="H17" s="20" t="n">
+      <c r="H17" s="26" t="n">
         <v>-1.13</v>
       </c>
-      <c r="I17" s="20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="J17" s="20" t="n">
-        <v>2.55</v>
+      <c r="I17" s="26" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>3.59</v>
       </c>
     </row>
     <row r="18">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>46</v>
+        <v>49.2</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>4.5</v>
@@ -7020,10 +7020,10 @@
         <v>0.14</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>7.84</v>
+        <v>6.9</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="19">
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>56.6</v>
+        <v>57.1</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>4.3</v>
@@ -7058,10 +7058,10 @@
         <v>-0.65</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>5.93</v>
+        <v>6.85</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>4.49</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="20">
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>46</v>
+        <v>45.1</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>3.7</v>
@@ -7096,10 +7096,10 @@
         <v>-2.34</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>1.57</v>
+        <v>0.74</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="21">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>46.7</v>
+        <v>49.9</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>4.4</v>
@@ -7134,48 +7134,48 @@
         <v>1.14</v>
       </c>
       <c r="I21" s="14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Charlotte-Concord-Gastonia</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J22" s="2" t="n">
         <v>1.64</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Charlotte-Concord-Gastonia</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>2.48</v>
       </c>
     </row>
     <row r="23">
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>4.3</v>
@@ -7210,10 +7210,10 @@
         <v>0.78</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>5.3</v>
+        <v>4.92</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="24">
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="D24" s="17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="F24" s="17" t="n">
-        <v>39.2</v>
+        <v>40.9</v>
       </c>
       <c r="G24" s="17" t="n">
         <v>4.3</v>
@@ -7248,48 +7248,48 @@
         <v>0.39</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>0.64</v>
+        <v>1.8</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>San Antonio-New Braunfels</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="G25" s="14" t="n">
+      <c r="D25" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G25" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="17" t="n">
         <v>-0.16</v>
       </c>
-      <c r="I25" s="14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <v>0.93</v>
+      <c r="I25" s="17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="26">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3.4</v>
@@ -7324,86 +7324,86 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="n">
+      <c r="A27" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>Portland</t>
         </is>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="J27" s="20" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Sacramento-Roseville-Folsom</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>C-</t>
         </is>
       </c>
-      <c r="F27" s="23" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H27" s="23" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="I27" s="23" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="J27" s="23" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>Sacramento-Roseville-Folsom</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="G28" s="20" t="n">
+      <c r="F28" s="23" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G28" s="23" t="n">
         <v>4.7</v>
       </c>
-      <c r="H28" s="20" t="n">
+      <c r="H28" s="23" t="n">
         <v>-0.59</v>
       </c>
-      <c r="I28" s="20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J28" s="20" t="n">
-        <v>4.57</v>
+      <c r="I28" s="23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>4.36</v>
       </c>
     </row>
     <row r="29">
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>58.5</v>
+        <v>58.2</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>4</v>
@@ -7438,48 +7438,48 @@
         <v>1.2</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="G30" s="5" t="n">
+      <c r="D30" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G30" s="8" t="n">
         <v>5.4</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="8" t="n">
         <v>2.43</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>2.13</v>
+      <c r="I30" s="8" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>2.37</v>
       </c>
     </row>
     <row r="31">
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>66.8</v>
+        <v>65.5</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>3.7</v>
@@ -7514,10 +7514,10 @@
         <v>-0.39</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3.26</v>
+        <v>4.25</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="32">
@@ -7535,15 +7535,15 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>68.7</v>
+        <v>66.2</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>3.9</v>
@@ -7552,10 +7552,10 @@
         <v>0.37</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6.99</v>
+        <v>7.97</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="33">
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>55.4</v>
+        <v>56</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>3.4</v>
@@ -7590,48 +7590,48 @@
         <v>-0.33</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>2.79</v>
+        <v>3.26</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="n">
+      <c r="A34" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>Indianapolis</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n">
-        <v>43</v>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="G34" s="17" t="n">
+      <c r="D34" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G34" s="20" t="n">
         <v>3.3</v>
       </c>
-      <c r="H34" s="17" t="n">
+      <c r="H34" s="20" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I34" s="17" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J34" s="17" t="n">
-        <v>4.68</v>
+      <c r="I34" s="20" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J34" s="20" t="n">
+        <v>5.29</v>
       </c>
     </row>
     <row r="35">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>3.4</v>
@@ -7666,7 +7666,7 @@
         <v>1.8</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>-0.25</v>
+        <v>-0.55</v>
       </c>
       <c r="J35" s="14" t="n"/>
     </row>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>2.9</v>
@@ -7702,10 +7702,10 @@
         <v>-0.4</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3.94</v>
+        <v>5.81</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="37">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>60.3</v>
+        <v>59.2</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>3.9</v>
@@ -7740,48 +7740,48 @@
         <v>-0.11</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>6.66</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="17" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="D38" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="G38" s="14" t="n">
+      <c r="D38" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G38" s="17" t="n">
         <v>3.9</v>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="H38" s="17" t="n">
         <v>-0.41</v>
       </c>
-      <c r="I38" s="14" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="J38" s="14" t="n">
-        <v>2.14</v>
+      <c r="I38" s="17" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>2.06</v>
       </c>
     </row>
     <row r="39">
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="D39" s="26" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E39" s="27" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="F39" s="26" t="n">
-        <v>22.6</v>
+        <v>18.9</v>
       </c>
       <c r="G39" s="26" t="n">
         <v>4.7</v>
@@ -7816,48 +7816,48 @@
         <v>-0.05</v>
       </c>
       <c r="I39" s="26" t="n">
-        <v>3.46</v>
+        <v>1.23</v>
       </c>
       <c r="J39" s="26" t="n">
-        <v>2.29</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n">
+      <c r="A40" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>Providence-Warwick</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>Providence</t>
         </is>
       </c>
-      <c r="D40" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G40" s="14" t="n">
+      <c r="D40" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G40" s="17" t="n">
         <v>4.3</v>
       </c>
-      <c r="H40" s="14" t="n">
+      <c r="H40" s="17" t="n">
         <v>1.69</v>
       </c>
-      <c r="I40" s="14" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="J40" s="14" t="n">
-        <v>6.57</v>
+      <c r="I40" s="17" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>6.7</v>
       </c>
     </row>
     <row r="41">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>35.6</v>
+        <v>33.3</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>4.2</v>
@@ -7892,10 +7892,10 @@
         <v>-0.01</v>
       </c>
       <c r="I41" s="20" t="n">
-        <v>2.83</v>
+        <v>1.49</v>
       </c>
       <c r="J41" s="20" t="n">
-        <v>4.22</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="42">
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>80.7</v>
+        <v>79.3</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>3</v>
@@ -7930,48 +7930,48 @@
         <v>1.72</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4.32</v>
+        <v>4.09</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>Oklahoma City</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="G43" s="11" t="n">
+      <c r="D43" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="G43" s="14" t="n">
         <v>3.4</v>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="H43" s="14" t="n">
         <v>-1.21</v>
       </c>
-      <c r="I43" s="11" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>0.9</v>
+      <c r="I43" s="14" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="44">
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="D44" s="23" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="F44" s="23" t="n">
-        <v>29.8</v>
+        <v>26.6</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>4.4</v>
@@ -8006,10 +8006,10 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>2.3</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="45">
@@ -8044,48 +8044,48 @@
         <v>-0.33</v>
       </c>
       <c r="I45" s="20" t="n">
-        <v>2.57</v>
+        <v>3.03</v>
       </c>
       <c r="J45" s="20" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="n">
+      <c r="A46" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Memphis</t>
         </is>
       </c>
-      <c r="D46" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="G46" s="14" t="n">
+      <c r="D46" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="G46" s="11" t="n">
         <v>4.2</v>
       </c>
-      <c r="H46" s="14" t="n">
+      <c r="H46" s="11" t="n">
         <v>-0.76</v>
       </c>
-      <c r="I46" s="14" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="J46" s="14" t="n">
-        <v>0.59</v>
+      <c r="I46" s="11" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="47">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="F47" s="8" t="n">
-        <v>58.5</v>
+        <v>57.1</v>
       </c>
       <c r="G47" s="8" t="n">
         <v>3.9</v>
@@ -8120,124 +8120,124 @@
         <v>-0.68</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>4.93</v>
+        <v>4.31</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="G48" s="5" t="n">
+      <c r="D48" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G48" s="8" t="n">
         <v>2.7</v>
       </c>
-      <c r="H48" s="5" t="n">
+      <c r="H48" s="8" t="n">
         <v>0.35</v>
       </c>
-      <c r="I48" s="5" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>3.4</v>
+      <c r="I48" s="8" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="n">
+      <c r="A49" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>Fresno</t>
         </is>
       </c>
-      <c r="D49" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="D49" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Grand Rapids</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="F49" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="G49" s="17" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H49" s="17" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="I49" s="17" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="J49" s="17" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>Grand Rapids</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>B-</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="G50" s="14" t="n">
+      <c r="F50" s="17" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G50" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H50" s="14" t="n">
+      <c r="H50" s="17" t="n">
         <v>-4.53</v>
       </c>
-      <c r="I50" s="14" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="J50" s="14" t="n">
-        <v>5.4</v>
+      <c r="I50" s="17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>6.03</v>
       </c>
     </row>
     <row r="51">
@@ -8255,15 +8255,15 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>2.7</v>
@@ -8272,10 +8272,10 @@
         <v>2.77</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.6</v>
+        <v>1.48</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.59</v>
+        <v>1.94</v>
       </c>
     </row>
   </sheetData>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="C3" s="39" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
@@ -8378,11 +8378,11 @@
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="G3" s="40" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         </is>
       </c>
       <c r="C4" s="39" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D4" s="39" t="inlineStr">
         <is>
@@ -8412,11 +8412,11 @@
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Milwaukee-Waukesha</t>
         </is>
       </c>
       <c r="G4" s="40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H4" s="40" t="inlineStr">
         <is>
@@ -8430,11 +8430,11 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="C5" s="39" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
@@ -8446,11 +8446,11 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="G5" s="40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H5" s="40" t="inlineStr">
         <is>
@@ -8464,11 +8464,11 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
@@ -8480,15 +8480,15 @@
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="G6" s="40" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H6" s="40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C7" s="39" t="n">
@@ -8514,11 +8514,11 @@
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="G7" s="40" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" s="40" t="inlineStr">
         <is>
@@ -8548,15 +8548,15 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Riverside-San Bernardino-Ontario</t>
         </is>
       </c>
       <c r="G8" s="40" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H8" s="40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C-</t>
         </is>
       </c>
     </row>
@@ -8566,11 +8566,11 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
@@ -8582,11 +8582,11 @@
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Sacramento-Roseville-Folsom</t>
         </is>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" s="40" t="inlineStr">
         <is>
@@ -8600,11 +8600,11 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C10" s="39" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" s="39" t="inlineStr">
         <is>
@@ -8616,11 +8616,11 @@
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Riverside-San Bernardino-Ontario</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="G10" s="40" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H10" s="40" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="C11" s="39" t="n">
@@ -8650,15 +8650,15 @@
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="G11" s="40" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H11" s="40" t="inlineStr">
         <is>
-          <t>C-</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -8672,11 +8672,11 @@
         </is>
       </c>
       <c r="C12" s="39" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="39" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="E12" s="40" t="n">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="G12" s="40" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H12" s="40" t="inlineStr">
         <is>

--- a/Economic_Metrics_All_Metros.xlsx
+++ b/Economic_Metrics_All_Metros.xlsx
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -729,20 +729,20 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -760,20 +760,20 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -822,20 +822,20 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>67.3</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -853,175 +853,175 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Hartford-West Hartford-East Hartford</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Hartford</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Cincinnati</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Cincinnati</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D10" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Very Good</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Very Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Dallas-Fort Worth-Arlington</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Salt Lake City-Murray</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F11" s="5" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
+    <row r="12">
+      <c r="A12" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Las Vegas</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D12" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="F12" s="8" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Above Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>San Jose</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>58.8</v>
+        <v>58.4</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1039,20 +1039,20 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>58.2</v>
+        <v>56</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1069,141 +1069,141 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>San Diego-Chula Vista-Carlsbad</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="D15" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Salt Lake City-Murray</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Salt Lake City</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A16" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia-Camden-Wilmington</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A17" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco-Oakland-Fremont</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Above Average</t>
+      <c r="A18" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Seattle-Tacoma-Bellevue</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1225,20 +1225,20 @@
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>54.4</v>
+        <v>52.8</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>51</v>
+        <v>52.4</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1287,20 +1287,20 @@
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="D22" s="13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="F22" s="11" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1349,16 +1349,16 @@
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="D24" s="13" t="n">
@@ -1380,20 +1380,20 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Miami-Fort Lauderdale-West Palm Beach</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
@@ -1411,20 +1411,20 @@
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Orlando-Kissimmee-Sanford</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>49.9</v>
+        <v>48.8</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -1442,16 +1442,16 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Tampa-St. Petersburg-Clearwater</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
@@ -1473,20 +1473,20 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>49</v>
+        <v>48.1</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Denver-Aurora-Centennial</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Phoenix-Mesa-Chandler</t>
+          <t>Miami-Fort Lauderdale-West Palm Beach</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -1566,20 +1566,20 @@
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Chicago-Naperville-Elgin</t>
+          <t>Virginia Beach-Chesapeake-Norfolk</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Denver-Aurora-Centennial</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>45.1</v>
+        <v>46.2</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
     </row>
     <row r="33">
       <c r="A33" s="14" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Phoenix-Mesa-Chandler</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>44.9</v>
+        <v>45.3</v>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
@@ -1659,16 +1659,16 @@
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Virginia Beach-Chesapeake-Norfolk</t>
+          <t>Providence-Warwick</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="D34" s="19" t="n">
@@ -1690,20 +1690,20 @@
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Providence-Warwick</t>
+          <t>Chicago-Naperville-Elgin</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>43.9</v>
+        <v>41.3</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Grand Rapids-Wyoming-Kentwood</t>
+          <t>Indianapolis-Carmel-Greenwood</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Grand Rapids</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>42.9</v>
+        <v>41.3</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
@@ -1752,20 +1752,20 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Baltimore-Columbia-Towson</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>40.9</v>
+        <v>39.1</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
@@ -1783,20 +1783,20 @@
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Baltimore-Columbia-Towson</t>
+          <t>San Antonio-New Braunfels</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>39.7</v>
+        <v>39.4</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
@@ -1813,52 +1813,52 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>San Antonio-New Braunfels</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>Poor</t>
+      <c r="A39" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Boston-Cambridge-Newton</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="20" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>Indianapolis-Carmel-Greenwood</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="D40" s="22" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
@@ -1876,20 +1876,20 @@
     </row>
     <row r="41">
       <c r="A41" s="20" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>Boston-Cambridge-Newton</t>
+          <t>Washington-Arlington-Alexandria</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>36.5</v>
+        <v>35.7</v>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
@@ -1907,16 +1907,16 @@
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Washington-Arlington-Alexandria</t>
+          <t>Detroit-Warren-Dearborn</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="D42" s="22" t="n">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>36.1</v>
+        <v>35.6</v>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D43" s="22" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>33.3</v>
+        <v>36.2</v>
       </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
@@ -1969,20 +1969,20 @@
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Portland-Vancouver-Hillsboro</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="D44" s="22" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>33</v>
+        <v>35.4</v>
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
@@ -1999,52 +1999,52 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>Detroit-Warren-Dearborn</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="A45" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Sacramento-Roseville-Folsom</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="20" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Portland-Vancouver-Hillsboro</t>
+          <t>Grand Rapids-Wyoming-Kentwood</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Grand Rapids</t>
         </is>
       </c>
       <c r="D46" s="22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>32.4</v>
+        <v>34.4</v>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F47" s="23" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
@@ -2093,16 +2093,16 @@
     </row>
     <row r="48">
       <c r="A48" s="23" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Sacramento-Roseville-Folsom</t>
+          <t>Louisville-Jefferson County</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="F48" s="23" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
@@ -2124,20 +2124,20 @@
     </row>
     <row r="49">
       <c r="A49" s="23" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Louisville-Jefferson County</t>
+          <t>Minneapolis-St. Paul-Bloomington</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F49" s="23" t="n">
-        <v>26.6</v>
+        <v>30.4</v>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
@@ -2154,33 +2154,33 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B50" s="27" t="inlineStr">
-        <is>
-          <t>Minneapolis-St. Paul-Bloomington</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="E50" s="27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F50" s="26" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G50" s="27" t="inlineStr">
-        <is>
-          <t>Emergency</t>
+      <c r="A50" s="23" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F51" s="26" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="B2" s="29" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2" s="30" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D2" s="30" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E2" s="31" t="n">
         <v>50</v>
       </c>
       <c r="F2" s="30" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G2" s="30" t="n">
         <v>98</v>
@@ -2337,10 +2337,10 @@
         <v>98</v>
       </c>
       <c r="J2" s="31" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="B3" s="29" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="30" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D3" s="30" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E3" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="F3" s="30" t="n">
-        <v>80</v>
+      <c r="F3" s="31" t="n">
+        <v>67</v>
       </c>
       <c r="G3" s="30" t="n">
         <v>78</v>
@@ -2371,396 +2371,396 @@
       <c r="I3" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="J3" s="33" t="n">
-        <v>40</v>
+      <c r="J3" s="31" t="n">
+        <v>64</v>
       </c>
       <c r="K3" s="31" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hartford-West Hartford-East Hartford</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>71</v>
+      </c>
+      <c r="E4" s="30" t="n">
         <v>98</v>
       </c>
-      <c r="D4" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="E4" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="F4" s="31" t="n">
-        <v>63</v>
+      <c r="F4" s="30" t="n">
+        <v>92</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H4" s="32" t="n"/>
-      <c r="I4" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="J4" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="K4" s="32" t="n">
-        <v>0</v>
+      <c r="I4" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="J4" s="30" t="n">
+        <v>92</v>
+      </c>
+      <c r="K4" s="33" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Austin-Round Rock-San Marcos</t>
+          <t>Charlotte-Concord-Gastonia</t>
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="D5" s="30" t="n">
+        <v>71</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>82</v>
+      </c>
+      <c r="H5" s="32" t="n"/>
+      <c r="I5" s="30" t="n">
+        <v>88</v>
+      </c>
+      <c r="J5" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" s="30" t="n">
         <v>74</v>
-      </c>
-      <c r="E5" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="F5" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="G5" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K5" s="30" t="n">
-        <v>86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Charlotte-Concord-Gastonia</t>
+          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
         </is>
       </c>
       <c r="B6" s="29" t="n">
         <v>67</v>
       </c>
       <c r="C6" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>63</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>57</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H6" s="32" t="n"/>
       <c r="I6" s="30" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J6" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="K6" s="30" t="n">
-        <v>76</v>
+        <v>22</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nashville-Davidson--Murfreesboro--Franklin</t>
+          <t>Austin-Round Rock-San Marcos</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>67</v>
-      </c>
-      <c r="C7" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>38</v>
+        <v>65</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>65</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>78</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="F7" s="31" t="n">
-        <v>65</v>
+        <v>86</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>94</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H7" s="32" t="n"/>
-      <c r="I7" s="30" t="n">
-        <v>82</v>
+      <c r="I7" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="J7" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" s="31" t="n">
-        <v>60</v>
+        <v>12</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Hartford-West Hartford-East Hartford</t>
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>88</v>
+        <v>98</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>55</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H8" s="32" t="n"/>
-      <c r="I8" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="J8" s="30" t="n">
-        <v>76</v>
-      </c>
-      <c r="K8" s="30" t="n">
-        <v>84</v>
+      <c r="I8" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="J8" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C9" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>64</v>
+        <v>78</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>90</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H9" s="32" t="n"/>
       <c r="I9" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="J9" s="30" t="n">
-        <v>82</v>
+        <v>34</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>46</v>
       </c>
       <c r="K9" s="33" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth-Arlington</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>61</v>
-      </c>
-      <c r="C10" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="D10" s="31" t="n">
-        <v>68</v>
-      </c>
-      <c r="E10" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="G10" s="30" t="n">
-        <v>96</v>
+        <v>63</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>71</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>40</v>
       </c>
       <c r="H10" s="32" t="n"/>
-      <c r="I10" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="J10" s="31" t="n">
-        <v>62</v>
+      <c r="I10" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>72</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Las Vegas-Henderson-North Las Vegas</t>
+          <t>Salt Lake City-Murray</t>
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>59</v>
-      </c>
-      <c r="C11" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" s="30" t="n">
+        <v>63</v>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>57</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>37</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>39</v>
+      </c>
+      <c r="G11" s="30" t="n">
         <v>94</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>47</v>
-      </c>
-      <c r="G11" s="30" t="n">
-        <v>86</v>
       </c>
       <c r="H11" s="32" t="n"/>
       <c r="I11" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="J11" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" s="30" t="n">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="J11" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="K11" s="31" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>San Jose-Sunnyvale-Santa Clara</t>
+          <t>Las Vegas-Henderson-North Las Vegas</t>
         </is>
       </c>
       <c r="B12" s="29" t="n">
         <v>59</v>
       </c>
-      <c r="C12" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="32" t="n">
-        <v>0</v>
+      <c r="C12" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>45</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="J12" s="30" t="n">
         <v>94</v>
       </c>
-      <c r="K12" s="33" t="n">
-        <v>48</v>
+      <c r="J12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Dallas-Fort Worth-Arlington</t>
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>59</v>
-      </c>
-      <c r="C13" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="D13" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="E13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <v>27</v>
-      </c>
-      <c r="G13" s="31" t="n">
         <v>58</v>
       </c>
+      <c r="C13" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>76</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>96</v>
+      </c>
       <c r="H13" s="32" t="n"/>
-      <c r="I13" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="J13" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="K13" s="33" t="n">
-        <v>40</v>
+      <c r="I13" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="J13" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="K13" s="31" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B14" s="29" t="n">
+        <v>56</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>39</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="G14" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="J14" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="D14" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>82</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>57</v>
-      </c>
-      <c r="G14" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="J14" s="33" t="n">
-        <v>48</v>
-      </c>
       <c r="K14" s="31" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
@@ -2770,19 +2770,19 @@
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>57</v>
-      </c>
-      <c r="C15" s="31" t="n">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>49</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>90</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G15" s="30" t="n">
         <v>74</v>
@@ -2792,955 +2792,955 @@
         <v>70</v>
       </c>
       <c r="J15" s="31" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="K15" s="31" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Salt Lake City-Murray</t>
+          <t>Philadelphia-Camden-Wilmington</t>
         </is>
       </c>
       <c r="B16" s="29" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C16" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="D16" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="E16" s="33" t="n">
+        <v>4</v>
       </c>
       <c r="F16" s="33" t="n">
-        <v>41</v>
-      </c>
-      <c r="G16" s="30" t="n">
-        <v>94</v>
+        <v>20</v>
+      </c>
+      <c r="G16" s="33" t="n">
+        <v>40</v>
       </c>
       <c r="H16" s="32" t="n"/>
       <c r="I16" s="30" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J16" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="K16" s="33" t="n">
-        <v>26</v>
+        <v>68</v>
+      </c>
+      <c r="K16" s="31" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Angeles-Long Beach-Anaheim</t>
+          <t>San Francisco-Oakland-Fremont</t>
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>56</v>
-      </c>
-      <c r="C17" s="33" t="n">
-        <v>36</v>
+        <v>54</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>63</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>32</v>
-      </c>
-      <c r="E17" s="31" t="n">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>84</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G17" s="31" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H17" s="32" t="n"/>
       <c r="I17" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="J17" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="K17" s="31" t="n">
-        <v>58</v>
+        <v>74</v>
+      </c>
+      <c r="J17" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="K17" s="33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Seattle-Tacoma-Bellevue</t>
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>56</v>
-      </c>
-      <c r="C18" s="30" t="n">
+        <v>54</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="E18" s="30" t="n">
         <v>96</v>
       </c>
-      <c r="D18" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="E18" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="F18" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="G18" s="33" t="n">
-        <v>32</v>
+      <c r="F18" s="33" t="n">
+        <v>41</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>84</v>
       </c>
       <c r="H18" s="32" t="n"/>
-      <c r="I18" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="J18" s="33" t="n">
-        <v>2</v>
+      <c r="I18" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>90</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>New York Newark-Jersey City</t>
+          <t>Tampa-St. Petersburg-Clearwater</t>
         </is>
       </c>
       <c r="B19" s="29" t="n">
         <v>54</v>
       </c>
       <c r="C19" s="33" t="n">
-        <v>36</v>
-      </c>
-      <c r="D19" s="30" t="n">
-        <v>70</v>
+        <v>6</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>63</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="F19" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="33" t="n">
-        <v>44</v>
+        <v>92</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>52</v>
       </c>
       <c r="H19" s="32" t="n"/>
       <c r="I19" s="31" t="n">
-        <v>66</v>
-      </c>
-      <c r="J19" s="30" t="n">
-        <v>92</v>
+        <v>56</v>
+      </c>
+      <c r="J19" s="31" t="n">
+        <v>54</v>
       </c>
       <c r="K19" s="33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Seattle-Tacoma-Bellevue</t>
+          <t>San Jose-Sunnyvale-Santa Clara</t>
         </is>
       </c>
       <c r="B20" s="29" t="n">
-        <v>54</v>
-      </c>
-      <c r="C20" s="33" t="n">
-        <v>10</v>
+        <v>53</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>73</v>
       </c>
       <c r="D20" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="E20" s="30" t="n">
+        <v>29</v>
+      </c>
+      <c r="E20" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="H20" s="32" t="n"/>
+      <c r="I20" s="30" t="n">
         <v>96</v>
       </c>
-      <c r="F20" s="33" t="n">
-        <v>39</v>
-      </c>
-      <c r="G20" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="H20" s="32" t="n"/>
-      <c r="I20" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="J20" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="K20" s="30" t="n">
-        <v>92</v>
+      <c r="J20" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="K20" s="33" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Houston-Pasadena-The Woodlands</t>
+          <t>New York Newark-Jersey City</t>
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" s="33" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D21" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="F21" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="G21" s="30" t="n">
-        <v>80</v>
+        <v>50</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="F21" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="33" t="n">
+        <v>44</v>
       </c>
       <c r="H21" s="32" t="n"/>
       <c r="I21" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="J21" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K21" s="30" t="n">
-        <v>78</v>
+        <v>66</v>
+      </c>
+      <c r="J21" s="30" t="n">
+        <v>86</v>
+      </c>
+      <c r="K21" s="33" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Philadelphia-Camden-Wilmington</t>
+          <t>Houston-Pasadena-The Woodlands</t>
         </is>
       </c>
       <c r="B22" s="29" t="n">
-        <v>51</v>
-      </c>
-      <c r="C22" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="D22" s="30" t="n">
-        <v>84</v>
+        <v>52</v>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>57</v>
       </c>
       <c r="E22" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="G22" s="33" t="n">
-        <v>40</v>
+        <v>26</v>
+      </c>
+      <c r="F22" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>80</v>
       </c>
       <c r="H22" s="32" t="n"/>
-      <c r="I22" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="J22" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="K22" s="31" t="n">
-        <v>54</v>
+      <c r="I22" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="J22" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="K22" s="30" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>San Francisco-Oakland-Fremont</t>
+          <t>Los Angeles-Long Beach-Anaheim</t>
         </is>
       </c>
       <c r="B23" s="29" t="n">
         <v>51</v>
       </c>
-      <c r="C23" s="31" t="n">
-        <v>68</v>
+      <c r="C23" s="33" t="n">
+        <v>18</v>
       </c>
       <c r="D23" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="F23" s="33" t="n">
-        <v>20</v>
-      </c>
       <c r="G23" s="31" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H23" s="32" t="n"/>
       <c r="I23" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="J23" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="K23" s="33" t="n">
-        <v>6</v>
+        <v>86</v>
+      </c>
+      <c r="J23" s="30" t="n">
+        <v>96</v>
+      </c>
+      <c r="K23" s="31" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Orlando-Kissimmee-Sanford</t>
         </is>
       </c>
       <c r="B24" s="29" t="n">
         <v>51</v>
       </c>
-      <c r="C24" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="D24" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="E24" s="30" t="n">
-        <v>76</v>
+      <c r="C24" s="33" t="n">
+        <v>8</v>
+      